--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,84 +422,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cari</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>enerji</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cari_12</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>altin_12</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enerji_12</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>diger_12</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>gsyh_tarih</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cari_gsyh</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>altin_gsyh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>enerji_gsyh</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>diger_gsyh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B2" t="n">
@@ -538,7 +526,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B3" t="n">
@@ -565,7 +553,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B4" t="n">
@@ -592,7 +580,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B5" t="n">
@@ -619,7 +607,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B6" t="n">
@@ -646,7 +634,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B7" t="n">
@@ -673,7 +661,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B8" t="n">
@@ -700,7 +688,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B9" t="n">
@@ -727,7 +715,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B10" t="n">
@@ -754,7 +742,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B11" t="n">
@@ -781,7 +769,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B12" t="n">
@@ -808,7 +796,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B13" t="n">
@@ -835,7 +823,7 @@
       <c r="I13" t="n">
         <v>2.68842</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K13" t="n">
@@ -855,7 +843,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B14" t="n">
@@ -882,7 +870,7 @@
       <c r="I14" t="n">
         <v>5.004020000000001</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K14" t="n">
@@ -902,7 +890,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B15" t="n">
@@ -929,7 +917,7 @@
       <c r="I15" t="n">
         <v>6.2034</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K15" t="n">
@@ -949,7 +937,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B16" t="n">
@@ -976,7 +964,7 @@
       <c r="I16" t="n">
         <v>7.860720000000001</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K16" t="n">
@@ -996,7 +984,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B17" t="n">
@@ -1023,7 +1011,7 @@
       <c r="I17" t="n">
         <v>9.52572</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K17" t="n">
@@ -1043,7 +1031,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B18" t="n">
@@ -1070,7 +1058,7 @@
       <c r="I18" t="n">
         <v>10.32989</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K18" t="n">
@@ -1090,7 +1078,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B19" t="n">
@@ -1117,7 +1105,7 @@
       <c r="I19" t="n">
         <v>11.23285</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K19" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B20" t="n">
@@ -1164,7 +1152,7 @@
       <c r="I20" t="n">
         <v>13.00463</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K20" t="n">
@@ -1184,7 +1172,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B21" t="n">
@@ -1211,7 +1199,7 @@
       <c r="I21" t="n">
         <v>12.93374</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K21" t="n">
@@ -1231,7 +1219,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B22" t="n">
@@ -1258,7 +1246,7 @@
       <c r="I22" t="n">
         <v>10.54887</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K22" t="n">
@@ -1278,7 +1266,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1293,7 @@
       <c r="I23" t="n">
         <v>12.80883</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K23" t="n">
@@ -1325,7 +1313,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B24" t="n">
@@ -1352,7 +1340,7 @@
       <c r="I24" t="n">
         <v>11.9196</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K24" t="n">
@@ -1372,7 +1360,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B25" t="n">
@@ -1399,7 +1387,7 @@
       <c r="I25" t="n">
         <v>11.61895</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K25" t="n">
@@ -1419,7 +1407,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B26" t="n">
@@ -1446,7 +1434,7 @@
       <c r="I26" t="n">
         <v>10.08681</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K26" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B27" t="n">
@@ -1493,7 +1481,7 @@
       <c r="I27" t="n">
         <v>10.03788</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K27" t="n">
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B28" t="n">
@@ -1540,7 +1528,7 @@
       <c r="I28" t="n">
         <v>8.120710000000001</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K28" t="n">
@@ -1560,7 +1548,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B29" t="n">
@@ -1587,7 +1575,7 @@
       <c r="I29" t="n">
         <v>6.80951</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K29" t="n">
@@ -1607,7 +1595,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B30" t="n">
@@ -1634,7 +1622,7 @@
       <c r="I30" t="n">
         <v>5.458740000000001</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K30" t="n">
@@ -1654,7 +1642,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B31" t="n">
@@ -1681,7 +1669,7 @@
       <c r="I31" t="n">
         <v>4.53857</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K31" t="n">
@@ -1701,7 +1689,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B32" t="n">
@@ -1728,7 +1716,7 @@
       <c r="I32" t="n">
         <v>2.42634</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K32" t="n">
@@ -1748,7 +1736,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B33" t="n">
@@ -1775,7 +1763,7 @@
       <c r="I33" t="n">
         <v>0.1354600000000002</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K33" t="n">
@@ -1795,7 +1783,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B34" t="n">
@@ -1822,7 +1810,7 @@
       <c r="I34" t="n">
         <v>-1.641</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K34" t="n">
@@ -1842,7 +1830,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B35" t="n">
@@ -1869,7 +1857,7 @@
       <c r="I35" t="n">
         <v>-4.08595</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K35" t="n">
@@ -1889,7 +1877,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B36" t="n">
@@ -1916,7 +1904,7 @@
       <c r="I36" t="n">
         <v>-7.33985</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K36" t="n">
@@ -1936,7 +1924,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B37" t="n">
@@ -1963,7 +1951,7 @@
       <c r="I37" t="n">
         <v>-10.14424</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K37" t="n">
@@ -1983,7 +1971,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B38" t="n">
@@ -2010,7 +1998,7 @@
       <c r="I38" t="n">
         <v>-11.7397</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K38" t="n">
@@ -2030,7 +2018,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B39" t="n">
@@ -2057,7 +2045,7 @@
       <c r="I39" t="n">
         <v>-14.14707</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="J39" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K39" t="n">
@@ -2077,7 +2065,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B40" t="n">
@@ -2104,7 +2092,7 @@
       <c r="I40" t="n">
         <v>-18.16812</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K40" t="n">
@@ -2124,7 +2112,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B41" t="n">
@@ -2151,7 +2139,7 @@
       <c r="I41" t="n">
         <v>-20.5611</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="J41" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K41" t="n">
@@ -2171,7 +2159,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B42" t="n">
@@ -2198,7 +2186,7 @@
       <c r="I42" t="n">
         <v>-23.39756</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K42" t="n">
@@ -2218,7 +2206,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B43" t="n">
@@ -2245,7 +2233,7 @@
       <c r="I43" t="n">
         <v>-26.26857</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J43" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K43" t="n">
@@ -2265,7 +2253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B44" t="n">
@@ -2292,7 +2280,7 @@
       <c r="I44" t="n">
         <v>-26.73468</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K44" t="n">
@@ -2312,7 +2300,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B45" t="n">
@@ -2339,7 +2327,7 @@
       <c r="I45" t="n">
         <v>-25.77266</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K45" t="n">
@@ -2359,7 +2347,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B46" t="n">
@@ -2386,7 +2374,7 @@
       <c r="I46" t="n">
         <v>-25.75811</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K46" t="n">
@@ -2406,7 +2394,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B47" t="n">
@@ -2433,7 +2421,7 @@
       <c r="I47" t="n">
         <v>-25.40919</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K47" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B48" t="n">
@@ -2480,7 +2468,7 @@
       <c r="I48" t="n">
         <v>-24.01676</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K48" t="n">
@@ -2500,7 +2488,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B49" t="n">
@@ -2527,7 +2515,7 @@
       <c r="I49" t="n">
         <v>-22.04643</v>
       </c>
-      <c r="J49" s="2" t="n">
+      <c r="J49" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K49" t="n">
@@ -2547,7 +2535,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B50" t="n">
@@ -2574,7 +2562,7 @@
       <c r="I50" t="n">
         <v>-21.51568</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K50" t="n">
@@ -2594,7 +2582,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B51" t="n">
@@ -2621,7 +2609,7 @@
       <c r="I51" t="n">
         <v>-19.64396</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K51" t="n">
@@ -2641,7 +2629,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B52" t="n">
@@ -2668,7 +2656,7 @@
       <c r="I52" t="n">
         <v>-15.79015</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K52" t="n">
@@ -2688,7 +2676,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B53" t="n">
@@ -2715,7 +2703,7 @@
       <c r="I53" t="n">
         <v>-13.06127</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K53" t="n">
@@ -2735,7 +2723,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B54" t="n">
@@ -2762,7 +2750,7 @@
       <c r="I54" t="n">
         <v>-10.51409</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K54" t="n">
@@ -2782,7 +2770,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B55" t="n">
@@ -2809,7 +2797,7 @@
       <c r="I55" t="n">
         <v>-6.249130000000001</v>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K55" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B56" t="n">
@@ -2856,7 +2844,7 @@
       <c r="I56" t="n">
         <v>-4.688590000000001</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K56" t="n">
@@ -2876,7 +2864,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B57" t="n">
@@ -2903,7 +2891,7 @@
       <c r="I57" t="n">
         <v>-2.382240000000001</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K57" t="n">
@@ -2923,7 +2911,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B58" t="n">
@@ -2950,7 +2938,7 @@
       <c r="I58" t="n">
         <v>0.395989999999999</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K58" t="n">
@@ -2970,7 +2958,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B59" t="n">
@@ -2997,7 +2985,7 @@
       <c r="I59" t="n">
         <v>1.845749999999999</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K59" t="n">
@@ -3017,7 +3005,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B60" t="n">
@@ -3044,7 +3032,7 @@
       <c r="I60" t="n">
         <v>3.21682</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K60" t="n">
@@ -3064,7 +3052,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B61" t="n">
@@ -3091,7 +3079,7 @@
       <c r="I61" t="n">
         <v>4.90424</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K61" t="n">
@@ -3111,7 +3099,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B62" t="n">
@@ -3138,7 +3126,7 @@
       <c r="I62" t="n">
         <v>5.24468</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K62" t="n">
@@ -3158,7 +3146,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B63" t="n">
@@ -3185,7 +3173,7 @@
       <c r="I63" t="n">
         <v>5.49649</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K63" t="n">
@@ -3205,7 +3193,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B64" t="n">
@@ -3232,7 +3220,7 @@
       <c r="I64" t="n">
         <v>6.803089999999999</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K64" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B65" t="n">
@@ -3279,7 +3267,7 @@
       <c r="I65" t="n">
         <v>7.07182</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K65" t="n">
@@ -3299,7 +3287,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B66" t="n">
@@ -3326,7 +3314,7 @@
       <c r="I66" t="n">
         <v>8.31753</v>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K66" t="n">
@@ -3346,7 +3334,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B67" t="n">
@@ -3373,7 +3361,7 @@
       <c r="I67" t="n">
         <v>9.40043</v>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K67" t="n">
@@ -3393,7 +3381,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B68" t="n">
@@ -3420,7 +3408,7 @@
       <c r="I68" t="n">
         <v>9.15676</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K68" t="n">
@@ -3440,7 +3428,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B69" t="n">
@@ -3467,7 +3455,7 @@
       <c r="I69" t="n">
         <v>9.691610000000001</v>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K69" t="n">
@@ -3487,7 +3475,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B70" t="n">
@@ -3514,7 +3502,7 @@
       <c r="I70" t="n">
         <v>10.6274</v>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K70" t="n">
@@ -3534,7 +3522,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B71" t="n">
@@ -3561,7 +3549,7 @@
       <c r="I71" t="n">
         <v>10.15893</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K71" t="n">
@@ -3581,7 +3569,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B72" t="n">
@@ -3608,7 +3596,7 @@
       <c r="I72" t="n">
         <v>11.57857</v>
       </c>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K72" t="n">
@@ -3628,7 +3616,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B73" t="n">
@@ -3655,7 +3643,7 @@
       <c r="I73" t="n">
         <v>10.08393</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K73" t="n">
@@ -3675,7 +3663,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B74" t="n">
@@ -3702,7 +3690,7 @@
       <c r="I74" t="n">
         <v>11.61466</v>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K74" t="n">
@@ -3722,7 +3710,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B75" t="n">
@@ -3749,7 +3737,7 @@
       <c r="I75" t="n">
         <v>12.55543</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K75" t="n">
@@ -3769,7 +3757,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B76" t="n">
@@ -3796,7 +3784,7 @@
       <c r="I76" t="n">
         <v>12.95175</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K76" t="n">
@@ -3816,7 +3804,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B77" t="n">
@@ -3843,7 +3831,7 @@
       <c r="I77" t="n">
         <v>13.82609</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K77" t="n">
@@ -3863,7 +3851,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B78" t="n">
@@ -3890,7 +3878,7 @@
       <c r="I78" t="n">
         <v>15.83389</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K78" t="n">
@@ -3910,7 +3898,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B79" t="n">
@@ -3937,7 +3925,7 @@
       <c r="I79" t="n">
         <v>15.8046</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K79" t="n">
@@ -3957,7 +3945,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B80" t="n">
@@ -3984,7 +3972,7 @@
       <c r="I80" t="n">
         <v>18.19608</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K80" t="n">
@@ -4004,7 +3992,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B81" t="n">
@@ -4031,7 +4019,7 @@
       <c r="I81" t="n">
         <v>18.488</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K81" t="n">
@@ -4051,7 +4039,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B82" t="n">
@@ -4078,7 +4066,7 @@
       <c r="I82" t="n">
         <v>19.80297</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K82" t="n">
@@ -4098,7 +4086,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B83" t="n">
@@ -4125,7 +4113,7 @@
       <c r="I83" t="n">
         <v>20.59569</v>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J83" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K83" t="n">
@@ -4145,7 +4133,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B84" t="n">
@@ -4172,7 +4160,7 @@
       <c r="I84" t="n">
         <v>19.85103</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K84" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B85" t="n">
@@ -4219,7 +4207,7 @@
       <c r="I85" t="n">
         <v>20.46028</v>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="J85" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K85" t="n">
@@ -4239,7 +4227,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B86" t="n">
@@ -4266,7 +4254,7 @@
       <c r="I86" t="n">
         <v>20.80432</v>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K86" t="n">
@@ -4286,7 +4274,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B87" t="n">
@@ -4313,7 +4301,7 @@
       <c r="I87" t="n">
         <v>18.98794</v>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K87" t="n">
@@ -4333,7 +4321,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B88" t="n">
@@ -4360,7 +4348,7 @@
       <c r="I88" t="n">
         <v>17.46199</v>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K88" t="n">
@@ -4380,7 +4368,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4395,7 @@
       <c r="I89" t="n">
         <v>15.2882</v>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J89" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K89" t="n">
@@ -4427,7 +4415,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B90" t="n">
@@ -4454,7 +4442,7 @@
       <c r="I90" t="n">
         <v>12.95619</v>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K90" t="n">
@@ -4474,7 +4462,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B91" t="n">
@@ -4501,7 +4489,7 @@
       <c r="I91" t="n">
         <v>11.8918</v>
       </c>
-      <c r="J91" s="2" t="n">
+      <c r="J91" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K91" t="n">
@@ -4521,7 +4509,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B92" t="n">
@@ -4548,7 +4536,7 @@
       <c r="I92" t="n">
         <v>10.00618</v>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K92" t="n">
@@ -4568,7 +4556,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B93" t="n">
@@ -4595,7 +4583,7 @@
       <c r="I93" t="n">
         <v>10.69088</v>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K93" t="n">
@@ -4615,7 +4603,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B94" t="n">
@@ -4642,7 +4630,7 @@
       <c r="I94" t="n">
         <v>9.682169999999999</v>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K94" t="n">
@@ -4662,7 +4650,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B95" t="n">
@@ -4689,7 +4677,7 @@
       <c r="I95" t="n">
         <v>9.299630000000001</v>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J95" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K95" t="n">
@@ -4709,7 +4697,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B96" t="n">
@@ -4736,7 +4724,7 @@
       <c r="I96" t="n">
         <v>9.04907</v>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K96" t="n">
@@ -4756,7 +4744,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B97" t="n">
@@ -4783,7 +4771,7 @@
       <c r="I97" t="n">
         <v>8.198219999999999</v>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K97" t="n">
@@ -4803,7 +4791,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B98" t="n">
@@ -4830,7 +4818,7 @@
       <c r="I98" t="n">
         <v>7.736389999999999</v>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K98" t="n">
@@ -4850,7 +4838,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B99" t="n">
@@ -4877,7 +4865,7 @@
       <c r="I99" t="n">
         <v>7.899969999999999</v>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J99" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K99" t="n">
@@ -4897,7 +4885,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B100" t="n">
@@ -4924,7 +4912,7 @@
       <c r="I100" t="n">
         <v>7.502359999999999</v>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K100" t="n">
@@ -4944,7 +4932,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B101" t="n">
@@ -4971,7 +4959,7 @@
       <c r="I101" t="n">
         <v>8.811169999999999</v>
       </c>
-      <c r="J101" s="2" t="n">
+      <c r="J101" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K101" t="n">
@@ -4991,7 +4979,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B102" t="n">
@@ -5018,7 +5006,7 @@
       <c r="I102" t="n">
         <v>7.943439999999999</v>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K102" t="n">
@@ -5038,7 +5026,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B103" t="n">
@@ -5065,7 +5053,7 @@
       <c r="I103" t="n">
         <v>4.534299999999999</v>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J103" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K103" t="n">
@@ -5085,7 +5073,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B104" t="n">
@@ -5112,7 +5100,7 @@
       <c r="I104" t="n">
         <v>2.886419999999999</v>
       </c>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K104" t="n">
@@ -5132,7 +5120,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B105" t="n">
@@ -5159,7 +5147,7 @@
       <c r="I105" t="n">
         <v>0.2952499999999989</v>
       </c>
-      <c r="J105" s="2" t="n">
+      <c r="J105" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K105" t="n">
@@ -5179,7 +5167,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B106" t="n">
@@ -5206,7 +5194,7 @@
       <c r="I106" t="n">
         <v>-1.300060000000001</v>
       </c>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K106" t="n">
@@ -5226,7 +5214,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B107" t="n">
@@ -5253,7 +5241,7 @@
       <c r="I107" t="n">
         <v>-1.551580000000001</v>
       </c>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K107" t="n">
@@ -5273,7 +5261,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B108" t="n">
@@ -5300,7 +5288,7 @@
       <c r="I108" t="n">
         <v>-1.618070000000001</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K108" t="n">
@@ -5320,7 +5308,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B109" t="n">
@@ -5347,7 +5335,7 @@
       <c r="I109" t="n">
         <v>0.1297299999999989</v>
       </c>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K109" t="n">
@@ -5367,7 +5355,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B110" t="n">
@@ -5394,7 +5382,7 @@
       <c r="I110" t="n">
         <v>0.3622699999999989</v>
       </c>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K110" t="n">
@@ -5414,7 +5402,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B111" t="n">
@@ -5441,7 +5429,7 @@
       <c r="I111" t="n">
         <v>2.062249999999999</v>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K111" t="n">
@@ -5461,7 +5449,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B112" t="n">
@@ -5488,7 +5476,7 @@
       <c r="I112" t="n">
         <v>4.506739999999999</v>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K112" t="n">
@@ -5508,7 +5496,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B113" t="n">
@@ -5535,7 +5523,7 @@
       <c r="I113" t="n">
         <v>4.95311</v>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K113" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B114" t="n">
@@ -5582,7 +5570,7 @@
       <c r="I114" t="n">
         <v>5.905279999999999</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K114" t="n">
@@ -5602,7 +5590,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B115" t="n">
@@ -5629,7 +5617,7 @@
       <c r="I115" t="n">
         <v>8.84371</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K115" t="n">
@@ -5649,7 +5637,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B116" t="n">
@@ -5676,7 +5664,7 @@
       <c r="I116" t="n">
         <v>9.860910000000001</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K116" t="n">
@@ -5696,7 +5684,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B117" t="n">
@@ -5723,7 +5711,7 @@
       <c r="I117" t="n">
         <v>12.08097</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K117" t="n">
@@ -5743,7 +5731,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B118" t="n">
@@ -5770,7 +5758,7 @@
       <c r="I118" t="n">
         <v>10.99841</v>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K118" t="n">
@@ -5790,7 +5778,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B119" t="n">
@@ -5817,7 +5805,7 @@
       <c r="I119" t="n">
         <v>9.6854</v>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J119" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K119" t="n">
@@ -5837,7 +5825,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B120" t="n">
@@ -5864,7 +5852,7 @@
       <c r="I120" t="n">
         <v>9.236190000000001</v>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J120" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K120" t="n">
@@ -5884,7 +5872,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B121" t="n">
@@ -5911,7 +5899,7 @@
       <c r="I121" t="n">
         <v>7.685680000000001</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J121" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K121" t="n">
@@ -5931,7 +5919,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B122" t="n">
@@ -5958,7 +5946,7 @@
       <c r="I122" t="n">
         <v>5.95812</v>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J122" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K122" t="n">
@@ -5978,7 +5966,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B123" t="n">
@@ -6005,7 +5993,7 @@
       <c r="I123" t="n">
         <v>4.993270000000001</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J123" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K123" t="n">
@@ -6025,7 +6013,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B124" t="n">
@@ -6052,7 +6040,7 @@
       <c r="I124" t="n">
         <v>4.364470000000001</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J124" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K124" t="n">
@@ -6072,7 +6060,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B125" t="n">
@@ -6099,7 +6087,7 @@
       <c r="I125" t="n">
         <v>3.48327</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J125" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K125" t="n">
@@ -6119,7 +6107,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B126" t="n">
@@ -6146,7 +6134,7 @@
       <c r="I126" t="n">
         <v>3.21001</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J126" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K126" t="n">
@@ -6166,7 +6154,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B127" t="n">
@@ -6193,7 +6181,7 @@
       <c r="I127" t="n">
         <v>3.74216</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J127" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K127" t="n">
@@ -6213,7 +6201,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B128" t="n">
@@ -6240,7 +6228,7 @@
       <c r="I128" t="n">
         <v>6.06072</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J128" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K128" t="n">
@@ -6260,7 +6248,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B129" t="n">
@@ -6287,7 +6275,7 @@
       <c r="I129" t="n">
         <v>7.804049999999999</v>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J129" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K129" t="n">
@@ -6307,7 +6295,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B130" t="n">
@@ -6334,7 +6322,7 @@
       <c r="I130" t="n">
         <v>14.08367</v>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J130" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K130" t="n">
@@ -6354,7 +6342,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B131" t="n">
@@ -6381,7 +6369,7 @@
       <c r="I131" t="n">
         <v>20.77072</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J131" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K131" t="n">
@@ -6401,7 +6389,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B132" t="n">
@@ -6428,7 +6416,7 @@
       <c r="I132" t="n">
         <v>26.56942</v>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J132" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K132" t="n">
@@ -6448,7 +6436,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B133" t="n">
@@ -6475,7 +6463,7 @@
       <c r="I133" t="n">
         <v>31.91968</v>
       </c>
-      <c r="J133" s="2" t="n">
+      <c r="J133" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K133" t="n">
@@ -6495,7 +6483,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B134" t="n">
@@ -6522,7 +6510,7 @@
       <c r="I134" t="n">
         <v>36.77216</v>
       </c>
-      <c r="J134" s="2" t="n">
+      <c r="J134" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K134" t="n">
@@ -6542,7 +6530,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B135" t="n">
@@ -6569,7 +6557,7 @@
       <c r="I135" t="n">
         <v>40.31249</v>
       </c>
-      <c r="J135" s="2" t="n">
+      <c r="J135" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K135" t="n">
@@ -6589,7 +6577,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B136" t="n">
@@ -6616,7 +6604,7 @@
       <c r="I136" t="n">
         <v>44.4252</v>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J136" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K136" t="n">
@@ -6636,7 +6624,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B137" t="n">
@@ -6663,7 +6651,7 @@
       <c r="I137" t="n">
         <v>48.80586</v>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J137" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K137" t="n">
@@ -6683,7 +6671,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B138" t="n">
@@ -6710,7 +6698,7 @@
       <c r="I138" t="n">
         <v>53.917</v>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="J138" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K138" t="n">
@@ -6730,7 +6718,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B139" t="n">
@@ -6757,7 +6745,7 @@
       <c r="I139" t="n">
         <v>56.12547</v>
       </c>
-      <c r="J139" s="2" t="n">
+      <c r="J139" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K139" t="n">
@@ -6777,7 +6765,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B140" t="n">
@@ -6804,7 +6792,7 @@
       <c r="I140" t="n">
         <v>59.44548</v>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="J140" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K140" t="n">
@@ -6824,7 +6812,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B141" t="n">
@@ -6851,7 +6839,7 @@
       <c r="I141" t="n">
         <v>60.96964</v>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="J141" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K141" t="n">
@@ -6871,7 +6859,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B142" t="n">
@@ -6898,7 +6886,7 @@
       <c r="I142" t="n">
         <v>61.12259999999999</v>
       </c>
-      <c r="J142" s="2" t="n">
+      <c r="J142" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K142" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B143" t="n">
@@ -6945,7 +6933,7 @@
       <c r="I143" t="n">
         <v>60.94875</v>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J143" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K143" t="n">
@@ -6965,7 +6953,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B144" t="n">
@@ -6992,7 +6980,7 @@
       <c r="I144" t="n">
         <v>59.31162999999999</v>
       </c>
-      <c r="J144" s="2" t="n">
+      <c r="J144" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K144" t="n">
@@ -7012,7 +7000,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B145" t="n">
@@ -7039,7 +7027,7 @@
       <c r="I145" t="n">
         <v>57.56779</v>
       </c>
-      <c r="J145" s="2" t="n">
+      <c r="J145" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K145" t="n">
@@ -7059,7 +7047,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B146" t="n">
@@ -7086,7 +7074,7 @@
       <c r="I146" t="n">
         <v>57.90269</v>
       </c>
-      <c r="J146" s="2" t="n">
+      <c r="J146" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K146" t="n">
@@ -7106,7 +7094,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B147" t="n">
@@ -7133,7 +7121,7 @@
       <c r="I147" t="n">
         <v>57.78574999999999</v>
       </c>
-      <c r="J147" s="2" t="n">
+      <c r="J147" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K147" t="n">
@@ -7153,7 +7141,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B148" t="n">
@@ -7180,7 +7168,7 @@
       <c r="I148" t="n">
         <v>52.78822</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J148" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K148" t="n">
@@ -7200,7 +7188,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B149" t="n">
@@ -7227,7 +7215,7 @@
       <c r="I149" t="n">
         <v>46.00505</v>
       </c>
-      <c r="J149" s="2" t="n">
+      <c r="J149" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K149" t="n">
@@ -7247,7 +7235,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B150" t="n">
@@ -7274,7 +7262,7 @@
       <c r="I150" t="n">
         <v>39.39304</v>
       </c>
-      <c r="J150" s="2" t="n">
+      <c r="J150" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K150" t="n">
@@ -7294,7 +7282,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B151" t="n">
@@ -7321,7 +7309,7 @@
       <c r="I151" t="n">
         <v>37.28101</v>
       </c>
-      <c r="J151" s="2" t="n">
+      <c r="J151" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K151" t="n">
@@ -7341,7 +7329,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B152" t="n">
@@ -7368,7 +7356,7 @@
       <c r="I152" t="n">
         <v>32.8163</v>
       </c>
-      <c r="J152" s="2" t="n">
+      <c r="J152" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K152" t="n">
@@ -7388,7 +7376,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B153" t="n">
@@ -7415,7 +7403,7 @@
       <c r="I153" t="n">
         <v>26.95827</v>
       </c>
-      <c r="J153" s="2" t="n">
+      <c r="J153" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K153" t="n">
@@ -7435,7 +7423,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B154" t="n">
@@ -7462,7 +7450,7 @@
       <c r="I154" t="n">
         <v>23.34406</v>
       </c>
-      <c r="J154" s="2" t="n">
+      <c r="J154" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K154" t="n">
@@ -7482,7 +7470,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B155" t="n">
@@ -7509,7 +7497,7 @@
       <c r="I155" t="n">
         <v>19.61043</v>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J155" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K155" t="n">
@@ -7529,7 +7517,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B156" t="n">
@@ -7556,7 +7544,7 @@
       <c r="I156" t="n">
         <v>16.41961</v>
       </c>
-      <c r="J156" s="2" t="n">
+      <c r="J156" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K156" t="n">
@@ -7576,7 +7564,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B157" t="n">
@@ -7603,7 +7591,7 @@
       <c r="I157" t="n">
         <v>15.58579</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J157" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K157" t="n">
@@ -7623,7 +7611,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B158" t="n">
@@ -7650,7 +7638,7 @@
       <c r="I158" t="n">
         <v>13.06948</v>
       </c>
-      <c r="J158" s="2" t="n">
+      <c r="J158" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K158" t="n">
@@ -7670,7 +7658,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B159" t="n">
@@ -7697,7 +7685,7 @@
       <c r="I159" t="n">
         <v>10.72014</v>
       </c>
-      <c r="J159" s="2" t="n">
+      <c r="J159" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K159" t="n">
@@ -7717,7 +7705,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B160" t="n">
@@ -7744,7 +7732,7 @@
       <c r="I160" t="n">
         <v>11.85764</v>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="J160" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K160" t="n">
@@ -7764,7 +7752,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B161" t="n">
@@ -7791,7 +7779,7 @@
       <c r="I161" t="n">
         <v>16.75192</v>
       </c>
-      <c r="J161" s="2" t="n">
+      <c r="J161" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K161" t="n">
@@ -7811,7 +7799,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B162" t="n">
@@ -7838,7 +7826,7 @@
       <c r="I162" t="n">
         <v>17.78087</v>
       </c>
-      <c r="J162" s="2" t="n">
+      <c r="J162" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K162" t="n">
@@ -7858,7 +7846,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B163" t="n">
@@ -7885,7 +7873,7 @@
       <c r="I163" t="n">
         <v>19.18315</v>
       </c>
-      <c r="J163" s="2" t="n">
+      <c r="J163" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K163" t="n">
@@ -7905,7 +7893,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B164" t="n">
@@ -7932,7 +7920,7 @@
       <c r="I164" t="n">
         <v>21.03445</v>
       </c>
-      <c r="J164" s="2" t="n">
+      <c r="J164" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K164" t="n">
@@ -7952,7 +7940,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B165" t="n">
@@ -7979,7 +7967,7 @@
       <c r="I165" t="n">
         <v>25.49619</v>
       </c>
-      <c r="J165" s="2" t="n">
+      <c r="J165" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K165" t="n">
@@ -7999,7 +7987,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B166" t="n">
@@ -8026,7 +8014,7 @@
       <c r="I166" t="n">
         <v>28.66052</v>
       </c>
-      <c r="J166" s="2" t="n">
+      <c r="J166" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K166" t="n">
@@ -8046,7 +8034,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B167" t="n">
@@ -8073,7 +8061,7 @@
       <c r="I167" t="n">
         <v>33.67982</v>
       </c>
-      <c r="J167" s="2" t="n">
+      <c r="J167" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K167" t="n">
@@ -8093,7 +8081,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B168" t="n">
@@ -8120,7 +8108,7 @@
       <c r="I168" t="n">
         <v>35.21025</v>
       </c>
-      <c r="J168" s="2" t="n">
+      <c r="J168" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K168" t="n">
@@ -8140,7 +8128,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B169" t="n">
@@ -8167,7 +8155,7 @@
       <c r="I169" t="n">
         <v>37.12937</v>
       </c>
-      <c r="J169" s="2" t="n">
+      <c r="J169" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K169" t="n">
@@ -8187,7 +8175,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B170" t="n">
@@ -8214,7 +8202,7 @@
       <c r="I170" t="n">
         <v>37.22411</v>
       </c>
-      <c r="J170" s="2" t="n">
+      <c r="J170" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K170" t="n">
@@ -8234,7 +8222,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B171" t="n">
@@ -8261,7 +8249,7 @@
       <c r="I171" t="n">
         <v>38.29664</v>
       </c>
-      <c r="J171" s="2" t="n">
+      <c r="J171" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K171" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B172" t="n">
@@ -8308,7 +8296,7 @@
       <c r="I172" t="n">
         <v>40.84047</v>
       </c>
-      <c r="J172" s="2" t="n">
+      <c r="J172" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K172" t="n">
@@ -8328,7 +8316,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B173" t="n">
@@ -8355,7 +8343,7 @@
       <c r="I173" t="n">
         <v>43.37856</v>
       </c>
-      <c r="J173" s="2" t="n">
+      <c r="J173" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K173" t="n">
@@ -8375,7 +8363,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B174" t="n">
@@ -8402,7 +8390,7 @@
       <c r="I174" t="n">
         <v>45.0951</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J174" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K174" t="n">
@@ -8422,7 +8410,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B175" t="n">
@@ -8449,7 +8437,7 @@
       <c r="I175" t="n">
         <v>47.7854</v>
       </c>
-      <c r="J175" s="2" t="n">
+      <c r="J175" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K175" t="n">
@@ -8469,7 +8457,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B176" t="n">
@@ -8496,7 +8484,7 @@
       <c r="I176" t="n">
         <v>48.45027</v>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="J176" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K176" t="n">
@@ -8516,7 +8504,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B177" t="n">
@@ -8543,7 +8531,7 @@
       <c r="I177" t="n">
         <v>49.68133</v>
       </c>
-      <c r="J177" s="2" t="n">
+      <c r="J177" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K177" t="n">
@@ -8563,7 +8551,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B178" t="n">
@@ -8590,7 +8578,7 @@
       <c r="I178" t="n">
         <v>50.47562</v>
       </c>
-      <c r="J178" s="2" t="n">
+      <c r="J178" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K178" t="n">
@@ -8610,7 +8598,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B179" t="n">
@@ -8637,7 +8625,7 @@
       <c r="I179" t="n">
         <v>50.11399</v>
       </c>
-      <c r="J179" s="2" t="n">
+      <c r="J179" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K179" t="n">
@@ -8657,7 +8645,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B180" t="n">
@@ -8684,7 +8672,7 @@
       <c r="I180" t="n">
         <v>52.17445</v>
       </c>
-      <c r="J180" s="2" t="n">
+      <c r="J180" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K180" t="n">
@@ -8704,7 +8692,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B181" t="n">
@@ -8731,7 +8719,7 @@
       <c r="I181" t="n">
         <v>52.84970999999999</v>
       </c>
-      <c r="J181" s="2" t="n">
+      <c r="J181" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K181" t="n">
@@ -8751,7 +8739,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B182" t="n">
@@ -8778,7 +8766,7 @@
       <c r="I182" t="n">
         <v>53.61758</v>
       </c>
-      <c r="J182" s="2" t="n">
+      <c r="J182" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K182" t="n">
@@ -8798,7 +8786,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B183" t="n">
@@ -8825,7 +8813,7 @@
       <c r="I183" t="n">
         <v>52.49454</v>
       </c>
-      <c r="J183" s="2" t="n">
+      <c r="J183" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K183" t="n">
@@ -8845,7 +8833,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B184" t="n">
@@ -8872,7 +8860,7 @@
       <c r="I184" t="n">
         <v>50.79395</v>
       </c>
-      <c r="J184" s="2" t="n">
+      <c r="J184" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K184" t="n">
@@ -8892,7 +8880,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B185" t="n">
@@ -8919,7 +8907,7 @@
       <c r="I185" t="n">
         <v>46.78892</v>
       </c>
-      <c r="J185" s="2" t="n">
+      <c r="J185" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K185" t="n">
@@ -8939,7 +8927,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B186" t="n">
@@ -8966,7 +8954,7 @@
       <c r="I186" t="n">
         <v>45.03124</v>
       </c>
-      <c r="J186" s="2" t="n">
+      <c r="J186" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K186" t="n">
@@ -8986,7 +8974,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B187" t="n">
@@ -9013,7 +9001,7 @@
       <c r="I187" t="n">
         <v>45.92217</v>
       </c>
-      <c r="J187" s="2" t="n">
+      <c r="J187" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K187" t="n">
@@ -9033,7 +9021,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B188" t="n">
@@ -9060,7 +9048,7 @@
       <c r="I188" t="n">
         <v>42.09453999999999</v>
       </c>
-      <c r="J188" s="2" t="n">
+      <c r="J188" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K188" t="n">
@@ -9080,7 +9068,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B189" t="n">
@@ -9107,7 +9095,7 @@
       <c r="I189" t="n">
         <v>41.36029</v>
       </c>
-      <c r="J189" s="2" t="n">
+      <c r="J189" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K189" t="n">
@@ -9127,7 +9115,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B190" t="n">
@@ -9154,7 +9142,7 @@
       <c r="I190" t="n">
         <v>41.33475</v>
       </c>
-      <c r="J190" s="2" t="n">
+      <c r="J190" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K190" t="n">
@@ -9174,7 +9162,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B191" t="n">
@@ -9201,7 +9189,7 @@
       <c r="I191" t="n">
         <v>38.13951</v>
       </c>
-      <c r="J191" s="2" t="n">
+      <c r="J191" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K191" t="n">
@@ -9221,7 +9209,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B192" t="n">
@@ -9248,7 +9236,7 @@
       <c r="I192" t="n">
         <v>35.59753</v>
       </c>
-      <c r="J192" s="2" t="n">
+      <c r="J192" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K192" t="n">
@@ -9268,7 +9256,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B193" t="n">
@@ -9295,7 +9283,7 @@
       <c r="I193" t="n">
         <v>36.55256</v>
       </c>
-      <c r="J193" s="2" t="n">
+      <c r="J193" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K193" t="n">
@@ -9315,7 +9303,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B194" t="n">
@@ -9342,7 +9330,7 @@
       <c r="I194" t="n">
         <v>37.88103</v>
       </c>
-      <c r="J194" s="2" t="n">
+      <c r="J194" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K194" t="n">
@@ -9362,7 +9350,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B195" t="n">
@@ -9389,7 +9377,7 @@
       <c r="I195" t="n">
         <v>39.19635</v>
       </c>
-      <c r="J195" s="2" t="n">
+      <c r="J195" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K195" t="n">
@@ -9409,7 +9397,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B196" t="n">
@@ -9436,7 +9424,7 @@
       <c r="I196" t="n">
         <v>39.56444</v>
       </c>
-      <c r="J196" s="2" t="n">
+      <c r="J196" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K196" t="n">
@@ -9456,7 +9444,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B197" t="n">
@@ -9483,7 +9471,7 @@
       <c r="I197" t="n">
         <v>39.30509</v>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="J197" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K197" t="n">
@@ -9503,7 +9491,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B198" t="n">
@@ -9530,7 +9518,7 @@
       <c r="I198" t="n">
         <v>43.89015</v>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="J198" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K198" t="n">
@@ -9550,7 +9538,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B199" t="n">
@@ -9577,7 +9565,7 @@
       <c r="I199" t="n">
         <v>42.70023</v>
       </c>
-      <c r="J199" s="2" t="n">
+      <c r="J199" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K199" t="n">
@@ -9597,7 +9585,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B200" t="n">
@@ -9624,7 +9612,7 @@
       <c r="I200" t="n">
         <v>47.27269999999999</v>
       </c>
-      <c r="J200" s="2" t="n">
+      <c r="J200" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K200" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B201" t="n">
@@ -9671,7 +9659,7 @@
       <c r="I201" t="n">
         <v>49.26831</v>
       </c>
-      <c r="J201" s="2" t="n">
+      <c r="J201" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K201" t="n">
@@ -9691,7 +9679,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B202" t="n">
@@ -9718,7 +9706,7 @@
       <c r="I202" t="n">
         <v>48.83308</v>
       </c>
-      <c r="J202" s="2" t="n">
+      <c r="J202" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K202" t="n">
@@ -9738,7 +9726,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B203" t="n">
@@ -9765,7 +9753,7 @@
       <c r="I203" t="n">
         <v>50.90073</v>
       </c>
-      <c r="J203" s="2" t="n">
+      <c r="J203" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K203" t="n">
@@ -9785,7 +9773,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B204" t="n">
@@ -9812,7 +9800,7 @@
       <c r="I204" t="n">
         <v>51.49107</v>
       </c>
-      <c r="J204" s="2" t="n">
+      <c r="J204" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K204" t="n">
@@ -9832,7 +9820,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B205" t="n">
@@ -9859,7 +9847,7 @@
       <c r="I205" t="n">
         <v>49.10525999999999</v>
       </c>
-      <c r="J205" s="2" t="n">
+      <c r="J205" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K205" t="n">
@@ -9879,7 +9867,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B206" t="n">
@@ -9906,7 +9894,7 @@
       <c r="I206" t="n">
         <v>47.73486</v>
       </c>
-      <c r="J206" s="2" t="n">
+      <c r="J206" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K206" t="n">
@@ -9926,7 +9914,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B207" t="n">
@@ -9953,7 +9941,7 @@
       <c r="I207" t="n">
         <v>46.86317999999999</v>
       </c>
-      <c r="J207" s="2" t="n">
+      <c r="J207" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K207" t="n">
@@ -9973,7 +9961,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B208" t="n">
@@ -10000,7 +9988,7 @@
       <c r="I208" t="n">
         <v>46.19519</v>
       </c>
-      <c r="J208" s="2" t="n">
+      <c r="J208" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K208" t="n">
@@ -10020,7 +10008,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B209" t="n">
@@ -10047,7 +10035,7 @@
       <c r="I209" t="n">
         <v>43.79043</v>
       </c>
-      <c r="J209" s="2" t="n">
+      <c r="J209" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K209" t="n">
@@ -10067,7 +10055,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B210" t="n">
@@ -10094,7 +10082,7 @@
       <c r="I210" t="n">
         <v>43.81728999999999</v>
       </c>
-      <c r="J210" s="2" t="n">
+      <c r="J210" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K210" t="n">
@@ -10114,7 +10102,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B211" t="n">
@@ -10141,7 +10129,7 @@
       <c r="I211" t="n">
         <v>41.48014</v>
       </c>
-      <c r="J211" s="2" t="n">
+      <c r="J211" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K211" t="n">
@@ -10161,7 +10149,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B212" t="n">
@@ -10188,7 +10176,7 @@
       <c r="I212" t="n">
         <v>41.96095999999999</v>
       </c>
-      <c r="J212" s="2" t="n">
+      <c r="J212" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K212" t="n">
@@ -10208,7 +10196,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B213" t="n">
@@ -10235,7 +10223,7 @@
       <c r="I213" t="n">
         <v>42.04255</v>
       </c>
-      <c r="J213" s="2" t="n">
+      <c r="J213" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K213" t="n">
@@ -10255,7 +10243,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B214" t="n">
@@ -10282,7 +10270,7 @@
       <c r="I214" t="n">
         <v>41.00722999999999</v>
       </c>
-      <c r="J214" s="2" t="n">
+      <c r="J214" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K214" t="n">
@@ -10302,7 +10290,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B215" t="n">
@@ -10329,7 +10317,7 @@
       <c r="I215" t="n">
         <v>41.04307</v>
       </c>
-      <c r="J215" s="2" t="n">
+      <c r="J215" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K215" t="n">
@@ -10349,7 +10337,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B216" t="n">
@@ -10376,7 +10364,7 @@
       <c r="I216" t="n">
         <v>40.10673999999999</v>
       </c>
-      <c r="J216" s="2" t="n">
+      <c r="J216" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K216" t="n">
@@ -10396,7 +10384,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B217" t="n">
@@ -10423,7 +10411,7 @@
       <c r="I217" t="n">
         <v>37.22207</v>
       </c>
-      <c r="J217" s="2" t="n">
+      <c r="J217" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K217" t="n">
@@ -10443,7 +10431,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B218" t="n">
@@ -10470,7 +10458,7 @@
       <c r="I218" t="n">
         <v>33.82858</v>
       </c>
-      <c r="J218" s="2" t="n">
+      <c r="J218" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K218" t="n">
@@ -10490,7 +10478,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B219" t="n">
@@ -10517,7 +10505,7 @@
       <c r="I219" t="n">
         <v>31.16933</v>
       </c>
-      <c r="J219" s="2" t="n">
+      <c r="J219" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K219" t="n">
@@ -10537,7 +10525,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B220" t="n">
@@ -10564,7 +10552,7 @@
       <c r="I220" t="n">
         <v>26.7406</v>
       </c>
-      <c r="J220" s="2" t="n">
+      <c r="J220" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K220" t="n">
@@ -10584,7 +10572,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B221" t="n">
@@ -10611,7 +10599,7 @@
       <c r="I221" t="n">
         <v>29.81743</v>
       </c>
-      <c r="J221" s="2" t="n">
+      <c r="J221" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K221" t="n">
@@ -10631,7 +10619,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B222" t="n">
@@ -10658,7 +10646,7 @@
       <c r="I222" t="n">
         <v>29.9388</v>
       </c>
-      <c r="J222" s="2" t="n">
+      <c r="J222" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K222" t="n">
@@ -10678,7 +10666,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B223" t="n">
@@ -10705,7 +10693,7 @@
       <c r="I223" t="n">
         <v>28.88884</v>
       </c>
-      <c r="J223" s="2" t="n">
+      <c r="J223" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K223" t="n">
@@ -10725,7 +10713,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B224" t="n">
@@ -10752,7 +10740,7 @@
       <c r="I224" t="n">
         <v>27.83844</v>
       </c>
-      <c r="J224" s="2" t="n">
+      <c r="J224" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K224" t="n">
@@ -10786,27 +10774,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>gsyh_tl</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>usd_ort</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gsyh_usd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
@@ -10823,7 +10811,7 @@
         <v>188.4470651431746</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>39538</v>
       </c>
     </row>
@@ -10838,7 +10826,7 @@
         <v>202.1165869692412</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>39629</v>
       </c>
     </row>
@@ -10853,7 +10841,7 @@
         <v>224.7668336608458</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>39721</v>
       </c>
     </row>
@@ -10870,7 +10858,7 @@
       <c r="D5" t="n">
         <v>784.2271960468236</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>39813</v>
       </c>
     </row>
@@ -10887,7 +10875,7 @@
       <c r="D6" t="n">
         <v>726.5630108224932</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>39903</v>
       </c>
     </row>
@@ -10904,7 +10892,7 @@
       <c r="D7" t="n">
         <v>680.8887296765091</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>39994</v>
       </c>
     </row>
@@ -10921,7 +10909,7 @@
       <c r="D8" t="n">
         <v>640.0868793971713</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>40086</v>
       </c>
     </row>
@@ -10938,7 +10926,7 @@
       <c r="D9" t="n">
         <v>658.9902820733863</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>40178</v>
       </c>
     </row>
@@ -10955,7 +10943,7 @@
       <c r="D10" t="n">
         <v>691.5463082981535</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>40268</v>
       </c>
     </row>
@@ -10972,7 +10960,7 @@
       <c r="D11" t="n">
         <v>719.6885900927989</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="1" t="n">
         <v>40359</v>
       </c>
     </row>
@@ -10989,7 +10977,7 @@
       <c r="D12" t="n">
         <v>749.0397936010979</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="1" t="n">
         <v>40451</v>
       </c>
     </row>
@@ -11006,7 +10994,7 @@
       <c r="D13" t="n">
         <v>784.9655005365125</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>40543</v>
       </c>
     </row>
@@ -11023,7 +11011,7 @@
       <c r="D14" t="n">
         <v>810.3253924162482</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="1" t="n">
         <v>40633</v>
       </c>
     </row>
@@ -11040,7 +11028,7 @@
       <c r="D15" t="n">
         <v>844.646504931485</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>40724</v>
       </c>
     </row>
@@ -11057,7 +11045,7 @@
       <c r="D16" t="n">
         <v>854.9653194859255</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="1" t="n">
         <v>40816</v>
       </c>
     </row>
@@ -11074,7 +11062,7 @@
       <c r="D17" t="n">
         <v>844.5068243568147</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="1" t="n">
         <v>40908</v>
       </c>
     </row>
@@ -11091,7 +11079,7 @@
       <c r="D18" t="n">
         <v>845.4079140024489</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>40999</v>
       </c>
     </row>
@@ -11108,7 +11096,7 @@
       <c r="D19" t="n">
         <v>841.945669848762</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="1" t="n">
         <v>41090</v>
       </c>
     </row>
@@ -11125,7 +11113,7 @@
       <c r="D20" t="n">
         <v>857.1420802056064</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="1" t="n">
         <v>41182</v>
       </c>
     </row>
@@ -11142,7 +11130,7 @@
       <c r="D21" t="n">
         <v>887.0698297363689</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="1" t="n">
         <v>41274</v>
       </c>
     </row>
@@ -11159,7 +11147,7 @@
       <c r="D22" t="n">
         <v>918.0892150612981</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="1" t="n">
         <v>41364</v>
       </c>
     </row>
@@ -11176,7 +11164,7 @@
       <c r="D23" t="n">
         <v>946.0043097899548</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="1" t="n">
         <v>41455</v>
       </c>
     </row>
@@ -11193,7 +11181,7 @@
       <c r="D24" t="n">
         <v>959.0932141449902</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="1" t="n">
         <v>41547</v>
       </c>
     </row>
@@ -11210,7 +11198,7 @@
       <c r="D25" t="n">
         <v>961.0481078717496</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="1" t="n">
         <v>41639</v>
       </c>
     </row>
@@ -11227,7 +11215,7 @@
       <c r="D26" t="n">
         <v>947.2834628100968</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="1" t="n">
         <v>41729</v>
       </c>
     </row>
@@ -11244,7 +11232,7 @@
       <c r="D27" t="n">
         <v>937.1937031513314</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="1" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -11261,7 +11249,7 @@
       <c r="D28" t="n">
         <v>940.6297640777781</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="1" t="n">
         <v>41912</v>
       </c>
     </row>
@@ -11278,7 +11266,7 @@
       <c r="D29" t="n">
         <v>942.8967695699519</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="1" t="n">
         <v>42004</v>
       </c>
     </row>
@@ -11295,7 +11283,7 @@
       <c r="D30" t="n">
         <v>940.1806740814401</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="1" t="n">
         <v>42094</v>
       </c>
     </row>
@@ -11312,7 +11300,7 @@
       <c r="D31" t="n">
         <v>919.6371330818704</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="1" t="n">
         <v>42185</v>
       </c>
     </row>
@@ -11329,7 +11317,7 @@
       <c r="D32" t="n">
         <v>887.3628039410262</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="1" t="n">
         <v>42277</v>
       </c>
     </row>
@@ -11346,7 +11334,7 @@
       <c r="D33" t="n">
         <v>863.921366521658</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="1" t="n">
         <v>42369</v>
       </c>
     </row>
@@ -11363,7 +11351,7 @@
       <c r="D34" t="n">
         <v>853.7046932188318</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="1" t="n">
         <v>42460</v>
       </c>
     </row>
@@ -11380,7 +11368,7 @@
       <c r="D35" t="n">
         <v>861.4305877129513</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="1" t="n">
         <v>42551</v>
       </c>
     </row>
@@ -11397,7 +11385,7 @@
       <c r="D36" t="n">
         <v>864.6856666920855</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="1" t="n">
         <v>42643</v>
       </c>
     </row>
@@ -11414,7 +11402,7 @@
       <c r="D37" t="n">
         <v>869.9030222927099</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="1" t="n">
         <v>42735</v>
       </c>
     </row>
@@ -11431,7 +11419,7 @@
       <c r="D38" t="n">
         <v>855.0244018960104</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="1" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -11448,7 +11436,7 @@
       <c r="D39" t="n">
         <v>842.4624338405587</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="1" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -11465,7 +11453,7 @@
       <c r="D40" t="n">
         <v>856.2791919679362</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="1" t="n">
         <v>43008</v>
       </c>
     </row>
@@ -11482,7 +11470,7 @@
       <c r="D41" t="n">
         <v>864.8788502660077</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="1" t="n">
         <v>43100</v>
       </c>
     </row>
@@ -11499,7 +11487,7 @@
       <c r="D42" t="n">
         <v>898.2531105139536</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="1" t="n">
         <v>43190</v>
       </c>
     </row>
@@ -11516,7 +11504,7 @@
       <c r="D43" t="n">
         <v>898.9553869128588</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="1" t="n">
         <v>43281</v>
       </c>
     </row>
@@ -11533,7 +11521,7 @@
       <c r="D44" t="n">
         <v>846.4394557072657</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="1" t="n">
         <v>43373</v>
       </c>
     </row>
@@ -11550,7 +11538,7 @@
       <c r="D45" t="n">
         <v>797.3238057726485</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="1" t="n">
         <v>43465</v>
       </c>
     </row>
@@ -11567,7 +11555,7 @@
       <c r="D46" t="n">
         <v>761.796683470352</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="1" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -11584,7 +11572,7 @@
       <c r="D47" t="n">
         <v>732.283041957087</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="1" t="n">
         <v>43646</v>
       </c>
     </row>
@@ -11601,7 +11589,7 @@
       <c r="D48" t="n">
         <v>752.4178296031997</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -11618,7 +11606,7 @@
       <c r="D49" t="n">
         <v>775.2901707093772</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="1" t="n">
         <v>43830</v>
       </c>
     </row>
@@ -11635,7 +11623,7 @@
       <c r="D50" t="n">
         <v>778.2260275513438</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -11652,7 +11640,7 @@
       <c r="D51" t="n">
         <v>754.0085363267242</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="1" t="n">
         <v>44012</v>
       </c>
     </row>
@@ -11669,7 +11657,7 @@
       <c r="D52" t="n">
         <v>746.091416266087</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="1" t="n">
         <v>44104</v>
       </c>
     </row>
@@ -11686,7 +11674,7 @@
       <c r="D53" t="n">
         <v>730.9546871917802</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="1" t="n">
         <v>44196</v>
       </c>
     </row>
@@ -11703,7 +11691,7 @@
       <c r="D54" t="n">
         <v>746.2494624509136</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="1" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -11720,7 +11708,7 @@
       <c r="D55" t="n">
         <v>786.5387429577326</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="1" t="n">
         <v>44377</v>
       </c>
     </row>
@@ -11737,7 +11725,7 @@
       <c r="D56" t="n">
         <v>818.3449224201991</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="1" t="n">
         <v>44469</v>
       </c>
     </row>
@@ -11754,7 +11742,7 @@
       <c r="D57" t="n">
         <v>835.6602257809595</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="1" t="n">
         <v>44561</v>
       </c>
     </row>
@@ -11771,7 +11759,7 @@
       <c r="D58" t="n">
         <v>826.4811453112486</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="1" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -11788,7 +11776,7 @@
       <c r="D59" t="n">
         <v>853.2410029660408</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="1" t="n">
         <v>44742</v>
       </c>
     </row>
@@ -11805,7 +11793,7 @@
       <c r="D60" t="n">
         <v>864.3854149792769</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="1" t="n">
         <v>44834</v>
       </c>
     </row>
@@ -11822,7 +11810,7 @@
       <c r="D61" t="n">
         <v>913.1863831015423</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="1" t="n">
         <v>44926</v>
       </c>
     </row>
@@ -11839,7 +11827,7 @@
       <c r="D62" t="n">
         <v>981.7702030343168</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="1" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11856,7 +11844,7 @@
       <c r="D63" t="n">
         <v>1035.745849934734</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="1" t="n">
         <v>45107</v>
       </c>
     </row>
@@ -11873,7 +11861,7 @@
       <c r="D64" t="n">
         <v>1087.793792245752</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="1" t="n">
         <v>45199</v>
       </c>
     </row>
@@ -11890,7 +11878,7 @@
       <c r="D65" t="n">
         <v>1131.01603472582</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="1" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -11907,7 +11895,7 @@
       <c r="D66" t="n">
         <v>1171.104959658617</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="1" t="n">
         <v>45382</v>
       </c>
     </row>
@@ -11924,7 +11912,7 @@
       <c r="D67" t="n">
         <v>1209.872581317634</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="1" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -11941,7 +11929,7 @@
       <c r="D68" t="n">
         <v>1283.797451942341</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="1" t="n">
         <v>45565</v>
       </c>
     </row>
@@ -11958,7 +11946,7 @@
       <c r="D69" t="n">
         <v>1357.572675785335</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -11975,7 +11963,7 @@
       <c r="D70" t="n">
         <v>1410.676074962415</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="1" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -11992,7 +11980,7 @@
       <c r="D71" t="n">
         <v>1473.820957975585</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="1" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -12009,7 +11997,7 @@
       <c r="D72" t="n">
         <v>1536.009359448403</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="1" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -12026,7 +12014,7 @@
       <c r="D73" t="n">
         <v>1595.814722617371</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -12043,7 +12031,7 @@
       <c r="D74" t="n">
         <v>1640.339363149401</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="1" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -12060,7 +12048,7 @@
       <c r="D75" t="n">
         <v>1700.354635555628</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="1" t="n">
         <v>46203</v>
       </c>
     </row>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,84 +434,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cari</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>enerji</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>cari_12</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>altin_12</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>enerji_12</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>diger_12</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>gsyh_tarih</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cari_gsyh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>altin_gsyh</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>enerji_gsyh</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>diger_gsyh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B2" t="n">
@@ -526,7 +538,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B3" t="n">
@@ -553,7 +565,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B4" t="n">
@@ -580,7 +592,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B5" t="n">
@@ -607,7 +619,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B6" t="n">
@@ -634,7 +646,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B7" t="n">
@@ -661,7 +673,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B8" t="n">
@@ -688,7 +700,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B9" t="n">
@@ -715,7 +727,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B10" t="n">
@@ -742,7 +754,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B11" t="n">
@@ -769,7 +781,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B12" t="n">
@@ -796,7 +808,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B13" t="n">
@@ -823,7 +835,7 @@
       <c r="I13" t="n">
         <v>2.68842</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K13" t="n">
@@ -843,7 +855,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B14" t="n">
@@ -870,7 +882,7 @@
       <c r="I14" t="n">
         <v>5.004020000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K14" t="n">
@@ -890,7 +902,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B15" t="n">
@@ -917,7 +929,7 @@
       <c r="I15" t="n">
         <v>6.2034</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K15" t="n">
@@ -937,7 +949,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B16" t="n">
@@ -964,7 +976,7 @@
       <c r="I16" t="n">
         <v>7.860720000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K16" t="n">
@@ -984,7 +996,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B17" t="n">
@@ -1011,7 +1023,7 @@
       <c r="I17" t="n">
         <v>9.52572</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K17" t="n">
@@ -1031,7 +1043,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B18" t="n">
@@ -1058,7 +1070,7 @@
       <c r="I18" t="n">
         <v>10.32989</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K18" t="n">
@@ -1078,7 +1090,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B19" t="n">
@@ -1105,7 +1117,7 @@
       <c r="I19" t="n">
         <v>11.23285</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K19" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B20" t="n">
@@ -1152,7 +1164,7 @@
       <c r="I20" t="n">
         <v>13.00463</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K20" t="n">
@@ -1172,7 +1184,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B21" t="n">
@@ -1199,7 +1211,7 @@
       <c r="I21" t="n">
         <v>12.93374</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K21" t="n">
@@ -1219,7 +1231,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B22" t="n">
@@ -1246,7 +1258,7 @@
       <c r="I22" t="n">
         <v>10.54887</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K22" t="n">
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B23" t="n">
@@ -1293,7 +1305,7 @@
       <c r="I23" t="n">
         <v>12.80883</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K23" t="n">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B24" t="n">
@@ -1340,7 +1352,7 @@
       <c r="I24" t="n">
         <v>11.9196</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K24" t="n">
@@ -1360,7 +1372,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B25" t="n">
@@ -1387,7 +1399,7 @@
       <c r="I25" t="n">
         <v>11.61895</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K25" t="n">
@@ -1407,7 +1419,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B26" t="n">
@@ -1434,7 +1446,7 @@
       <c r="I26" t="n">
         <v>10.08681</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K26" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B27" t="n">
@@ -1481,7 +1493,7 @@
       <c r="I27" t="n">
         <v>10.03788</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K27" t="n">
@@ -1501,7 +1513,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B28" t="n">
@@ -1528,7 +1540,7 @@
       <c r="I28" t="n">
         <v>8.120710000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K28" t="n">
@@ -1548,7 +1560,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B29" t="n">
@@ -1575,7 +1587,7 @@
       <c r="I29" t="n">
         <v>6.80951</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K29" t="n">
@@ -1595,7 +1607,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B30" t="n">
@@ -1622,7 +1634,7 @@
       <c r="I30" t="n">
         <v>5.458740000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K30" t="n">
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B31" t="n">
@@ -1669,7 +1681,7 @@
       <c r="I31" t="n">
         <v>4.53857</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K31" t="n">
@@ -1689,7 +1701,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B32" t="n">
@@ -1716,7 +1728,7 @@
       <c r="I32" t="n">
         <v>2.42634</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K32" t="n">
@@ -1736,7 +1748,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B33" t="n">
@@ -1763,7 +1775,7 @@
       <c r="I33" t="n">
         <v>0.1354600000000002</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K33" t="n">
@@ -1783,7 +1795,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B34" t="n">
@@ -1810,7 +1822,7 @@
       <c r="I34" t="n">
         <v>-1.641</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K34" t="n">
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B35" t="n">
@@ -1857,7 +1869,7 @@
       <c r="I35" t="n">
         <v>-4.08595</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K35" t="n">
@@ -1877,7 +1889,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B36" t="n">
@@ -1904,7 +1916,7 @@
       <c r="I36" t="n">
         <v>-7.33985</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K36" t="n">
@@ -1924,7 +1936,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B37" t="n">
@@ -1951,7 +1963,7 @@
       <c r="I37" t="n">
         <v>-10.14424</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K37" t="n">
@@ -1971,7 +1983,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B38" t="n">
@@ -1998,7 +2010,7 @@
       <c r="I38" t="n">
         <v>-11.7397</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K38" t="n">
@@ -2018,7 +2030,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B39" t="n">
@@ -2045,7 +2057,7 @@
       <c r="I39" t="n">
         <v>-14.14707</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K39" t="n">
@@ -2065,7 +2077,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B40" t="n">
@@ -2092,7 +2104,7 @@
       <c r="I40" t="n">
         <v>-18.16812</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K40" t="n">
@@ -2112,7 +2124,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B41" t="n">
@@ -2139,7 +2151,7 @@
       <c r="I41" t="n">
         <v>-20.5611</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K41" t="n">
@@ -2159,7 +2171,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B42" t="n">
@@ -2186,7 +2198,7 @@
       <c r="I42" t="n">
         <v>-23.39756</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K42" t="n">
@@ -2206,7 +2218,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B43" t="n">
@@ -2233,7 +2245,7 @@
       <c r="I43" t="n">
         <v>-26.26857</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K43" t="n">
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B44" t="n">
@@ -2280,7 +2292,7 @@
       <c r="I44" t="n">
         <v>-26.73468</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K44" t="n">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B45" t="n">
@@ -2327,7 +2339,7 @@
       <c r="I45" t="n">
         <v>-25.77266</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K45" t="n">
@@ -2347,7 +2359,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B46" t="n">
@@ -2374,7 +2386,7 @@
       <c r="I46" t="n">
         <v>-25.75811</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K46" t="n">
@@ -2394,7 +2406,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B47" t="n">
@@ -2421,7 +2433,7 @@
       <c r="I47" t="n">
         <v>-25.40919</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K47" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B48" t="n">
@@ -2468,7 +2480,7 @@
       <c r="I48" t="n">
         <v>-24.01676</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K48" t="n">
@@ -2488,7 +2500,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B49" t="n">
@@ -2515,7 +2527,7 @@
       <c r="I49" t="n">
         <v>-22.04643</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K49" t="n">
@@ -2535,7 +2547,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B50" t="n">
@@ -2562,7 +2574,7 @@
       <c r="I50" t="n">
         <v>-21.51568</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K50" t="n">
@@ -2582,7 +2594,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B51" t="n">
@@ -2609,7 +2621,7 @@
       <c r="I51" t="n">
         <v>-19.64396</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K51" t="n">
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B52" t="n">
@@ -2656,7 +2668,7 @@
       <c r="I52" t="n">
         <v>-15.79015</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K52" t="n">
@@ -2676,7 +2688,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B53" t="n">
@@ -2703,7 +2715,7 @@
       <c r="I53" t="n">
         <v>-13.06127</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K53" t="n">
@@ -2723,7 +2735,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B54" t="n">
@@ -2750,7 +2762,7 @@
       <c r="I54" t="n">
         <v>-10.51409</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K54" t="n">
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B55" t="n">
@@ -2797,7 +2809,7 @@
       <c r="I55" t="n">
         <v>-6.249130000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K55" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B56" t="n">
@@ -2844,7 +2856,7 @@
       <c r="I56" t="n">
         <v>-4.688590000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K56" t="n">
@@ -2864,7 +2876,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B57" t="n">
@@ -2891,7 +2903,7 @@
       <c r="I57" t="n">
         <v>-2.382240000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K57" t="n">
@@ -2911,7 +2923,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B58" t="n">
@@ -2938,7 +2950,7 @@
       <c r="I58" t="n">
         <v>0.395989999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K58" t="n">
@@ -2958,7 +2970,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B59" t="n">
@@ -2985,7 +2997,7 @@
       <c r="I59" t="n">
         <v>1.845749999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K59" t="n">
@@ -3005,7 +3017,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B60" t="n">
@@ -3032,7 +3044,7 @@
       <c r="I60" t="n">
         <v>3.21682</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K60" t="n">
@@ -3052,7 +3064,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B61" t="n">
@@ -3079,7 +3091,7 @@
       <c r="I61" t="n">
         <v>4.90424</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K61" t="n">
@@ -3099,7 +3111,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B62" t="n">
@@ -3126,7 +3138,7 @@
       <c r="I62" t="n">
         <v>5.24468</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K62" t="n">
@@ -3146,7 +3158,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B63" t="n">
@@ -3173,7 +3185,7 @@
       <c r="I63" t="n">
         <v>5.49649</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K63" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B64" t="n">
@@ -3220,7 +3232,7 @@
       <c r="I64" t="n">
         <v>6.803089999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K64" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B65" t="n">
@@ -3267,7 +3279,7 @@
       <c r="I65" t="n">
         <v>7.07182</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K65" t="n">
@@ -3287,7 +3299,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B66" t="n">
@@ -3314,7 +3326,7 @@
       <c r="I66" t="n">
         <v>8.31753</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K66" t="n">
@@ -3334,7 +3346,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B67" t="n">
@@ -3361,7 +3373,7 @@
       <c r="I67" t="n">
         <v>9.40043</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K67" t="n">
@@ -3381,7 +3393,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B68" t="n">
@@ -3408,7 +3420,7 @@
       <c r="I68" t="n">
         <v>9.15676</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K68" t="n">
@@ -3428,7 +3440,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B69" t="n">
@@ -3455,7 +3467,7 @@
       <c r="I69" t="n">
         <v>9.691610000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K69" t="n">
@@ -3475,7 +3487,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B70" t="n">
@@ -3502,7 +3514,7 @@
       <c r="I70" t="n">
         <v>10.6274</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K70" t="n">
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B71" t="n">
@@ -3549,7 +3561,7 @@
       <c r="I71" t="n">
         <v>10.15893</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K71" t="n">
@@ -3569,7 +3581,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B72" t="n">
@@ -3596,7 +3608,7 @@
       <c r="I72" t="n">
         <v>11.57857</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K72" t="n">
@@ -3616,7 +3628,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B73" t="n">
@@ -3643,7 +3655,7 @@
       <c r="I73" t="n">
         <v>10.08393</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K73" t="n">
@@ -3663,7 +3675,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B74" t="n">
@@ -3690,7 +3702,7 @@
       <c r="I74" t="n">
         <v>11.61466</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K74" t="n">
@@ -3710,7 +3722,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B75" t="n">
@@ -3737,7 +3749,7 @@
       <c r="I75" t="n">
         <v>12.55543</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K75" t="n">
@@ -3757,7 +3769,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B76" t="n">
@@ -3784,7 +3796,7 @@
       <c r="I76" t="n">
         <v>12.95175</v>
       </c>
-      <c r="J76" s="1" t="n">
+      <c r="J76" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K76" t="n">
@@ -3804,7 +3816,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B77" t="n">
@@ -3831,7 +3843,7 @@
       <c r="I77" t="n">
         <v>13.82609</v>
       </c>
-      <c r="J77" s="1" t="n">
+      <c r="J77" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K77" t="n">
@@ -3851,7 +3863,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B78" t="n">
@@ -3878,7 +3890,7 @@
       <c r="I78" t="n">
         <v>15.83389</v>
       </c>
-      <c r="J78" s="1" t="n">
+      <c r="J78" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K78" t="n">
@@ -3898,7 +3910,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B79" t="n">
@@ -3925,7 +3937,7 @@
       <c r="I79" t="n">
         <v>15.8046</v>
       </c>
-      <c r="J79" s="1" t="n">
+      <c r="J79" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K79" t="n">
@@ -3945,7 +3957,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B80" t="n">
@@ -3972,7 +3984,7 @@
       <c r="I80" t="n">
         <v>18.19608</v>
       </c>
-      <c r="J80" s="1" t="n">
+      <c r="J80" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K80" t="n">
@@ -3992,7 +4004,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B81" t="n">
@@ -4019,7 +4031,7 @@
       <c r="I81" t="n">
         <v>18.488</v>
       </c>
-      <c r="J81" s="1" t="n">
+      <c r="J81" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K81" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B82" t="n">
@@ -4066,7 +4078,7 @@
       <c r="I82" t="n">
         <v>19.80297</v>
       </c>
-      <c r="J82" s="1" t="n">
+      <c r="J82" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K82" t="n">
@@ -4086,7 +4098,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B83" t="n">
@@ -4113,7 +4125,7 @@
       <c r="I83" t="n">
         <v>20.59569</v>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="J83" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K83" t="n">
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B84" t="n">
@@ -4160,7 +4172,7 @@
       <c r="I84" t="n">
         <v>19.85103</v>
       </c>
-      <c r="J84" s="1" t="n">
+      <c r="J84" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K84" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B85" t="n">
@@ -4207,7 +4219,7 @@
       <c r="I85" t="n">
         <v>20.46028</v>
       </c>
-      <c r="J85" s="1" t="n">
+      <c r="J85" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K85" t="n">
@@ -4227,7 +4239,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B86" t="n">
@@ -4254,7 +4266,7 @@
       <c r="I86" t="n">
         <v>20.80432</v>
       </c>
-      <c r="J86" s="1" t="n">
+      <c r="J86" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K86" t="n">
@@ -4274,7 +4286,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B87" t="n">
@@ -4301,7 +4313,7 @@
       <c r="I87" t="n">
         <v>18.98794</v>
       </c>
-      <c r="J87" s="1" t="n">
+      <c r="J87" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K87" t="n">
@@ -4321,7 +4333,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B88" t="n">
@@ -4348,7 +4360,7 @@
       <c r="I88" t="n">
         <v>17.46199</v>
       </c>
-      <c r="J88" s="1" t="n">
+      <c r="J88" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K88" t="n">
@@ -4368,7 +4380,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B89" t="n">
@@ -4395,7 +4407,7 @@
       <c r="I89" t="n">
         <v>15.2882</v>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="J89" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K89" t="n">
@@ -4415,7 +4427,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B90" t="n">
@@ -4442,7 +4454,7 @@
       <c r="I90" t="n">
         <v>12.95619</v>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="J90" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K90" t="n">
@@ -4462,7 +4474,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B91" t="n">
@@ -4489,7 +4501,7 @@
       <c r="I91" t="n">
         <v>11.8918</v>
       </c>
-      <c r="J91" s="1" t="n">
+      <c r="J91" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K91" t="n">
@@ -4509,7 +4521,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B92" t="n">
@@ -4536,7 +4548,7 @@
       <c r="I92" t="n">
         <v>10.00618</v>
       </c>
-      <c r="J92" s="1" t="n">
+      <c r="J92" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K92" t="n">
@@ -4556,7 +4568,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4595,7 @@
       <c r="I93" t="n">
         <v>10.69088</v>
       </c>
-      <c r="J93" s="1" t="n">
+      <c r="J93" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K93" t="n">
@@ -4603,7 +4615,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B94" t="n">
@@ -4630,7 +4642,7 @@
       <c r="I94" t="n">
         <v>9.682169999999999</v>
       </c>
-      <c r="J94" s="1" t="n">
+      <c r="J94" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K94" t="n">
@@ -4650,7 +4662,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B95" t="n">
@@ -4677,7 +4689,7 @@
       <c r="I95" t="n">
         <v>9.299630000000001</v>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="J95" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K95" t="n">
@@ -4697,7 +4709,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B96" t="n">
@@ -4724,7 +4736,7 @@
       <c r="I96" t="n">
         <v>9.04907</v>
       </c>
-      <c r="J96" s="1" t="n">
+      <c r="J96" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K96" t="n">
@@ -4744,7 +4756,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B97" t="n">
@@ -4771,7 +4783,7 @@
       <c r="I97" t="n">
         <v>8.198219999999999</v>
       </c>
-      <c r="J97" s="1" t="n">
+      <c r="J97" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K97" t="n">
@@ -4791,7 +4803,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B98" t="n">
@@ -4818,7 +4830,7 @@
       <c r="I98" t="n">
         <v>7.736389999999999</v>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="J98" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K98" t="n">
@@ -4838,7 +4850,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B99" t="n">
@@ -4865,7 +4877,7 @@
       <c r="I99" t="n">
         <v>7.899969999999999</v>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="J99" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K99" t="n">
@@ -4885,7 +4897,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B100" t="n">
@@ -4912,7 +4924,7 @@
       <c r="I100" t="n">
         <v>7.502359999999999</v>
       </c>
-      <c r="J100" s="1" t="n">
+      <c r="J100" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K100" t="n">
@@ -4932,7 +4944,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4971,7 @@
       <c r="I101" t="n">
         <v>8.811169999999999</v>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="J101" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K101" t="n">
@@ -4979,7 +4991,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B102" t="n">
@@ -5006,7 +5018,7 @@
       <c r="I102" t="n">
         <v>7.943439999999999</v>
       </c>
-      <c r="J102" s="1" t="n">
+      <c r="J102" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K102" t="n">
@@ -5026,7 +5038,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B103" t="n">
@@ -5053,7 +5065,7 @@
       <c r="I103" t="n">
         <v>4.534299999999999</v>
       </c>
-      <c r="J103" s="1" t="n">
+      <c r="J103" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K103" t="n">
@@ -5073,7 +5085,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B104" t="n">
@@ -5100,7 +5112,7 @@
       <c r="I104" t="n">
         <v>2.886419999999999</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="J104" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K104" t="n">
@@ -5120,7 +5132,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B105" t="n">
@@ -5147,7 +5159,7 @@
       <c r="I105" t="n">
         <v>0.2952499999999989</v>
       </c>
-      <c r="J105" s="1" t="n">
+      <c r="J105" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K105" t="n">
@@ -5167,7 +5179,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B106" t="n">
@@ -5194,7 +5206,7 @@
       <c r="I106" t="n">
         <v>-1.300060000000001</v>
       </c>
-      <c r="J106" s="1" t="n">
+      <c r="J106" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K106" t="n">
@@ -5214,7 +5226,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B107" t="n">
@@ -5241,7 +5253,7 @@
       <c r="I107" t="n">
         <v>-1.551580000000001</v>
       </c>
-      <c r="J107" s="1" t="n">
+      <c r="J107" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K107" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B108" t="n">
@@ -5288,7 +5300,7 @@
       <c r="I108" t="n">
         <v>-1.618070000000001</v>
       </c>
-      <c r="J108" s="1" t="n">
+      <c r="J108" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K108" t="n">
@@ -5308,7 +5320,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B109" t="n">
@@ -5335,7 +5347,7 @@
       <c r="I109" t="n">
         <v>0.1297299999999989</v>
       </c>
-      <c r="J109" s="1" t="n">
+      <c r="J109" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K109" t="n">
@@ -5355,7 +5367,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B110" t="n">
@@ -5382,7 +5394,7 @@
       <c r="I110" t="n">
         <v>0.3622699999999989</v>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="J110" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K110" t="n">
@@ -5402,7 +5414,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B111" t="n">
@@ -5429,7 +5441,7 @@
       <c r="I111" t="n">
         <v>2.062249999999999</v>
       </c>
-      <c r="J111" s="1" t="n">
+      <c r="J111" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K111" t="n">
@@ -5449,7 +5461,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B112" t="n">
@@ -5476,7 +5488,7 @@
       <c r="I112" t="n">
         <v>4.506739999999999</v>
       </c>
-      <c r="J112" s="1" t="n">
+      <c r="J112" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K112" t="n">
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B113" t="n">
@@ -5523,7 +5535,7 @@
       <c r="I113" t="n">
         <v>4.95311</v>
       </c>
-      <c r="J113" s="1" t="n">
+      <c r="J113" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K113" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B114" t="n">
@@ -5570,7 +5582,7 @@
       <c r="I114" t="n">
         <v>5.905279999999999</v>
       </c>
-      <c r="J114" s="1" t="n">
+      <c r="J114" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K114" t="n">
@@ -5590,7 +5602,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B115" t="n">
@@ -5617,7 +5629,7 @@
       <c r="I115" t="n">
         <v>8.84371</v>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="J115" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K115" t="n">
@@ -5637,7 +5649,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B116" t="n">
@@ -5664,7 +5676,7 @@
       <c r="I116" t="n">
         <v>9.860910000000001</v>
       </c>
-      <c r="J116" s="1" t="n">
+      <c r="J116" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K116" t="n">
@@ -5684,7 +5696,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B117" t="n">
@@ -5711,7 +5723,7 @@
       <c r="I117" t="n">
         <v>12.08097</v>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="J117" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K117" t="n">
@@ -5731,7 +5743,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B118" t="n">
@@ -5758,7 +5770,7 @@
       <c r="I118" t="n">
         <v>10.99841</v>
       </c>
-      <c r="J118" s="1" t="n">
+      <c r="J118" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K118" t="n">
@@ -5778,7 +5790,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B119" t="n">
@@ -5805,7 +5817,7 @@
       <c r="I119" t="n">
         <v>9.6854</v>
       </c>
-      <c r="J119" s="1" t="n">
+      <c r="J119" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K119" t="n">
@@ -5825,7 +5837,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B120" t="n">
@@ -5852,7 +5864,7 @@
       <c r="I120" t="n">
         <v>9.236190000000001</v>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="J120" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K120" t="n">
@@ -5872,7 +5884,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B121" t="n">
@@ -5899,7 +5911,7 @@
       <c r="I121" t="n">
         <v>7.685680000000001</v>
       </c>
-      <c r="J121" s="1" t="n">
+      <c r="J121" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K121" t="n">
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B122" t="n">
@@ -5946,7 +5958,7 @@
       <c r="I122" t="n">
         <v>5.95812</v>
       </c>
-      <c r="J122" s="1" t="n">
+      <c r="J122" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K122" t="n">
@@ -5966,7 +5978,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B123" t="n">
@@ -5993,7 +6005,7 @@
       <c r="I123" t="n">
         <v>4.993270000000001</v>
       </c>
-      <c r="J123" s="1" t="n">
+      <c r="J123" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K123" t="n">
@@ -6013,7 +6025,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B124" t="n">
@@ -6040,7 +6052,7 @@
       <c r="I124" t="n">
         <v>4.364470000000001</v>
       </c>
-      <c r="J124" s="1" t="n">
+      <c r="J124" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K124" t="n">
@@ -6060,7 +6072,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B125" t="n">
@@ -6087,7 +6099,7 @@
       <c r="I125" t="n">
         <v>3.48327</v>
       </c>
-      <c r="J125" s="1" t="n">
+      <c r="J125" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K125" t="n">
@@ -6107,7 +6119,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B126" t="n">
@@ -6134,7 +6146,7 @@
       <c r="I126" t="n">
         <v>3.21001</v>
       </c>
-      <c r="J126" s="1" t="n">
+      <c r="J126" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K126" t="n">
@@ -6154,7 +6166,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B127" t="n">
@@ -6181,7 +6193,7 @@
       <c r="I127" t="n">
         <v>3.74216</v>
       </c>
-      <c r="J127" s="1" t="n">
+      <c r="J127" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K127" t="n">
@@ -6201,7 +6213,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B128" t="n">
@@ -6228,7 +6240,7 @@
       <c r="I128" t="n">
         <v>6.06072</v>
       </c>
-      <c r="J128" s="1" t="n">
+      <c r="J128" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K128" t="n">
@@ -6248,7 +6260,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B129" t="n">
@@ -6275,7 +6287,7 @@
       <c r="I129" t="n">
         <v>7.804049999999999</v>
       </c>
-      <c r="J129" s="1" t="n">
+      <c r="J129" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K129" t="n">
@@ -6295,7 +6307,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B130" t="n">
@@ -6322,7 +6334,7 @@
       <c r="I130" t="n">
         <v>14.08367</v>
       </c>
-      <c r="J130" s="1" t="n">
+      <c r="J130" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K130" t="n">
@@ -6342,7 +6354,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B131" t="n">
@@ -6369,7 +6381,7 @@
       <c r="I131" t="n">
         <v>20.77072</v>
       </c>
-      <c r="J131" s="1" t="n">
+      <c r="J131" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K131" t="n">
@@ -6389,7 +6401,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B132" t="n">
@@ -6416,7 +6428,7 @@
       <c r="I132" t="n">
         <v>26.56942</v>
       </c>
-      <c r="J132" s="1" t="n">
+      <c r="J132" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K132" t="n">
@@ -6436,7 +6448,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B133" t="n">
@@ -6463,7 +6475,7 @@
       <c r="I133" t="n">
         <v>31.91968</v>
       </c>
-      <c r="J133" s="1" t="n">
+      <c r="J133" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K133" t="n">
@@ -6483,7 +6495,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B134" t="n">
@@ -6510,7 +6522,7 @@
       <c r="I134" t="n">
         <v>36.77216</v>
       </c>
-      <c r="J134" s="1" t="n">
+      <c r="J134" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K134" t="n">
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B135" t="n">
@@ -6557,7 +6569,7 @@
       <c r="I135" t="n">
         <v>40.31249</v>
       </c>
-      <c r="J135" s="1" t="n">
+      <c r="J135" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K135" t="n">
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B136" t="n">
@@ -6604,7 +6616,7 @@
       <c r="I136" t="n">
         <v>44.4252</v>
       </c>
-      <c r="J136" s="1" t="n">
+      <c r="J136" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K136" t="n">
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B137" t="n">
@@ -6651,7 +6663,7 @@
       <c r="I137" t="n">
         <v>48.80586</v>
       </c>
-      <c r="J137" s="1" t="n">
+      <c r="J137" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K137" t="n">
@@ -6671,7 +6683,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B138" t="n">
@@ -6698,7 +6710,7 @@
       <c r="I138" t="n">
         <v>53.917</v>
       </c>
-      <c r="J138" s="1" t="n">
+      <c r="J138" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K138" t="n">
@@ -6718,7 +6730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B139" t="n">
@@ -6745,7 +6757,7 @@
       <c r="I139" t="n">
         <v>56.12547</v>
       </c>
-      <c r="J139" s="1" t="n">
+      <c r="J139" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K139" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B140" t="n">
@@ -6792,7 +6804,7 @@
       <c r="I140" t="n">
         <v>59.44548</v>
       </c>
-      <c r="J140" s="1" t="n">
+      <c r="J140" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K140" t="n">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B141" t="n">
@@ -6839,7 +6851,7 @@
       <c r="I141" t="n">
         <v>60.96964</v>
       </c>
-      <c r="J141" s="1" t="n">
+      <c r="J141" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K141" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B142" t="n">
@@ -6886,7 +6898,7 @@
       <c r="I142" t="n">
         <v>61.12259999999999</v>
       </c>
-      <c r="J142" s="1" t="n">
+      <c r="J142" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K142" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B143" t="n">
@@ -6933,7 +6945,7 @@
       <c r="I143" t="n">
         <v>60.94875</v>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="J143" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K143" t="n">
@@ -6953,7 +6965,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B144" t="n">
@@ -6980,7 +6992,7 @@
       <c r="I144" t="n">
         <v>59.31162999999999</v>
       </c>
-      <c r="J144" s="1" t="n">
+      <c r="J144" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K144" t="n">
@@ -7000,7 +7012,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B145" t="n">
@@ -7027,7 +7039,7 @@
       <c r="I145" t="n">
         <v>57.56779</v>
       </c>
-      <c r="J145" s="1" t="n">
+      <c r="J145" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K145" t="n">
@@ -7047,7 +7059,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B146" t="n">
@@ -7074,7 +7086,7 @@
       <c r="I146" t="n">
         <v>57.90269</v>
       </c>
-      <c r="J146" s="1" t="n">
+      <c r="J146" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K146" t="n">
@@ -7094,7 +7106,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B147" t="n">
@@ -7121,7 +7133,7 @@
       <c r="I147" t="n">
         <v>57.78574999999999</v>
       </c>
-      <c r="J147" s="1" t="n">
+      <c r="J147" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K147" t="n">
@@ -7141,7 +7153,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B148" t="n">
@@ -7168,7 +7180,7 @@
       <c r="I148" t="n">
         <v>52.78822</v>
       </c>
-      <c r="J148" s="1" t="n">
+      <c r="J148" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K148" t="n">
@@ -7188,7 +7200,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B149" t="n">
@@ -7215,7 +7227,7 @@
       <c r="I149" t="n">
         <v>46.00505</v>
       </c>
-      <c r="J149" s="1" t="n">
+      <c r="J149" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K149" t="n">
@@ -7235,7 +7247,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B150" t="n">
@@ -7262,7 +7274,7 @@
       <c r="I150" t="n">
         <v>39.39304</v>
       </c>
-      <c r="J150" s="1" t="n">
+      <c r="J150" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K150" t="n">
@@ -7282,7 +7294,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B151" t="n">
@@ -7309,7 +7321,7 @@
       <c r="I151" t="n">
         <v>37.28101</v>
       </c>
-      <c r="J151" s="1" t="n">
+      <c r="J151" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K151" t="n">
@@ -7329,7 +7341,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B152" t="n">
@@ -7356,7 +7368,7 @@
       <c r="I152" t="n">
         <v>32.8163</v>
       </c>
-      <c r="J152" s="1" t="n">
+      <c r="J152" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K152" t="n">
@@ -7376,7 +7388,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B153" t="n">
@@ -7403,7 +7415,7 @@
       <c r="I153" t="n">
         <v>26.95827</v>
       </c>
-      <c r="J153" s="1" t="n">
+      <c r="J153" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K153" t="n">
@@ -7423,7 +7435,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B154" t="n">
@@ -7450,7 +7462,7 @@
       <c r="I154" t="n">
         <v>23.34406</v>
       </c>
-      <c r="J154" s="1" t="n">
+      <c r="J154" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K154" t="n">
@@ -7470,7 +7482,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B155" t="n">
@@ -7497,7 +7509,7 @@
       <c r="I155" t="n">
         <v>19.61043</v>
       </c>
-      <c r="J155" s="1" t="n">
+      <c r="J155" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K155" t="n">
@@ -7517,7 +7529,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B156" t="n">
@@ -7544,7 +7556,7 @@
       <c r="I156" t="n">
         <v>16.41961</v>
       </c>
-      <c r="J156" s="1" t="n">
+      <c r="J156" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K156" t="n">
@@ -7564,7 +7576,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B157" t="n">
@@ -7591,7 +7603,7 @@
       <c r="I157" t="n">
         <v>15.58579</v>
       </c>
-      <c r="J157" s="1" t="n">
+      <c r="J157" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K157" t="n">
@@ -7611,7 +7623,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B158" t="n">
@@ -7638,7 +7650,7 @@
       <c r="I158" t="n">
         <v>13.06948</v>
       </c>
-      <c r="J158" s="1" t="n">
+      <c r="J158" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K158" t="n">
@@ -7658,7 +7670,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B159" t="n">
@@ -7685,7 +7697,7 @@
       <c r="I159" t="n">
         <v>10.72014</v>
       </c>
-      <c r="J159" s="1" t="n">
+      <c r="J159" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K159" t="n">
@@ -7705,7 +7717,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B160" t="n">
@@ -7732,7 +7744,7 @@
       <c r="I160" t="n">
         <v>11.85764</v>
       </c>
-      <c r="J160" s="1" t="n">
+      <c r="J160" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K160" t="n">
@@ -7752,7 +7764,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B161" t="n">
@@ -7779,7 +7791,7 @@
       <c r="I161" t="n">
         <v>16.75192</v>
       </c>
-      <c r="J161" s="1" t="n">
+      <c r="J161" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K161" t="n">
@@ -7799,7 +7811,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B162" t="n">
@@ -7826,7 +7838,7 @@
       <c r="I162" t="n">
         <v>17.78087</v>
       </c>
-      <c r="J162" s="1" t="n">
+      <c r="J162" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K162" t="n">
@@ -7846,7 +7858,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B163" t="n">
@@ -7873,7 +7885,7 @@
       <c r="I163" t="n">
         <v>19.18315</v>
       </c>
-      <c r="J163" s="1" t="n">
+      <c r="J163" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K163" t="n">
@@ -7893,7 +7905,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B164" t="n">
@@ -7920,7 +7932,7 @@
       <c r="I164" t="n">
         <v>21.03445</v>
       </c>
-      <c r="J164" s="1" t="n">
+      <c r="J164" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K164" t="n">
@@ -7940,7 +7952,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B165" t="n">
@@ -7967,7 +7979,7 @@
       <c r="I165" t="n">
         <v>25.49619</v>
       </c>
-      <c r="J165" s="1" t="n">
+      <c r="J165" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K165" t="n">
@@ -7987,7 +7999,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B166" t="n">
@@ -8014,7 +8026,7 @@
       <c r="I166" t="n">
         <v>28.66052</v>
       </c>
-      <c r="J166" s="1" t="n">
+      <c r="J166" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K166" t="n">
@@ -8034,7 +8046,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B167" t="n">
@@ -8061,7 +8073,7 @@
       <c r="I167" t="n">
         <v>33.67982</v>
       </c>
-      <c r="J167" s="1" t="n">
+      <c r="J167" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K167" t="n">
@@ -8081,7 +8093,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B168" t="n">
@@ -8108,7 +8120,7 @@
       <c r="I168" t="n">
         <v>35.21025</v>
       </c>
-      <c r="J168" s="1" t="n">
+      <c r="J168" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K168" t="n">
@@ -8128,7 +8140,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B169" t="n">
@@ -8155,7 +8167,7 @@
       <c r="I169" t="n">
         <v>37.12937</v>
       </c>
-      <c r="J169" s="1" t="n">
+      <c r="J169" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K169" t="n">
@@ -8175,7 +8187,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B170" t="n">
@@ -8202,7 +8214,7 @@
       <c r="I170" t="n">
         <v>37.22411</v>
       </c>
-      <c r="J170" s="1" t="n">
+      <c r="J170" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K170" t="n">
@@ -8222,7 +8234,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B171" t="n">
@@ -8249,7 +8261,7 @@
       <c r="I171" t="n">
         <v>38.29664</v>
       </c>
-      <c r="J171" s="1" t="n">
+      <c r="J171" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K171" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B172" t="n">
@@ -8296,7 +8308,7 @@
       <c r="I172" t="n">
         <v>40.84047</v>
       </c>
-      <c r="J172" s="1" t="n">
+      <c r="J172" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K172" t="n">
@@ -8316,7 +8328,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B173" t="n">
@@ -8343,7 +8355,7 @@
       <c r="I173" t="n">
         <v>43.37856</v>
       </c>
-      <c r="J173" s="1" t="n">
+      <c r="J173" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K173" t="n">
@@ -8363,7 +8375,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B174" t="n">
@@ -8390,7 +8402,7 @@
       <c r="I174" t="n">
         <v>45.0951</v>
       </c>
-      <c r="J174" s="1" t="n">
+      <c r="J174" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K174" t="n">
@@ -8410,7 +8422,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B175" t="n">
@@ -8437,7 +8449,7 @@
       <c r="I175" t="n">
         <v>47.7854</v>
       </c>
-      <c r="J175" s="1" t="n">
+      <c r="J175" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K175" t="n">
@@ -8457,7 +8469,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B176" t="n">
@@ -8484,7 +8496,7 @@
       <c r="I176" t="n">
         <v>48.45027</v>
       </c>
-      <c r="J176" s="1" t="n">
+      <c r="J176" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K176" t="n">
@@ -8504,7 +8516,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B177" t="n">
@@ -8531,7 +8543,7 @@
       <c r="I177" t="n">
         <v>49.68133</v>
       </c>
-      <c r="J177" s="1" t="n">
+      <c r="J177" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K177" t="n">
@@ -8551,7 +8563,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B178" t="n">
@@ -8578,7 +8590,7 @@
       <c r="I178" t="n">
         <v>50.47562</v>
       </c>
-      <c r="J178" s="1" t="n">
+      <c r="J178" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K178" t="n">
@@ -8598,7 +8610,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B179" t="n">
@@ -8625,7 +8637,7 @@
       <c r="I179" t="n">
         <v>50.11399</v>
       </c>
-      <c r="J179" s="1" t="n">
+      <c r="J179" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K179" t="n">
@@ -8645,7 +8657,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B180" t="n">
@@ -8672,7 +8684,7 @@
       <c r="I180" t="n">
         <v>52.17445</v>
       </c>
-      <c r="J180" s="1" t="n">
+      <c r="J180" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K180" t="n">
@@ -8692,7 +8704,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B181" t="n">
@@ -8719,7 +8731,7 @@
       <c r="I181" t="n">
         <v>52.84970999999999</v>
       </c>
-      <c r="J181" s="1" t="n">
+      <c r="J181" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K181" t="n">
@@ -8739,7 +8751,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B182" t="n">
@@ -8766,7 +8778,7 @@
       <c r="I182" t="n">
         <v>53.61758</v>
       </c>
-      <c r="J182" s="1" t="n">
+      <c r="J182" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K182" t="n">
@@ -8786,7 +8798,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B183" t="n">
@@ -8813,7 +8825,7 @@
       <c r="I183" t="n">
         <v>52.49454</v>
       </c>
-      <c r="J183" s="1" t="n">
+      <c r="J183" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K183" t="n">
@@ -8833,7 +8845,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B184" t="n">
@@ -8860,7 +8872,7 @@
       <c r="I184" t="n">
         <v>50.79395</v>
       </c>
-      <c r="J184" s="1" t="n">
+      <c r="J184" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K184" t="n">
@@ -8880,7 +8892,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B185" t="n">
@@ -8907,7 +8919,7 @@
       <c r="I185" t="n">
         <v>46.78892</v>
       </c>
-      <c r="J185" s="1" t="n">
+      <c r="J185" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K185" t="n">
@@ -8927,7 +8939,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B186" t="n">
@@ -8954,7 +8966,7 @@
       <c r="I186" t="n">
         <v>45.03124</v>
       </c>
-      <c r="J186" s="1" t="n">
+      <c r="J186" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K186" t="n">
@@ -8974,7 +8986,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B187" t="n">
@@ -9001,7 +9013,7 @@
       <c r="I187" t="n">
         <v>45.92217</v>
       </c>
-      <c r="J187" s="1" t="n">
+      <c r="J187" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K187" t="n">
@@ -9021,7 +9033,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B188" t="n">
@@ -9048,7 +9060,7 @@
       <c r="I188" t="n">
         <v>42.09453999999999</v>
       </c>
-      <c r="J188" s="1" t="n">
+      <c r="J188" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K188" t="n">
@@ -9068,7 +9080,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B189" t="n">
@@ -9095,7 +9107,7 @@
       <c r="I189" t="n">
         <v>41.36029</v>
       </c>
-      <c r="J189" s="1" t="n">
+      <c r="J189" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K189" t="n">
@@ -9115,7 +9127,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B190" t="n">
@@ -9142,7 +9154,7 @@
       <c r="I190" t="n">
         <v>41.33475</v>
       </c>
-      <c r="J190" s="1" t="n">
+      <c r="J190" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K190" t="n">
@@ -9162,7 +9174,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B191" t="n">
@@ -9189,7 +9201,7 @@
       <c r="I191" t="n">
         <v>38.13951</v>
       </c>
-      <c r="J191" s="1" t="n">
+      <c r="J191" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K191" t="n">
@@ -9209,7 +9221,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B192" t="n">
@@ -9236,7 +9248,7 @@
       <c r="I192" t="n">
         <v>35.59753</v>
       </c>
-      <c r="J192" s="1" t="n">
+      <c r="J192" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K192" t="n">
@@ -9256,7 +9268,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B193" t="n">
@@ -9283,7 +9295,7 @@
       <c r="I193" t="n">
         <v>36.55256</v>
       </c>
-      <c r="J193" s="1" t="n">
+      <c r="J193" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K193" t="n">
@@ -9303,7 +9315,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B194" t="n">
@@ -9330,7 +9342,7 @@
       <c r="I194" t="n">
         <v>37.88103</v>
       </c>
-      <c r="J194" s="1" t="n">
+      <c r="J194" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K194" t="n">
@@ -9350,7 +9362,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B195" t="n">
@@ -9377,7 +9389,7 @@
       <c r="I195" t="n">
         <v>39.19635</v>
       </c>
-      <c r="J195" s="1" t="n">
+      <c r="J195" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K195" t="n">
@@ -9397,7 +9409,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B196" t="n">
@@ -9424,7 +9436,7 @@
       <c r="I196" t="n">
         <v>39.56444</v>
       </c>
-      <c r="J196" s="1" t="n">
+      <c r="J196" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K196" t="n">
@@ -9444,7 +9456,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B197" t="n">
@@ -9471,7 +9483,7 @@
       <c r="I197" t="n">
         <v>39.30509</v>
       </c>
-      <c r="J197" s="1" t="n">
+      <c r="J197" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K197" t="n">
@@ -9491,7 +9503,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B198" t="n">
@@ -9518,7 +9530,7 @@
       <c r="I198" t="n">
         <v>43.89015</v>
       </c>
-      <c r="J198" s="1" t="n">
+      <c r="J198" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K198" t="n">
@@ -9538,7 +9550,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B199" t="n">
@@ -9565,7 +9577,7 @@
       <c r="I199" t="n">
         <v>42.70023</v>
       </c>
-      <c r="J199" s="1" t="n">
+      <c r="J199" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K199" t="n">
@@ -9585,7 +9597,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B200" t="n">
@@ -9612,7 +9624,7 @@
       <c r="I200" t="n">
         <v>47.27269999999999</v>
       </c>
-      <c r="J200" s="1" t="n">
+      <c r="J200" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K200" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B201" t="n">
@@ -9659,7 +9671,7 @@
       <c r="I201" t="n">
         <v>49.26831</v>
       </c>
-      <c r="J201" s="1" t="n">
+      <c r="J201" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K201" t="n">
@@ -9679,7 +9691,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B202" t="n">
@@ -9706,7 +9718,7 @@
       <c r="I202" t="n">
         <v>48.83308</v>
       </c>
-      <c r="J202" s="1" t="n">
+      <c r="J202" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K202" t="n">
@@ -9726,7 +9738,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B203" t="n">
@@ -9753,7 +9765,7 @@
       <c r="I203" t="n">
         <v>50.90073</v>
       </c>
-      <c r="J203" s="1" t="n">
+      <c r="J203" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K203" t="n">
@@ -9773,7 +9785,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B204" t="n">
@@ -9800,7 +9812,7 @@
       <c r="I204" t="n">
         <v>51.49107</v>
       </c>
-      <c r="J204" s="1" t="n">
+      <c r="J204" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K204" t="n">
@@ -9820,7 +9832,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B205" t="n">
@@ -9847,7 +9859,7 @@
       <c r="I205" t="n">
         <v>49.10525999999999</v>
       </c>
-      <c r="J205" s="1" t="n">
+      <c r="J205" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K205" t="n">
@@ -9867,7 +9879,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B206" t="n">
@@ -9894,7 +9906,7 @@
       <c r="I206" t="n">
         <v>47.73486</v>
       </c>
-      <c r="J206" s="1" t="n">
+      <c r="J206" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K206" t="n">
@@ -9914,7 +9926,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B207" t="n">
@@ -9941,7 +9953,7 @@
       <c r="I207" t="n">
         <v>46.86317999999999</v>
       </c>
-      <c r="J207" s="1" t="n">
+      <c r="J207" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K207" t="n">
@@ -9961,7 +9973,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B208" t="n">
@@ -9988,7 +10000,7 @@
       <c r="I208" t="n">
         <v>46.19519</v>
       </c>
-      <c r="J208" s="1" t="n">
+      <c r="J208" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K208" t="n">
@@ -10008,7 +10020,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B209" t="n">
@@ -10035,7 +10047,7 @@
       <c r="I209" t="n">
         <v>43.79043</v>
       </c>
-      <c r="J209" s="1" t="n">
+      <c r="J209" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K209" t="n">
@@ -10055,7 +10067,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B210" t="n">
@@ -10082,7 +10094,7 @@
       <c r="I210" t="n">
         <v>43.81728999999999</v>
       </c>
-      <c r="J210" s="1" t="n">
+      <c r="J210" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K210" t="n">
@@ -10102,7 +10114,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B211" t="n">
@@ -10129,7 +10141,7 @@
       <c r="I211" t="n">
         <v>41.48014</v>
       </c>
-      <c r="J211" s="1" t="n">
+      <c r="J211" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K211" t="n">
@@ -10149,7 +10161,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B212" t="n">
@@ -10176,7 +10188,7 @@
       <c r="I212" t="n">
         <v>41.96095999999999</v>
       </c>
-      <c r="J212" s="1" t="n">
+      <c r="J212" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K212" t="n">
@@ -10196,7 +10208,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B213" t="n">
@@ -10223,7 +10235,7 @@
       <c r="I213" t="n">
         <v>42.04255</v>
       </c>
-      <c r="J213" s="1" t="n">
+      <c r="J213" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K213" t="n">
@@ -10243,7 +10255,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B214" t="n">
@@ -10270,7 +10282,7 @@
       <c r="I214" t="n">
         <v>41.00722999999999</v>
       </c>
-      <c r="J214" s="1" t="n">
+      <c r="J214" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K214" t="n">
@@ -10290,7 +10302,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B215" t="n">
@@ -10317,7 +10329,7 @@
       <c r="I215" t="n">
         <v>41.04307</v>
       </c>
-      <c r="J215" s="1" t="n">
+      <c r="J215" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K215" t="n">
@@ -10337,7 +10349,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B216" t="n">
@@ -10364,7 +10376,7 @@
       <c r="I216" t="n">
         <v>40.10673999999999</v>
       </c>
-      <c r="J216" s="1" t="n">
+      <c r="J216" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K216" t="n">
@@ -10384,7 +10396,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B217" t="n">
@@ -10411,7 +10423,7 @@
       <c r="I217" t="n">
         <v>37.22207</v>
       </c>
-      <c r="J217" s="1" t="n">
+      <c r="J217" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K217" t="n">
@@ -10431,7 +10443,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B218" t="n">
@@ -10458,7 +10470,7 @@
       <c r="I218" t="n">
         <v>33.82858</v>
       </c>
-      <c r="J218" s="1" t="n">
+      <c r="J218" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K218" t="n">
@@ -10478,7 +10490,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B219" t="n">
@@ -10505,7 +10517,7 @@
       <c r="I219" t="n">
         <v>31.16933</v>
       </c>
-      <c r="J219" s="1" t="n">
+      <c r="J219" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K219" t="n">
@@ -10525,7 +10537,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B220" t="n">
@@ -10552,7 +10564,7 @@
       <c r="I220" t="n">
         <v>26.7406</v>
       </c>
-      <c r="J220" s="1" t="n">
+      <c r="J220" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K220" t="n">
@@ -10572,7 +10584,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B221" t="n">
@@ -10599,7 +10611,7 @@
       <c r="I221" t="n">
         <v>29.81743</v>
       </c>
-      <c r="J221" s="1" t="n">
+      <c r="J221" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K221" t="n">
@@ -10619,7 +10631,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B222" t="n">
@@ -10646,7 +10658,7 @@
       <c r="I222" t="n">
         <v>29.9388</v>
       </c>
-      <c r="J222" s="1" t="n">
+      <c r="J222" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K222" t="n">
@@ -10666,7 +10678,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B223" t="n">
@@ -10693,7 +10705,7 @@
       <c r="I223" t="n">
         <v>28.88884</v>
       </c>
-      <c r="J223" s="1" t="n">
+      <c r="J223" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K223" t="n">
@@ -10713,7 +10725,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B224" t="n">
@@ -10740,7 +10752,7 @@
       <c r="I224" t="n">
         <v>27.83844</v>
       </c>
-      <c r="J224" s="1" t="n">
+      <c r="J224" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K224" t="n">
@@ -10774,27 +10786,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>gsyh_tl</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>usd_ort</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gsyh_usd</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
@@ -10811,7 +10823,7 @@
         <v>188.4470651431746</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>39538</v>
       </c>
     </row>
@@ -10826,7 +10838,7 @@
         <v>202.1165869692412</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>39629</v>
       </c>
     </row>
@@ -10841,7 +10853,7 @@
         <v>224.7668336608458</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>39721</v>
       </c>
     </row>
@@ -10858,7 +10870,7 @@
       <c r="D5" t="n">
         <v>784.2271960468236</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>39813</v>
       </c>
     </row>
@@ -10875,7 +10887,7 @@
       <c r="D6" t="n">
         <v>726.5630108224932</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>39903</v>
       </c>
     </row>
@@ -10892,7 +10904,7 @@
       <c r="D7" t="n">
         <v>680.8887296765091</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>39994</v>
       </c>
     </row>
@@ -10909,7 +10921,7 @@
       <c r="D8" t="n">
         <v>640.0868793971713</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>40086</v>
       </c>
     </row>
@@ -10926,7 +10938,7 @@
       <c r="D9" t="n">
         <v>658.9902820733863</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>40178</v>
       </c>
     </row>
@@ -10943,7 +10955,7 @@
       <c r="D10" t="n">
         <v>691.5463082981535</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>40268</v>
       </c>
     </row>
@@ -10960,7 +10972,7 @@
       <c r="D11" t="n">
         <v>719.6885900927989</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>40359</v>
       </c>
     </row>
@@ -10977,7 +10989,7 @@
       <c r="D12" t="n">
         <v>749.0397936010979</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>40451</v>
       </c>
     </row>
@@ -10994,7 +11006,7 @@
       <c r="D13" t="n">
         <v>784.9655005365125</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>40543</v>
       </c>
     </row>
@@ -11011,7 +11023,7 @@
       <c r="D14" t="n">
         <v>810.3253924162482</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>40633</v>
       </c>
     </row>
@@ -11028,7 +11040,7 @@
       <c r="D15" t="n">
         <v>844.646504931485</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>40724</v>
       </c>
     </row>
@@ -11045,7 +11057,7 @@
       <c r="D16" t="n">
         <v>854.9653194859255</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>40816</v>
       </c>
     </row>
@@ -11062,7 +11074,7 @@
       <c r="D17" t="n">
         <v>844.5068243568147</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>40908</v>
       </c>
     </row>
@@ -11079,7 +11091,7 @@
       <c r="D18" t="n">
         <v>845.4079140024489</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>40999</v>
       </c>
     </row>
@@ -11096,7 +11108,7 @@
       <c r="D19" t="n">
         <v>841.945669848762</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>41090</v>
       </c>
     </row>
@@ -11113,7 +11125,7 @@
       <c r="D20" t="n">
         <v>857.1420802056064</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>41182</v>
       </c>
     </row>
@@ -11130,7 +11142,7 @@
       <c r="D21" t="n">
         <v>887.0698297363689</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>41274</v>
       </c>
     </row>
@@ -11147,7 +11159,7 @@
       <c r="D22" t="n">
         <v>918.0892150612981</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>41364</v>
       </c>
     </row>
@@ -11164,7 +11176,7 @@
       <c r="D23" t="n">
         <v>946.0043097899548</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>41455</v>
       </c>
     </row>
@@ -11181,7 +11193,7 @@
       <c r="D24" t="n">
         <v>959.0932141449902</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>41547</v>
       </c>
     </row>
@@ -11198,7 +11210,7 @@
       <c r="D25" t="n">
         <v>961.0481078717496</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>41639</v>
       </c>
     </row>
@@ -11215,7 +11227,7 @@
       <c r="D26" t="n">
         <v>947.2834628100968</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>41729</v>
       </c>
     </row>
@@ -11232,7 +11244,7 @@
       <c r="D27" t="n">
         <v>937.1937031513314</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -11249,7 +11261,7 @@
       <c r="D28" t="n">
         <v>940.6297640777781</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>41912</v>
       </c>
     </row>
@@ -11266,7 +11278,7 @@
       <c r="D29" t="n">
         <v>942.8967695699519</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>42004</v>
       </c>
     </row>
@@ -11283,7 +11295,7 @@
       <c r="D30" t="n">
         <v>940.1806740814401</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>42094</v>
       </c>
     </row>
@@ -11300,7 +11312,7 @@
       <c r="D31" t="n">
         <v>919.6371330818704</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>42185</v>
       </c>
     </row>
@@ -11317,7 +11329,7 @@
       <c r="D32" t="n">
         <v>887.3628039410262</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>42277</v>
       </c>
     </row>
@@ -11334,7 +11346,7 @@
       <c r="D33" t="n">
         <v>863.921366521658</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="2" t="n">
         <v>42369</v>
       </c>
     </row>
@@ -11351,7 +11363,7 @@
       <c r="D34" t="n">
         <v>853.7046932188318</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="2" t="n">
         <v>42460</v>
       </c>
     </row>
@@ -11368,7 +11380,7 @@
       <c r="D35" t="n">
         <v>861.4305877129513</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="2" t="n">
         <v>42551</v>
       </c>
     </row>
@@ -11385,7 +11397,7 @@
       <c r="D36" t="n">
         <v>864.6856666920855</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>42643</v>
       </c>
     </row>
@@ -11402,7 +11414,7 @@
       <c r="D37" t="n">
         <v>869.9030222927099</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>42735</v>
       </c>
     </row>
@@ -11419,7 +11431,7 @@
       <c r="D38" t="n">
         <v>855.0244018960104</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -11436,7 +11448,7 @@
       <c r="D39" t="n">
         <v>842.4624338405587</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -11453,7 +11465,7 @@
       <c r="D40" t="n">
         <v>856.2791919679362</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>43008</v>
       </c>
     </row>
@@ -11470,7 +11482,7 @@
       <c r="D41" t="n">
         <v>864.8788502660077</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>43100</v>
       </c>
     </row>
@@ -11487,7 +11499,7 @@
       <c r="D42" t="n">
         <v>898.2531105139536</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>43190</v>
       </c>
     </row>
@@ -11504,7 +11516,7 @@
       <c r="D43" t="n">
         <v>898.9553869128588</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>43281</v>
       </c>
     </row>
@@ -11521,7 +11533,7 @@
       <c r="D44" t="n">
         <v>846.4394557072657</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>43373</v>
       </c>
     </row>
@@ -11538,7 +11550,7 @@
       <c r="D45" t="n">
         <v>797.3238057726485</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>43465</v>
       </c>
     </row>
@@ -11555,7 +11567,7 @@
       <c r="D46" t="n">
         <v>761.796683470352</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -11572,7 +11584,7 @@
       <c r="D47" t="n">
         <v>732.283041957087</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>43646</v>
       </c>
     </row>
@@ -11589,7 +11601,7 @@
       <c r="D48" t="n">
         <v>752.4178296031997</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -11606,7 +11618,7 @@
       <c r="D49" t="n">
         <v>775.2901707093772</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>43830</v>
       </c>
     </row>
@@ -11623,7 +11635,7 @@
       <c r="D50" t="n">
         <v>778.2260275513438</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -11640,7 +11652,7 @@
       <c r="D51" t="n">
         <v>754.0085363267242</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>44012</v>
       </c>
     </row>
@@ -11657,7 +11669,7 @@
       <c r="D52" t="n">
         <v>746.091416266087</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>44104</v>
       </c>
     </row>
@@ -11674,7 +11686,7 @@
       <c r="D53" t="n">
         <v>730.9546871917802</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>44196</v>
       </c>
     </row>
@@ -11691,7 +11703,7 @@
       <c r="D54" t="n">
         <v>746.2494624509136</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -11708,7 +11720,7 @@
       <c r="D55" t="n">
         <v>786.5387429577326</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>44377</v>
       </c>
     </row>
@@ -11725,7 +11737,7 @@
       <c r="D56" t="n">
         <v>818.3449224201991</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>44469</v>
       </c>
     </row>
@@ -11742,7 +11754,7 @@
       <c r="D57" t="n">
         <v>835.6602257809595</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>44561</v>
       </c>
     </row>
@@ -11759,7 +11771,7 @@
       <c r="D58" t="n">
         <v>826.4811453112486</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -11776,7 +11788,7 @@
       <c r="D59" t="n">
         <v>853.2410029660408</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>44742</v>
       </c>
     </row>
@@ -11793,7 +11805,7 @@
       <c r="D60" t="n">
         <v>864.3854149792769</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>44834</v>
       </c>
     </row>
@@ -11810,7 +11822,7 @@
       <c r="D61" t="n">
         <v>913.1863831015423</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="2" t="n">
         <v>44926</v>
       </c>
     </row>
@@ -11827,7 +11839,7 @@
       <c r="D62" t="n">
         <v>981.7702030343168</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11844,7 +11856,7 @@
       <c r="D63" t="n">
         <v>1035.745849934734</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>45107</v>
       </c>
     </row>
@@ -11861,7 +11873,7 @@
       <c r="D64" t="n">
         <v>1087.793792245752</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>45199</v>
       </c>
     </row>
@@ -11878,7 +11890,7 @@
       <c r="D65" t="n">
         <v>1131.01603472582</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -11895,7 +11907,7 @@
       <c r="D66" t="n">
         <v>1171.104959658617</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>45382</v>
       </c>
     </row>
@@ -11912,7 +11924,7 @@
       <c r="D67" t="n">
         <v>1209.872581317634</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -11929,7 +11941,7 @@
       <c r="D68" t="n">
         <v>1283.797451942341</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>45565</v>
       </c>
     </row>
@@ -11946,7 +11958,7 @@
       <c r="D69" t="n">
         <v>1357.572675785335</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="2" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -11963,7 +11975,7 @@
       <c r="D70" t="n">
         <v>1410.676074962415</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="2" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -11980,7 +11992,7 @@
       <c r="D71" t="n">
         <v>1473.820957975585</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -11997,7 +12009,7 @@
       <c r="D72" t="n">
         <v>1536.009359448403</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="2" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -12014,7 +12026,7 @@
       <c r="D73" t="n">
         <v>1595.814722617371</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -12031,7 +12043,7 @@
       <c r="D74" t="n">
         <v>1640.339363149401</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="2" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -12048,7 +12060,7 @@
       <c r="D75" t="n">
         <v>1700.354635555628</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="2" t="n">
         <v>46203</v>
       </c>
     </row>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O224"/>
+  <dimension ref="A1:O225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9307,7 +9307,7 @@
         <v>45292</v>
       </c>
       <c r="B194" t="n">
-        <v>-2.543</v>
+        <v>-2.538</v>
       </c>
       <c r="C194" t="n">
         <v>-0.944</v>
@@ -9316,10 +9316,10 @@
         <v>-5.17083</v>
       </c>
       <c r="E194" t="n">
-        <v>3.57183</v>
+        <v>3.57683</v>
       </c>
       <c r="F194" t="n">
-        <v>-34.16</v>
+        <v>-34.155</v>
       </c>
       <c r="G194" t="n">
         <v>-21.797</v>
@@ -9328,7 +9328,7 @@
         <v>-50.24402</v>
       </c>
       <c r="I194" t="n">
-        <v>37.88103</v>
+        <v>37.88603</v>
       </c>
       <c r="J194" s="1" t="n">
         <v>45291</v>
@@ -9337,7 +9337,7 @@
         <v>1131.01603472582</v>
       </c>
       <c r="L194" t="n">
-        <v>-3.020293165718118</v>
+        <v>-3.01985108533672</v>
       </c>
       <c r="M194" t="n">
         <v>-1.927205214670897</v>
@@ -9346,7 +9346,7 @@
         <v>-4.442379104924018</v>
       </c>
       <c r="O194" t="n">
-        <v>3.349292038037559</v>
+        <v>3.349734118418958</v>
       </c>
     </row>
     <row r="195">
@@ -9354,7 +9354,7 @@
         <v>45323</v>
       </c>
       <c r="B195" t="n">
-        <v>-3.202</v>
+        <v>-3.197</v>
       </c>
       <c r="C195" t="n">
         <v>-0.998</v>
@@ -9363,10 +9363,10 @@
         <v>-4.35173</v>
       </c>
       <c r="E195" t="n">
-        <v>2.14773</v>
+        <v>2.15273</v>
       </c>
       <c r="F195" t="n">
-        <v>-28.585</v>
+        <v>-28.575</v>
       </c>
       <c r="G195" t="n">
         <v>-19.001</v>
@@ -9375,7 +9375,7 @@
         <v>-48.78034</v>
       </c>
       <c r="I195" t="n">
-        <v>39.19635</v>
+        <v>39.20635</v>
       </c>
       <c r="J195" s="1" t="n">
         <v>45291</v>
@@ -9384,7 +9384,7 @@
         <v>1131.01603472582</v>
       </c>
       <c r="L195" t="n">
-        <v>-2.527373540458209</v>
+        <v>-2.526489379695411</v>
       </c>
       <c r="M195" t="n">
         <v>-1.679993865392564</v>
@@ -9393,7 +9393,7 @@
         <v>-4.312966262394793</v>
       </c>
       <c r="O195" t="n">
-        <v>3.465587471489911</v>
+        <v>3.466471632252709</v>
       </c>
     </row>
     <row r="196">
@@ -9401,7 +9401,7 @@
         <v>45352</v>
       </c>
       <c r="B196" t="n">
-        <v>-4.079</v>
+        <v>-4.074</v>
       </c>
       <c r="C196" t="n">
         <v>-1.519</v>
@@ -9410,10 +9410,10 @@
         <v>-3.77509</v>
       </c>
       <c r="E196" t="n">
-        <v>1.21509</v>
+        <v>1.22009</v>
       </c>
       <c r="F196" t="n">
-        <v>-27.669</v>
+        <v>-27.654</v>
       </c>
       <c r="G196" t="n">
         <v>-19.258</v>
@@ -9422,7 +9422,7 @@
         <v>-47.97543</v>
       </c>
       <c r="I196" t="n">
-        <v>39.56444</v>
+        <v>39.57944</v>
       </c>
       <c r="J196" s="1" t="n">
         <v>45382</v>
@@ -9431,7 +9431,7 @@
         <v>1171.104959658617</v>
       </c>
       <c r="L196" t="n">
-        <v>-2.362640493646758</v>
+        <v>-2.361359652004317</v>
       </c>
       <c r="M196" t="n">
         <v>-1.644429890008647</v>
@@ -9440,7 +9440,7 @@
         <v>-4.096595237201036</v>
       </c>
       <c r="O196" t="n">
-        <v>3.378385487457354</v>
+        <v>3.379666329099794</v>
       </c>
     </row>
     <row r="197">
@@ -9460,7 +9460,7 @@
         <v>-0.16934</v>
       </c>
       <c r="F197" t="n">
-        <v>-27.883</v>
+        <v>-27.868</v>
       </c>
       <c r="G197" t="n">
         <v>-19.355</v>
@@ -9469,7 +9469,7 @@
         <v>-47.83306999999999</v>
       </c>
       <c r="I197" t="n">
-        <v>39.30509</v>
+        <v>39.32009</v>
       </c>
       <c r="J197" s="1" t="n">
         <v>45382</v>
@@ -9478,7 +9478,7 @@
         <v>1171.104959658617</v>
       </c>
       <c r="L197" t="n">
-        <v>-2.38091383441225</v>
+        <v>-2.379632992769809</v>
       </c>
       <c r="M197" t="n">
         <v>-1.652712665963099</v>
@@ -9487,7 +9487,7 @@
         <v>-4.084439196119841</v>
       </c>
       <c r="O197" t="n">
-        <v>3.356239735459549</v>
+        <v>3.357520577101989</v>
       </c>
     </row>
     <row r="198">
@@ -9495,7 +9495,7 @@
         <v>45413</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.855</v>
+        <v>-0.853</v>
       </c>
       <c r="C198" t="n">
         <v>-1.017</v>
@@ -9504,10 +9504,10 @@
         <v>-3.48698</v>
       </c>
       <c r="E198" t="n">
-        <v>3.64898</v>
+        <v>3.65098</v>
       </c>
       <c r="F198" t="n">
-        <v>-21.26</v>
+        <v>-21.243</v>
       </c>
       <c r="G198" t="n">
         <v>-17.739</v>
@@ -9516,7 +9516,7 @@
         <v>-47.41114</v>
       </c>
       <c r="I198" t="n">
-        <v>43.89015</v>
+        <v>43.90715</v>
       </c>
       <c r="J198" s="1" t="n">
         <v>45382</v>
@@ -9525,7 +9525,7 @@
         <v>1171.104959658617</v>
       </c>
       <c r="L198" t="n">
-        <v>-1.815379554553112</v>
+        <v>-1.813927934025013</v>
       </c>
       <c r="M198" t="n">
         <v>-1.514723326350784</v>
@@ -9534,7 +9534,7 @@
         <v>-4.048410828506832</v>
       </c>
       <c r="O198" t="n">
-        <v>3.747755454198932</v>
+        <v>3.749207074727032</v>
       </c>
     </row>
     <row r="199">
@@ -9542,7 +9542,7 @@
         <v>45444</v>
       </c>
       <c r="B199" t="n">
-        <v>0.587</v>
+        <v>0.588</v>
       </c>
       <c r="C199" t="n">
         <v>-0.9340000000000001</v>
@@ -9551,10 +9551,10 @@
         <v>-3.20217</v>
       </c>
       <c r="E199" t="n">
-        <v>4.72317</v>
+        <v>4.72417</v>
       </c>
       <c r="F199" t="n">
-        <v>-21.737</v>
+        <v>-21.719</v>
       </c>
       <c r="G199" t="n">
         <v>-17.063</v>
@@ -9563,7 +9563,7 @@
         <v>-47.37422</v>
       </c>
       <c r="I199" t="n">
-        <v>42.70023</v>
+        <v>42.71823</v>
       </c>
       <c r="J199" s="1" t="n">
         <v>45473</v>
@@ -9572,7 +9572,7 @@
         <v>1209.872581317634</v>
       </c>
       <c r="L199" t="n">
-        <v>-1.796635475144575</v>
+        <v>-1.795147715170678</v>
       </c>
       <c r="M199" t="n">
         <v>-1.410313801922615</v>
@@ -9581,7 +9581,7 @@
         <v>-3.915637128366547</v>
       </c>
       <c r="O199" t="n">
-        <v>3.529316281677905</v>
+        <v>3.530804041651803</v>
       </c>
     </row>
     <row r="200">
@@ -9589,7 +9589,7 @@
         <v>45474</v>
       </c>
       <c r="B200" t="n">
-        <v>1.227</v>
+        <v>1.225</v>
       </c>
       <c r="C200" t="n">
         <v>-0.267</v>
@@ -9598,10 +9598,10 @@
         <v>-4.04794</v>
       </c>
       <c r="E200" t="n">
-        <v>5.541939999999999</v>
+        <v>5.53994</v>
       </c>
       <c r="F200" t="n">
-        <v>-15.328</v>
+        <v>-15.312</v>
       </c>
       <c r="G200" t="n">
         <v>-14.873</v>
@@ -9610,7 +9610,7 @@
         <v>-47.72769</v>
       </c>
       <c r="I200" t="n">
-        <v>47.27269999999999</v>
+        <v>47.2887</v>
       </c>
       <c r="J200" s="1" t="n">
         <v>45473</v>
@@ -9619,7 +9619,7 @@
         <v>1209.872581317634</v>
       </c>
       <c r="L200" t="n">
-        <v>-1.266910271105306</v>
+        <v>-1.265587817795176</v>
       </c>
       <c r="M200" t="n">
         <v>-1.229303005098462</v>
@@ -9628,7 +9628,7 @@
         <v>-3.944852601587292</v>
       </c>
       <c r="O200" t="n">
-        <v>3.907246162113766</v>
+        <v>3.908568615423898</v>
       </c>
     </row>
     <row r="201">
@@ -9636,7 +9636,7 @@
         <v>45505</v>
       </c>
       <c r="B201" t="n">
-        <v>4.415</v>
+        <v>4.412</v>
       </c>
       <c r="C201" t="n">
         <v>-0.75</v>
@@ -9645,10 +9645,10 @@
         <v>-3.96283</v>
       </c>
       <c r="E201" t="n">
-        <v>9.127829999999999</v>
+        <v>9.124829999999999</v>
       </c>
       <c r="F201" t="n">
-        <v>-11.339</v>
+        <v>-11.326</v>
       </c>
       <c r="G201" t="n">
         <v>-12.601</v>
@@ -9657,7 +9657,7 @@
         <v>-48.0063</v>
       </c>
       <c r="I201" t="n">
-        <v>49.26831</v>
+        <v>49.28131</v>
       </c>
       <c r="J201" s="1" t="n">
         <v>45473</v>
@@ -9666,7 +9666,7 @@
         <v>1209.872581317634</v>
       </c>
       <c r="L201" t="n">
-        <v>-0.9372061302233212</v>
+        <v>-0.93613163690884</v>
       </c>
       <c r="M201" t="n">
         <v>-1.041514635059888</v>
@@ -9675,7 +9675,7 @@
         <v>-3.967880646383264</v>
       </c>
       <c r="O201" t="n">
-        <v>4.072189977753149</v>
+        <v>4.073264471067631</v>
       </c>
     </row>
     <row r="202">
@@ -9683,7 +9683,7 @@
         <v>45536</v>
       </c>
       <c r="B202" t="n">
-        <v>2.598</v>
+        <v>2.595</v>
       </c>
       <c r="C202" t="n">
         <v>-1.017</v>
@@ -9692,10 +9692,10 @@
         <v>-3.72466</v>
       </c>
       <c r="E202" t="n">
-        <v>7.33966</v>
+        <v>7.33666</v>
       </c>
       <c r="F202" t="n">
-        <v>-11.476</v>
+        <v>-11.466</v>
       </c>
       <c r="G202" t="n">
         <v>-12.512</v>
@@ -9704,7 +9704,7 @@
         <v>-47.79707000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>48.83308</v>
+        <v>48.84308</v>
       </c>
       <c r="J202" s="1" t="n">
         <v>45565</v>
@@ -9713,7 +9713,7 @@
         <v>1283.797451942341</v>
       </c>
       <c r="L202" t="n">
-        <v>-0.8939104827352017</v>
+        <v>-0.8931315436599706</v>
       </c>
       <c r="M202" t="n">
         <v>-0.9746085709291429</v>
@@ -9722,7 +9722,7 @@
         <v>-3.72310055045558</v>
       </c>
       <c r="O202" t="n">
-        <v>3.803799417588596</v>
+        <v>3.804578356663827</v>
       </c>
     </row>
     <row r="203">
@@ -9730,7 +9730,7 @@
         <v>45566</v>
       </c>
       <c r="B203" t="n">
-        <v>1.714</v>
+        <v>1.697</v>
       </c>
       <c r="C203" t="n">
         <v>-1.597</v>
@@ -9739,10 +9739,10 @@
         <v>-3.68261</v>
       </c>
       <c r="E203" t="n">
-        <v>6.993609999999999</v>
+        <v>6.97661</v>
       </c>
       <c r="F203" t="n">
-        <v>-9.670999999999999</v>
+        <v>-9.677999999999999</v>
       </c>
       <c r="G203" t="n">
         <v>-12.734</v>
@@ -9751,7 +9751,7 @@
         <v>-47.83772</v>
       </c>
       <c r="I203" t="n">
-        <v>50.90073</v>
+        <v>50.89373</v>
       </c>
       <c r="J203" s="1" t="n">
         <v>45565</v>
@@ -9760,7 +9760,7 @@
         <v>1283.797451942341</v>
       </c>
       <c r="L203" t="n">
-        <v>-0.7533119796559895</v>
+        <v>-0.7538572370086513</v>
       </c>
       <c r="M203" t="n">
         <v>-0.9919010183992731</v>
@@ -9769,7 +9769,7 @@
         <v>-3.726266937796394</v>
       </c>
       <c r="O203" t="n">
-        <v>3.964856755478753</v>
+        <v>3.964311498126091</v>
       </c>
     </row>
     <row r="204">
@@ -9777,7 +9777,7 @@
         <v>45597</v>
       </c>
       <c r="B204" t="n">
-        <v>-3.448</v>
+        <v>-3.446</v>
       </c>
       <c r="C204" t="n">
         <v>-1.769</v>
@@ -9786,10 +9786,10 @@
         <v>-4.549840000000001</v>
       </c>
       <c r="E204" t="n">
-        <v>2.87084</v>
+        <v>2.87284</v>
       </c>
       <c r="F204" t="n">
-        <v>-10.37</v>
+        <v>-10.375</v>
       </c>
       <c r="G204" t="n">
         <v>-13.164</v>
@@ -9798,7 +9798,7 @@
         <v>-48.69706</v>
       </c>
       <c r="I204" t="n">
-        <v>51.49107</v>
+        <v>51.48607</v>
       </c>
       <c r="J204" s="1" t="n">
         <v>45565</v>
@@ -9807,7 +9807,7 @@
         <v>1283.797451942341</v>
       </c>
       <c r="L204" t="n">
-        <v>-0.8077598210146428</v>
+        <v>-0.8081492905522585</v>
       </c>
       <c r="M204" t="n">
         <v>-1.02539539863421</v>
@@ -9816,7 +9816,7 @@
         <v>-3.793204288287302</v>
       </c>
       <c r="O204" t="n">
-        <v>4.010840644845945</v>
+        <v>4.010451175308329</v>
       </c>
     </row>
     <row r="205">
@@ -9824,7 +9824,7 @@
         <v>45627</v>
       </c>
       <c r="B205" t="n">
-        <v>-5.01</v>
+        <v>-5.003</v>
       </c>
       <c r="C205" t="n">
         <v>-1.655</v>
@@ -9833,10 +9833,10 @@
         <v>-5.44892</v>
       </c>
       <c r="E205" t="n">
-        <v>2.09392</v>
+        <v>2.10092</v>
       </c>
       <c r="F205" t="n">
-        <v>-13.589</v>
+        <v>-13.587</v>
       </c>
       <c r="G205" t="n">
         <v>-13.656</v>
@@ -9845,7 +9845,7 @@
         <v>-49.03825000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>49.10525999999999</v>
+        <v>49.10726</v>
       </c>
       <c r="J205" s="1" t="n">
         <v>45657</v>
@@ -9854,7 +9854,7 @@
         <v>1357.572675785335</v>
       </c>
       <c r="L205" t="n">
-        <v>-1.000977718716898</v>
+        <v>-1.000830396953896</v>
       </c>
       <c r="M205" t="n">
         <v>-1.005912997777464</v>
@@ -9863,7 +9863,7 @@
         <v>-3.612200722265725</v>
       </c>
       <c r="O205" t="n">
-        <v>3.617136737935105</v>
+        <v>3.617284059698108</v>
       </c>
     </row>
     <row r="206">
@@ -9871,7 +9871,7 @@
         <v>45658</v>
       </c>
       <c r="B206" t="n">
-        <v>-3.987</v>
+        <v>-3.989</v>
       </c>
       <c r="C206" t="n">
         <v>-1.092</v>
@@ -9880,10 +9880,10 @@
         <v>-5.096430000000001</v>
       </c>
       <c r="E206" t="n">
-        <v>2.20143</v>
+        <v>2.19943</v>
       </c>
       <c r="F206" t="n">
-        <v>-15.033</v>
+        <v>-15.038</v>
       </c>
       <c r="G206" t="n">
         <v>-13.804</v>
@@ -9892,7 +9892,7 @@
         <v>-48.96385</v>
       </c>
       <c r="I206" t="n">
-        <v>47.73486</v>
+        <v>47.72986</v>
       </c>
       <c r="J206" s="1" t="n">
         <v>45657</v>
@@ -9901,7 +9901,7 @@
         <v>1357.572675785335</v>
       </c>
       <c r="L206" t="n">
-        <v>-1.107344031604322</v>
+        <v>-1.107712336011827</v>
       </c>
       <c r="M206" t="n">
         <v>-1.01681480823961</v>
@@ -9910,7 +9910,7 @@
         <v>-3.606720352682051</v>
       </c>
       <c r="O206" t="n">
-        <v>3.516191865926154</v>
+        <v>3.515823561518649</v>
       </c>
     </row>
     <row r="207">
@@ -9918,7 +9918,7 @@
         <v>45689</v>
       </c>
       <c r="B207" t="n">
-        <v>-5.29</v>
+        <v>-5.284</v>
       </c>
       <c r="C207" t="n">
         <v>-1.85</v>
@@ -9927,10 +9927,10 @@
         <v>-4.71605</v>
       </c>
       <c r="E207" t="n">
-        <v>1.27605</v>
+        <v>1.28205</v>
       </c>
       <c r="F207" t="n">
-        <v>-17.121</v>
+        <v>-17.125</v>
       </c>
       <c r="G207" t="n">
         <v>-14.656</v>
@@ -9939,7 +9939,7 @@
         <v>-49.32817000000001</v>
       </c>
       <c r="I207" t="n">
-        <v>46.86317999999999</v>
+        <v>46.85917999999999</v>
       </c>
       <c r="J207" s="1" t="n">
         <v>45657</v>
@@ -9948,7 +9948,7 @@
         <v>1357.572675785335</v>
       </c>
       <c r="L207" t="n">
-        <v>-1.261147952178381</v>
+        <v>-1.261442595704385</v>
       </c>
       <c r="M207" t="n">
         <v>-1.07957387927845</v>
@@ -9957,7 +9957,7 @@
         <v>-3.633556485030491</v>
       </c>
       <c r="O207" t="n">
-        <v>3.451983148739374</v>
+        <v>3.451688505213371</v>
       </c>
     </row>
     <row r="208">
@@ -9965,7 +9965,7 @@
         <v>45717</v>
       </c>
       <c r="B208" t="n">
-        <v>-4.996</v>
+        <v>-4.994</v>
       </c>
       <c r="C208" t="n">
         <v>-1.147</v>
@@ -9974,10 +9974,10 @@
         <v>-4.396100000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>0.5471</v>
+        <v>0.5491</v>
       </c>
       <c r="F208" t="n">
-        <v>-18.038</v>
+        <v>-18.045</v>
       </c>
       <c r="G208" t="n">
         <v>-14.284</v>
@@ -9986,7 +9986,7 @@
         <v>-49.94918</v>
       </c>
       <c r="I208" t="n">
-        <v>46.19519</v>
+        <v>46.18819</v>
       </c>
       <c r="J208" s="1" t="n">
         <v>45747</v>
@@ -9995,7 +9995,7 @@
         <v>1410.676074962415</v>
       </c>
       <c r="L208" t="n">
-        <v>-1.278677672369299</v>
+        <v>-1.279173888341501</v>
       </c>
       <c r="M208" t="n">
         <v>-1.012564135276808</v>
@@ -10004,7 +10004,7 @@
         <v>-3.540797273486814</v>
       </c>
       <c r="O208" t="n">
-        <v>3.274684445274282</v>
+        <v>3.27418822930208</v>
       </c>
     </row>
     <row r="209">
@@ -10012,7 +10012,7 @@
         <v>45748</v>
       </c>
       <c r="B209" t="n">
-        <v>-8.497</v>
+        <v>-8.503</v>
       </c>
       <c r="C209" t="n">
         <v>-2.185</v>
@@ -10021,10 +10021,10 @@
         <v>-3.73789</v>
       </c>
       <c r="E209" t="n">
-        <v>-2.5741</v>
+        <v>-2.5801</v>
       </c>
       <c r="F209" t="n">
-        <v>-21.542</v>
+        <v>-21.555</v>
       </c>
       <c r="G209" t="n">
         <v>-15.28</v>
@@ -10033,7 +10033,7 @@
         <v>-50.05242000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>43.79043</v>
+        <v>43.77743</v>
       </c>
       <c r="J209" s="1" t="n">
         <v>45747</v>
@@ -10042,7 +10042,7 @@
         <v>1410.676074962415</v>
       </c>
       <c r="L209" t="n">
-        <v>-1.527069210454565</v>
+        <v>-1.52799075440294</v>
       </c>
       <c r="M209" t="n">
         <v>-1.083168579321593</v>
@@ -10051,7 +10051,7 @@
         <v>-3.548115750196838</v>
       </c>
       <c r="O209" t="n">
-        <v>3.104215827943825</v>
+        <v>3.103294283995449</v>
       </c>
     </row>
     <row r="210">
@@ -10059,7 +10059,7 @@
         <v>45778</v>
       </c>
       <c r="B210" t="n">
-        <v>-1.049</v>
+        <v>-1.057</v>
       </c>
       <c r="C210" t="n">
         <v>-1.774</v>
@@ -10068,10 +10068,10 @@
         <v>-2.95084</v>
       </c>
       <c r="E210" t="n">
-        <v>3.67584</v>
+        <v>3.66784</v>
       </c>
       <c r="F210" t="n">
-        <v>-21.736</v>
+        <v>-21.759</v>
       </c>
       <c r="G210" t="n">
         <v>-16.037</v>
@@ -10080,7 +10080,7 @@
         <v>-49.51628</v>
       </c>
       <c r="I210" t="n">
-        <v>43.81728999999999</v>
+        <v>43.79429</v>
       </c>
       <c r="J210" s="1" t="n">
         <v>45747</v>
@@ -10089,7 +10089,7 @@
         <v>1410.676074962415</v>
       </c>
       <c r="L210" t="n">
-        <v>-1.540821481684171</v>
+        <v>-1.542451905592836</v>
       </c>
       <c r="M210" t="n">
         <v>-1.13683079231547</v>
@@ -10098,7 +10098,7 @@
         <v>-3.510109860005903</v>
       </c>
       <c r="O210" t="n">
-        <v>3.106119879517161</v>
+        <v>3.104489455608497</v>
       </c>
     </row>
     <row r="211">
@@ -10106,7 +10106,7 @@
         <v>45809</v>
       </c>
       <c r="B211" t="n">
-        <v>-2.197</v>
+        <v>-2.205</v>
       </c>
       <c r="C211" t="n">
         <v>-1.423</v>
@@ -10115,10 +10115,10 @@
         <v>-3.16002</v>
       </c>
       <c r="E211" t="n">
-        <v>2.38602</v>
+        <v>2.37802</v>
       </c>
       <c r="F211" t="n">
-        <v>-24.52</v>
+        <v>-24.552</v>
       </c>
       <c r="G211" t="n">
         <v>-16.526</v>
@@ -10127,7 +10127,7 @@
         <v>-49.47413</v>
       </c>
       <c r="I211" t="n">
-        <v>41.48014</v>
+        <v>41.44814</v>
       </c>
       <c r="J211" s="1" t="n">
         <v>45838</v>
@@ -10136,7 +10136,7 @@
         <v>1473.820957975585</v>
       </c>
       <c r="L211" t="n">
-        <v>-1.663702763033052</v>
+        <v>-1.665873990129995</v>
       </c>
       <c r="M211" t="n">
         <v>-1.121303093877823</v>
@@ -10145,7 +10145,7 @@
         <v>-3.356861614178483</v>
       </c>
       <c r="O211" t="n">
-        <v>2.814462623531721</v>
+        <v>2.812291396434778</v>
       </c>
     </row>
     <row r="212">
@@ -10153,7 +10153,7 @@
         <v>45839</v>
       </c>
       <c r="B212" t="n">
-        <v>1.762</v>
+        <v>1.739</v>
       </c>
       <c r="C212" t="n">
         <v>-0.501</v>
@@ -10162,10 +10162,10 @@
         <v>-3.75976</v>
       </c>
       <c r="E212" t="n">
-        <v>6.02276</v>
+        <v>5.99976</v>
       </c>
       <c r="F212" t="n">
-        <v>-23.985</v>
+        <v>-24.038</v>
       </c>
       <c r="G212" t="n">
         <v>-16.76</v>
@@ -10174,7 +10174,7 @@
         <v>-49.18595000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>41.96095999999999</v>
+        <v>41.90796</v>
       </c>
       <c r="J212" s="1" t="n">
         <v>45838</v>
@@ -10183,7 +10183,7 @@
         <v>1473.820957975585</v>
       </c>
       <c r="L212" t="n">
-        <v>-1.627402560006025</v>
+        <v>-1.630998654885339</v>
       </c>
       <c r="M212" t="n">
         <v>-1.137180192024223</v>
@@ -10192,7 +10192,7 @@
         <v>-3.33730835715357</v>
       </c>
       <c r="O212" t="n">
-        <v>2.847086667680234</v>
+        <v>2.843490572800921</v>
       </c>
     </row>
     <row r="213">
@@ -10200,7 +10200,7 @@
         <v>45870</v>
       </c>
       <c r="B213" t="n">
-        <v>4.654</v>
+        <v>4.622</v>
       </c>
       <c r="C213" t="n">
         <v>-0.987</v>
@@ -10209,10 +10209,10 @@
         <v>-3.56842</v>
       </c>
       <c r="E213" t="n">
-        <v>9.20942</v>
+        <v>9.17742</v>
       </c>
       <c r="F213" t="n">
-        <v>-23.746</v>
+        <v>-23.828</v>
       </c>
       <c r="G213" t="n">
         <v>-16.997</v>
@@ -10221,7 +10221,7 @@
         <v>-48.79154</v>
       </c>
       <c r="I213" t="n">
-        <v>42.04255</v>
+        <v>41.96055</v>
       </c>
       <c r="J213" s="1" t="n">
         <v>45838</v>
@@ -10230,7 +10230,7 @@
         <v>1473.820957975585</v>
       </c>
       <c r="L213" t="n">
-        <v>-1.611186207625728</v>
+        <v>-1.616749977061646</v>
       </c>
       <c r="M213" t="n">
         <v>-1.153260842710962</v>
@@ -10239,7 +10239,7 @@
         <v>-3.310547304675272</v>
       </c>
       <c r="O213" t="n">
-        <v>2.852622618268973</v>
+        <v>2.847058848833055</v>
       </c>
     </row>
     <row r="214">
@@ -10247,7 +10247,7 @@
         <v>45901</v>
       </c>
       <c r="B214" t="n">
-        <v>0.611</v>
+        <v>0.588</v>
       </c>
       <c r="C214" t="n">
         <v>-2.329</v>
@@ -10256,10 +10256,10 @@
         <v>-3.36434</v>
       </c>
       <c r="E214" t="n">
-        <v>6.30434</v>
+        <v>6.28134</v>
       </c>
       <c r="F214" t="n">
-        <v>-25.733</v>
+        <v>-25.835</v>
       </c>
       <c r="G214" t="n">
         <v>-18.309</v>
@@ -10268,7 +10268,7 @@
         <v>-48.43122</v>
       </c>
       <c r="I214" t="n">
-        <v>41.00722999999999</v>
+        <v>40.90523</v>
       </c>
       <c r="J214" s="1" t="n">
         <v>45930</v>
@@ -10277,7 +10277,7 @@
         <v>1536.009359448403</v>
       </c>
       <c r="L214" t="n">
-        <v>-1.675315312482275</v>
+        <v>-1.681955897018597</v>
       </c>
       <c r="M214" t="n">
         <v>-1.191984924269925</v>
@@ -10286,7 +10286,7 @@
         <v>-3.153055005953359</v>
       </c>
       <c r="O214" t="n">
-        <v>2.669725268778708</v>
+        <v>2.663084684242385</v>
       </c>
     </row>
     <row r="215">
@@ -10294,7 +10294,7 @@
         <v>45931</v>
       </c>
       <c r="B215" t="n">
-        <v>0.477</v>
+        <v>0.448</v>
       </c>
       <c r="C215" t="n">
         <v>-2.744</v>
@@ -10303,10 +10303,10 @@
         <v>-3.80845</v>
       </c>
       <c r="E215" t="n">
-        <v>7.02945</v>
+        <v>7.00045</v>
       </c>
       <c r="F215" t="n">
-        <v>-26.97</v>
+        <v>-27.084</v>
       </c>
       <c r="G215" t="n">
         <v>-19.456</v>
@@ -10315,7 +10315,7 @@
         <v>-48.55706000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>41.04307</v>
+        <v>40.92907</v>
       </c>
       <c r="J215" s="1" t="n">
         <v>45930</v>
@@ -10324,7 +10324,7 @@
         <v>1536.009359448403</v>
       </c>
       <c r="L215" t="n">
-        <v>-1.755848675927678</v>
+        <v>-1.763270505703568</v>
       </c>
       <c r="M215" t="n">
         <v>-1.266658948418573</v>
@@ -10333,7 +10333,7 @@
         <v>-3.161247664365622</v>
       </c>
       <c r="O215" t="n">
-        <v>2.672058587894217</v>
+        <v>2.664636758118326</v>
       </c>
     </row>
     <row r="216">
@@ -10341,7 +10341,7 @@
         <v>45962</v>
       </c>
       <c r="B216" t="n">
-        <v>-4.198</v>
+        <v>-4.209</v>
       </c>
       <c r="C216" t="n">
         <v>-2.385</v>
@@ -10350,10 +10350,10 @@
         <v>-3.74751</v>
       </c>
       <c r="E216" t="n">
-        <v>1.93451</v>
+        <v>1.92351</v>
       </c>
       <c r="F216" t="n">
-        <v>-27.72</v>
+        <v>-27.847</v>
       </c>
       <c r="G216" t="n">
         <v>-20.072</v>
@@ -10362,7 +10362,7 @@
         <v>-47.75473</v>
       </c>
       <c r="I216" t="n">
-        <v>40.10673999999999</v>
+        <v>39.97973999999999</v>
       </c>
       <c r="J216" s="1" t="n">
         <v>45930</v>
@@ -10371,7 +10371,7 @@
         <v>1536.009359448403</v>
       </c>
       <c r="L216" t="n">
-        <v>-1.804676503400639</v>
+        <v>-1.812944682186061</v>
       </c>
       <c r="M216" t="n">
         <v>-1.306762870716365</v>
@@ -10380,7 +10380,7 @@
         <v>-3.109012956610448</v>
       </c>
       <c r="O216" t="n">
-        <v>2.611099974963873</v>
+        <v>2.602831796178451</v>
       </c>
     </row>
     <row r="217">
@@ -10388,7 +10388,7 @@
         <v>45992</v>
       </c>
       <c r="B217" t="n">
-        <v>-7.42</v>
+        <v>-7.432</v>
       </c>
       <c r="C217" t="n">
         <v>-1.658</v>
@@ -10397,10 +10397,10 @@
         <v>-4.97124</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.79075</v>
+        <v>-0.80275</v>
       </c>
       <c r="F217" t="n">
-        <v>-30.13</v>
+        <v>-30.276</v>
       </c>
       <c r="G217" t="n">
         <v>-20.075</v>
@@ -10409,7 +10409,7 @@
         <v>-47.27705</v>
       </c>
       <c r="I217" t="n">
-        <v>37.22207</v>
+        <v>37.07607</v>
       </c>
       <c r="J217" s="1" t="n">
         <v>46022</v>
@@ -10418,7 +10418,7 @@
         <v>1595.814722617371</v>
       </c>
       <c r="L217" t="n">
-        <v>-1.888063794184225</v>
+        <v>-1.897212725944958</v>
       </c>
       <c r="M217" t="n">
         <v>-1.25797811710084</v>
@@ -10427,7 +10427,7 @@
         <v>-2.962565097936851</v>
       </c>
       <c r="O217" t="n">
-        <v>2.332480674131789</v>
+        <v>2.323331742371056</v>
       </c>
     </row>
     <row r="218">
@@ -10435,7 +10435,7 @@
         <v>46023</v>
       </c>
       <c r="B218" t="n">
-        <v>-6.739</v>
+        <v>-6.758</v>
       </c>
       <c r="C218" t="n">
         <v>-1.371</v>
@@ -10444,10 +10444,10 @@
         <v>-4.17593</v>
       </c>
       <c r="E218" t="n">
-        <v>-1.19206</v>
+        <v>-1.21106</v>
       </c>
       <c r="F218" t="n">
-        <v>-32.882</v>
+        <v>-33.045</v>
       </c>
       <c r="G218" t="n">
         <v>-20.354</v>
@@ -10456,7 +10456,7 @@
         <v>-46.35655</v>
       </c>
       <c r="I218" t="n">
-        <v>33.82858</v>
+        <v>33.66558</v>
       </c>
       <c r="J218" s="1" t="n">
         <v>46022</v>
@@ -10465,7 +10465,7 @@
         <v>1595.814722617371</v>
       </c>
       <c r="L218" t="n">
-        <v>-2.060514891482432</v>
+        <v>-2.070729109818046</v>
       </c>
       <c r="M218" t="n">
         <v>-1.275461349712105</v>
@@ -10474,7 +10474,7 @@
         <v>-2.904882963102912</v>
       </c>
       <c r="O218" t="n">
-        <v>2.119831301250069</v>
+        <v>2.109617082914456</v>
       </c>
     </row>
     <row r="219">
@@ -10482,7 +10482,7 @@
         <v>46054</v>
       </c>
       <c r="B219" t="n">
-        <v>-7.365</v>
+        <v>-7.495</v>
       </c>
       <c r="C219" t="n">
         <v>-1.946</v>
@@ -10491,10 +10491,10 @@
         <v>-4.03579</v>
       </c>
       <c r="E219" t="n">
-        <v>-1.3832</v>
+        <v>-1.5132</v>
       </c>
       <c r="F219" t="n">
-        <v>-34.957</v>
+        <v>-35.256</v>
       </c>
       <c r="G219" t="n">
         <v>-20.45</v>
@@ -10503,7 +10503,7 @@
         <v>-45.67628999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>31.16933</v>
+        <v>30.87032999999999</v>
       </c>
       <c r="J219" s="1" t="n">
         <v>46022</v>
@@ -10512,7 +10512,7 @@
         <v>1595.814722617371</v>
       </c>
       <c r="L219" t="n">
-        <v>-2.190542517533951</v>
+        <v>-2.209279028468604</v>
       </c>
       <c r="M219" t="n">
         <v>-1.281477085664368</v>
@@ -10521,7 +10521,7 @@
         <v>-2.862255207489511</v>
       </c>
       <c r="O219" t="n">
-        <v>1.953192282176575</v>
+        <v>1.934455771241921</v>
       </c>
     </row>
     <row r="220">
@@ -10529,7 +10529,7 @@
         <v>46082</v>
       </c>
       <c r="B220" t="n">
-        <v>-9.603999999999999</v>
+        <v>-9.749000000000001</v>
       </c>
       <c r="C220" t="n">
         <v>-1.603</v>
@@ -10538,10 +10538,10 @@
         <v>-4.119359999999999</v>
       </c>
       <c r="E220" t="n">
-        <v>-3.88163</v>
+        <v>-4.02663</v>
       </c>
       <c r="F220" t="n">
-        <v>-39.565</v>
+        <v>-40.011</v>
       </c>
       <c r="G220" t="n">
         <v>-20.906</v>
@@ -10550,7 +10550,7 @@
         <v>-45.39955</v>
       </c>
       <c r="I220" t="n">
-        <v>26.7406</v>
+        <v>26.2946</v>
       </c>
       <c r="J220" s="1" t="n">
         <v>46112</v>
@@ -10559,7 +10559,7 @@
         <v>1640.339363149401</v>
       </c>
       <c r="L220" t="n">
-        <v>-2.412000887672195</v>
+        <v>-2.439190383335075</v>
       </c>
       <c r="M220" t="n">
         <v>-1.274492368448753</v>
@@ -10568,7 +10568,7 @@
         <v>-2.767692528748091</v>
       </c>
       <c r="O220" t="n">
-        <v>1.630187057674386</v>
+        <v>1.602997562011508</v>
       </c>
     </row>
     <row r="221">
@@ -10576,28 +10576,28 @@
         <v>46113</v>
       </c>
       <c r="B221" t="n">
-        <v>-5.505</v>
+        <v>-5.621</v>
       </c>
       <c r="C221" t="n">
         <v>-0.824</v>
       </c>
       <c r="D221" t="n">
-        <v>-5.18373</v>
+        <v>-5.183739999999999</v>
       </c>
       <c r="E221" t="n">
-        <v>0.50273</v>
+        <v>0.38674</v>
       </c>
       <c r="F221" t="n">
-        <v>-36.573</v>
+        <v>-37.129</v>
       </c>
       <c r="G221" t="n">
         <v>-19.545</v>
       </c>
       <c r="H221" t="n">
-        <v>-46.84539</v>
+        <v>-46.8454</v>
       </c>
       <c r="I221" t="n">
-        <v>29.81743</v>
+        <v>29.26144</v>
       </c>
       <c r="J221" s="1" t="n">
         <v>46112</v>
@@ -10606,16 +10606,16 @@
         <v>1640.339363149401</v>
       </c>
       <c r="L221" t="n">
-        <v>-2.229599607350821</v>
+        <v>-2.263495032437279</v>
       </c>
       <c r="M221" t="n">
         <v>-1.191521732580641</v>
       </c>
       <c r="N221" t="n">
-        <v>-2.855835265091626</v>
+        <v>-2.855835874721574</v>
       </c>
       <c r="O221" t="n">
-        <v>1.817759828841237</v>
+        <v>1.783865013384726</v>
       </c>
     </row>
     <row r="222">
@@ -10623,28 +10623,28 @@
         <v>46143</v>
       </c>
       <c r="B222" t="n">
-        <v>-1.32</v>
+        <v>-1.367</v>
       </c>
       <c r="C222" t="n">
         <v>-0.5629999999999999</v>
       </c>
       <c r="D222" t="n">
-        <v>-4.55421</v>
+        <v>-4.5584</v>
       </c>
       <c r="E222" t="n">
-        <v>3.79721</v>
+        <v>3.7544</v>
       </c>
       <c r="F222" t="n">
-        <v>-36.844</v>
+        <v>-37.439</v>
       </c>
       <c r="G222" t="n">
         <v>-18.334</v>
       </c>
       <c r="H222" t="n">
-        <v>-48.44876</v>
+        <v>-48.45296</v>
       </c>
       <c r="I222" t="n">
-        <v>29.9388</v>
+        <v>29.34799999999999</v>
       </c>
       <c r="J222" s="1" t="n">
         <v>46112</v>
@@ -10653,16 +10653,16 @@
         <v>1640.339363149401</v>
       </c>
       <c r="L222" t="n">
-        <v>-2.246120578930731</v>
+        <v>-2.282393560812822</v>
       </c>
       <c r="M222" t="n">
         <v>-1.117695545926501</v>
       </c>
       <c r="N222" t="n">
-        <v>-2.953581501999675</v>
+        <v>-2.953837546577667</v>
       </c>
       <c r="O222" t="n">
-        <v>1.825158907515236</v>
+        <v>1.789141970211135</v>
       </c>
     </row>
     <row r="223">
@@ -10670,28 +10670,28 @@
         <v>46174</v>
       </c>
       <c r="B223" t="n">
-        <v>-4.333</v>
+        <v>-4.472</v>
       </c>
       <c r="C223" t="n">
         <v>-1.16</v>
       </c>
       <c r="D223" t="n">
-        <v>-4.509060000000001</v>
+        <v>-4.50405</v>
       </c>
       <c r="E223" t="n">
-        <v>1.33606</v>
+        <v>1.19205</v>
       </c>
       <c r="F223" t="n">
-        <v>-38.98</v>
+        <v>-39.706</v>
       </c>
       <c r="G223" t="n">
         <v>-18.071</v>
       </c>
       <c r="H223" t="n">
-        <v>-49.7978</v>
+        <v>-49.79698999999999</v>
       </c>
       <c r="I223" t="n">
-        <v>28.88884</v>
+        <v>28.16202999999999</v>
       </c>
       <c r="J223" s="1" t="n">
         <v>46203</v>
@@ -10700,16 +10700,16 @@
         <v>1700.354635555628</v>
       </c>
       <c r="L223" t="n">
-        <v>-2.29246294772281</v>
+        <v>-2.335159923095996</v>
       </c>
       <c r="M223" t="n">
         <v>-1.062778294722907</v>
       </c>
       <c r="N223" t="n">
-        <v>-2.928671405287607</v>
+        <v>-2.928623768166323</v>
       </c>
       <c r="O223" t="n">
-        <v>1.698989104738138</v>
+        <v>1.656244492243669</v>
       </c>
     </row>
     <row r="224">
@@ -10717,28 +10717,28 @@
         <v>46204</v>
       </c>
       <c r="B224" t="n">
-        <v>0.036</v>
+        <v>-0.089</v>
       </c>
       <c r="C224" t="n">
         <v>-0.462</v>
       </c>
       <c r="D224" t="n">
-        <v>-4.47436</v>
+        <v>-4.46383</v>
       </c>
       <c r="E224" t="n">
-        <v>4.97236</v>
+        <v>4.83683</v>
       </c>
       <c r="F224" t="n">
-        <v>-40.706</v>
+        <v>-41.534</v>
       </c>
       <c r="G224" t="n">
         <v>-18.032</v>
       </c>
       <c r="H224" t="n">
-        <v>-50.5124</v>
+        <v>-50.50106</v>
       </c>
       <c r="I224" t="n">
-        <v>27.83844</v>
+        <v>26.99909999999999</v>
       </c>
       <c r="J224" s="1" t="n">
         <v>46203</v>
@@ -10747,16 +10747,63 @@
         <v>1700.354635555628</v>
       </c>
       <c r="L224" t="n">
-        <v>-2.393971183940603</v>
+        <v>-2.442666907919938</v>
       </c>
       <c r="M224" t="n">
         <v>-1.060484655549967</v>
       </c>
       <c r="N224" t="n">
-        <v>-2.970697932287164</v>
+        <v>-2.970031012589186</v>
       </c>
       <c r="O224" t="n">
-        <v>1.637213756346962</v>
+        <v>1.587851112669649</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B225" t="n">
+        <v>4.053</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-4.97759</v>
+      </c>
+      <c r="E225" t="n">
+        <v>8.20459</v>
+      </c>
+      <c r="F225" t="n">
+        <v>-42.10300000000001</v>
+      </c>
+      <c r="G225" t="n">
+        <v>-16.219</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-51.91023</v>
+      </c>
+      <c r="I225" t="n">
+        <v>26.02626999999999</v>
+      </c>
+      <c r="J225" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1700.354635555628</v>
+      </c>
+      <c r="L225" t="n">
+        <v>-2.47613051534052</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-0.9538598396386933</v>
+      </c>
+      <c r="N225" t="n">
+        <v>-3.052906077033583</v>
+      </c>
+      <c r="O225" t="n">
+        <v>1.530637753782189</v>
       </c>
     </row>
   </sheetData>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,84 +434,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cari</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>enerji</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>cari_12</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>altin_12</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>enerji_12</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>diger_12</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>gsyh_tarih</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cari_gsyh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>altin_gsyh</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>enerji_gsyh</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>diger_gsyh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B2" t="n">
@@ -526,7 +538,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B3" t="n">
@@ -553,7 +565,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B4" t="n">
@@ -580,7 +592,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B5" t="n">
@@ -607,7 +619,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B6" t="n">
@@ -634,7 +646,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B7" t="n">
@@ -661,7 +673,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B8" t="n">
@@ -688,7 +700,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B9" t="n">
@@ -715,7 +727,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B10" t="n">
@@ -742,7 +754,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B11" t="n">
@@ -769,7 +781,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B12" t="n">
@@ -796,7 +808,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B13" t="n">
@@ -823,7 +835,7 @@
       <c r="I13" t="n">
         <v>2.68842</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K13" t="n">
@@ -843,7 +855,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B14" t="n">
@@ -870,7 +882,7 @@
       <c r="I14" t="n">
         <v>5.004020000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K14" t="n">
@@ -890,7 +902,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B15" t="n">
@@ -917,7 +929,7 @@
       <c r="I15" t="n">
         <v>6.2034</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K15" t="n">
@@ -937,7 +949,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B16" t="n">
@@ -964,7 +976,7 @@
       <c r="I16" t="n">
         <v>7.860720000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K16" t="n">
@@ -984,7 +996,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B17" t="n">
@@ -1011,7 +1023,7 @@
       <c r="I17" t="n">
         <v>9.52572</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K17" t="n">
@@ -1031,7 +1043,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B18" t="n">
@@ -1058,7 +1070,7 @@
       <c r="I18" t="n">
         <v>10.32989</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K18" t="n">
@@ -1078,7 +1090,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B19" t="n">
@@ -1105,7 +1117,7 @@
       <c r="I19" t="n">
         <v>11.23285</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K19" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B20" t="n">
@@ -1152,7 +1164,7 @@
       <c r="I20" t="n">
         <v>13.00463</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K20" t="n">
@@ -1172,7 +1184,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B21" t="n">
@@ -1199,7 +1211,7 @@
       <c r="I21" t="n">
         <v>12.93374</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K21" t="n">
@@ -1219,7 +1231,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B22" t="n">
@@ -1246,7 +1258,7 @@
       <c r="I22" t="n">
         <v>10.54887</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K22" t="n">
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B23" t="n">
@@ -1293,7 +1305,7 @@
       <c r="I23" t="n">
         <v>12.80883</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K23" t="n">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B24" t="n">
@@ -1340,7 +1352,7 @@
       <c r="I24" t="n">
         <v>11.9196</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K24" t="n">
@@ -1360,7 +1372,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B25" t="n">
@@ -1387,7 +1399,7 @@
       <c r="I25" t="n">
         <v>11.61895</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K25" t="n">
@@ -1407,7 +1419,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B26" t="n">
@@ -1434,7 +1446,7 @@
       <c r="I26" t="n">
         <v>10.08681</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K26" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B27" t="n">
@@ -1481,7 +1493,7 @@
       <c r="I27" t="n">
         <v>10.03788</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K27" t="n">
@@ -1501,7 +1513,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B28" t="n">
@@ -1528,7 +1540,7 @@
       <c r="I28" t="n">
         <v>8.120710000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K28" t="n">
@@ -1548,7 +1560,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B29" t="n">
@@ -1575,7 +1587,7 @@
       <c r="I29" t="n">
         <v>6.80951</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K29" t="n">
@@ -1595,7 +1607,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B30" t="n">
@@ -1622,7 +1634,7 @@
       <c r="I30" t="n">
         <v>5.458740000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K30" t="n">
@@ -1642,7 +1654,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B31" t="n">
@@ -1669,7 +1681,7 @@
       <c r="I31" t="n">
         <v>4.53857</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K31" t="n">
@@ -1689,7 +1701,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B32" t="n">
@@ -1716,7 +1728,7 @@
       <c r="I32" t="n">
         <v>2.42634</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K32" t="n">
@@ -1736,7 +1748,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B33" t="n">
@@ -1763,7 +1775,7 @@
       <c r="I33" t="n">
         <v>0.1354600000000002</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K33" t="n">
@@ -1783,7 +1795,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B34" t="n">
@@ -1810,7 +1822,7 @@
       <c r="I34" t="n">
         <v>-1.641</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K34" t="n">
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B35" t="n">
@@ -1857,7 +1869,7 @@
       <c r="I35" t="n">
         <v>-4.08595</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K35" t="n">
@@ -1877,7 +1889,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B36" t="n">
@@ -1904,7 +1916,7 @@
       <c r="I36" t="n">
         <v>-7.33985</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K36" t="n">
@@ -1924,7 +1936,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B37" t="n">
@@ -1951,7 +1963,7 @@
       <c r="I37" t="n">
         <v>-10.14424</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K37" t="n">
@@ -1971,7 +1983,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B38" t="n">
@@ -1998,7 +2010,7 @@
       <c r="I38" t="n">
         <v>-11.7397</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K38" t="n">
@@ -2018,7 +2030,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B39" t="n">
@@ -2045,7 +2057,7 @@
       <c r="I39" t="n">
         <v>-14.14707</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K39" t="n">
@@ -2065,7 +2077,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B40" t="n">
@@ -2092,7 +2104,7 @@
       <c r="I40" t="n">
         <v>-18.16812</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K40" t="n">
@@ -2112,7 +2124,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B41" t="n">
@@ -2139,7 +2151,7 @@
       <c r="I41" t="n">
         <v>-20.5611</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K41" t="n">
@@ -2159,7 +2171,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B42" t="n">
@@ -2186,7 +2198,7 @@
       <c r="I42" t="n">
         <v>-23.39756</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K42" t="n">
@@ -2206,7 +2218,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B43" t="n">
@@ -2233,7 +2245,7 @@
       <c r="I43" t="n">
         <v>-26.26857</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K43" t="n">
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B44" t="n">
@@ -2280,7 +2292,7 @@
       <c r="I44" t="n">
         <v>-26.73468</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K44" t="n">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B45" t="n">
@@ -2327,7 +2339,7 @@
       <c r="I45" t="n">
         <v>-25.77266</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K45" t="n">
@@ -2347,7 +2359,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B46" t="n">
@@ -2374,7 +2386,7 @@
       <c r="I46" t="n">
         <v>-25.75811</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K46" t="n">
@@ -2394,7 +2406,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B47" t="n">
@@ -2421,7 +2433,7 @@
       <c r="I47" t="n">
         <v>-25.40919</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K47" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B48" t="n">
@@ -2468,7 +2480,7 @@
       <c r="I48" t="n">
         <v>-24.01676</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K48" t="n">
@@ -2488,7 +2500,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B49" t="n">
@@ -2515,7 +2527,7 @@
       <c r="I49" t="n">
         <v>-22.04643</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K49" t="n">
@@ -2535,7 +2547,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B50" t="n">
@@ -2562,7 +2574,7 @@
       <c r="I50" t="n">
         <v>-21.51568</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K50" t="n">
@@ -2582,7 +2594,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B51" t="n">
@@ -2609,7 +2621,7 @@
       <c r="I51" t="n">
         <v>-19.64396</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K51" t="n">
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B52" t="n">
@@ -2656,7 +2668,7 @@
       <c r="I52" t="n">
         <v>-15.79015</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K52" t="n">
@@ -2676,7 +2688,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B53" t="n">
@@ -2703,7 +2715,7 @@
       <c r="I53" t="n">
         <v>-13.06127</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K53" t="n">
@@ -2723,7 +2735,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B54" t="n">
@@ -2750,7 +2762,7 @@
       <c r="I54" t="n">
         <v>-10.51409</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K54" t="n">
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B55" t="n">
@@ -2797,7 +2809,7 @@
       <c r="I55" t="n">
         <v>-6.249130000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K55" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B56" t="n">
@@ -2844,7 +2856,7 @@
       <c r="I56" t="n">
         <v>-4.688590000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K56" t="n">
@@ -2864,7 +2876,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B57" t="n">
@@ -2891,7 +2903,7 @@
       <c r="I57" t="n">
         <v>-2.382240000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K57" t="n">
@@ -2911,7 +2923,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B58" t="n">
@@ -2938,7 +2950,7 @@
       <c r="I58" t="n">
         <v>0.395989999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K58" t="n">
@@ -2958,7 +2970,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B59" t="n">
@@ -2985,7 +2997,7 @@
       <c r="I59" t="n">
         <v>1.845749999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K59" t="n">
@@ -3005,7 +3017,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B60" t="n">
@@ -3032,7 +3044,7 @@
       <c r="I60" t="n">
         <v>3.21682</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K60" t="n">
@@ -3052,7 +3064,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B61" t="n">
@@ -3079,7 +3091,7 @@
       <c r="I61" t="n">
         <v>4.90424</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K61" t="n">
@@ -3099,7 +3111,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B62" t="n">
@@ -3126,7 +3138,7 @@
       <c r="I62" t="n">
         <v>5.24468</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K62" t="n">
@@ -3146,7 +3158,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B63" t="n">
@@ -3173,7 +3185,7 @@
       <c r="I63" t="n">
         <v>5.49649</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K63" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B64" t="n">
@@ -3220,7 +3232,7 @@
       <c r="I64" t="n">
         <v>6.803089999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K64" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B65" t="n">
@@ -3267,7 +3279,7 @@
       <c r="I65" t="n">
         <v>7.07182</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K65" t="n">
@@ -3287,7 +3299,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B66" t="n">
@@ -3314,7 +3326,7 @@
       <c r="I66" t="n">
         <v>8.31753</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K66" t="n">
@@ -3334,7 +3346,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B67" t="n">
@@ -3361,7 +3373,7 @@
       <c r="I67" t="n">
         <v>9.40043</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K67" t="n">
@@ -3381,7 +3393,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B68" t="n">
@@ -3408,7 +3420,7 @@
       <c r="I68" t="n">
         <v>9.15676</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K68" t="n">
@@ -3428,7 +3440,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B69" t="n">
@@ -3455,7 +3467,7 @@
       <c r="I69" t="n">
         <v>9.691610000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K69" t="n">
@@ -3475,7 +3487,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B70" t="n">
@@ -3502,7 +3514,7 @@
       <c r="I70" t="n">
         <v>10.6274</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K70" t="n">
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B71" t="n">
@@ -3549,7 +3561,7 @@
       <c r="I71" t="n">
         <v>10.15893</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K71" t="n">
@@ -3569,7 +3581,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B72" t="n">
@@ -3596,7 +3608,7 @@
       <c r="I72" t="n">
         <v>11.57857</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K72" t="n">
@@ -3616,7 +3628,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B73" t="n">
@@ -3643,7 +3655,7 @@
       <c r="I73" t="n">
         <v>10.08393</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K73" t="n">
@@ -3663,7 +3675,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B74" t="n">
@@ -3690,7 +3702,7 @@
       <c r="I74" t="n">
         <v>11.61466</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K74" t="n">
@@ -3710,7 +3722,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B75" t="n">
@@ -3737,7 +3749,7 @@
       <c r="I75" t="n">
         <v>12.55543</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K75" t="n">
@@ -3757,7 +3769,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B76" t="n">
@@ -3784,7 +3796,7 @@
       <c r="I76" t="n">
         <v>12.95175</v>
       </c>
-      <c r="J76" s="1" t="n">
+      <c r="J76" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K76" t="n">
@@ -3804,7 +3816,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B77" t="n">
@@ -3831,7 +3843,7 @@
       <c r="I77" t="n">
         <v>13.82609</v>
       </c>
-      <c r="J77" s="1" t="n">
+      <c r="J77" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K77" t="n">
@@ -3851,7 +3863,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B78" t="n">
@@ -3878,7 +3890,7 @@
       <c r="I78" t="n">
         <v>15.83389</v>
       </c>
-      <c r="J78" s="1" t="n">
+      <c r="J78" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K78" t="n">
@@ -3898,7 +3910,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B79" t="n">
@@ -3925,7 +3937,7 @@
       <c r="I79" t="n">
         <v>15.8046</v>
       </c>
-      <c r="J79" s="1" t="n">
+      <c r="J79" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K79" t="n">
@@ -3945,7 +3957,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B80" t="n">
@@ -3972,7 +3984,7 @@
       <c r="I80" t="n">
         <v>18.19608</v>
       </c>
-      <c r="J80" s="1" t="n">
+      <c r="J80" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K80" t="n">
@@ -3992,7 +4004,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B81" t="n">
@@ -4019,7 +4031,7 @@
       <c r="I81" t="n">
         <v>18.488</v>
       </c>
-      <c r="J81" s="1" t="n">
+      <c r="J81" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K81" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B82" t="n">
@@ -4066,7 +4078,7 @@
       <c r="I82" t="n">
         <v>19.80297</v>
       </c>
-      <c r="J82" s="1" t="n">
+      <c r="J82" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K82" t="n">
@@ -4086,7 +4098,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B83" t="n">
@@ -4113,7 +4125,7 @@
       <c r="I83" t="n">
         <v>20.59569</v>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="J83" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K83" t="n">
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B84" t="n">
@@ -4160,7 +4172,7 @@
       <c r="I84" t="n">
         <v>19.85103</v>
       </c>
-      <c r="J84" s="1" t="n">
+      <c r="J84" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K84" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B85" t="n">
@@ -4207,7 +4219,7 @@
       <c r="I85" t="n">
         <v>20.46028</v>
       </c>
-      <c r="J85" s="1" t="n">
+      <c r="J85" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K85" t="n">
@@ -4227,7 +4239,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B86" t="n">
@@ -4254,7 +4266,7 @@
       <c r="I86" t="n">
         <v>20.80432</v>
       </c>
-      <c r="J86" s="1" t="n">
+      <c r="J86" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K86" t="n">
@@ -4274,7 +4286,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B87" t="n">
@@ -4301,7 +4313,7 @@
       <c r="I87" t="n">
         <v>18.98794</v>
       </c>
-      <c r="J87" s="1" t="n">
+      <c r="J87" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K87" t="n">
@@ -4321,7 +4333,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B88" t="n">
@@ -4348,7 +4360,7 @@
       <c r="I88" t="n">
         <v>17.46199</v>
       </c>
-      <c r="J88" s="1" t="n">
+      <c r="J88" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K88" t="n">
@@ -4368,7 +4380,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B89" t="n">
@@ -4395,7 +4407,7 @@
       <c r="I89" t="n">
         <v>15.2882</v>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="J89" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K89" t="n">
@@ -4415,7 +4427,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B90" t="n">
@@ -4442,7 +4454,7 @@
       <c r="I90" t="n">
         <v>12.95619</v>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="J90" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K90" t="n">
@@ -4462,7 +4474,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B91" t="n">
@@ -4489,7 +4501,7 @@
       <c r="I91" t="n">
         <v>11.8918</v>
       </c>
-      <c r="J91" s="1" t="n">
+      <c r="J91" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K91" t="n">
@@ -4509,7 +4521,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B92" t="n">
@@ -4536,7 +4548,7 @@
       <c r="I92" t="n">
         <v>10.00618</v>
       </c>
-      <c r="J92" s="1" t="n">
+      <c r="J92" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K92" t="n">
@@ -4556,7 +4568,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4595,7 @@
       <c r="I93" t="n">
         <v>10.69088</v>
       </c>
-      <c r="J93" s="1" t="n">
+      <c r="J93" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K93" t="n">
@@ -4603,7 +4615,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B94" t="n">
@@ -4630,7 +4642,7 @@
       <c r="I94" t="n">
         <v>9.682169999999999</v>
       </c>
-      <c r="J94" s="1" t="n">
+      <c r="J94" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K94" t="n">
@@ -4650,7 +4662,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B95" t="n">
@@ -4677,7 +4689,7 @@
       <c r="I95" t="n">
         <v>9.299630000000001</v>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="J95" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K95" t="n">
@@ -4697,7 +4709,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B96" t="n">
@@ -4724,7 +4736,7 @@
       <c r="I96" t="n">
         <v>9.04907</v>
       </c>
-      <c r="J96" s="1" t="n">
+      <c r="J96" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K96" t="n">
@@ -4744,7 +4756,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B97" t="n">
@@ -4771,7 +4783,7 @@
       <c r="I97" t="n">
         <v>8.198219999999999</v>
       </c>
-      <c r="J97" s="1" t="n">
+      <c r="J97" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K97" t="n">
@@ -4791,7 +4803,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B98" t="n">
@@ -4818,7 +4830,7 @@
       <c r="I98" t="n">
         <v>7.736389999999999</v>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="J98" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K98" t="n">
@@ -4838,7 +4850,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B99" t="n">
@@ -4865,7 +4877,7 @@
       <c r="I99" t="n">
         <v>7.899969999999999</v>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="J99" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K99" t="n">
@@ -4885,7 +4897,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B100" t="n">
@@ -4912,7 +4924,7 @@
       <c r="I100" t="n">
         <v>7.502359999999999</v>
       </c>
-      <c r="J100" s="1" t="n">
+      <c r="J100" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K100" t="n">
@@ -4932,7 +4944,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B101" t="n">
@@ -4959,7 +4971,7 @@
       <c r="I101" t="n">
         <v>8.811169999999999</v>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="J101" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K101" t="n">
@@ -4979,7 +4991,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B102" t="n">
@@ -5006,7 +5018,7 @@
       <c r="I102" t="n">
         <v>7.943439999999999</v>
       </c>
-      <c r="J102" s="1" t="n">
+      <c r="J102" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K102" t="n">
@@ -5026,7 +5038,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B103" t="n">
@@ -5053,7 +5065,7 @@
       <c r="I103" t="n">
         <v>4.534299999999999</v>
       </c>
-      <c r="J103" s="1" t="n">
+      <c r="J103" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K103" t="n">
@@ -5073,7 +5085,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B104" t="n">
@@ -5100,7 +5112,7 @@
       <c r="I104" t="n">
         <v>2.886419999999999</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="J104" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K104" t="n">
@@ -5120,7 +5132,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B105" t="n">
@@ -5147,7 +5159,7 @@
       <c r="I105" t="n">
         <v>0.2952499999999989</v>
       </c>
-      <c r="J105" s="1" t="n">
+      <c r="J105" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K105" t="n">
@@ -5167,7 +5179,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B106" t="n">
@@ -5194,7 +5206,7 @@
       <c r="I106" t="n">
         <v>-1.300060000000001</v>
       </c>
-      <c r="J106" s="1" t="n">
+      <c r="J106" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K106" t="n">
@@ -5214,7 +5226,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B107" t="n">
@@ -5241,7 +5253,7 @@
       <c r="I107" t="n">
         <v>-1.551580000000001</v>
       </c>
-      <c r="J107" s="1" t="n">
+      <c r="J107" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K107" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B108" t="n">
@@ -5288,7 +5300,7 @@
       <c r="I108" t="n">
         <v>-1.618070000000001</v>
       </c>
-      <c r="J108" s="1" t="n">
+      <c r="J108" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K108" t="n">
@@ -5308,7 +5320,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B109" t="n">
@@ -5335,7 +5347,7 @@
       <c r="I109" t="n">
         <v>0.1297299999999989</v>
       </c>
-      <c r="J109" s="1" t="n">
+      <c r="J109" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K109" t="n">
@@ -5355,7 +5367,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B110" t="n">
@@ -5382,7 +5394,7 @@
       <c r="I110" t="n">
         <v>0.3622699999999989</v>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="J110" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K110" t="n">
@@ -5402,7 +5414,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B111" t="n">
@@ -5429,7 +5441,7 @@
       <c r="I111" t="n">
         <v>2.062249999999999</v>
       </c>
-      <c r="J111" s="1" t="n">
+      <c r="J111" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K111" t="n">
@@ -5449,7 +5461,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B112" t="n">
@@ -5476,7 +5488,7 @@
       <c r="I112" t="n">
         <v>4.506739999999999</v>
       </c>
-      <c r="J112" s="1" t="n">
+      <c r="J112" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K112" t="n">
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B113" t="n">
@@ -5523,7 +5535,7 @@
       <c r="I113" t="n">
         <v>4.95311</v>
       </c>
-      <c r="J113" s="1" t="n">
+      <c r="J113" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K113" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B114" t="n">
@@ -5570,7 +5582,7 @@
       <c r="I114" t="n">
         <v>5.905279999999999</v>
       </c>
-      <c r="J114" s="1" t="n">
+      <c r="J114" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K114" t="n">
@@ -5590,7 +5602,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B115" t="n">
@@ -5617,7 +5629,7 @@
       <c r="I115" t="n">
         <v>8.84371</v>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="J115" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K115" t="n">
@@ -5637,7 +5649,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B116" t="n">
@@ -5664,7 +5676,7 @@
       <c r="I116" t="n">
         <v>9.860910000000001</v>
       </c>
-      <c r="J116" s="1" t="n">
+      <c r="J116" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K116" t="n">
@@ -5684,7 +5696,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B117" t="n">
@@ -5711,7 +5723,7 @@
       <c r="I117" t="n">
         <v>12.08097</v>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="J117" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K117" t="n">
@@ -5731,7 +5743,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B118" t="n">
@@ -5758,7 +5770,7 @@
       <c r="I118" t="n">
         <v>10.99841</v>
       </c>
-      <c r="J118" s="1" t="n">
+      <c r="J118" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K118" t="n">
@@ -5778,7 +5790,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B119" t="n">
@@ -5805,7 +5817,7 @@
       <c r="I119" t="n">
         <v>9.6854</v>
       </c>
-      <c r="J119" s="1" t="n">
+      <c r="J119" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K119" t="n">
@@ -5825,7 +5837,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B120" t="n">
@@ -5852,7 +5864,7 @@
       <c r="I120" t="n">
         <v>9.236190000000001</v>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="J120" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K120" t="n">
@@ -5872,7 +5884,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B121" t="n">
@@ -5899,7 +5911,7 @@
       <c r="I121" t="n">
         <v>7.685680000000001</v>
       </c>
-      <c r="J121" s="1" t="n">
+      <c r="J121" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K121" t="n">
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B122" t="n">
@@ -5946,7 +5958,7 @@
       <c r="I122" t="n">
         <v>5.95812</v>
       </c>
-      <c r="J122" s="1" t="n">
+      <c r="J122" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K122" t="n">
@@ -5966,7 +5978,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B123" t="n">
@@ -5993,7 +6005,7 @@
       <c r="I123" t="n">
         <v>4.993270000000001</v>
       </c>
-      <c r="J123" s="1" t="n">
+      <c r="J123" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K123" t="n">
@@ -6013,7 +6025,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B124" t="n">
@@ -6040,7 +6052,7 @@
       <c r="I124" t="n">
         <v>4.364470000000001</v>
       </c>
-      <c r="J124" s="1" t="n">
+      <c r="J124" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K124" t="n">
@@ -6060,7 +6072,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B125" t="n">
@@ -6087,7 +6099,7 @@
       <c r="I125" t="n">
         <v>3.48327</v>
       </c>
-      <c r="J125" s="1" t="n">
+      <c r="J125" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K125" t="n">
@@ -6107,7 +6119,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B126" t="n">
@@ -6134,7 +6146,7 @@
       <c r="I126" t="n">
         <v>3.21001</v>
       </c>
-      <c r="J126" s="1" t="n">
+      <c r="J126" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K126" t="n">
@@ -6154,7 +6166,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B127" t="n">
@@ -6181,7 +6193,7 @@
       <c r="I127" t="n">
         <v>3.74216</v>
       </c>
-      <c r="J127" s="1" t="n">
+      <c r="J127" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K127" t="n">
@@ -6201,7 +6213,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B128" t="n">
@@ -6228,7 +6240,7 @@
       <c r="I128" t="n">
         <v>6.06072</v>
       </c>
-      <c r="J128" s="1" t="n">
+      <c r="J128" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K128" t="n">
@@ -6248,7 +6260,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B129" t="n">
@@ -6275,7 +6287,7 @@
       <c r="I129" t="n">
         <v>7.804049999999999</v>
       </c>
-      <c r="J129" s="1" t="n">
+      <c r="J129" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K129" t="n">
@@ -6295,7 +6307,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B130" t="n">
@@ -6322,7 +6334,7 @@
       <c r="I130" t="n">
         <v>14.08367</v>
       </c>
-      <c r="J130" s="1" t="n">
+      <c r="J130" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K130" t="n">
@@ -6342,7 +6354,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B131" t="n">
@@ -6369,7 +6381,7 @@
       <c r="I131" t="n">
         <v>20.77072</v>
       </c>
-      <c r="J131" s="1" t="n">
+      <c r="J131" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K131" t="n">
@@ -6389,7 +6401,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B132" t="n">
@@ -6416,7 +6428,7 @@
       <c r="I132" t="n">
         <v>26.56942</v>
       </c>
-      <c r="J132" s="1" t="n">
+      <c r="J132" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K132" t="n">
@@ -6436,7 +6448,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B133" t="n">
@@ -6463,7 +6475,7 @@
       <c r="I133" t="n">
         <v>31.91968</v>
       </c>
-      <c r="J133" s="1" t="n">
+      <c r="J133" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K133" t="n">
@@ -6483,7 +6495,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B134" t="n">
@@ -6510,7 +6522,7 @@
       <c r="I134" t="n">
         <v>36.77216</v>
       </c>
-      <c r="J134" s="1" t="n">
+      <c r="J134" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K134" t="n">
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B135" t="n">
@@ -6557,7 +6569,7 @@
       <c r="I135" t="n">
         <v>40.31249</v>
       </c>
-      <c r="J135" s="1" t="n">
+      <c r="J135" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K135" t="n">
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B136" t="n">
@@ -6604,7 +6616,7 @@
       <c r="I136" t="n">
         <v>44.4252</v>
       </c>
-      <c r="J136" s="1" t="n">
+      <c r="J136" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K136" t="n">
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B137" t="n">
@@ -6651,7 +6663,7 @@
       <c r="I137" t="n">
         <v>48.80586</v>
       </c>
-      <c r="J137" s="1" t="n">
+      <c r="J137" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K137" t="n">
@@ -6671,7 +6683,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B138" t="n">
@@ -6698,7 +6710,7 @@
       <c r="I138" t="n">
         <v>53.917</v>
       </c>
-      <c r="J138" s="1" t="n">
+      <c r="J138" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K138" t="n">
@@ -6718,7 +6730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B139" t="n">
@@ -6745,7 +6757,7 @@
       <c r="I139" t="n">
         <v>56.12547</v>
       </c>
-      <c r="J139" s="1" t="n">
+      <c r="J139" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K139" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B140" t="n">
@@ -6792,7 +6804,7 @@
       <c r="I140" t="n">
         <v>59.44548</v>
       </c>
-      <c r="J140" s="1" t="n">
+      <c r="J140" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K140" t="n">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B141" t="n">
@@ -6839,7 +6851,7 @@
       <c r="I141" t="n">
         <v>60.96964</v>
       </c>
-      <c r="J141" s="1" t="n">
+      <c r="J141" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K141" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B142" t="n">
@@ -6886,7 +6898,7 @@
       <c r="I142" t="n">
         <v>61.12259999999999</v>
       </c>
-      <c r="J142" s="1" t="n">
+      <c r="J142" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K142" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B143" t="n">
@@ -6933,7 +6945,7 @@
       <c r="I143" t="n">
         <v>60.94875</v>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="J143" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K143" t="n">
@@ -6953,7 +6965,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B144" t="n">
@@ -6980,7 +6992,7 @@
       <c r="I144" t="n">
         <v>59.31162999999999</v>
       </c>
-      <c r="J144" s="1" t="n">
+      <c r="J144" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K144" t="n">
@@ -7000,7 +7012,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B145" t="n">
@@ -7027,7 +7039,7 @@
       <c r="I145" t="n">
         <v>57.56779</v>
       </c>
-      <c r="J145" s="1" t="n">
+      <c r="J145" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K145" t="n">
@@ -7047,7 +7059,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B146" t="n">
@@ -7074,7 +7086,7 @@
       <c r="I146" t="n">
         <v>57.90269</v>
       </c>
-      <c r="J146" s="1" t="n">
+      <c r="J146" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K146" t="n">
@@ -7094,7 +7106,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B147" t="n">
@@ -7121,7 +7133,7 @@
       <c r="I147" t="n">
         <v>57.78574999999999</v>
       </c>
-      <c r="J147" s="1" t="n">
+      <c r="J147" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K147" t="n">
@@ -7141,7 +7153,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B148" t="n">
@@ -7168,7 +7180,7 @@
       <c r="I148" t="n">
         <v>52.78822</v>
       </c>
-      <c r="J148" s="1" t="n">
+      <c r="J148" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K148" t="n">
@@ -7188,7 +7200,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B149" t="n">
@@ -7215,7 +7227,7 @@
       <c r="I149" t="n">
         <v>46.00505</v>
       </c>
-      <c r="J149" s="1" t="n">
+      <c r="J149" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K149" t="n">
@@ -7235,7 +7247,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B150" t="n">
@@ -7262,7 +7274,7 @@
       <c r="I150" t="n">
         <v>39.39304</v>
       </c>
-      <c r="J150" s="1" t="n">
+      <c r="J150" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K150" t="n">
@@ -7282,7 +7294,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B151" t="n">
@@ -7309,7 +7321,7 @@
       <c r="I151" t="n">
         <v>37.28101</v>
       </c>
-      <c r="J151" s="1" t="n">
+      <c r="J151" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K151" t="n">
@@ -7329,7 +7341,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B152" t="n">
@@ -7356,7 +7368,7 @@
       <c r="I152" t="n">
         <v>32.8163</v>
       </c>
-      <c r="J152" s="1" t="n">
+      <c r="J152" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K152" t="n">
@@ -7376,7 +7388,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B153" t="n">
@@ -7403,7 +7415,7 @@
       <c r="I153" t="n">
         <v>26.95827</v>
       </c>
-      <c r="J153" s="1" t="n">
+      <c r="J153" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K153" t="n">
@@ -7423,7 +7435,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B154" t="n">
@@ -7450,7 +7462,7 @@
       <c r="I154" t="n">
         <v>23.34406</v>
       </c>
-      <c r="J154" s="1" t="n">
+      <c r="J154" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K154" t="n">
@@ -7470,7 +7482,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B155" t="n">
@@ -7497,7 +7509,7 @@
       <c r="I155" t="n">
         <v>19.61043</v>
       </c>
-      <c r="J155" s="1" t="n">
+      <c r="J155" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K155" t="n">
@@ -7517,7 +7529,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B156" t="n">
@@ -7544,7 +7556,7 @@
       <c r="I156" t="n">
         <v>16.41961</v>
       </c>
-      <c r="J156" s="1" t="n">
+      <c r="J156" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K156" t="n">
@@ -7564,7 +7576,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B157" t="n">
@@ -7591,7 +7603,7 @@
       <c r="I157" t="n">
         <v>15.58579</v>
       </c>
-      <c r="J157" s="1" t="n">
+      <c r="J157" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K157" t="n">
@@ -7611,7 +7623,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B158" t="n">
@@ -7638,7 +7650,7 @@
       <c r="I158" t="n">
         <v>13.06948</v>
       </c>
-      <c r="J158" s="1" t="n">
+      <c r="J158" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K158" t="n">
@@ -7658,7 +7670,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B159" t="n">
@@ -7685,7 +7697,7 @@
       <c r="I159" t="n">
         <v>10.72014</v>
       </c>
-      <c r="J159" s="1" t="n">
+      <c r="J159" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K159" t="n">
@@ -7705,7 +7717,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B160" t="n">
@@ -7732,7 +7744,7 @@
       <c r="I160" t="n">
         <v>11.85764</v>
       </c>
-      <c r="J160" s="1" t="n">
+      <c r="J160" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K160" t="n">
@@ -7752,7 +7764,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B161" t="n">
@@ -7779,7 +7791,7 @@
       <c r="I161" t="n">
         <v>16.75192</v>
       </c>
-      <c r="J161" s="1" t="n">
+      <c r="J161" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K161" t="n">
@@ -7799,7 +7811,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B162" t="n">
@@ -7826,7 +7838,7 @@
       <c r="I162" t="n">
         <v>17.78087</v>
       </c>
-      <c r="J162" s="1" t="n">
+      <c r="J162" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K162" t="n">
@@ -7846,7 +7858,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B163" t="n">
@@ -7873,7 +7885,7 @@
       <c r="I163" t="n">
         <v>19.18315</v>
       </c>
-      <c r="J163" s="1" t="n">
+      <c r="J163" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K163" t="n">
@@ -7893,7 +7905,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B164" t="n">
@@ -7920,7 +7932,7 @@
       <c r="I164" t="n">
         <v>21.03445</v>
       </c>
-      <c r="J164" s="1" t="n">
+      <c r="J164" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K164" t="n">
@@ -7940,7 +7952,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B165" t="n">
@@ -7967,7 +7979,7 @@
       <c r="I165" t="n">
         <v>25.49619</v>
       </c>
-      <c r="J165" s="1" t="n">
+      <c r="J165" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K165" t="n">
@@ -7987,7 +7999,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B166" t="n">
@@ -8014,7 +8026,7 @@
       <c r="I166" t="n">
         <v>28.66052</v>
       </c>
-      <c r="J166" s="1" t="n">
+      <c r="J166" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K166" t="n">
@@ -8034,7 +8046,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B167" t="n">
@@ -8061,7 +8073,7 @@
       <c r="I167" t="n">
         <v>33.67982</v>
       </c>
-      <c r="J167" s="1" t="n">
+      <c r="J167" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K167" t="n">
@@ -8081,7 +8093,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B168" t="n">
@@ -8108,7 +8120,7 @@
       <c r="I168" t="n">
         <v>35.21025</v>
       </c>
-      <c r="J168" s="1" t="n">
+      <c r="J168" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K168" t="n">
@@ -8128,7 +8140,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B169" t="n">
@@ -8155,7 +8167,7 @@
       <c r="I169" t="n">
         <v>37.12937</v>
       </c>
-      <c r="J169" s="1" t="n">
+      <c r="J169" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K169" t="n">
@@ -8175,7 +8187,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B170" t="n">
@@ -8202,7 +8214,7 @@
       <c r="I170" t="n">
         <v>37.22411</v>
       </c>
-      <c r="J170" s="1" t="n">
+      <c r="J170" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K170" t="n">
@@ -8222,7 +8234,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B171" t="n">
@@ -8249,7 +8261,7 @@
       <c r="I171" t="n">
         <v>38.29664</v>
       </c>
-      <c r="J171" s="1" t="n">
+      <c r="J171" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K171" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B172" t="n">
@@ -8296,7 +8308,7 @@
       <c r="I172" t="n">
         <v>40.84047</v>
       </c>
-      <c r="J172" s="1" t="n">
+      <c r="J172" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K172" t="n">
@@ -8316,7 +8328,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B173" t="n">
@@ -8343,7 +8355,7 @@
       <c r="I173" t="n">
         <v>43.37856</v>
       </c>
-      <c r="J173" s="1" t="n">
+      <c r="J173" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K173" t="n">
@@ -8363,7 +8375,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B174" t="n">
@@ -8390,7 +8402,7 @@
       <c r="I174" t="n">
         <v>45.0951</v>
       </c>
-      <c r="J174" s="1" t="n">
+      <c r="J174" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K174" t="n">
@@ -8410,7 +8422,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B175" t="n">
@@ -8437,7 +8449,7 @@
       <c r="I175" t="n">
         <v>47.7854</v>
       </c>
-      <c r="J175" s="1" t="n">
+      <c r="J175" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K175" t="n">
@@ -8457,7 +8469,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B176" t="n">
@@ -8484,7 +8496,7 @@
       <c r="I176" t="n">
         <v>48.45027</v>
       </c>
-      <c r="J176" s="1" t="n">
+      <c r="J176" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K176" t="n">
@@ -8504,7 +8516,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B177" t="n">
@@ -8531,7 +8543,7 @@
       <c r="I177" t="n">
         <v>49.68133</v>
       </c>
-      <c r="J177" s="1" t="n">
+      <c r="J177" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K177" t="n">
@@ -8551,7 +8563,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B178" t="n">
@@ -8578,7 +8590,7 @@
       <c r="I178" t="n">
         <v>50.47562</v>
       </c>
-      <c r="J178" s="1" t="n">
+      <c r="J178" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K178" t="n">
@@ -8598,7 +8610,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B179" t="n">
@@ -8625,7 +8637,7 @@
       <c r="I179" t="n">
         <v>50.11399</v>
       </c>
-      <c r="J179" s="1" t="n">
+      <c r="J179" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K179" t="n">
@@ -8645,7 +8657,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B180" t="n">
@@ -8672,7 +8684,7 @@
       <c r="I180" t="n">
         <v>52.17445</v>
       </c>
-      <c r="J180" s="1" t="n">
+      <c r="J180" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K180" t="n">
@@ -8692,7 +8704,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B181" t="n">
@@ -8719,7 +8731,7 @@
       <c r="I181" t="n">
         <v>52.84970999999999</v>
       </c>
-      <c r="J181" s="1" t="n">
+      <c r="J181" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K181" t="n">
@@ -8739,7 +8751,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B182" t="n">
@@ -8766,7 +8778,7 @@
       <c r="I182" t="n">
         <v>53.61758</v>
       </c>
-      <c r="J182" s="1" t="n">
+      <c r="J182" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K182" t="n">
@@ -8786,7 +8798,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B183" t="n">
@@ -8813,7 +8825,7 @@
       <c r="I183" t="n">
         <v>52.49454</v>
       </c>
-      <c r="J183" s="1" t="n">
+      <c r="J183" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K183" t="n">
@@ -8833,7 +8845,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B184" t="n">
@@ -8860,7 +8872,7 @@
       <c r="I184" t="n">
         <v>50.79395</v>
       </c>
-      <c r="J184" s="1" t="n">
+      <c r="J184" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K184" t="n">
@@ -8880,7 +8892,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B185" t="n">
@@ -8907,7 +8919,7 @@
       <c r="I185" t="n">
         <v>46.78892</v>
       </c>
-      <c r="J185" s="1" t="n">
+      <c r="J185" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K185" t="n">
@@ -8927,7 +8939,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B186" t="n">
@@ -8954,7 +8966,7 @@
       <c r="I186" t="n">
         <v>45.03124</v>
       </c>
-      <c r="J186" s="1" t="n">
+      <c r="J186" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K186" t="n">
@@ -8974,7 +8986,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B187" t="n">
@@ -9001,7 +9013,7 @@
       <c r="I187" t="n">
         <v>45.92217</v>
       </c>
-      <c r="J187" s="1" t="n">
+      <c r="J187" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K187" t="n">
@@ -9021,7 +9033,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B188" t="n">
@@ -9048,7 +9060,7 @@
       <c r="I188" t="n">
         <v>42.09453999999999</v>
       </c>
-      <c r="J188" s="1" t="n">
+      <c r="J188" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K188" t="n">
@@ -9068,7 +9080,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B189" t="n">
@@ -9095,7 +9107,7 @@
       <c r="I189" t="n">
         <v>41.36029</v>
       </c>
-      <c r="J189" s="1" t="n">
+      <c r="J189" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K189" t="n">
@@ -9115,7 +9127,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B190" t="n">
@@ -9142,7 +9154,7 @@
       <c r="I190" t="n">
         <v>41.33475</v>
       </c>
-      <c r="J190" s="1" t="n">
+      <c r="J190" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K190" t="n">
@@ -9162,7 +9174,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B191" t="n">
@@ -9189,7 +9201,7 @@
       <c r="I191" t="n">
         <v>38.13951</v>
       </c>
-      <c r="J191" s="1" t="n">
+      <c r="J191" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K191" t="n">
@@ -9209,7 +9221,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B192" t="n">
@@ -9236,7 +9248,7 @@
       <c r="I192" t="n">
         <v>35.59753</v>
       </c>
-      <c r="J192" s="1" t="n">
+      <c r="J192" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K192" t="n">
@@ -9256,7 +9268,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B193" t="n">
@@ -9283,7 +9295,7 @@
       <c r="I193" t="n">
         <v>36.55256</v>
       </c>
-      <c r="J193" s="1" t="n">
+      <c r="J193" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K193" t="n">
@@ -9303,7 +9315,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B194" t="n">
@@ -9330,7 +9342,7 @@
       <c r="I194" t="n">
         <v>37.88603</v>
       </c>
-      <c r="J194" s="1" t="n">
+      <c r="J194" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K194" t="n">
@@ -9350,7 +9362,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B195" t="n">
@@ -9377,7 +9389,7 @@
       <c r="I195" t="n">
         <v>39.20635</v>
       </c>
-      <c r="J195" s="1" t="n">
+      <c r="J195" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K195" t="n">
@@ -9397,7 +9409,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B196" t="n">
@@ -9424,7 +9436,7 @@
       <c r="I196" t="n">
         <v>39.57944</v>
       </c>
-      <c r="J196" s="1" t="n">
+      <c r="J196" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K196" t="n">
@@ -9444,7 +9456,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B197" t="n">
@@ -9471,7 +9483,7 @@
       <c r="I197" t="n">
         <v>39.32009</v>
       </c>
-      <c r="J197" s="1" t="n">
+      <c r="J197" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K197" t="n">
@@ -9491,7 +9503,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B198" t="n">
@@ -9518,7 +9530,7 @@
       <c r="I198" t="n">
         <v>43.90715</v>
       </c>
-      <c r="J198" s="1" t="n">
+      <c r="J198" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K198" t="n">
@@ -9538,7 +9550,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B199" t="n">
@@ -9565,7 +9577,7 @@
       <c r="I199" t="n">
         <v>42.71823</v>
       </c>
-      <c r="J199" s="1" t="n">
+      <c r="J199" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K199" t="n">
@@ -9585,7 +9597,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B200" t="n">
@@ -9612,7 +9624,7 @@
       <c r="I200" t="n">
         <v>47.2887</v>
       </c>
-      <c r="J200" s="1" t="n">
+      <c r="J200" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K200" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B201" t="n">
@@ -9659,7 +9671,7 @@
       <c r="I201" t="n">
         <v>49.28131</v>
       </c>
-      <c r="J201" s="1" t="n">
+      <c r="J201" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K201" t="n">
@@ -9679,7 +9691,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B202" t="n">
@@ -9706,7 +9718,7 @@
       <c r="I202" t="n">
         <v>48.84308</v>
       </c>
-      <c r="J202" s="1" t="n">
+      <c r="J202" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K202" t="n">
@@ -9726,7 +9738,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B203" t="n">
@@ -9753,7 +9765,7 @@
       <c r="I203" t="n">
         <v>50.89373</v>
       </c>
-      <c r="J203" s="1" t="n">
+      <c r="J203" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K203" t="n">
@@ -9773,7 +9785,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B204" t="n">
@@ -9800,7 +9812,7 @@
       <c r="I204" t="n">
         <v>51.48607</v>
       </c>
-      <c r="J204" s="1" t="n">
+      <c r="J204" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K204" t="n">
@@ -9820,7 +9832,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B205" t="n">
@@ -9847,7 +9859,7 @@
       <c r="I205" t="n">
         <v>49.10726</v>
       </c>
-      <c r="J205" s="1" t="n">
+      <c r="J205" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K205" t="n">
@@ -9867,7 +9879,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B206" t="n">
@@ -9894,7 +9906,7 @@
       <c r="I206" t="n">
         <v>47.72986</v>
       </c>
-      <c r="J206" s="1" t="n">
+      <c r="J206" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K206" t="n">
@@ -9914,7 +9926,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B207" t="n">
@@ -9941,7 +9953,7 @@
       <c r="I207" t="n">
         <v>46.85917999999999</v>
       </c>
-      <c r="J207" s="1" t="n">
+      <c r="J207" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K207" t="n">
@@ -9961,7 +9973,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B208" t="n">
@@ -9988,7 +10000,7 @@
       <c r="I208" t="n">
         <v>46.18819</v>
       </c>
-      <c r="J208" s="1" t="n">
+      <c r="J208" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K208" t="n">
@@ -10008,7 +10020,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B209" t="n">
@@ -10035,7 +10047,7 @@
       <c r="I209" t="n">
         <v>43.77743</v>
       </c>
-      <c r="J209" s="1" t="n">
+      <c r="J209" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K209" t="n">
@@ -10055,7 +10067,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B210" t="n">
@@ -10082,7 +10094,7 @@
       <c r="I210" t="n">
         <v>43.79429</v>
       </c>
-      <c r="J210" s="1" t="n">
+      <c r="J210" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K210" t="n">
@@ -10102,7 +10114,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B211" t="n">
@@ -10129,7 +10141,7 @@
       <c r="I211" t="n">
         <v>41.44814</v>
       </c>
-      <c r="J211" s="1" t="n">
+      <c r="J211" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K211" t="n">
@@ -10149,7 +10161,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B212" t="n">
@@ -10176,7 +10188,7 @@
       <c r="I212" t="n">
         <v>41.90796</v>
       </c>
-      <c r="J212" s="1" t="n">
+      <c r="J212" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K212" t="n">
@@ -10196,7 +10208,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B213" t="n">
@@ -10223,7 +10235,7 @@
       <c r="I213" t="n">
         <v>41.96055</v>
       </c>
-      <c r="J213" s="1" t="n">
+      <c r="J213" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K213" t="n">
@@ -10243,7 +10255,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B214" t="n">
@@ -10270,7 +10282,7 @@
       <c r="I214" t="n">
         <v>40.90523</v>
       </c>
-      <c r="J214" s="1" t="n">
+      <c r="J214" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K214" t="n">
@@ -10290,7 +10302,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B215" t="n">
@@ -10317,7 +10329,7 @@
       <c r="I215" t="n">
         <v>40.92907</v>
       </c>
-      <c r="J215" s="1" t="n">
+      <c r="J215" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K215" t="n">
@@ -10337,7 +10349,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B216" t="n">
@@ -10364,7 +10376,7 @@
       <c r="I216" t="n">
         <v>39.97973999999999</v>
       </c>
-      <c r="J216" s="1" t="n">
+      <c r="J216" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K216" t="n">
@@ -10384,7 +10396,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B217" t="n">
@@ -10411,7 +10423,7 @@
       <c r="I217" t="n">
         <v>37.07607</v>
       </c>
-      <c r="J217" s="1" t="n">
+      <c r="J217" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K217" t="n">
@@ -10431,7 +10443,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B218" t="n">
@@ -10458,7 +10470,7 @@
       <c r="I218" t="n">
         <v>33.66558</v>
       </c>
-      <c r="J218" s="1" t="n">
+      <c r="J218" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K218" t="n">
@@ -10478,7 +10490,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B219" t="n">
@@ -10505,7 +10517,7 @@
       <c r="I219" t="n">
         <v>30.87032999999999</v>
       </c>
-      <c r="J219" s="1" t="n">
+      <c r="J219" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K219" t="n">
@@ -10525,7 +10537,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B220" t="n">
@@ -10552,7 +10564,7 @@
       <c r="I220" t="n">
         <v>26.2946</v>
       </c>
-      <c r="J220" s="1" t="n">
+      <c r="J220" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K220" t="n">
@@ -10572,7 +10584,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B221" t="n">
@@ -10599,7 +10611,7 @@
       <c r="I221" t="n">
         <v>29.26144</v>
       </c>
-      <c r="J221" s="1" t="n">
+      <c r="J221" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K221" t="n">
@@ -10619,7 +10631,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B222" t="n">
@@ -10646,7 +10658,7 @@
       <c r="I222" t="n">
         <v>29.34799999999999</v>
       </c>
-      <c r="J222" s="1" t="n">
+      <c r="J222" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K222" t="n">
@@ -10666,7 +10678,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B223" t="n">
@@ -10693,7 +10705,7 @@
       <c r="I223" t="n">
         <v>28.16202999999999</v>
       </c>
-      <c r="J223" s="1" t="n">
+      <c r="J223" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K223" t="n">
@@ -10713,7 +10725,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B224" t="n">
@@ -10740,7 +10752,7 @@
       <c r="I224" t="n">
         <v>26.99909999999999</v>
       </c>
-      <c r="J224" s="1" t="n">
+      <c r="J224" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K224" t="n">
@@ -10760,7 +10772,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B225" t="n">
@@ -10787,7 +10799,7 @@
       <c r="I225" t="n">
         <v>26.02626999999999</v>
       </c>
-      <c r="J225" s="1" t="n">
+      <c r="J225" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K225" t="n">
@@ -10821,27 +10833,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>gsyh_tl</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>usd_ort</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gsyh_usd</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
@@ -10858,7 +10870,7 @@
         <v>188.4470651431746</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>39538</v>
       </c>
     </row>
@@ -10873,7 +10885,7 @@
         <v>202.1165869692412</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>39629</v>
       </c>
     </row>
@@ -10888,7 +10900,7 @@
         <v>224.7668336608458</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>39721</v>
       </c>
     </row>
@@ -10905,7 +10917,7 @@
       <c r="D5" t="n">
         <v>784.2271960468236</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>39813</v>
       </c>
     </row>
@@ -10922,7 +10934,7 @@
       <c r="D6" t="n">
         <v>726.5630108224932</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>39903</v>
       </c>
     </row>
@@ -10939,7 +10951,7 @@
       <c r="D7" t="n">
         <v>680.8887296765091</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>39994</v>
       </c>
     </row>
@@ -10956,7 +10968,7 @@
       <c r="D8" t="n">
         <v>640.0868793971713</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>40086</v>
       </c>
     </row>
@@ -10973,7 +10985,7 @@
       <c r="D9" t="n">
         <v>658.9902820733863</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>40178</v>
       </c>
     </row>
@@ -10990,7 +11002,7 @@
       <c r="D10" t="n">
         <v>691.5463082981535</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>40268</v>
       </c>
     </row>
@@ -11007,7 +11019,7 @@
       <c r="D11" t="n">
         <v>719.6885900927989</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>40359</v>
       </c>
     </row>
@@ -11024,7 +11036,7 @@
       <c r="D12" t="n">
         <v>749.0397936010979</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>40451</v>
       </c>
     </row>
@@ -11041,7 +11053,7 @@
       <c r="D13" t="n">
         <v>784.9655005365125</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>40543</v>
       </c>
     </row>
@@ -11058,7 +11070,7 @@
       <c r="D14" t="n">
         <v>810.3253924162482</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>40633</v>
       </c>
     </row>
@@ -11075,7 +11087,7 @@
       <c r="D15" t="n">
         <v>844.646504931485</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>40724</v>
       </c>
     </row>
@@ -11092,7 +11104,7 @@
       <c r="D16" t="n">
         <v>854.9653194859255</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>40816</v>
       </c>
     </row>
@@ -11109,7 +11121,7 @@
       <c r="D17" t="n">
         <v>844.5068243568147</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>40908</v>
       </c>
     </row>
@@ -11126,7 +11138,7 @@
       <c r="D18" t="n">
         <v>845.4079140024489</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>40999</v>
       </c>
     </row>
@@ -11143,7 +11155,7 @@
       <c r="D19" t="n">
         <v>841.945669848762</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>41090</v>
       </c>
     </row>
@@ -11160,7 +11172,7 @@
       <c r="D20" t="n">
         <v>857.1420802056064</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>41182</v>
       </c>
     </row>
@@ -11177,7 +11189,7 @@
       <c r="D21" t="n">
         <v>887.0698297363689</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>41274</v>
       </c>
     </row>
@@ -11194,7 +11206,7 @@
       <c r="D22" t="n">
         <v>918.0892150612981</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>41364</v>
       </c>
     </row>
@@ -11211,7 +11223,7 @@
       <c r="D23" t="n">
         <v>946.0043097899548</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>41455</v>
       </c>
     </row>
@@ -11228,7 +11240,7 @@
       <c r="D24" t="n">
         <v>959.0932141449902</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>41547</v>
       </c>
     </row>
@@ -11245,7 +11257,7 @@
       <c r="D25" t="n">
         <v>961.0481078717496</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>41639</v>
       </c>
     </row>
@@ -11262,7 +11274,7 @@
       <c r="D26" t="n">
         <v>947.2834628100968</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>41729</v>
       </c>
     </row>
@@ -11279,7 +11291,7 @@
       <c r="D27" t="n">
         <v>937.1937031513314</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -11296,7 +11308,7 @@
       <c r="D28" t="n">
         <v>940.6297640777781</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>41912</v>
       </c>
     </row>
@@ -11313,7 +11325,7 @@
       <c r="D29" t="n">
         <v>942.8967695699519</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>42004</v>
       </c>
     </row>
@@ -11330,7 +11342,7 @@
       <c r="D30" t="n">
         <v>940.1806740814401</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>42094</v>
       </c>
     </row>
@@ -11347,7 +11359,7 @@
       <c r="D31" t="n">
         <v>919.6371330818704</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>42185</v>
       </c>
     </row>
@@ -11364,7 +11376,7 @@
       <c r="D32" t="n">
         <v>887.3628039410262</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>42277</v>
       </c>
     </row>
@@ -11381,7 +11393,7 @@
       <c r="D33" t="n">
         <v>863.921366521658</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="2" t="n">
         <v>42369</v>
       </c>
     </row>
@@ -11398,7 +11410,7 @@
       <c r="D34" t="n">
         <v>853.7046932188318</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="2" t="n">
         <v>42460</v>
       </c>
     </row>
@@ -11415,7 +11427,7 @@
       <c r="D35" t="n">
         <v>861.4305877129513</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="2" t="n">
         <v>42551</v>
       </c>
     </row>
@@ -11432,7 +11444,7 @@
       <c r="D36" t="n">
         <v>864.6856666920855</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>42643</v>
       </c>
     </row>
@@ -11449,7 +11461,7 @@
       <c r="D37" t="n">
         <v>869.9030222927099</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>42735</v>
       </c>
     </row>
@@ -11466,7 +11478,7 @@
       <c r="D38" t="n">
         <v>855.0244018960104</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -11483,7 +11495,7 @@
       <c r="D39" t="n">
         <v>842.4624338405587</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -11500,7 +11512,7 @@
       <c r="D40" t="n">
         <v>856.2791919679362</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>43008</v>
       </c>
     </row>
@@ -11517,7 +11529,7 @@
       <c r="D41" t="n">
         <v>864.8788502660077</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>43100</v>
       </c>
     </row>
@@ -11534,7 +11546,7 @@
       <c r="D42" t="n">
         <v>898.2531105139536</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>43190</v>
       </c>
     </row>
@@ -11551,7 +11563,7 @@
       <c r="D43" t="n">
         <v>898.9553869128588</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>43281</v>
       </c>
     </row>
@@ -11568,7 +11580,7 @@
       <c r="D44" t="n">
         <v>846.4394557072657</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>43373</v>
       </c>
     </row>
@@ -11585,7 +11597,7 @@
       <c r="D45" t="n">
         <v>797.3238057726485</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>43465</v>
       </c>
     </row>
@@ -11602,7 +11614,7 @@
       <c r="D46" t="n">
         <v>761.796683470352</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -11619,7 +11631,7 @@
       <c r="D47" t="n">
         <v>732.283041957087</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>43646</v>
       </c>
     </row>
@@ -11636,7 +11648,7 @@
       <c r="D48" t="n">
         <v>752.4178296031997</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -11653,7 +11665,7 @@
       <c r="D49" t="n">
         <v>775.2901707093772</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>43830</v>
       </c>
     </row>
@@ -11670,7 +11682,7 @@
       <c r="D50" t="n">
         <v>778.2260275513438</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -11687,7 +11699,7 @@
       <c r="D51" t="n">
         <v>754.0085363267242</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>44012</v>
       </c>
     </row>
@@ -11704,7 +11716,7 @@
       <c r="D52" t="n">
         <v>746.091416266087</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>44104</v>
       </c>
     </row>
@@ -11721,7 +11733,7 @@
       <c r="D53" t="n">
         <v>730.9546871917802</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>44196</v>
       </c>
     </row>
@@ -11738,7 +11750,7 @@
       <c r="D54" t="n">
         <v>746.2494624509136</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -11755,7 +11767,7 @@
       <c r="D55" t="n">
         <v>786.5387429577326</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>44377</v>
       </c>
     </row>
@@ -11772,7 +11784,7 @@
       <c r="D56" t="n">
         <v>818.3449224201991</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>44469</v>
       </c>
     </row>
@@ -11789,7 +11801,7 @@
       <c r="D57" t="n">
         <v>835.6602257809595</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>44561</v>
       </c>
     </row>
@@ -11806,7 +11818,7 @@
       <c r="D58" t="n">
         <v>826.4811453112486</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -11823,7 +11835,7 @@
       <c r="D59" t="n">
         <v>853.2410029660408</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>44742</v>
       </c>
     </row>
@@ -11840,7 +11852,7 @@
       <c r="D60" t="n">
         <v>864.3854149792769</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>44834</v>
       </c>
     </row>
@@ -11857,7 +11869,7 @@
       <c r="D61" t="n">
         <v>913.1863831015423</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="2" t="n">
         <v>44926</v>
       </c>
     </row>
@@ -11874,7 +11886,7 @@
       <c r="D62" t="n">
         <v>981.7702030343168</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11891,7 +11903,7 @@
       <c r="D63" t="n">
         <v>1035.745849934734</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>45107</v>
       </c>
     </row>
@@ -11908,7 +11920,7 @@
       <c r="D64" t="n">
         <v>1087.793792245752</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>45199</v>
       </c>
     </row>
@@ -11925,7 +11937,7 @@
       <c r="D65" t="n">
         <v>1131.01603472582</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -11942,7 +11954,7 @@
       <c r="D66" t="n">
         <v>1171.104959658617</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>45382</v>
       </c>
     </row>
@@ -11959,7 +11971,7 @@
       <c r="D67" t="n">
         <v>1209.872581317634</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -11976,7 +11988,7 @@
       <c r="D68" t="n">
         <v>1283.797451942341</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>45565</v>
       </c>
     </row>
@@ -11993,7 +12005,7 @@
       <c r="D69" t="n">
         <v>1357.572675785335</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="2" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -12010,7 +12022,7 @@
       <c r="D70" t="n">
         <v>1410.676074962415</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="2" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -12027,7 +12039,7 @@
       <c r="D71" t="n">
         <v>1473.820957975585</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -12044,7 +12056,7 @@
       <c r="D72" t="n">
         <v>1536.009359448403</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="2" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -12061,7 +12073,7 @@
       <c r="D73" t="n">
         <v>1595.814722617371</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -12078,7 +12090,7 @@
       <c r="D74" t="n">
         <v>1640.339363149401</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="2" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -12095,7 +12107,7 @@
       <c r="D75" t="n">
         <v>1700.354635555628</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="2" t="n">
         <v>46203</v>
       </c>
     </row>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,84 +422,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cari</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>enerji</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cari_12</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>altin_12</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enerji_12</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>diger_12</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>gsyh_tarih</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cari_gsyh</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>altin_gsyh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>enerji_gsyh</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>diger_gsyh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B2" t="n">
@@ -538,7 +526,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B3" t="n">
@@ -565,7 +553,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B4" t="n">
@@ -592,7 +580,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B5" t="n">
@@ -619,7 +607,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B6" t="n">
@@ -646,7 +634,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B7" t="n">
@@ -673,7 +661,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B8" t="n">
@@ -700,7 +688,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B9" t="n">
@@ -727,7 +715,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B10" t="n">
@@ -754,7 +742,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B11" t="n">
@@ -781,7 +769,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B12" t="n">
@@ -808,7 +796,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B13" t="n">
@@ -835,7 +823,7 @@
       <c r="I13" t="n">
         <v>2.68842</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K13" t="n">
@@ -855,7 +843,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B14" t="n">
@@ -882,7 +870,7 @@
       <c r="I14" t="n">
         <v>5.004020000000001</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K14" t="n">
@@ -902,7 +890,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B15" t="n">
@@ -929,7 +917,7 @@
       <c r="I15" t="n">
         <v>6.2034</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K15" t="n">
@@ -949,7 +937,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B16" t="n">
@@ -976,7 +964,7 @@
       <c r="I16" t="n">
         <v>7.860720000000001</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K16" t="n">
@@ -996,7 +984,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B17" t="n">
@@ -1023,7 +1011,7 @@
       <c r="I17" t="n">
         <v>9.52572</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K17" t="n">
@@ -1043,7 +1031,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B18" t="n">
@@ -1070,7 +1058,7 @@
       <c r="I18" t="n">
         <v>10.32989</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K18" t="n">
@@ -1090,7 +1078,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B19" t="n">
@@ -1117,7 +1105,7 @@
       <c r="I19" t="n">
         <v>11.23285</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K19" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B20" t="n">
@@ -1164,7 +1152,7 @@
       <c r="I20" t="n">
         <v>13.00463</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K20" t="n">
@@ -1184,7 +1172,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B21" t="n">
@@ -1211,7 +1199,7 @@
       <c r="I21" t="n">
         <v>12.93374</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K21" t="n">
@@ -1231,7 +1219,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B22" t="n">
@@ -1258,7 +1246,7 @@
       <c r="I22" t="n">
         <v>10.54887</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K22" t="n">
@@ -1278,7 +1266,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1293,7 @@
       <c r="I23" t="n">
         <v>12.80883</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K23" t="n">
@@ -1325,7 +1313,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B24" t="n">
@@ -1352,7 +1340,7 @@
       <c r="I24" t="n">
         <v>11.9196</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K24" t="n">
@@ -1372,7 +1360,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B25" t="n">
@@ -1399,7 +1387,7 @@
       <c r="I25" t="n">
         <v>11.61895</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K25" t="n">
@@ -1419,7 +1407,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B26" t="n">
@@ -1446,7 +1434,7 @@
       <c r="I26" t="n">
         <v>10.08681</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K26" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B27" t="n">
@@ -1493,7 +1481,7 @@
       <c r="I27" t="n">
         <v>10.03788</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K27" t="n">
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B28" t="n">
@@ -1540,7 +1528,7 @@
       <c r="I28" t="n">
         <v>8.120710000000001</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K28" t="n">
@@ -1560,7 +1548,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B29" t="n">
@@ -1587,7 +1575,7 @@
       <c r="I29" t="n">
         <v>6.80951</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K29" t="n">
@@ -1607,7 +1595,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B30" t="n">
@@ -1634,7 +1622,7 @@
       <c r="I30" t="n">
         <v>5.458740000000001</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K30" t="n">
@@ -1654,7 +1642,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B31" t="n">
@@ -1681,7 +1669,7 @@
       <c r="I31" t="n">
         <v>4.53857</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K31" t="n">
@@ -1701,7 +1689,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B32" t="n">
@@ -1728,7 +1716,7 @@
       <c r="I32" t="n">
         <v>2.42634</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K32" t="n">
@@ -1748,7 +1736,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B33" t="n">
@@ -1775,7 +1763,7 @@
       <c r="I33" t="n">
         <v>0.1354600000000002</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K33" t="n">
@@ -1795,7 +1783,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B34" t="n">
@@ -1822,7 +1810,7 @@
       <c r="I34" t="n">
         <v>-1.641</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K34" t="n">
@@ -1842,7 +1830,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B35" t="n">
@@ -1869,7 +1857,7 @@
       <c r="I35" t="n">
         <v>-4.08595</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K35" t="n">
@@ -1889,7 +1877,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B36" t="n">
@@ -1916,7 +1904,7 @@
       <c r="I36" t="n">
         <v>-7.33985</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K36" t="n">
@@ -1936,7 +1924,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B37" t="n">
@@ -1963,7 +1951,7 @@
       <c r="I37" t="n">
         <v>-10.14424</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K37" t="n">
@@ -1983,7 +1971,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B38" t="n">
@@ -2010,7 +1998,7 @@
       <c r="I38" t="n">
         <v>-11.7397</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K38" t="n">
@@ -2030,7 +2018,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B39" t="n">
@@ -2057,7 +2045,7 @@
       <c r="I39" t="n">
         <v>-14.14707</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="J39" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K39" t="n">
@@ -2077,7 +2065,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B40" t="n">
@@ -2104,7 +2092,7 @@
       <c r="I40" t="n">
         <v>-18.16812</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K40" t="n">
@@ -2124,7 +2112,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B41" t="n">
@@ -2151,7 +2139,7 @@
       <c r="I41" t="n">
         <v>-20.5611</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="J41" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K41" t="n">
@@ -2171,7 +2159,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B42" t="n">
@@ -2198,7 +2186,7 @@
       <c r="I42" t="n">
         <v>-23.39756</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K42" t="n">
@@ -2218,7 +2206,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B43" t="n">
@@ -2245,7 +2233,7 @@
       <c r="I43" t="n">
         <v>-26.26857</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J43" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K43" t="n">
@@ -2265,7 +2253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B44" t="n">
@@ -2292,7 +2280,7 @@
       <c r="I44" t="n">
         <v>-26.73468</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K44" t="n">
@@ -2312,7 +2300,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B45" t="n">
@@ -2339,7 +2327,7 @@
       <c r="I45" t="n">
         <v>-25.77266</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K45" t="n">
@@ -2359,7 +2347,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B46" t="n">
@@ -2386,7 +2374,7 @@
       <c r="I46" t="n">
         <v>-25.75811</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K46" t="n">
@@ -2406,7 +2394,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B47" t="n">
@@ -2433,7 +2421,7 @@
       <c r="I47" t="n">
         <v>-25.40919</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K47" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B48" t="n">
@@ -2480,7 +2468,7 @@
       <c r="I48" t="n">
         <v>-24.01676</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K48" t="n">
@@ -2500,7 +2488,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B49" t="n">
@@ -2527,7 +2515,7 @@
       <c r="I49" t="n">
         <v>-22.04643</v>
       </c>
-      <c r="J49" s="2" t="n">
+      <c r="J49" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K49" t="n">
@@ -2547,7 +2535,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B50" t="n">
@@ -2574,7 +2562,7 @@
       <c r="I50" t="n">
         <v>-21.51568</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K50" t="n">
@@ -2594,7 +2582,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B51" t="n">
@@ -2621,7 +2609,7 @@
       <c r="I51" t="n">
         <v>-19.64396</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K51" t="n">
@@ -2641,7 +2629,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B52" t="n">
@@ -2668,7 +2656,7 @@
       <c r="I52" t="n">
         <v>-15.79015</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K52" t="n">
@@ -2688,7 +2676,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B53" t="n">
@@ -2715,7 +2703,7 @@
       <c r="I53" t="n">
         <v>-13.06127</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K53" t="n">
@@ -2735,7 +2723,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B54" t="n">
@@ -2762,7 +2750,7 @@
       <c r="I54" t="n">
         <v>-10.51409</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K54" t="n">
@@ -2782,7 +2770,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B55" t="n">
@@ -2809,7 +2797,7 @@
       <c r="I55" t="n">
         <v>-6.249130000000001</v>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K55" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B56" t="n">
@@ -2856,7 +2844,7 @@
       <c r="I56" t="n">
         <v>-4.688590000000001</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K56" t="n">
@@ -2876,7 +2864,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B57" t="n">
@@ -2903,7 +2891,7 @@
       <c r="I57" t="n">
         <v>-2.382240000000001</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K57" t="n">
@@ -2923,7 +2911,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B58" t="n">
@@ -2950,7 +2938,7 @@
       <c r="I58" t="n">
         <v>0.395989999999999</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K58" t="n">
@@ -2970,7 +2958,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B59" t="n">
@@ -2997,7 +2985,7 @@
       <c r="I59" t="n">
         <v>1.845749999999999</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K59" t="n">
@@ -3017,7 +3005,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B60" t="n">
@@ -3044,7 +3032,7 @@
       <c r="I60" t="n">
         <v>3.21682</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K60" t="n">
@@ -3064,7 +3052,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B61" t="n">
@@ -3091,7 +3079,7 @@
       <c r="I61" t="n">
         <v>4.90424</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K61" t="n">
@@ -3111,7 +3099,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B62" t="n">
@@ -3138,7 +3126,7 @@
       <c r="I62" t="n">
         <v>5.24468</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K62" t="n">
@@ -3158,7 +3146,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B63" t="n">
@@ -3185,7 +3173,7 @@
       <c r="I63" t="n">
         <v>5.49649</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K63" t="n">
@@ -3205,7 +3193,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B64" t="n">
@@ -3232,7 +3220,7 @@
       <c r="I64" t="n">
         <v>6.803089999999999</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K64" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B65" t="n">
@@ -3279,7 +3267,7 @@
       <c r="I65" t="n">
         <v>7.07182</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K65" t="n">
@@ -3299,7 +3287,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B66" t="n">
@@ -3326,7 +3314,7 @@
       <c r="I66" t="n">
         <v>8.31753</v>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K66" t="n">
@@ -3346,7 +3334,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B67" t="n">
@@ -3373,7 +3361,7 @@
       <c r="I67" t="n">
         <v>9.40043</v>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K67" t="n">
@@ -3393,7 +3381,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B68" t="n">
@@ -3420,7 +3408,7 @@
       <c r="I68" t="n">
         <v>9.15676</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K68" t="n">
@@ -3440,7 +3428,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B69" t="n">
@@ -3467,7 +3455,7 @@
       <c r="I69" t="n">
         <v>9.691610000000001</v>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K69" t="n">
@@ -3487,7 +3475,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B70" t="n">
@@ -3514,7 +3502,7 @@
       <c r="I70" t="n">
         <v>10.6274</v>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K70" t="n">
@@ -3534,7 +3522,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B71" t="n">
@@ -3561,7 +3549,7 @@
       <c r="I71" t="n">
         <v>10.15893</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K71" t="n">
@@ -3581,7 +3569,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B72" t="n">
@@ -3608,7 +3596,7 @@
       <c r="I72" t="n">
         <v>11.57857</v>
       </c>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K72" t="n">
@@ -3628,7 +3616,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B73" t="n">
@@ -3655,7 +3643,7 @@
       <c r="I73" t="n">
         <v>10.08393</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K73" t="n">
@@ -3675,7 +3663,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B74" t="n">
@@ -3702,7 +3690,7 @@
       <c r="I74" t="n">
         <v>11.61466</v>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K74" t="n">
@@ -3722,7 +3710,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B75" t="n">
@@ -3749,7 +3737,7 @@
       <c r="I75" t="n">
         <v>12.55543</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K75" t="n">
@@ -3769,7 +3757,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B76" t="n">
@@ -3796,7 +3784,7 @@
       <c r="I76" t="n">
         <v>12.95175</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K76" t="n">
@@ -3816,7 +3804,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B77" t="n">
@@ -3843,7 +3831,7 @@
       <c r="I77" t="n">
         <v>13.82609</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K77" t="n">
@@ -3863,7 +3851,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B78" t="n">
@@ -3890,7 +3878,7 @@
       <c r="I78" t="n">
         <v>15.83389</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K78" t="n">
@@ -3910,7 +3898,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B79" t="n">
@@ -3937,7 +3925,7 @@
       <c r="I79" t="n">
         <v>15.8046</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K79" t="n">
@@ -3957,7 +3945,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B80" t="n">
@@ -3984,7 +3972,7 @@
       <c r="I80" t="n">
         <v>18.19608</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K80" t="n">
@@ -4004,7 +3992,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B81" t="n">
@@ -4031,7 +4019,7 @@
       <c r="I81" t="n">
         <v>18.488</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K81" t="n">
@@ -4051,7 +4039,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B82" t="n">
@@ -4078,7 +4066,7 @@
       <c r="I82" t="n">
         <v>19.80297</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K82" t="n">
@@ -4098,7 +4086,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B83" t="n">
@@ -4125,7 +4113,7 @@
       <c r="I83" t="n">
         <v>20.59569</v>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J83" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K83" t="n">
@@ -4145,7 +4133,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B84" t="n">
@@ -4172,7 +4160,7 @@
       <c r="I84" t="n">
         <v>19.85103</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K84" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B85" t="n">
@@ -4219,7 +4207,7 @@
       <c r="I85" t="n">
         <v>20.46028</v>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="J85" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K85" t="n">
@@ -4239,7 +4227,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B86" t="n">
@@ -4266,7 +4254,7 @@
       <c r="I86" t="n">
         <v>20.80432</v>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K86" t="n">
@@ -4286,7 +4274,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B87" t="n">
@@ -4313,7 +4301,7 @@
       <c r="I87" t="n">
         <v>18.98794</v>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K87" t="n">
@@ -4333,7 +4321,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B88" t="n">
@@ -4360,7 +4348,7 @@
       <c r="I88" t="n">
         <v>17.46199</v>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K88" t="n">
@@ -4380,7 +4368,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4395,7 @@
       <c r="I89" t="n">
         <v>15.2882</v>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J89" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K89" t="n">
@@ -4427,7 +4415,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B90" t="n">
@@ -4454,7 +4442,7 @@
       <c r="I90" t="n">
         <v>12.95619</v>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K90" t="n">
@@ -4474,7 +4462,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B91" t="n">
@@ -4501,7 +4489,7 @@
       <c r="I91" t="n">
         <v>11.8918</v>
       </c>
-      <c r="J91" s="2" t="n">
+      <c r="J91" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K91" t="n">
@@ -4521,7 +4509,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B92" t="n">
@@ -4548,7 +4536,7 @@
       <c r="I92" t="n">
         <v>10.00618</v>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K92" t="n">
@@ -4568,7 +4556,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B93" t="n">
@@ -4595,7 +4583,7 @@
       <c r="I93" t="n">
         <v>10.69088</v>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K93" t="n">
@@ -4615,7 +4603,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B94" t="n">
@@ -4642,7 +4630,7 @@
       <c r="I94" t="n">
         <v>9.682169999999999</v>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K94" t="n">
@@ -4662,7 +4650,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B95" t="n">
@@ -4689,7 +4677,7 @@
       <c r="I95" t="n">
         <v>9.299630000000001</v>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J95" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K95" t="n">
@@ -4709,7 +4697,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B96" t="n">
@@ -4736,7 +4724,7 @@
       <c r="I96" t="n">
         <v>9.04907</v>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K96" t="n">
@@ -4756,7 +4744,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B97" t="n">
@@ -4783,7 +4771,7 @@
       <c r="I97" t="n">
         <v>8.198219999999999</v>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K97" t="n">
@@ -4803,7 +4791,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B98" t="n">
@@ -4830,7 +4818,7 @@
       <c r="I98" t="n">
         <v>7.736389999999999</v>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K98" t="n">
@@ -4850,7 +4838,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B99" t="n">
@@ -4877,7 +4865,7 @@
       <c r="I99" t="n">
         <v>7.899969999999999</v>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J99" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K99" t="n">
@@ -4897,7 +4885,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B100" t="n">
@@ -4924,7 +4912,7 @@
       <c r="I100" t="n">
         <v>7.502359999999999</v>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K100" t="n">
@@ -4944,7 +4932,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B101" t="n">
@@ -4971,7 +4959,7 @@
       <c r="I101" t="n">
         <v>8.811169999999999</v>
       </c>
-      <c r="J101" s="2" t="n">
+      <c r="J101" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K101" t="n">
@@ -4991,7 +4979,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B102" t="n">
@@ -5018,7 +5006,7 @@
       <c r="I102" t="n">
         <v>7.943439999999999</v>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K102" t="n">
@@ -5038,7 +5026,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B103" t="n">
@@ -5065,7 +5053,7 @@
       <c r="I103" t="n">
         <v>4.534299999999999</v>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J103" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K103" t="n">
@@ -5085,7 +5073,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B104" t="n">
@@ -5112,7 +5100,7 @@
       <c r="I104" t="n">
         <v>2.886419999999999</v>
       </c>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K104" t="n">
@@ -5132,7 +5120,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B105" t="n">
@@ -5159,7 +5147,7 @@
       <c r="I105" t="n">
         <v>0.2952499999999989</v>
       </c>
-      <c r="J105" s="2" t="n">
+      <c r="J105" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K105" t="n">
@@ -5179,7 +5167,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B106" t="n">
@@ -5206,7 +5194,7 @@
       <c r="I106" t="n">
         <v>-1.300060000000001</v>
       </c>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K106" t="n">
@@ -5226,7 +5214,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B107" t="n">
@@ -5253,7 +5241,7 @@
       <c r="I107" t="n">
         <v>-1.551580000000001</v>
       </c>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K107" t="n">
@@ -5273,7 +5261,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B108" t="n">
@@ -5300,7 +5288,7 @@
       <c r="I108" t="n">
         <v>-1.618070000000001</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K108" t="n">
@@ -5320,7 +5308,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B109" t="n">
@@ -5347,7 +5335,7 @@
       <c r="I109" t="n">
         <v>0.1297299999999989</v>
       </c>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K109" t="n">
@@ -5367,7 +5355,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B110" t="n">
@@ -5394,7 +5382,7 @@
       <c r="I110" t="n">
         <v>0.3622699999999989</v>
       </c>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K110" t="n">
@@ -5414,7 +5402,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B111" t="n">
@@ -5441,7 +5429,7 @@
       <c r="I111" t="n">
         <v>2.062249999999999</v>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K111" t="n">
@@ -5461,7 +5449,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B112" t="n">
@@ -5488,7 +5476,7 @@
       <c r="I112" t="n">
         <v>4.506739999999999</v>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K112" t="n">
@@ -5508,7 +5496,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B113" t="n">
@@ -5535,7 +5523,7 @@
       <c r="I113" t="n">
         <v>4.95311</v>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K113" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B114" t="n">
@@ -5582,7 +5570,7 @@
       <c r="I114" t="n">
         <v>5.905279999999999</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K114" t="n">
@@ -5602,7 +5590,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B115" t="n">
@@ -5629,7 +5617,7 @@
       <c r="I115" t="n">
         <v>8.84371</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K115" t="n">
@@ -5649,7 +5637,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B116" t="n">
@@ -5676,7 +5664,7 @@
       <c r="I116" t="n">
         <v>9.860910000000001</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K116" t="n">
@@ -5696,7 +5684,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B117" t="n">
@@ -5723,7 +5711,7 @@
       <c r="I117" t="n">
         <v>12.08097</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K117" t="n">
@@ -5743,7 +5731,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B118" t="n">
@@ -5770,7 +5758,7 @@
       <c r="I118" t="n">
         <v>10.99841</v>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K118" t="n">
@@ -5790,7 +5778,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B119" t="n">
@@ -5817,7 +5805,7 @@
       <c r="I119" t="n">
         <v>9.6854</v>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J119" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K119" t="n">
@@ -5837,7 +5825,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B120" t="n">
@@ -5864,7 +5852,7 @@
       <c r="I120" t="n">
         <v>9.236190000000001</v>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J120" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K120" t="n">
@@ -5884,7 +5872,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B121" t="n">
@@ -5911,7 +5899,7 @@
       <c r="I121" t="n">
         <v>7.685680000000001</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J121" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K121" t="n">
@@ -5931,7 +5919,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B122" t="n">
@@ -5958,7 +5946,7 @@
       <c r="I122" t="n">
         <v>5.95812</v>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J122" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K122" t="n">
@@ -5978,7 +5966,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B123" t="n">
@@ -6005,7 +5993,7 @@
       <c r="I123" t="n">
         <v>4.993270000000001</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J123" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K123" t="n">
@@ -6025,7 +6013,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B124" t="n">
@@ -6052,7 +6040,7 @@
       <c r="I124" t="n">
         <v>4.364470000000001</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J124" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K124" t="n">
@@ -6072,7 +6060,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B125" t="n">
@@ -6099,7 +6087,7 @@
       <c r="I125" t="n">
         <v>3.48327</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J125" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K125" t="n">
@@ -6119,7 +6107,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B126" t="n">
@@ -6146,7 +6134,7 @@
       <c r="I126" t="n">
         <v>3.21001</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J126" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K126" t="n">
@@ -6166,7 +6154,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B127" t="n">
@@ -6193,7 +6181,7 @@
       <c r="I127" t="n">
         <v>3.74216</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J127" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K127" t="n">
@@ -6213,7 +6201,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B128" t="n">
@@ -6240,7 +6228,7 @@
       <c r="I128" t="n">
         <v>6.06072</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J128" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K128" t="n">
@@ -6260,7 +6248,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B129" t="n">
@@ -6287,7 +6275,7 @@
       <c r="I129" t="n">
         <v>7.804049999999999</v>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J129" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K129" t="n">
@@ -6307,7 +6295,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B130" t="n">
@@ -6334,7 +6322,7 @@
       <c r="I130" t="n">
         <v>14.08367</v>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J130" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K130" t="n">
@@ -6354,7 +6342,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B131" t="n">
@@ -6381,7 +6369,7 @@
       <c r="I131" t="n">
         <v>20.77072</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J131" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K131" t="n">
@@ -6401,7 +6389,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B132" t="n">
@@ -6428,7 +6416,7 @@
       <c r="I132" t="n">
         <v>26.56942</v>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J132" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K132" t="n">
@@ -6448,7 +6436,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B133" t="n">
@@ -6475,7 +6463,7 @@
       <c r="I133" t="n">
         <v>31.91968</v>
       </c>
-      <c r="J133" s="2" t="n">
+      <c r="J133" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K133" t="n">
@@ -6495,7 +6483,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B134" t="n">
@@ -6522,7 +6510,7 @@
       <c r="I134" t="n">
         <v>36.77216</v>
       </c>
-      <c r="J134" s="2" t="n">
+      <c r="J134" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K134" t="n">
@@ -6542,7 +6530,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B135" t="n">
@@ -6569,7 +6557,7 @@
       <c r="I135" t="n">
         <v>40.31249</v>
       </c>
-      <c r="J135" s="2" t="n">
+      <c r="J135" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K135" t="n">
@@ -6589,7 +6577,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B136" t="n">
@@ -6616,7 +6604,7 @@
       <c r="I136" t="n">
         <v>44.4252</v>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J136" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K136" t="n">
@@ -6636,7 +6624,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B137" t="n">
@@ -6663,7 +6651,7 @@
       <c r="I137" t="n">
         <v>48.80586</v>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J137" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K137" t="n">
@@ -6683,7 +6671,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B138" t="n">
@@ -6710,7 +6698,7 @@
       <c r="I138" t="n">
         <v>53.917</v>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="J138" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K138" t="n">
@@ -6730,7 +6718,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B139" t="n">
@@ -6757,7 +6745,7 @@
       <c r="I139" t="n">
         <v>56.12547</v>
       </c>
-      <c r="J139" s="2" t="n">
+      <c r="J139" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K139" t="n">
@@ -6777,7 +6765,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B140" t="n">
@@ -6804,7 +6792,7 @@
       <c r="I140" t="n">
         <v>59.44548</v>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="J140" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K140" t="n">
@@ -6824,7 +6812,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B141" t="n">
@@ -6851,7 +6839,7 @@
       <c r="I141" t="n">
         <v>60.96964</v>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="J141" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K141" t="n">
@@ -6871,7 +6859,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B142" t="n">
@@ -6898,7 +6886,7 @@
       <c r="I142" t="n">
         <v>61.12259999999999</v>
       </c>
-      <c r="J142" s="2" t="n">
+      <c r="J142" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K142" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B143" t="n">
@@ -6945,7 +6933,7 @@
       <c r="I143" t="n">
         <v>60.94875</v>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J143" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K143" t="n">
@@ -6965,7 +6953,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B144" t="n">
@@ -6992,7 +6980,7 @@
       <c r="I144" t="n">
         <v>59.31162999999999</v>
       </c>
-      <c r="J144" s="2" t="n">
+      <c r="J144" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K144" t="n">
@@ -7012,7 +7000,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B145" t="n">
@@ -7039,7 +7027,7 @@
       <c r="I145" t="n">
         <v>57.56779</v>
       </c>
-      <c r="J145" s="2" t="n">
+      <c r="J145" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K145" t="n">
@@ -7059,7 +7047,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B146" t="n">
@@ -7086,7 +7074,7 @@
       <c r="I146" t="n">
         <v>57.90269</v>
       </c>
-      <c r="J146" s="2" t="n">
+      <c r="J146" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K146" t="n">
@@ -7106,7 +7094,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B147" t="n">
@@ -7133,7 +7121,7 @@
       <c r="I147" t="n">
         <v>57.78574999999999</v>
       </c>
-      <c r="J147" s="2" t="n">
+      <c r="J147" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K147" t="n">
@@ -7153,7 +7141,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B148" t="n">
@@ -7180,7 +7168,7 @@
       <c r="I148" t="n">
         <v>52.78822</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J148" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K148" t="n">
@@ -7200,7 +7188,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B149" t="n">
@@ -7227,7 +7215,7 @@
       <c r="I149" t="n">
         <v>46.00505</v>
       </c>
-      <c r="J149" s="2" t="n">
+      <c r="J149" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K149" t="n">
@@ -7247,7 +7235,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B150" t="n">
@@ -7274,7 +7262,7 @@
       <c r="I150" t="n">
         <v>39.39304</v>
       </c>
-      <c r="J150" s="2" t="n">
+      <c r="J150" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K150" t="n">
@@ -7294,7 +7282,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B151" t="n">
@@ -7321,7 +7309,7 @@
       <c r="I151" t="n">
         <v>37.28101</v>
       </c>
-      <c r="J151" s="2" t="n">
+      <c r="J151" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K151" t="n">
@@ -7341,7 +7329,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B152" t="n">
@@ -7368,7 +7356,7 @@
       <c r="I152" t="n">
         <v>32.8163</v>
       </c>
-      <c r="J152" s="2" t="n">
+      <c r="J152" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K152" t="n">
@@ -7388,7 +7376,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B153" t="n">
@@ -7415,7 +7403,7 @@
       <c r="I153" t="n">
         <v>26.95827</v>
       </c>
-      <c r="J153" s="2" t="n">
+      <c r="J153" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K153" t="n">
@@ -7435,7 +7423,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B154" t="n">
@@ -7462,7 +7450,7 @@
       <c r="I154" t="n">
         <v>23.34406</v>
       </c>
-      <c r="J154" s="2" t="n">
+      <c r="J154" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K154" t="n">
@@ -7482,7 +7470,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B155" t="n">
@@ -7509,7 +7497,7 @@
       <c r="I155" t="n">
         <v>19.61043</v>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J155" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K155" t="n">
@@ -7529,7 +7517,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B156" t="n">
@@ -7556,7 +7544,7 @@
       <c r="I156" t="n">
         <v>16.41961</v>
       </c>
-      <c r="J156" s="2" t="n">
+      <c r="J156" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K156" t="n">
@@ -7576,7 +7564,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B157" t="n">
@@ -7603,7 +7591,7 @@
       <c r="I157" t="n">
         <v>15.58579</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J157" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K157" t="n">
@@ -7623,7 +7611,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B158" t="n">
@@ -7650,7 +7638,7 @@
       <c r="I158" t="n">
         <v>13.06948</v>
       </c>
-      <c r="J158" s="2" t="n">
+      <c r="J158" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K158" t="n">
@@ -7670,7 +7658,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B159" t="n">
@@ -7697,7 +7685,7 @@
       <c r="I159" t="n">
         <v>10.72014</v>
       </c>
-      <c r="J159" s="2" t="n">
+      <c r="J159" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K159" t="n">
@@ -7717,7 +7705,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B160" t="n">
@@ -7744,7 +7732,7 @@
       <c r="I160" t="n">
         <v>11.85764</v>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="J160" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K160" t="n">
@@ -7764,7 +7752,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B161" t="n">
@@ -7791,7 +7779,7 @@
       <c r="I161" t="n">
         <v>16.75192</v>
       </c>
-      <c r="J161" s="2" t="n">
+      <c r="J161" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K161" t="n">
@@ -7811,7 +7799,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B162" t="n">
@@ -7838,7 +7826,7 @@
       <c r="I162" t="n">
         <v>17.78087</v>
       </c>
-      <c r="J162" s="2" t="n">
+      <c r="J162" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K162" t="n">
@@ -7858,7 +7846,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B163" t="n">
@@ -7885,7 +7873,7 @@
       <c r="I163" t="n">
         <v>19.18315</v>
       </c>
-      <c r="J163" s="2" t="n">
+      <c r="J163" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K163" t="n">
@@ -7905,7 +7893,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B164" t="n">
@@ -7932,7 +7920,7 @@
       <c r="I164" t="n">
         <v>21.03445</v>
       </c>
-      <c r="J164" s="2" t="n">
+      <c r="J164" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K164" t="n">
@@ -7952,7 +7940,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B165" t="n">
@@ -7979,7 +7967,7 @@
       <c r="I165" t="n">
         <v>25.49619</v>
       </c>
-      <c r="J165" s="2" t="n">
+      <c r="J165" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K165" t="n">
@@ -7999,7 +7987,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B166" t="n">
@@ -8026,7 +8014,7 @@
       <c r="I166" t="n">
         <v>28.66052</v>
       </c>
-      <c r="J166" s="2" t="n">
+      <c r="J166" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K166" t="n">
@@ -8046,7 +8034,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B167" t="n">
@@ -8073,7 +8061,7 @@
       <c r="I167" t="n">
         <v>33.67982</v>
       </c>
-      <c r="J167" s="2" t="n">
+      <c r="J167" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K167" t="n">
@@ -8093,7 +8081,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B168" t="n">
@@ -8120,7 +8108,7 @@
       <c r="I168" t="n">
         <v>35.21025</v>
       </c>
-      <c r="J168" s="2" t="n">
+      <c r="J168" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K168" t="n">
@@ -8140,7 +8128,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B169" t="n">
@@ -8167,7 +8155,7 @@
       <c r="I169" t="n">
         <v>37.12937</v>
       </c>
-      <c r="J169" s="2" t="n">
+      <c r="J169" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K169" t="n">
@@ -8187,7 +8175,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B170" t="n">
@@ -8214,7 +8202,7 @@
       <c r="I170" t="n">
         <v>37.22411</v>
       </c>
-      <c r="J170" s="2" t="n">
+      <c r="J170" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K170" t="n">
@@ -8234,7 +8222,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B171" t="n">
@@ -8261,7 +8249,7 @@
       <c r="I171" t="n">
         <v>38.29664</v>
       </c>
-      <c r="J171" s="2" t="n">
+      <c r="J171" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K171" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B172" t="n">
@@ -8308,7 +8296,7 @@
       <c r="I172" t="n">
         <v>40.84047</v>
       </c>
-      <c r="J172" s="2" t="n">
+      <c r="J172" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K172" t="n">
@@ -8328,7 +8316,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B173" t="n">
@@ -8355,7 +8343,7 @@
       <c r="I173" t="n">
         <v>43.37856</v>
       </c>
-      <c r="J173" s="2" t="n">
+      <c r="J173" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K173" t="n">
@@ -8375,7 +8363,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B174" t="n">
@@ -8402,7 +8390,7 @@
       <c r="I174" t="n">
         <v>45.0951</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J174" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K174" t="n">
@@ -8422,7 +8410,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B175" t="n">
@@ -8449,7 +8437,7 @@
       <c r="I175" t="n">
         <v>47.7854</v>
       </c>
-      <c r="J175" s="2" t="n">
+      <c r="J175" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K175" t="n">
@@ -8469,7 +8457,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B176" t="n">
@@ -8496,7 +8484,7 @@
       <c r="I176" t="n">
         <v>48.45027</v>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="J176" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K176" t="n">
@@ -8516,7 +8504,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B177" t="n">
@@ -8543,7 +8531,7 @@
       <c r="I177" t="n">
         <v>49.68133</v>
       </c>
-      <c r="J177" s="2" t="n">
+      <c r="J177" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K177" t="n">
@@ -8563,7 +8551,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B178" t="n">
@@ -8590,7 +8578,7 @@
       <c r="I178" t="n">
         <v>50.47562</v>
       </c>
-      <c r="J178" s="2" t="n">
+      <c r="J178" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K178" t="n">
@@ -8610,7 +8598,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B179" t="n">
@@ -8637,7 +8625,7 @@
       <c r="I179" t="n">
         <v>50.11399</v>
       </c>
-      <c r="J179" s="2" t="n">
+      <c r="J179" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K179" t="n">
@@ -8657,7 +8645,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B180" t="n">
@@ -8684,7 +8672,7 @@
       <c r="I180" t="n">
         <v>52.17445</v>
       </c>
-      <c r="J180" s="2" t="n">
+      <c r="J180" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K180" t="n">
@@ -8704,7 +8692,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B181" t="n">
@@ -8731,7 +8719,7 @@
       <c r="I181" t="n">
         <v>52.84970999999999</v>
       </c>
-      <c r="J181" s="2" t="n">
+      <c r="J181" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K181" t="n">
@@ -8751,7 +8739,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B182" t="n">
@@ -8778,7 +8766,7 @@
       <c r="I182" t="n">
         <v>53.61758</v>
       </c>
-      <c r="J182" s="2" t="n">
+      <c r="J182" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K182" t="n">
@@ -8798,7 +8786,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B183" t="n">
@@ -8825,7 +8813,7 @@
       <c r="I183" t="n">
         <v>52.49454</v>
       </c>
-      <c r="J183" s="2" t="n">
+      <c r="J183" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K183" t="n">
@@ -8845,7 +8833,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B184" t="n">
@@ -8872,7 +8860,7 @@
       <c r="I184" t="n">
         <v>50.79395</v>
       </c>
-      <c r="J184" s="2" t="n">
+      <c r="J184" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K184" t="n">
@@ -8892,7 +8880,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B185" t="n">
@@ -8919,7 +8907,7 @@
       <c r="I185" t="n">
         <v>46.78892</v>
       </c>
-      <c r="J185" s="2" t="n">
+      <c r="J185" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K185" t="n">
@@ -8939,7 +8927,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B186" t="n">
@@ -8966,7 +8954,7 @@
       <c r="I186" t="n">
         <v>45.03124</v>
       </c>
-      <c r="J186" s="2" t="n">
+      <c r="J186" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K186" t="n">
@@ -8986,7 +8974,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B187" t="n">
@@ -9013,7 +9001,7 @@
       <c r="I187" t="n">
         <v>45.92217</v>
       </c>
-      <c r="J187" s="2" t="n">
+      <c r="J187" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K187" t="n">
@@ -9033,7 +9021,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B188" t="n">
@@ -9060,7 +9048,7 @@
       <c r="I188" t="n">
         <v>42.09453999999999</v>
       </c>
-      <c r="J188" s="2" t="n">
+      <c r="J188" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K188" t="n">
@@ -9080,7 +9068,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B189" t="n">
@@ -9107,7 +9095,7 @@
       <c r="I189" t="n">
         <v>41.36029</v>
       </c>
-      <c r="J189" s="2" t="n">
+      <c r="J189" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K189" t="n">
@@ -9127,7 +9115,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B190" t="n">
@@ -9154,7 +9142,7 @@
       <c r="I190" t="n">
         <v>41.33475</v>
       </c>
-      <c r="J190" s="2" t="n">
+      <c r="J190" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K190" t="n">
@@ -9174,7 +9162,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B191" t="n">
@@ -9201,7 +9189,7 @@
       <c r="I191" t="n">
         <v>38.13951</v>
       </c>
-      <c r="J191" s="2" t="n">
+      <c r="J191" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K191" t="n">
@@ -9221,7 +9209,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B192" t="n">
@@ -9248,7 +9236,7 @@
       <c r="I192" t="n">
         <v>35.59753</v>
       </c>
-      <c r="J192" s="2" t="n">
+      <c r="J192" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K192" t="n">
@@ -9268,7 +9256,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B193" t="n">
@@ -9295,7 +9283,7 @@
       <c r="I193" t="n">
         <v>36.55256</v>
       </c>
-      <c r="J193" s="2" t="n">
+      <c r="J193" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K193" t="n">
@@ -9315,7 +9303,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B194" t="n">
@@ -9342,7 +9330,7 @@
       <c r="I194" t="n">
         <v>37.88603</v>
       </c>
-      <c r="J194" s="2" t="n">
+      <c r="J194" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K194" t="n">
@@ -9362,7 +9350,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B195" t="n">
@@ -9389,7 +9377,7 @@
       <c r="I195" t="n">
         <v>39.20635</v>
       </c>
-      <c r="J195" s="2" t="n">
+      <c r="J195" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K195" t="n">
@@ -9409,7 +9397,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B196" t="n">
@@ -9436,7 +9424,7 @@
       <c r="I196" t="n">
         <v>39.57944</v>
       </c>
-      <c r="J196" s="2" t="n">
+      <c r="J196" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K196" t="n">
@@ -9456,7 +9444,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B197" t="n">
@@ -9483,7 +9471,7 @@
       <c r="I197" t="n">
         <v>39.32009</v>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="J197" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K197" t="n">
@@ -9503,7 +9491,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B198" t="n">
@@ -9530,7 +9518,7 @@
       <c r="I198" t="n">
         <v>43.90715</v>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="J198" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K198" t="n">
@@ -9550,7 +9538,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B199" t="n">
@@ -9577,7 +9565,7 @@
       <c r="I199" t="n">
         <v>42.71823</v>
       </c>
-      <c r="J199" s="2" t="n">
+      <c r="J199" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K199" t="n">
@@ -9597,7 +9585,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B200" t="n">
@@ -9624,7 +9612,7 @@
       <c r="I200" t="n">
         <v>47.2887</v>
       </c>
-      <c r="J200" s="2" t="n">
+      <c r="J200" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K200" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B201" t="n">
@@ -9671,7 +9659,7 @@
       <c r="I201" t="n">
         <v>49.28131</v>
       </c>
-      <c r="J201" s="2" t="n">
+      <c r="J201" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K201" t="n">
@@ -9691,7 +9679,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B202" t="n">
@@ -9718,7 +9706,7 @@
       <c r="I202" t="n">
         <v>48.84308</v>
       </c>
-      <c r="J202" s="2" t="n">
+      <c r="J202" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K202" t="n">
@@ -9738,7 +9726,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B203" t="n">
@@ -9765,7 +9753,7 @@
       <c r="I203" t="n">
         <v>50.89373</v>
       </c>
-      <c r="J203" s="2" t="n">
+      <c r="J203" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K203" t="n">
@@ -9785,7 +9773,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B204" t="n">
@@ -9812,7 +9800,7 @@
       <c r="I204" t="n">
         <v>51.48607</v>
       </c>
-      <c r="J204" s="2" t="n">
+      <c r="J204" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K204" t="n">
@@ -9832,7 +9820,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B205" t="n">
@@ -9859,7 +9847,7 @@
       <c r="I205" t="n">
         <v>49.10726</v>
       </c>
-      <c r="J205" s="2" t="n">
+      <c r="J205" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K205" t="n">
@@ -9879,7 +9867,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B206" t="n">
@@ -9906,7 +9894,7 @@
       <c r="I206" t="n">
         <v>47.72986</v>
       </c>
-      <c r="J206" s="2" t="n">
+      <c r="J206" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K206" t="n">
@@ -9926,7 +9914,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B207" t="n">
@@ -9953,7 +9941,7 @@
       <c r="I207" t="n">
         <v>46.85917999999999</v>
       </c>
-      <c r="J207" s="2" t="n">
+      <c r="J207" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K207" t="n">
@@ -9973,7 +9961,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B208" t="n">
@@ -10000,7 +9988,7 @@
       <c r="I208" t="n">
         <v>46.18819</v>
       </c>
-      <c r="J208" s="2" t="n">
+      <c r="J208" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K208" t="n">
@@ -10020,7 +10008,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B209" t="n">
@@ -10047,7 +10035,7 @@
       <c r="I209" t="n">
         <v>43.77743</v>
       </c>
-      <c r="J209" s="2" t="n">
+      <c r="J209" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K209" t="n">
@@ -10067,7 +10055,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B210" t="n">
@@ -10094,7 +10082,7 @@
       <c r="I210" t="n">
         <v>43.79429</v>
       </c>
-      <c r="J210" s="2" t="n">
+      <c r="J210" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K210" t="n">
@@ -10114,7 +10102,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B211" t="n">
@@ -10141,7 +10129,7 @@
       <c r="I211" t="n">
         <v>41.44814</v>
       </c>
-      <c r="J211" s="2" t="n">
+      <c r="J211" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K211" t="n">
@@ -10161,7 +10149,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B212" t="n">
@@ -10188,7 +10176,7 @@
       <c r="I212" t="n">
         <v>41.90796</v>
       </c>
-      <c r="J212" s="2" t="n">
+      <c r="J212" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K212" t="n">
@@ -10208,7 +10196,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B213" t="n">
@@ -10235,7 +10223,7 @@
       <c r="I213" t="n">
         <v>41.96055</v>
       </c>
-      <c r="J213" s="2" t="n">
+      <c r="J213" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K213" t="n">
@@ -10255,7 +10243,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B214" t="n">
@@ -10282,7 +10270,7 @@
       <c r="I214" t="n">
         <v>40.90523</v>
       </c>
-      <c r="J214" s="2" t="n">
+      <c r="J214" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K214" t="n">
@@ -10302,7 +10290,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B215" t="n">
@@ -10329,7 +10317,7 @@
       <c r="I215" t="n">
         <v>40.92907</v>
       </c>
-      <c r="J215" s="2" t="n">
+      <c r="J215" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K215" t="n">
@@ -10349,7 +10337,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B216" t="n">
@@ -10376,7 +10364,7 @@
       <c r="I216" t="n">
         <v>39.97973999999999</v>
       </c>
-      <c r="J216" s="2" t="n">
+      <c r="J216" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K216" t="n">
@@ -10396,7 +10384,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B217" t="n">
@@ -10423,7 +10411,7 @@
       <c r="I217" t="n">
         <v>37.07607</v>
       </c>
-      <c r="J217" s="2" t="n">
+      <c r="J217" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K217" t="n">
@@ -10443,7 +10431,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B218" t="n">
@@ -10470,7 +10458,7 @@
       <c r="I218" t="n">
         <v>33.66558</v>
       </c>
-      <c r="J218" s="2" t="n">
+      <c r="J218" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K218" t="n">
@@ -10490,7 +10478,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B219" t="n">
@@ -10517,7 +10505,7 @@
       <c r="I219" t="n">
         <v>30.87032999999999</v>
       </c>
-      <c r="J219" s="2" t="n">
+      <c r="J219" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K219" t="n">
@@ -10537,7 +10525,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B220" t="n">
@@ -10564,7 +10552,7 @@
       <c r="I220" t="n">
         <v>26.2946</v>
       </c>
-      <c r="J220" s="2" t="n">
+      <c r="J220" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K220" t="n">
@@ -10584,7 +10572,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B221" t="n">
@@ -10611,7 +10599,7 @@
       <c r="I221" t="n">
         <v>29.26144</v>
       </c>
-      <c r="J221" s="2" t="n">
+      <c r="J221" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K221" t="n">
@@ -10631,7 +10619,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B222" t="n">
@@ -10658,7 +10646,7 @@
       <c r="I222" t="n">
         <v>29.34799999999999</v>
       </c>
-      <c r="J222" s="2" t="n">
+      <c r="J222" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K222" t="n">
@@ -10678,7 +10666,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B223" t="n">
@@ -10705,7 +10693,7 @@
       <c r="I223" t="n">
         <v>28.16202999999999</v>
       </c>
-      <c r="J223" s="2" t="n">
+      <c r="J223" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K223" t="n">
@@ -10725,7 +10713,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B224" t="n">
@@ -10752,7 +10740,7 @@
       <c r="I224" t="n">
         <v>26.99909999999999</v>
       </c>
-      <c r="J224" s="2" t="n">
+      <c r="J224" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K224" t="n">
@@ -10772,7 +10760,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B225" t="n">
@@ -10799,7 +10787,7 @@
       <c r="I225" t="n">
         <v>26.02626999999999</v>
       </c>
-      <c r="J225" s="2" t="n">
+      <c r="J225" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K225" t="n">
@@ -10833,27 +10821,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>gsyh_tl</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>usd_ort</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gsyh_usd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
@@ -10870,7 +10858,7 @@
         <v>188.4470651431746</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>39538</v>
       </c>
     </row>
@@ -10885,7 +10873,7 @@
         <v>202.1165869692412</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>39629</v>
       </c>
     </row>
@@ -10900,7 +10888,7 @@
         <v>224.7668336608458</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>39721</v>
       </c>
     </row>
@@ -10917,7 +10905,7 @@
       <c r="D5" t="n">
         <v>784.2271960468236</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>39813</v>
       </c>
     </row>
@@ -10934,7 +10922,7 @@
       <c r="D6" t="n">
         <v>726.5630108224932</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>39903</v>
       </c>
     </row>
@@ -10951,7 +10939,7 @@
       <c r="D7" t="n">
         <v>680.8887296765091</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>39994</v>
       </c>
     </row>
@@ -10968,7 +10956,7 @@
       <c r="D8" t="n">
         <v>640.0868793971713</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>40086</v>
       </c>
     </row>
@@ -10985,7 +10973,7 @@
       <c r="D9" t="n">
         <v>658.9902820733863</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>40178</v>
       </c>
     </row>
@@ -11002,7 +10990,7 @@
       <c r="D10" t="n">
         <v>691.5463082981535</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>40268</v>
       </c>
     </row>
@@ -11019,7 +11007,7 @@
       <c r="D11" t="n">
         <v>719.6885900927989</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="1" t="n">
         <v>40359</v>
       </c>
     </row>
@@ -11036,7 +11024,7 @@
       <c r="D12" t="n">
         <v>749.0397936010979</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="1" t="n">
         <v>40451</v>
       </c>
     </row>
@@ -11053,7 +11041,7 @@
       <c r="D13" t="n">
         <v>784.9655005365125</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>40543</v>
       </c>
     </row>
@@ -11070,7 +11058,7 @@
       <c r="D14" t="n">
         <v>810.3253924162482</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="1" t="n">
         <v>40633</v>
       </c>
     </row>
@@ -11087,7 +11075,7 @@
       <c r="D15" t="n">
         <v>844.646504931485</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>40724</v>
       </c>
     </row>
@@ -11104,7 +11092,7 @@
       <c r="D16" t="n">
         <v>854.9653194859255</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="1" t="n">
         <v>40816</v>
       </c>
     </row>
@@ -11121,7 +11109,7 @@
       <c r="D17" t="n">
         <v>844.5068243568147</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="1" t="n">
         <v>40908</v>
       </c>
     </row>
@@ -11138,7 +11126,7 @@
       <c r="D18" t="n">
         <v>845.4079140024489</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>40999</v>
       </c>
     </row>
@@ -11155,7 +11143,7 @@
       <c r="D19" t="n">
         <v>841.945669848762</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="1" t="n">
         <v>41090</v>
       </c>
     </row>
@@ -11172,7 +11160,7 @@
       <c r="D20" t="n">
         <v>857.1420802056064</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="1" t="n">
         <v>41182</v>
       </c>
     </row>
@@ -11189,7 +11177,7 @@
       <c r="D21" t="n">
         <v>887.0698297363689</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="1" t="n">
         <v>41274</v>
       </c>
     </row>
@@ -11206,7 +11194,7 @@
       <c r="D22" t="n">
         <v>918.0892150612981</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="1" t="n">
         <v>41364</v>
       </c>
     </row>
@@ -11223,7 +11211,7 @@
       <c r="D23" t="n">
         <v>946.0043097899548</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="1" t="n">
         <v>41455</v>
       </c>
     </row>
@@ -11240,7 +11228,7 @@
       <c r="D24" t="n">
         <v>959.0932141449902</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="1" t="n">
         <v>41547</v>
       </c>
     </row>
@@ -11257,7 +11245,7 @@
       <c r="D25" t="n">
         <v>961.0481078717496</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="1" t="n">
         <v>41639</v>
       </c>
     </row>
@@ -11274,7 +11262,7 @@
       <c r="D26" t="n">
         <v>947.2834628100968</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="1" t="n">
         <v>41729</v>
       </c>
     </row>
@@ -11291,7 +11279,7 @@
       <c r="D27" t="n">
         <v>937.1937031513314</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="1" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -11308,7 +11296,7 @@
       <c r="D28" t="n">
         <v>940.6297640777781</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="1" t="n">
         <v>41912</v>
       </c>
     </row>
@@ -11325,7 +11313,7 @@
       <c r="D29" t="n">
         <v>942.8967695699519</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="1" t="n">
         <v>42004</v>
       </c>
     </row>
@@ -11342,7 +11330,7 @@
       <c r="D30" t="n">
         <v>940.1806740814401</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="1" t="n">
         <v>42094</v>
       </c>
     </row>
@@ -11359,7 +11347,7 @@
       <c r="D31" t="n">
         <v>919.6371330818704</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="1" t="n">
         <v>42185</v>
       </c>
     </row>
@@ -11376,7 +11364,7 @@
       <c r="D32" t="n">
         <v>887.3628039410262</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="1" t="n">
         <v>42277</v>
       </c>
     </row>
@@ -11393,7 +11381,7 @@
       <c r="D33" t="n">
         <v>863.921366521658</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="1" t="n">
         <v>42369</v>
       </c>
     </row>
@@ -11410,7 +11398,7 @@
       <c r="D34" t="n">
         <v>853.7046932188318</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="1" t="n">
         <v>42460</v>
       </c>
     </row>
@@ -11427,7 +11415,7 @@
       <c r="D35" t="n">
         <v>861.4305877129513</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="1" t="n">
         <v>42551</v>
       </c>
     </row>
@@ -11444,7 +11432,7 @@
       <c r="D36" t="n">
         <v>864.6856666920855</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="1" t="n">
         <v>42643</v>
       </c>
     </row>
@@ -11461,7 +11449,7 @@
       <c r="D37" t="n">
         <v>869.9030222927099</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="1" t="n">
         <v>42735</v>
       </c>
     </row>
@@ -11478,7 +11466,7 @@
       <c r="D38" t="n">
         <v>855.0244018960104</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="1" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -11495,7 +11483,7 @@
       <c r="D39" t="n">
         <v>842.4624338405587</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="1" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -11512,7 +11500,7 @@
       <c r="D40" t="n">
         <v>856.2791919679362</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="1" t="n">
         <v>43008</v>
       </c>
     </row>
@@ -11529,7 +11517,7 @@
       <c r="D41" t="n">
         <v>864.8788502660077</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="1" t="n">
         <v>43100</v>
       </c>
     </row>
@@ -11546,7 +11534,7 @@
       <c r="D42" t="n">
         <v>898.2531105139536</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="1" t="n">
         <v>43190</v>
       </c>
     </row>
@@ -11563,7 +11551,7 @@
       <c r="D43" t="n">
         <v>898.9553869128588</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="1" t="n">
         <v>43281</v>
       </c>
     </row>
@@ -11580,7 +11568,7 @@
       <c r="D44" t="n">
         <v>846.4394557072657</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="1" t="n">
         <v>43373</v>
       </c>
     </row>
@@ -11597,7 +11585,7 @@
       <c r="D45" t="n">
         <v>797.3238057726485</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="1" t="n">
         <v>43465</v>
       </c>
     </row>
@@ -11614,7 +11602,7 @@
       <c r="D46" t="n">
         <v>761.796683470352</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="1" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -11631,7 +11619,7 @@
       <c r="D47" t="n">
         <v>732.283041957087</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="1" t="n">
         <v>43646</v>
       </c>
     </row>
@@ -11648,7 +11636,7 @@
       <c r="D48" t="n">
         <v>752.4178296031997</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -11665,7 +11653,7 @@
       <c r="D49" t="n">
         <v>775.2901707093772</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="1" t="n">
         <v>43830</v>
       </c>
     </row>
@@ -11682,7 +11670,7 @@
       <c r="D50" t="n">
         <v>778.2260275513438</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -11699,7 +11687,7 @@
       <c r="D51" t="n">
         <v>754.0085363267242</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="1" t="n">
         <v>44012</v>
       </c>
     </row>
@@ -11716,7 +11704,7 @@
       <c r="D52" t="n">
         <v>746.091416266087</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="1" t="n">
         <v>44104</v>
       </c>
     </row>
@@ -11733,7 +11721,7 @@
       <c r="D53" t="n">
         <v>730.9546871917802</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="1" t="n">
         <v>44196</v>
       </c>
     </row>
@@ -11750,7 +11738,7 @@
       <c r="D54" t="n">
         <v>746.2494624509136</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="1" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -11767,7 +11755,7 @@
       <c r="D55" t="n">
         <v>786.5387429577326</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="1" t="n">
         <v>44377</v>
       </c>
     </row>
@@ -11784,7 +11772,7 @@
       <c r="D56" t="n">
         <v>818.3449224201991</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="1" t="n">
         <v>44469</v>
       </c>
     </row>
@@ -11801,7 +11789,7 @@
       <c r="D57" t="n">
         <v>835.6602257809595</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="1" t="n">
         <v>44561</v>
       </c>
     </row>
@@ -11818,7 +11806,7 @@
       <c r="D58" t="n">
         <v>826.4811453112486</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="1" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -11835,7 +11823,7 @@
       <c r="D59" t="n">
         <v>853.2410029660408</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="1" t="n">
         <v>44742</v>
       </c>
     </row>
@@ -11852,7 +11840,7 @@
       <c r="D60" t="n">
         <v>864.3854149792769</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="1" t="n">
         <v>44834</v>
       </c>
     </row>
@@ -11869,7 +11857,7 @@
       <c r="D61" t="n">
         <v>913.1863831015423</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="1" t="n">
         <v>44926</v>
       </c>
     </row>
@@ -11886,7 +11874,7 @@
       <c r="D62" t="n">
         <v>981.7702030343168</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="1" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11903,7 +11891,7 @@
       <c r="D63" t="n">
         <v>1035.745849934734</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="1" t="n">
         <v>45107</v>
       </c>
     </row>
@@ -11920,7 +11908,7 @@
       <c r="D64" t="n">
         <v>1087.793792245752</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="1" t="n">
         <v>45199</v>
       </c>
     </row>
@@ -11937,7 +11925,7 @@
       <c r="D65" t="n">
         <v>1131.01603472582</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="1" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -11954,7 +11942,7 @@
       <c r="D66" t="n">
         <v>1171.104959658617</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="1" t="n">
         <v>45382</v>
       </c>
     </row>
@@ -11971,7 +11959,7 @@
       <c r="D67" t="n">
         <v>1209.872581317634</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="1" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -11988,7 +11976,7 @@
       <c r="D68" t="n">
         <v>1283.797451942341</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="1" t="n">
         <v>45565</v>
       </c>
     </row>
@@ -12005,7 +11993,7 @@
       <c r="D69" t="n">
         <v>1357.572675785335</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -12022,7 +12010,7 @@
       <c r="D70" t="n">
         <v>1410.676074962415</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="1" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -12039,7 +12027,7 @@
       <c r="D71" t="n">
         <v>1473.820957975585</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="1" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -12056,7 +12044,7 @@
       <c r="D72" t="n">
         <v>1536.009359448403</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="1" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -12073,7 +12061,7 @@
       <c r="D73" t="n">
         <v>1595.814722617371</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -12090,7 +12078,7 @@
       <c r="D74" t="n">
         <v>1640.339363149401</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="1" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -12107,7 +12095,7 @@
       <c r="D75" t="n">
         <v>1700.354635555628</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="1" t="n">
         <v>46203</v>
       </c>
     </row>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -827,7 +827,7 @@
         <v>39813</v>
       </c>
       <c r="K13" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="L13" t="n">
         <v>-5.027369644758661</v>
@@ -836,10 +836,10 @@
         <v>-0.1740567028127523</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.196115386639434</v>
+        <v>-5.196115386639433</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3428113706782854</v>
+        <v>0.3428113706782853</v>
       </c>
     </row>
     <row r="14">
@@ -874,19 +874,19 @@
         <v>39813</v>
       </c>
       <c r="K14" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.554930022838334</v>
+        <v>-4.554930022838333</v>
       </c>
       <c r="M14" t="n">
         <v>-0.1109372391553806</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.082068079365663</v>
+        <v>-5.082068079365662</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6380829465267903</v>
+        <v>0.6380829465267902</v>
       </c>
     </row>
     <row r="15">
@@ -921,7 +921,7 @@
         <v>39813</v>
       </c>
       <c r="K15" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="L15" t="n">
         <v>-4.096261920261432</v>
@@ -933,7 +933,7 @@
         <v>-4.937134314542218</v>
       </c>
       <c r="O15" t="n">
-        <v>0.791020769398262</v>
+        <v>0.7910207693982618</v>
       </c>
     </row>
     <row r="16">
@@ -968,7 +968,7 @@
         <v>39903</v>
       </c>
       <c r="K16" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="L16" t="n">
         <v>-4.000066004887826</v>
@@ -977,10 +977,10 @@
         <v>0.1260730296417179</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.208038316892053</v>
+        <v>-5.208038316892054</v>
       </c>
       <c r="O16" t="n">
-        <v>1.081904787734983</v>
+        <v>1.081904787734984</v>
       </c>
     </row>
     <row r="17">
@@ -1015,16 +1015,16 @@
         <v>39903</v>
       </c>
       <c r="K17" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.500453452923375</v>
+        <v>-3.500453452923376</v>
       </c>
       <c r="M17" t="n">
         <v>0.1328171109216788</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.944332351757517</v>
+        <v>-4.944332351757518</v>
       </c>
       <c r="O17" t="n">
         <v>1.311065916941818</v>
@@ -1062,16 +1062,16 @@
         <v>39903</v>
       </c>
       <c r="K18" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.060023655048378</v>
+        <v>-3.060023655048379</v>
       </c>
       <c r="M18" t="n">
         <v>0.2153976980232408</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.697165901876305</v>
+        <v>-4.697165901876306</v>
       </c>
       <c r="O18" t="n">
         <v>1.421747301490923</v>
@@ -1109,7 +1109,7 @@
         <v>39994</v>
       </c>
       <c r="K19" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="L19" t="n">
         <v>-2.77358093575323</v>
@@ -1118,7 +1118,7 @@
         <v>0.3170855832825641</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.740398628030568</v>
+        <v>-4.740398628030569</v>
       </c>
       <c r="O19" t="n">
         <v>1.649733577663525</v>
@@ -1156,16 +1156,16 @@
         <v>39994</v>
       </c>
       <c r="K20" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="L20" t="n">
         <v>-2.256756402371413</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2974054220227847</v>
+        <v>0.2974054220227848</v>
       </c>
       <c r="N20" t="n">
-        <v>-4.464109725305776</v>
+        <v>-4.464109725305778</v>
       </c>
       <c r="O20" t="n">
         <v>1.90994936958033</v>
@@ -1203,16 +1203,16 @@
         <v>39994</v>
       </c>
       <c r="K21" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.891498484064911</v>
+        <v>-1.891498484064912</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4460346995966406</v>
+        <v>0.4460346995966407</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.237069691799207</v>
+        <v>-4.237069691799208</v>
       </c>
       <c r="O21" t="n">
         <v>1.899537976806406</v>
@@ -1391,10 +1391,10 @@
         <v>40178</v>
       </c>
       <c r="K25" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.723545901809695</v>
+        <v>-1.723545901809696</v>
       </c>
       <c r="M25" t="n">
         <v>0.4563041492112831</v>
@@ -1438,19 +1438,19 @@
         <v>40178</v>
       </c>
       <c r="K26" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.115357445961186</v>
+        <v>-2.115357445961187</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3314161163543207</v>
+        <v>0.3314161163543208</v>
       </c>
       <c r="N26" t="n">
         <v>-3.977416771235653</v>
       </c>
       <c r="O26" t="n">
-        <v>1.530646243866266</v>
+        <v>1.530646243866267</v>
       </c>
     </row>
     <row r="27">
@@ -1485,16 +1485,16 @@
         <v>40178</v>
       </c>
       <c r="K27" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="L27" t="n">
         <v>-2.398973160918249</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09757351777281512</v>
+        <v>0.09757351777281513</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.019764891927503</v>
+        <v>-4.019764891927504</v>
       </c>
       <c r="O27" t="n">
         <v>1.523221248182559</v>
@@ -1532,16 +1532,16 @@
         <v>40268</v>
       </c>
       <c r="K28" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="L28" t="n">
         <v>-2.718834555891187</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.004048897328207281</v>
+        <v>-0.004048897328207282</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.889064214106776</v>
+        <v>-3.889064214106777</v>
       </c>
       <c r="O28" t="n">
         <v>1.174282893648076</v>
@@ -1579,7 +1579,7 @@
         <v>40268</v>
       </c>
       <c r="K29" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="L29" t="n">
         <v>-3.115481890579493</v>
@@ -1588,10 +1588,10 @@
         <v>-0.01879845188096237</v>
       </c>
       <c r="N29" t="n">
-        <v>-4.081356470466659</v>
+        <v>-4.08135647046666</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9846788159071693</v>
+        <v>0.9846788159071695</v>
       </c>
     </row>
     <row r="30">
@@ -1626,7 +1626,7 @@
         <v>40268</v>
       </c>
       <c r="K30" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="L30" t="n">
         <v>-3.30274339200908</v>
@@ -1635,7 +1635,7 @@
         <v>0.08777430993649349</v>
       </c>
       <c r="N30" t="n">
-        <v>-4.179863250392423</v>
+        <v>-4.179863250392424</v>
       </c>
       <c r="O30" t="n">
         <v>0.78935277862065</v>
@@ -1673,10 +1673,10 @@
         <v>40359</v>
       </c>
       <c r="K31" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.336443057531844</v>
+        <v>-3.336443057531845</v>
       </c>
       <c r="M31" t="n">
         <v>0.1161613524944454</v>
@@ -1685,7 +1685,7 @@
         <v>-4.083225773554478</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6306297004673622</v>
+        <v>0.6306297004673623</v>
       </c>
     </row>
     <row r="32">
@@ -1720,16 +1720,16 @@
         <v>40359</v>
       </c>
       <c r="K32" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="L32" t="n">
         <v>-3.7600985165696</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06711236035265207</v>
+        <v>0.06711236035265208</v>
       </c>
       <c r="N32" t="n">
-        <v>-4.164340023250269</v>
+        <v>-4.16434002325027</v>
       </c>
       <c r="O32" t="n">
         <v>0.3371374832671921</v>
@@ -1767,16 +1767,16 @@
         <v>40359</v>
       </c>
       <c r="K33" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="L33" t="n">
         <v>-4.10469200243829</v>
       </c>
       <c r="M33" t="n">
-        <v>0.08420308565984914</v>
+        <v>0.08420308565984917</v>
       </c>
       <c r="N33" t="n">
-        <v>-4.207708780834679</v>
+        <v>-4.20770878083468</v>
       </c>
       <c r="O33" t="n">
         <v>0.01882202967571483</v>
@@ -1955,16 +1955,16 @@
         <v>40543</v>
       </c>
       <c r="K37" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.684963220612812</v>
+        <v>-5.68496322061281</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.05770954260924602</v>
+        <v>-0.057709542609246</v>
       </c>
       <c r="N37" t="n">
-        <v>-4.334926818661786</v>
+        <v>-4.334926818661785</v>
       </c>
       <c r="O37" t="n">
         <v>-1.292316667811077</v>
@@ -2002,19 +2002,19 @@
         <v>40543</v>
       </c>
       <c r="K38" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="L38" t="n">
-        <v>-6.061922462512942</v>
+        <v>-6.061922462512941</v>
       </c>
       <c r="M38" t="n">
         <v>-0.1451019183927841</v>
       </c>
       <c r="N38" t="n">
-        <v>-4.421241440073415</v>
+        <v>-4.421241440073414</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.495568912516039</v>
+        <v>-1.495568912516038</v>
       </c>
     </row>
     <row r="39">
@@ -2049,16 +2049,16 @@
         <v>40543</v>
       </c>
       <c r="K39" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.556721278173675</v>
+        <v>-6.556721278173673</v>
       </c>
       <c r="M39" t="n">
         <v>-0.1833201585313576</v>
       </c>
       <c r="N39" t="n">
-        <v>-4.571135925779577</v>
+        <v>-4.571135925779576</v>
       </c>
       <c r="O39" t="n">
         <v>-1.802253728390698</v>
@@ -2096,13 +2096,13 @@
         <v>40633</v>
       </c>
       <c r="K40" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="L40" t="n">
         <v>-7.009776631906647</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.2052261987053405</v>
+        <v>-0.2052261987053406</v>
       </c>
       <c r="N40" t="n">
         <v>-4.562462233814442</v>
@@ -2143,7 +2143,7 @@
         <v>40633</v>
       </c>
       <c r="K41" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="L41" t="n">
         <v>-7.424178060200413</v>
@@ -2152,10 +2152,10 @@
         <v>-0.2268224613472134</v>
       </c>
       <c r="N41" t="n">
-        <v>-4.659956401884912</v>
+        <v>-4.659956401884913</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.537388090318928</v>
+        <v>-2.537388090318929</v>
       </c>
     </row>
     <row r="42">
@@ -2190,19 +2190,19 @@
         <v>40633</v>
       </c>
       <c r="K42" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="L42" t="n">
-        <v>-8.038869398595661</v>
+        <v>-8.038869398595663</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.3299908931678175</v>
+        <v>-0.3299908931678176</v>
       </c>
       <c r="N42" t="n">
-        <v>-4.821439679127177</v>
+        <v>-4.821439679127178</v>
       </c>
       <c r="O42" t="n">
-        <v>-2.887427719651309</v>
+        <v>-2.88742771965131</v>
       </c>
     </row>
     <row r="43">
@@ -2378,7 +2378,7 @@
         <v>40816</v>
       </c>
       <c r="K46" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="L46" t="n">
         <v>-8.785151665001129</v>
@@ -2387,10 +2387,10 @@
         <v>-0.5844681516443967</v>
       </c>
       <c r="N46" t="n">
-        <v>-5.18790516867628</v>
+        <v>-5.187905168676281</v>
       </c>
       <c r="O46" t="n">
-        <v>-3.01276664829959</v>
+        <v>-3.012766648299591</v>
       </c>
     </row>
     <row r="47">
@@ -2425,16 +2425,16 @@
         <v>40816</v>
       </c>
       <c r="K47" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="L47" t="n">
-        <v>-8.906092243108054</v>
+        <v>-8.906092243108056</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6077439495585921</v>
+        <v>-0.6077439495585922</v>
       </c>
       <c r="N47" t="n">
-        <v>-5.326380960970623</v>
+        <v>-5.326380960970624</v>
       </c>
       <c r="O47" t="n">
         <v>-2.971955636197977</v>
@@ -2472,19 +2472,19 @@
         <v>40816</v>
       </c>
       <c r="K48" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="L48" t="n">
-        <v>-8.824685432312675</v>
+        <v>-8.824685432312677</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.5637655575197102</v>
+        <v>-0.5637655575197104</v>
       </c>
       <c r="N48" t="n">
-        <v>-5.451816458242586</v>
+        <v>-5.451816458242587</v>
       </c>
       <c r="O48" t="n">
-        <v>-2.809091720169518</v>
+        <v>-2.809091720169519</v>
       </c>
     </row>
     <row r="49">
@@ -2801,7 +2801,7 @@
         <v>41090</v>
       </c>
       <c r="K55" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="L55" t="n">
         <v>-7.087036864352339</v>
@@ -2810,10 +2810,10 @@
         <v>-0.2076143464594327</v>
       </c>
       <c r="N55" t="n">
-        <v>-6.137186976599305</v>
+        <v>-6.137186976599304</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.7422248517677544</v>
+        <v>-0.7422248517677543</v>
       </c>
     </row>
     <row r="56">
@@ -2848,10 +2848,10 @@
         <v>41090</v>
       </c>
       <c r="K56" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.792481041000283</v>
+        <v>-6.792481041000281</v>
       </c>
       <c r="M56" t="n">
         <v>-0.140389106129891</v>
@@ -2860,7 +2860,7 @@
         <v>-6.095206833146166</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.5568755999234736</v>
+        <v>-0.5568755999234735</v>
       </c>
     </row>
     <row r="57">
@@ -2895,10 +2895,10 @@
         <v>41090</v>
       </c>
       <c r="K57" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.312877647977865</v>
+        <v>-6.312877647977863</v>
       </c>
       <c r="M57" t="n">
         <v>0.1644999255413697</v>
@@ -3365,7 +3365,7 @@
         <v>41455</v>
       </c>
       <c r="K67" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="L67" t="n">
         <v>-4.563087033883022</v>
@@ -3374,7 +3374,7 @@
         <v>-0.3136349347772818</v>
       </c>
       <c r="N67" t="n">
-        <v>-5.24314524645379</v>
+        <v>-5.243145246453791</v>
       </c>
       <c r="O67" t="n">
         <v>0.9936984327362332</v>
@@ -3412,16 +3412,16 @@
         <v>41455</v>
       </c>
       <c r="K68" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="L68" t="n">
-        <v>-4.738984752612175</v>
+        <v>-4.738984752612176</v>
       </c>
       <c r="M68" t="n">
         <v>-0.4570803700630154</v>
       </c>
       <c r="N68" t="n">
-        <v>-5.249839719126335</v>
+        <v>-5.249839719126336</v>
       </c>
       <c r="O68" t="n">
         <v>0.96794062196536</v>
@@ -3459,13 +3459,13 @@
         <v>41455</v>
       </c>
       <c r="K69" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="L69" t="n">
         <v>-4.782959182294463</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6621534315621481</v>
+        <v>-0.6621534315621482</v>
       </c>
       <c r="N69" t="n">
         <v>-5.145278884702694</v>
@@ -3788,16 +3788,16 @@
         <v>41729</v>
       </c>
       <c r="K76" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="L76" t="n">
         <v>-4.738180466790009</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9309779328184005</v>
+        <v>-0.9309779328184004</v>
       </c>
       <c r="N76" t="n">
-        <v>-5.174451146290775</v>
+        <v>-5.174451146290774</v>
       </c>
       <c r="O76" t="n">
         <v>1.36725177926984</v>
@@ -3835,13 +3835,13 @@
         <v>41729</v>
       </c>
       <c r="K77" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="L77" t="n">
         <v>-4.474690170802399</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.7381106368370853</v>
+        <v>-0.7381106368370852</v>
       </c>
       <c r="N77" t="n">
         <v>-5.196128923646967</v>
@@ -3882,19 +3882,19 @@
         <v>41729</v>
       </c>
       <c r="K78" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="L78" t="n">
-        <v>-4.107323892742752</v>
+        <v>-4.107323892742751</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.6158663408620646</v>
+        <v>-0.6158663408620645</v>
       </c>
       <c r="N78" t="n">
         <v>-5.162960393599167</v>
       </c>
       <c r="O78" t="n">
-        <v>1.67150495301893</v>
+        <v>1.671504953018929</v>
       </c>
     </row>
     <row r="79">
@@ -3929,16 +3929,16 @@
         <v>41820</v>
       </c>
       <c r="K79" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="L79" t="n">
-        <v>-4.125614573592227</v>
+        <v>-4.125614573592226</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.5494061668026995</v>
+        <v>-0.5494061668026994</v>
       </c>
       <c r="N79" t="n">
-        <v>-5.262581239519495</v>
+        <v>-5.262581239519494</v>
       </c>
       <c r="O79" t="n">
         <v>1.686374966760525</v>
@@ -3976,7 +3976,7 @@
         <v>41820</v>
       </c>
       <c r="K80" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="L80" t="n">
         <v>-3.73498028020231</v>
@@ -3985,7 +3985,7 @@
         <v>-0.381244558940774</v>
       </c>
       <c r="N80" t="n">
-        <v>-5.295283123769193</v>
+        <v>-5.295283123769192</v>
       </c>
       <c r="O80" t="n">
         <v>1.941549536538214</v>
@@ -4023,7 +4023,7 @@
         <v>41820</v>
       </c>
       <c r="K81" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="L81" t="n">
         <v>-3.693366684348153</v>
@@ -4032,7 +4032,7 @@
         <v>-0.3436856211442018</v>
       </c>
       <c r="N81" t="n">
-        <v>-5.322376775716084</v>
+        <v>-5.322376775716083</v>
       </c>
       <c r="O81" t="n">
         <v>1.972697846542689</v>
@@ -4070,16 +4070,16 @@
         <v>41912</v>
       </c>
       <c r="K82" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="L82" t="n">
-        <v>-3.592380476406647</v>
+        <v>-3.592380476406646</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.4030278590766062</v>
+        <v>-0.4030278590766061</v>
       </c>
       <c r="N82" t="n">
-        <v>-5.294638964441904</v>
+        <v>-5.294638964441903</v>
       </c>
       <c r="O82" t="n">
         <v>2.105288473346942</v>
@@ -4117,7 +4117,7 @@
         <v>41912</v>
       </c>
       <c r="K83" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="L83" t="n">
         <v>-3.459809719279627</v>
@@ -4126,7 +4126,7 @@
         <v>-0.3685828508094417</v>
       </c>
       <c r="N83" t="n">
-        <v>-5.280788669142379</v>
+        <v>-5.280788669142378</v>
       </c>
       <c r="O83" t="n">
         <v>2.189563926907271</v>
@@ -4164,7 +4164,7 @@
         <v>41912</v>
       </c>
       <c r="K84" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="L84" t="n">
         <v>-3.618852103130485</v>
@@ -4211,16 +4211,16 @@
         <v>42004</v>
       </c>
       <c r="K85" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="L85" t="n">
-        <v>-3.405675046977417</v>
+        <v>-3.405675046977416</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.4133008114745576</v>
+        <v>-0.4133008114745574</v>
       </c>
       <c r="N85" t="n">
-        <v>-5.162310612454471</v>
+        <v>-5.16231061245447</v>
       </c>
       <c r="O85" t="n">
         <v>2.169938498074585</v>
@@ -4258,19 +4258,19 @@
         <v>42004</v>
       </c>
       <c r="K86" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="L86" t="n">
-        <v>-3.096203205077812</v>
+        <v>-3.096203205077811</v>
       </c>
       <c r="M86" t="n">
         <v>-0.2807306256025542</v>
       </c>
       <c r="N86" t="n">
-        <v>-5.021896513824793</v>
+        <v>-5.021896513824792</v>
       </c>
       <c r="O86" t="n">
-        <v>2.206426055472509</v>
+        <v>2.206426055472508</v>
       </c>
     </row>
     <row r="87">
@@ -4305,16 +4305,16 @@
         <v>42004</v>
       </c>
       <c r="K87" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="L87" t="n">
-        <v>-3.116565985627752</v>
+        <v>-3.116565985627751</v>
       </c>
       <c r="M87" t="n">
         <v>-0.1818862950163885</v>
       </c>
       <c r="N87" t="n">
-        <v>-4.948464297028059</v>
+        <v>-4.948464297028058</v>
       </c>
       <c r="O87" t="n">
         <v>2.013787788101157</v>
@@ -4775,10 +4775,10 @@
         <v>42369</v>
       </c>
       <c r="K97" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="L97" t="n">
-        <v>-2.471521231841731</v>
+        <v>-2.471521231841732</v>
       </c>
       <c r="M97" t="n">
         <v>0.4575647915638049</v>
@@ -4822,7 +4822,7 @@
         <v>42369</v>
       </c>
       <c r="K98" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="L98" t="n">
         <v>-2.503584335121057</v>
@@ -4869,7 +4869,7 @@
         <v>42369</v>
       </c>
       <c r="K99" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="L99" t="n">
         <v>-2.355654205189728</v>
@@ -4878,10 +4878,10 @@
         <v>0.3043101029651514</v>
       </c>
       <c r="N99" t="n">
-        <v>-3.574390123528199</v>
+        <v>-3.5743901235282</v>
       </c>
       <c r="O99" t="n">
-        <v>0.9144316029370887</v>
+        <v>0.9144316029370889</v>
       </c>
     </row>
     <row r="100">
@@ -4916,7 +4916,7 @@
         <v>42460</v>
       </c>
       <c r="K100" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="L100" t="n">
         <v>-2.272682832144938</v>
@@ -4925,10 +4925,10 @@
         <v>0.3023293675789138</v>
       </c>
       <c r="N100" t="n">
-        <v>-3.453806712579706</v>
+        <v>-3.453806712579707</v>
       </c>
       <c r="O100" t="n">
-        <v>0.8788003696820377</v>
+        <v>0.8788003696820378</v>
       </c>
     </row>
     <row r="101">
@@ -4963,10 +4963,10 @@
         <v>42460</v>
       </c>
       <c r="K101" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="L101" t="n">
-        <v>-2.167494233893924</v>
+        <v>-2.167494233893925</v>
       </c>
       <c r="M101" t="n">
         <v>0.1567286686635361</v>
@@ -4975,7 +4975,7 @@
         <v>-3.356326868951075</v>
       </c>
       <c r="O101" t="n">
-        <v>1.032109823219797</v>
+        <v>1.032109823219798</v>
       </c>
     </row>
     <row r="102">
@@ -5010,10 +5010,10 @@
         <v>42460</v>
       </c>
       <c r="K102" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="L102" t="n">
-        <v>-2.074019288009394</v>
+        <v>-2.074019288009395</v>
       </c>
       <c r="M102" t="n">
         <v>0.2287676307174036</v>
@@ -5022,7 +5022,7 @@
         <v>-3.233248009440734</v>
       </c>
       <c r="O102" t="n">
-        <v>0.9304669475401187</v>
+        <v>0.9304669475401188</v>
       </c>
     </row>
     <row r="103">
@@ -5057,7 +5057,7 @@
         <v>42551</v>
       </c>
       <c r="K103" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="L103" t="n">
         <v>-2.294671245942201</v>
@@ -5069,7 +5069,7 @@
         <v>-3.102657414448132</v>
       </c>
       <c r="O103" t="n">
-        <v>0.5263685855453897</v>
+        <v>0.5263685855453898</v>
       </c>
     </row>
     <row r="104">
@@ -5104,16 +5104,16 @@
         <v>42551</v>
       </c>
       <c r="K104" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="L104" t="n">
         <v>-2.250906837598992</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4071134749592401</v>
+        <v>0.4071134749592402</v>
       </c>
       <c r="N104" t="n">
-        <v>-2.9930861949601</v>
+        <v>-2.993086194960101</v>
       </c>
       <c r="O104" t="n">
         <v>0.3350728475596947</v>
@@ -5151,13 +5151,13 @@
         <v>42551</v>
       </c>
       <c r="K105" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="L105" t="n">
         <v>-2.482846593221621</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4477435622805215</v>
+        <v>0.4477435622805216</v>
       </c>
       <c r="N105" t="n">
         <v>-2.964857571148912</v>
@@ -5339,19 +5339,19 @@
         <v>42735</v>
       </c>
       <c r="K109" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="L109" t="n">
         <v>-2.547985169839058</v>
       </c>
       <c r="M109" t="n">
-        <v>0.205770063343646</v>
+        <v>0.2057700633436461</v>
       </c>
       <c r="N109" t="n">
         <v>-2.76866149246414</v>
       </c>
       <c r="O109" t="n">
-        <v>0.01491315660199495</v>
+        <v>0.01491315660199496</v>
       </c>
     </row>
     <row r="110">
@@ -5386,19 +5386,19 @@
         <v>42735</v>
       </c>
       <c r="K110" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="L110" t="n">
-        <v>-2.60856663541565</v>
+        <v>-2.608566635415651</v>
       </c>
       <c r="M110" t="n">
-        <v>0.2080691701966476</v>
+        <v>0.2080691701966477</v>
       </c>
       <c r="N110" t="n">
-        <v>-2.858273780273584</v>
+        <v>-2.858273780273585</v>
       </c>
       <c r="O110" t="n">
-        <v>0.04164487198184492</v>
+        <v>0.04164487198184493</v>
       </c>
     </row>
     <row r="111">
@@ -5433,16 +5433,16 @@
         <v>42735</v>
       </c>
       <c r="K111" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="L111" t="n">
-        <v>-2.645697211091627</v>
+        <v>-2.645697211091628</v>
       </c>
       <c r="M111" t="n">
-        <v>0.04218861075257995</v>
+        <v>0.04218861075257997</v>
       </c>
       <c r="N111" t="n">
-        <v>-2.924946729457205</v>
+        <v>-2.924946729457206</v>
       </c>
       <c r="O111" t="n">
         <v>0.2370666553801306</v>
@@ -5480,7 +5480,7 @@
         <v>42825</v>
       </c>
       <c r="K112" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="L112" t="n">
         <v>-2.636883807059121</v>
@@ -5492,7 +5492,7 @@
         <v>-3.040345976366841</v>
       </c>
       <c r="O112" t="n">
-        <v>0.5270890503249188</v>
+        <v>0.5270890503249189</v>
       </c>
     </row>
     <row r="113">
@@ -5527,19 +5527,19 @@
         <v>42825</v>
       </c>
       <c r="K113" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="L113" t="n">
-        <v>-2.71957150561278</v>
+        <v>-2.719571505612781</v>
       </c>
       <c r="M113" t="n">
         <v>-0.1638549726643231</v>
       </c>
       <c r="N113" t="n">
-        <v>-3.135006432630455</v>
+        <v>-3.135006432630456</v>
       </c>
       <c r="O113" t="n">
-        <v>0.579294577911053</v>
+        <v>0.5792945779110531</v>
       </c>
     </row>
     <row r="114">
@@ -5574,7 +5574,7 @@
         <v>42825</v>
       </c>
       <c r="K114" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="L114" t="n">
         <v>-2.920969266446445</v>
@@ -5583,10 +5583,10 @@
         <v>-0.4046668132894775</v>
       </c>
       <c r="N114" t="n">
-        <v>-3.206954086830248</v>
+        <v>-3.206954086830249</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6906563119023367</v>
+        <v>0.6906563119023368</v>
       </c>
     </row>
     <row r="115">
@@ -5621,13 +5621,13 @@
         <v>42916</v>
       </c>
       <c r="K115" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="L115" t="n">
-        <v>-2.833123358532704</v>
+        <v>-2.833123358532705</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.6031129455632926</v>
+        <v>-0.6031129455632928</v>
       </c>
       <c r="N115" t="n">
         <v>-3.279752175303437</v>
@@ -5668,13 +5668,13 @@
         <v>42916</v>
       </c>
       <c r="K116" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="L116" t="n">
         <v>-3.057228306618415</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.8652017831550562</v>
+        <v>-0.8652017831550565</v>
       </c>
       <c r="N116" t="n">
         <v>-3.362509574564749</v>
@@ -5715,13 +5715,13 @@
         <v>42916</v>
       </c>
       <c r="K117" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="L117" t="n">
         <v>-2.948974221526166</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.9328605863377125</v>
+        <v>-0.9328605863377127</v>
       </c>
       <c r="N117" t="n">
         <v>-3.450117041717365</v>
@@ -5903,7 +5903,7 @@
         <v>43100</v>
       </c>
       <c r="K121" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="L121" t="n">
         <v>-4.063112421952717</v>
@@ -5915,7 +5915,7 @@
         <v>-3.798873101116382</v>
       </c>
       <c r="O121" t="n">
-        <v>0.8886423801016921</v>
+        <v>0.8886423801016922</v>
       </c>
     </row>
     <row r="122">
@@ -5950,10 +5950,10 @@
         <v>43100</v>
       </c>
       <c r="K122" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="L122" t="n">
-        <v>-4.577172859276691</v>
+        <v>-4.577172859276692</v>
       </c>
       <c r="M122" t="n">
         <v>-1.421355140806032</v>
@@ -5962,7 +5962,7 @@
         <v>-3.844709578662119</v>
       </c>
       <c r="O122" t="n">
-        <v>0.6888964851166707</v>
+        <v>0.6888964851166708</v>
       </c>
     </row>
     <row r="123">
@@ -5997,7 +5997,7 @@
         <v>43100</v>
       </c>
       <c r="K123" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="L123" t="n">
         <v>-4.848540346096162</v>
@@ -6006,10 +6006,10 @@
         <v>-1.502406955147936</v>
       </c>
       <c r="N123" t="n">
-        <v>-3.923465117636219</v>
+        <v>-3.92346511763622</v>
       </c>
       <c r="O123" t="n">
-        <v>0.5773375078445078</v>
+        <v>0.5773375078445079</v>
       </c>
     </row>
     <row r="124">
@@ -6044,19 +6044,19 @@
         <v>43190</v>
       </c>
       <c r="K124" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="L124" t="n">
-        <v>-4.851416542834566</v>
+        <v>-4.851416542834565</v>
       </c>
       <c r="M124" t="n">
-        <v>-1.505032361342432</v>
+        <v>-1.505032361342431</v>
       </c>
       <c r="N124" t="n">
-        <v>-3.832261708540475</v>
+        <v>-3.832261708540474</v>
       </c>
       <c r="O124" t="n">
-        <v>0.4858842066800951</v>
+        <v>0.485884206680095</v>
       </c>
     </row>
     <row r="125">
@@ -6091,10 +6091,10 @@
         <v>43190</v>
       </c>
       <c r="K125" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="L125" t="n">
-        <v>-5.067057321288615</v>
+        <v>-5.067057321288614</v>
       </c>
       <c r="M125" t="n">
         <v>-1.586857850327319</v>
@@ -6103,7 +6103,7 @@
         <v>-3.867975472984491</v>
       </c>
       <c r="O125" t="n">
-        <v>0.3877826816549488</v>
+        <v>0.3877826816549487</v>
       </c>
     </row>
     <row r="126">
@@ -6138,16 +6138,16 @@
         <v>43190</v>
       </c>
       <c r="K126" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="L126" t="n">
-        <v>-5.192523071065441</v>
+        <v>-5.19252307106544</v>
       </c>
       <c r="M126" t="n">
         <v>-1.588973067049377</v>
       </c>
       <c r="N126" t="n">
-        <v>-3.960904736488225</v>
+        <v>-3.960904736488224</v>
       </c>
       <c r="O126" t="n">
         <v>0.3573614121039145</v>
@@ -6185,10 +6185,10 @@
         <v>43281</v>
       </c>
       <c r="K127" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="L127" t="n">
-        <v>-5.125282152012538</v>
+        <v>-5.125282152012537</v>
       </c>
       <c r="M127" t="n">
         <v>-1.494846150947269</v>
@@ -6197,7 +6197,7 @@
         <v>-4.046708049097697</v>
       </c>
       <c r="O127" t="n">
-        <v>0.4162787224459617</v>
+        <v>0.4162787224459616</v>
       </c>
     </row>
     <row r="128">
@@ -6232,19 +6232,19 @@
         <v>43281</v>
       </c>
       <c r="K128" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="L128" t="n">
-        <v>-4.854523443022684</v>
+        <v>-4.854523443022683</v>
       </c>
       <c r="M128" t="n">
         <v>-1.366141209985371</v>
       </c>
       <c r="N128" t="n">
-        <v>-4.162571418422049</v>
+        <v>-4.162571418422048</v>
       </c>
       <c r="O128" t="n">
-        <v>0.6741958597982686</v>
+        <v>0.6741958597982685</v>
       </c>
     </row>
     <row r="129">
@@ -6279,10 +6279,10 @@
         <v>43281</v>
       </c>
       <c r="K129" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="L129" t="n">
-        <v>-4.552172509976495</v>
+        <v>-4.552172509976494</v>
       </c>
       <c r="M129" t="n">
         <v>-1.254900984434897</v>
@@ -6326,16 +6326,16 @@
         <v>43373</v>
       </c>
       <c r="K130" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="L130" t="n">
-        <v>-4.00583878402361</v>
+        <v>-4.005838784023609</v>
       </c>
       <c r="M130" t="n">
-        <v>-1.218988544358263</v>
+        <v>-1.218988544358262</v>
       </c>
       <c r="N130" t="n">
-        <v>-4.450715257421645</v>
+        <v>-4.450715257421644</v>
       </c>
       <c r="O130" t="n">
         <v>1.66387210627274</v>
@@ -6373,7 +6373,7 @@
         <v>43373</v>
       </c>
       <c r="K131" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="L131" t="n">
         <v>-3.203182438765805</v>
@@ -6382,7 +6382,7 @@
         <v>-1.171731768069902</v>
       </c>
       <c r="N131" t="n">
-        <v>-4.485336753149905</v>
+        <v>-4.485336753149904</v>
       </c>
       <c r="O131" t="n">
         <v>2.453893170970445</v>
@@ -6420,10 +6420,10 @@
         <v>43373</v>
       </c>
       <c r="K132" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="L132" t="n">
-        <v>-2.510752524200601</v>
+        <v>-2.5107525242006</v>
       </c>
       <c r="M132" t="n">
         <v>-1.180710555564691</v>
@@ -6432,7 +6432,7 @@
         <v>-4.468997722748204</v>
       </c>
       <c r="O132" t="n">
-        <v>3.138962842628738</v>
+        <v>3.138962842628737</v>
       </c>
     </row>
     <row r="133">
@@ -6890,19 +6890,19 @@
         <v>43738</v>
       </c>
       <c r="K142" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="L142" t="n">
         <v>2.688665686014994</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.8210863375284544</v>
+        <v>-0.8210863375284545</v>
       </c>
       <c r="N142" t="n">
-        <v>-4.613739684811473</v>
+        <v>-4.613739684811474</v>
       </c>
       <c r="O142" t="n">
-        <v>8.123491708354921</v>
+        <v>8.123491708354923</v>
       </c>
     </row>
     <row r="143">
@@ -6937,19 +6937,19 @@
         <v>43738</v>
       </c>
       <c r="K143" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="L143" t="n">
         <v>2.580082400524423</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.9857554816200302</v>
+        <v>-0.9857554816200305</v>
       </c>
       <c r="N143" t="n">
-        <v>-4.53454831313515</v>
+        <v>-4.534548313135151</v>
       </c>
       <c r="O143" t="n">
-        <v>8.100386195279603</v>
+        <v>8.100386195279604</v>
       </c>
     </row>
     <row r="144">
@@ -6984,7 +6984,7 @@
         <v>43738</v>
       </c>
       <c r="K144" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="L144" t="n">
         <v>2.27745799285976</v>
@@ -6993,10 +6993,10 @@
         <v>-1.121982981776499</v>
       </c>
       <c r="N144" t="n">
-        <v>-4.483363986442214</v>
+        <v>-4.483363986442215</v>
       </c>
       <c r="O144" t="n">
-        <v>7.882804961078473</v>
+        <v>7.882804961078474</v>
       </c>
     </row>
     <row r="145">
@@ -7172,19 +7172,19 @@
         <v>43921</v>
       </c>
       <c r="K148" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="L148" t="n">
         <v>1.108675332685499</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.484658645554966</v>
+        <v>-1.484658645554967</v>
       </c>
       <c r="N148" t="n">
-        <v>-4.189812322596572</v>
+        <v>-4.189812322596573</v>
       </c>
       <c r="O148" t="n">
-        <v>6.783147585810766</v>
+        <v>6.783147585810767</v>
       </c>
     </row>
     <row r="149">
@@ -7219,7 +7219,7 @@
         <v>43921</v>
       </c>
       <c r="K149" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="L149" t="n">
         <v>0.4912454562884402</v>
@@ -7228,10 +7228,10 @@
         <v>-1.45343378395986</v>
       </c>
       <c r="N149" t="n">
-        <v>-3.966846251227863</v>
+        <v>-3.966846251227864</v>
       </c>
       <c r="O149" t="n">
-        <v>5.91152806142362</v>
+        <v>5.911528061423621</v>
       </c>
     </row>
     <row r="150">
@@ -7266,16 +7266,16 @@
         <v>43921</v>
       </c>
       <c r="K150" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="L150" t="n">
-        <v>-0.1841367352501528</v>
+        <v>-0.1841367352501529</v>
       </c>
       <c r="M150" t="n">
         <v>-1.527962260195093</v>
       </c>
       <c r="N150" t="n">
-        <v>-3.718072767502112</v>
+        <v>-3.718072767502113</v>
       </c>
       <c r="O150" t="n">
         <v>5.061902147368238</v>
@@ -7313,19 +7313,19 @@
         <v>44012</v>
       </c>
       <c r="K151" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="L151" t="n">
-        <v>-0.5193575153774033</v>
+        <v>-0.5193575153774034</v>
       </c>
       <c r="M151" t="n">
-        <v>-1.758600779853005</v>
+        <v>-1.758600779853006</v>
       </c>
       <c r="N151" t="n">
         <v>-3.705127814082791</v>
       </c>
       <c r="O151" t="n">
-        <v>4.944375057293189</v>
+        <v>4.94437505729319</v>
       </c>
     </row>
     <row r="152">
@@ -7360,19 +7360,19 @@
         <v>44012</v>
       </c>
       <c r="K152" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="L152" t="n">
         <v>-1.184999846756154</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.924646645341388</v>
+        <v>-1.924646645341389</v>
       </c>
       <c r="N152" t="n">
-        <v>-3.612594378931113</v>
+        <v>-3.612594378931114</v>
       </c>
       <c r="O152" t="n">
-        <v>4.352245156251143</v>
+        <v>4.352245156251145</v>
       </c>
     </row>
     <row r="153">
@@ -7407,19 +7407,19 @@
         <v>44012</v>
       </c>
       <c r="K153" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="L153" t="n">
-        <v>-2.316021524779263</v>
+        <v>-2.316021524779264</v>
       </c>
       <c r="M153" t="n">
-        <v>-2.37358055482875</v>
+        <v>-2.373580554828751</v>
       </c>
       <c r="N153" t="n">
         <v>-3.517763887557185</v>
       </c>
       <c r="O153" t="n">
-        <v>3.575326896341468</v>
+        <v>3.575326896341469</v>
       </c>
     </row>
     <row r="154">
@@ -8723,19 +8723,19 @@
         <v>44926</v>
       </c>
       <c r="K181" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="L181" t="n">
-        <v>-5.110457280527663</v>
+        <v>-5.110457280527664</v>
       </c>
       <c r="M181" t="n">
-        <v>-2.12223926666294</v>
+        <v>-2.122239266662941</v>
       </c>
       <c r="N181" t="n">
-        <v>-8.775613772056108</v>
+        <v>-8.77561377205611</v>
       </c>
       <c r="O181" t="n">
-        <v>5.787395758191385</v>
+        <v>5.787395758191386</v>
       </c>
     </row>
     <row r="182">
@@ -8770,19 +8770,19 @@
         <v>44926</v>
       </c>
       <c r="K182" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="L182" t="n">
-        <v>-5.448832891156583</v>
+        <v>-5.448832891156584</v>
       </c>
       <c r="M182" t="n">
         <v>-2.589613734677255</v>
       </c>
       <c r="N182" t="n">
-        <v>-8.730701801445351</v>
+        <v>-8.730701801445353</v>
       </c>
       <c r="O182" t="n">
-        <v>5.871482644966023</v>
+        <v>5.871482644966024</v>
       </c>
     </row>
     <row r="183">
@@ -8817,19 +8817,19 @@
         <v>44926</v>
       </c>
       <c r="K183" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="L183" t="n">
-        <v>-5.824221756281482</v>
+        <v>-5.824221756281483</v>
       </c>
       <c r="M183" t="n">
-        <v>-2.967411746544497</v>
+        <v>-2.967411746544498</v>
       </c>
       <c r="N183" t="n">
-        <v>-8.605312283906665</v>
+        <v>-8.605312283906667</v>
       </c>
       <c r="O183" t="n">
-        <v>5.748502274169679</v>
+        <v>5.74850227416968</v>
       </c>
     </row>
     <row r="184">
@@ -9011,13 +9011,13 @@
         <v>-5.067266260666861</v>
       </c>
       <c r="M187" t="n">
-        <v>-2.879181220168936</v>
+        <v>-2.879181220168937</v>
       </c>
       <c r="N187" t="n">
-        <v>-6.6218136432139</v>
+        <v>-6.621813643213901</v>
       </c>
       <c r="O187" t="n">
-        <v>4.433729568203793</v>
+        <v>4.433729568203795</v>
       </c>
     </row>
     <row r="188">
@@ -9055,16 +9055,16 @@
         <v>1035.745849934734</v>
       </c>
       <c r="L188" t="n">
-        <v>-5.281314909777036</v>
+        <v>-5.281314909777037</v>
       </c>
       <c r="M188" t="n">
-        <v>-2.953620330887901</v>
+        <v>-2.953620330887902</v>
       </c>
       <c r="N188" t="n">
-        <v>-6.391870168166419</v>
+        <v>-6.39187016816642</v>
       </c>
       <c r="O188" t="n">
-        <v>4.064176554765101</v>
+        <v>4.064176554765102</v>
       </c>
     </row>
     <row r="189">
@@ -9102,16 +9102,16 @@
         <v>1035.745849934734</v>
       </c>
       <c r="L189" t="n">
-        <v>-5.092562041481866</v>
+        <v>-5.092562041481867</v>
       </c>
       <c r="M189" t="n">
-        <v>-3.028928380642496</v>
+        <v>-3.028928380642497</v>
       </c>
       <c r="N189" t="n">
-        <v>-6.056918307126511</v>
+        <v>-6.056918307126512</v>
       </c>
       <c r="O189" t="n">
-        <v>3.993285611774959</v>
+        <v>3.99328561177496</v>
       </c>
     </row>
     <row r="190">
@@ -9149,16 +9149,16 @@
         <v>1087.793792245752</v>
       </c>
       <c r="L190" t="n">
-        <v>-4.417840986276109</v>
+        <v>-4.41784098627611</v>
       </c>
       <c r="M190" t="n">
         <v>-2.743718544153749</v>
       </c>
       <c r="N190" t="n">
-        <v>-5.473991525275</v>
+        <v>-5.473991525275002</v>
       </c>
       <c r="O190" t="n">
-        <v>3.799870002444521</v>
+        <v>3.799870002444522</v>
       </c>
     </row>
     <row r="191">
@@ -9196,16 +9196,16 @@
         <v>1087.793792245752</v>
       </c>
       <c r="L191" t="n">
-        <v>-4.346779723975269</v>
+        <v>-4.34677972397527</v>
       </c>
       <c r="M191" t="n">
-        <v>-2.592035384003187</v>
+        <v>-2.592035384003188</v>
       </c>
       <c r="N191" t="n">
         <v>-5.260877604555341</v>
       </c>
       <c r="O191" t="n">
-        <v>3.506134183875138</v>
+        <v>3.506134183875139</v>
       </c>
     </row>
     <row r="192">
@@ -9243,16 +9243,16 @@
         <v>1087.793792245752</v>
       </c>
       <c r="L192" t="n">
-        <v>-4.220836736456317</v>
+        <v>-4.220836736456318</v>
       </c>
       <c r="M192" t="n">
-        <v>-2.491280993988025</v>
+        <v>-2.491280993988026</v>
       </c>
       <c r="N192" t="n">
         <v>-5.002006849815474</v>
       </c>
       <c r="O192" t="n">
-        <v>3.272452026639061</v>
+        <v>3.272452026639062</v>
       </c>
     </row>
     <row r="193">
@@ -10192,7 +10192,7 @@
         <v>-3.33730835715357</v>
       </c>
       <c r="O212" t="n">
-        <v>2.843490572800921</v>
+        <v>2.843490572800922</v>
       </c>
     </row>
     <row r="213">
@@ -10556,16 +10556,16 @@
         <v>46112</v>
       </c>
       <c r="K220" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="L220" t="n">
-        <v>-2.439190383335075</v>
+        <v>-2.439190383335074</v>
       </c>
       <c r="M220" t="n">
         <v>-1.274492368448753</v>
       </c>
       <c r="N220" t="n">
-        <v>-2.767692528748091</v>
+        <v>-2.76769252874809</v>
       </c>
       <c r="O220" t="n">
         <v>1.602997562011508</v>
@@ -10603,7 +10603,7 @@
         <v>46112</v>
       </c>
       <c r="K221" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="L221" t="n">
         <v>-2.263495032437279</v>
@@ -10612,7 +10612,7 @@
         <v>-1.191521732580641</v>
       </c>
       <c r="N221" t="n">
-        <v>-2.855835874721574</v>
+        <v>-2.855835874721573</v>
       </c>
       <c r="O221" t="n">
         <v>1.783865013384726</v>
@@ -10650,7 +10650,7 @@
         <v>46112</v>
       </c>
       <c r="K222" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="L222" t="n">
         <v>-2.282393560812822</v>
@@ -10659,7 +10659,7 @@
         <v>-1.117695545926501</v>
       </c>
       <c r="N222" t="n">
-        <v>-2.953837546577667</v>
+        <v>-2.953837546577666</v>
       </c>
       <c r="O222" t="n">
         <v>1.789141970211135</v>
@@ -10700,7 +10700,7 @@
         <v>1700.354635555628</v>
       </c>
       <c r="L223" t="n">
-        <v>-2.335159923095996</v>
+        <v>-2.335159923095995</v>
       </c>
       <c r="M223" t="n">
         <v>-1.062778294722907</v>
@@ -10709,7 +10709,7 @@
         <v>-2.928623768166323</v>
       </c>
       <c r="O223" t="n">
-        <v>1.656244492243669</v>
+        <v>1.656244492243668</v>
       </c>
     </row>
     <row r="224">
@@ -10797,10 +10797,10 @@
         <v>-2.47613051534052</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.9538598396386933</v>
+        <v>-0.953859839638693</v>
       </c>
       <c r="N225" t="n">
-        <v>-3.052906077033583</v>
+        <v>-3.052906077033582</v>
       </c>
       <c r="O225" t="n">
         <v>1.530637753782189</v>
@@ -10900,10 +10900,10 @@
         <v>1.533215254237288</v>
       </c>
       <c r="C5" t="n">
-        <v>168.8967102735621</v>
+        <v>168.896710273562</v>
       </c>
       <c r="D5" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>39813</v>
@@ -10920,7 +10920,7 @@
         <v>130.7828799188441</v>
       </c>
       <c r="D6" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>39903</v>
@@ -10937,7 +10937,7 @@
         <v>156.4423058232571</v>
       </c>
       <c r="D7" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>39994</v>
@@ -10965,13 +10965,13 @@
         <v>278.165055869949</v>
       </c>
       <c r="B9" t="n">
-        <v>1.48117619047619</v>
+        <v>1.481176190476191</v>
       </c>
       <c r="C9" t="n">
-        <v>187.800112949777</v>
+        <v>187.8001129497769</v>
       </c>
       <c r="D9" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>40178</v>
@@ -10988,7 +10988,7 @@
         <v>163.3389061436113</v>
       </c>
       <c r="D10" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>40268</v>
@@ -11005,7 +11005,7 @@
         <v>184.5845876179025</v>
       </c>
       <c r="D11" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>40359</v>
@@ -11036,10 +11036,10 @@
         <v>1.457427868852459</v>
       </c>
       <c r="C13" t="n">
-        <v>223.7258198851917</v>
+        <v>223.7258198851916</v>
       </c>
       <c r="D13" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>40543</v>
@@ -11056,7 +11056,7 @@
         <v>188.6987980233468</v>
       </c>
       <c r="D14" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>40633</v>
@@ -11090,7 +11090,7 @@
         <v>223.6350014442476</v>
       </c>
       <c r="D16" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>40816</v>
@@ -11135,13 +11135,13 @@
         <v>387.344421610499</v>
       </c>
       <c r="B19" t="n">
-        <v>1.797893650793651</v>
+        <v>1.79789365079365</v>
       </c>
       <c r="C19" t="n">
         <v>215.4434559794525</v>
       </c>
       <c r="D19" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>41090</v>
@@ -11155,7 +11155,7 @@
         <v>1.795756451612903</v>
       </c>
       <c r="C20" t="n">
-        <v>238.831411801092</v>
+        <v>238.8314118010919</v>
       </c>
       <c r="D20" t="n">
         <v>857.1420802056064</v>
@@ -11209,7 +11209,7 @@
         <v>243.3585507081091</v>
       </c>
       <c r="D23" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>41455</v>
@@ -11240,7 +11240,7 @@
         <v>2.025490163934426</v>
       </c>
       <c r="C25" t="n">
-        <v>245.1499680136029</v>
+        <v>245.149968013603</v>
       </c>
       <c r="D25" t="n">
         <v>961.0481078717496</v>
@@ -11260,7 +11260,7 @@
         <v>206.8546279322574</v>
       </c>
       <c r="D26" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>41729</v>
@@ -11277,7 +11277,7 @@
         <v>233.2687910493438</v>
       </c>
       <c r="D27" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>41820</v>
@@ -11288,13 +11288,13 @@
         <v>551.958483650141</v>
       </c>
       <c r="B28" t="n">
-        <v>2.161522222222223</v>
+        <v>2.161522222222222</v>
       </c>
       <c r="C28" t="n">
-        <v>255.3563770825739</v>
+        <v>255.356377082574</v>
       </c>
       <c r="D28" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>41912</v>
@@ -11311,7 +11311,7 @@
         <v>247.4169735057768</v>
       </c>
       <c r="D29" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>42004</v>
@@ -11339,10 +11339,10 @@
         <v>567.197911838763</v>
       </c>
       <c r="B31" t="n">
-        <v>2.666340322580645</v>
+        <v>2.666340322580646</v>
       </c>
       <c r="C31" t="n">
-        <v>212.7252500497741</v>
+        <v>212.725250049774</v>
       </c>
       <c r="D31" t="n">
         <v>919.6371330818704</v>
@@ -11356,10 +11356,10 @@
         <v>634.163127850709</v>
       </c>
       <c r="B32" t="n">
-        <v>2.84273492063492</v>
+        <v>2.842734920634921</v>
       </c>
       <c r="C32" t="n">
-        <v>223.0820479417299</v>
+        <v>223.0820479417298</v>
       </c>
       <c r="D32" t="n">
         <v>887.3628039410262</v>
@@ -11379,7 +11379,7 @@
         <v>223.9755360864084</v>
       </c>
       <c r="D33" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>42369</v>
@@ -11393,10 +11393,10 @@
         <v>2.9437953125</v>
       </c>
       <c r="C34" t="n">
-        <v>193.9218591409195</v>
+        <v>193.9218591409194</v>
       </c>
       <c r="D34" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>42460</v>
@@ -11413,7 +11413,7 @@
         <v>220.4511445438936</v>
       </c>
       <c r="D35" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>42551</v>
@@ -11424,7 +11424,7 @@
         <v>670.039064862309</v>
       </c>
       <c r="B36" t="n">
-        <v>2.960358620689655</v>
+        <v>2.960358620689656</v>
       </c>
       <c r="C36" t="n">
         <v>226.3371269208642</v>
@@ -11444,10 +11444,10 @@
         <v>3.277955384615385</v>
       </c>
       <c r="C37" t="n">
-        <v>229.1928916870326</v>
+        <v>229.1928916870325</v>
       </c>
       <c r="D37" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>42735</v>
@@ -11464,7 +11464,7 @@
         <v>179.04323874422</v>
       </c>
       <c r="D38" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>42825</v>
@@ -11481,7 +11481,7 @@
         <v>207.8891764884418</v>
       </c>
       <c r="D39" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>42916</v>
@@ -11495,7 +11495,7 @@
         <v>3.514912903225806</v>
       </c>
       <c r="C40" t="n">
-        <v>240.1538850482417</v>
+        <v>240.1538850482418</v>
       </c>
       <c r="D40" t="n">
         <v>856.2791919679362</v>
@@ -11512,10 +11512,10 @@
         <v>3.795547692307693</v>
       </c>
       <c r="C41" t="n">
-        <v>237.792549985104</v>
+        <v>237.7925499851039</v>
       </c>
       <c r="D41" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>43100</v>
@@ -11532,7 +11532,7 @@
         <v>212.4174989921661</v>
       </c>
       <c r="D42" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>43190</v>
@@ -11543,13 +11543,13 @@
         <v>908.77201241503</v>
       </c>
       <c r="B43" t="n">
-        <v>4.3567078125</v>
+        <v>4.356707812499999</v>
       </c>
       <c r="C43" t="n">
         <v>208.5914528873469</v>
       </c>
       <c r="D43" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>43281</v>
@@ -11566,7 +11566,7 @@
         <v>187.6379538426487</v>
       </c>
       <c r="D44" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>43373</v>
@@ -11611,7 +11611,7 @@
         <v>1051.61027178976</v>
       </c>
       <c r="B47" t="n">
-        <v>5.872365</v>
+        <v>5.872364999999999</v>
       </c>
       <c r="C47" t="n">
         <v>179.0778113740818</v>
@@ -11628,13 +11628,13 @@
         <v>1178.52377571783</v>
       </c>
       <c r="B48" t="n">
-        <v>5.672177049180328</v>
+        <v>5.67217704918033</v>
       </c>
       <c r="C48" t="n">
-        <v>207.7727414887615</v>
+        <v>207.7727414887614</v>
       </c>
       <c r="D48" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>43738</v>
@@ -11645,7 +11645,7 @@
         <v>1223.87257025994</v>
       </c>
       <c r="B49" t="n">
-        <v>5.785284615384615</v>
+        <v>5.785284615384616</v>
       </c>
       <c r="C49" t="n">
         <v>211.5492411566643</v>
@@ -11662,13 +11662,13 @@
         <v>1095.83409320798</v>
       </c>
       <c r="B50" t="n">
-        <v>6.09385</v>
+        <v>6.093850000000002</v>
       </c>
       <c r="C50" t="n">
         <v>179.8262335318362</v>
       </c>
       <c r="D50" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>43921</v>
@@ -11679,13 +11679,13 @@
         <v>1061.24590135972</v>
       </c>
       <c r="B51" t="n">
-        <v>6.852923333333334</v>
+        <v>6.852923333333333</v>
       </c>
       <c r="C51" t="n">
         <v>154.8603201494622</v>
       </c>
       <c r="D51" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>44012</v>
@@ -11696,7 +11696,7 @@
         <v>1440.5085622707</v>
       </c>
       <c r="B52" t="n">
-        <v>7.207746031746032</v>
+        <v>7.207746031746031</v>
       </c>
       <c r="C52" t="n">
         <v>199.8556214281243</v>
@@ -11781,10 +11781,10 @@
         <v>2385.4197650929</v>
       </c>
       <c r="B57" t="n">
-        <v>11.16101692307692</v>
+        <v>11.16101692307693</v>
       </c>
       <c r="C57" t="n">
-        <v>213.7278154431179</v>
+        <v>213.7278154431178</v>
       </c>
       <c r="D57" t="n">
         <v>835.6602257809595</v>
@@ -11832,10 +11832,10 @@
         <v>4351.145687052261</v>
       </c>
       <c r="B60" t="n">
-        <v>17.92024032258065</v>
+        <v>17.92024032258064</v>
       </c>
       <c r="C60" t="n">
-        <v>242.8062129038269</v>
+        <v>242.806212903827</v>
       </c>
       <c r="D60" t="n">
         <v>864.3854149792769</v>
@@ -11855,7 +11855,7 @@
         <v>262.5287835653832</v>
       </c>
       <c r="D61" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>44926</v>
@@ -11869,7 +11869,7 @@
         <v>18.85272153846154</v>
       </c>
       <c r="C62" t="n">
-        <v>254.5257482540332</v>
+        <v>254.5257482540331</v>
       </c>
       <c r="D62" t="n">
         <v>981.7702030343168</v>
@@ -12002,7 +12002,7 @@
         <v>12570.1485248555</v>
       </c>
       <c r="B70" t="n">
-        <v>36.15040322580645</v>
+        <v>36.15040322580646</v>
       </c>
       <c r="C70" t="n">
         <v>347.7180723639102</v>
@@ -12039,7 +12039,7 @@
         <v>40.68386923076923</v>
       </c>
       <c r="C72" t="n">
-        <v>430.9674273123699</v>
+        <v>430.96742731237</v>
       </c>
       <c r="D72" t="n">
         <v>1536.009359448403</v>
@@ -12053,10 +12053,10 @@
         <v>18527.1474036199</v>
       </c>
       <c r="B73" t="n">
-        <v>42.17121384615385</v>
+        <v>42.17121384615384</v>
       </c>
       <c r="C73" t="n">
-        <v>439.3316130574135</v>
+        <v>439.3316130574136</v>
       </c>
       <c r="D73" t="n">
         <v>1595.814722617371</v>
@@ -12070,13 +12070,13 @@
         <v>17098.1382209303</v>
       </c>
       <c r="B74" t="n">
-        <v>43.59070967741935</v>
+        <v>43.59070967741936</v>
       </c>
       <c r="C74" t="n">
-        <v>392.2427128959407</v>
+        <v>392.2427128959406</v>
       </c>
       <c r="D74" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="E74" s="1" t="n">
         <v>46112</v>
@@ -12090,7 +12090,7 @@
         <v>45.38410847457627</v>
       </c>
       <c r="C75" t="n">
-        <v>437.8128822899041</v>
+        <v>437.8128822899042</v>
       </c>
       <c r="D75" t="n">
         <v>1700.354635555628</v>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,84 +434,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cari</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>enerji</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>cari_12</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>altin_12</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>enerji_12</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>diger_12</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>gsyh_tarih</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cari_gsyh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>altin_gsyh</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>enerji_gsyh</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>diger_gsyh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B2" t="n">
@@ -526,7 +538,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B3" t="n">
@@ -553,7 +565,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B4" t="n">
@@ -580,7 +592,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B5" t="n">
@@ -607,7 +619,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B6" t="n">
@@ -634,7 +646,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B7" t="n">
@@ -661,7 +673,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B8" t="n">
@@ -688,7 +700,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B9" t="n">
@@ -715,7 +727,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B10" t="n">
@@ -742,7 +754,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B11" t="n">
@@ -769,7 +781,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B12" t="n">
@@ -796,7 +808,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B13" t="n">
@@ -823,11 +835,11 @@
       <c r="I13" t="n">
         <v>2.68842</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K13" t="n">
-        <v>784.2271960468237</v>
+        <v>784.2271960468236</v>
       </c>
       <c r="L13" t="n">
         <v>-5.027369644758661</v>
@@ -836,14 +848,14 @@
         <v>-0.1740567028127523</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.196115386639433</v>
+        <v>-5.196115386639434</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3428113706782853</v>
+        <v>0.3428113706782854</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B14" t="n">
@@ -870,27 +882,27 @@
       <c r="I14" t="n">
         <v>5.004020000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K14" t="n">
-        <v>784.2271960468237</v>
+        <v>784.2271960468236</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.554930022838333</v>
+        <v>-4.554930022838334</v>
       </c>
       <c r="M14" t="n">
         <v>-0.1109372391553806</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.082068079365662</v>
+        <v>-5.082068079365663</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6380829465267902</v>
+        <v>0.6380829465267903</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B15" t="n">
@@ -917,11 +929,11 @@
       <c r="I15" t="n">
         <v>6.2034</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="K15" t="n">
-        <v>784.2271960468237</v>
+        <v>784.2271960468236</v>
       </c>
       <c r="L15" t="n">
         <v>-4.096261920261432</v>
@@ -933,11 +945,11 @@
         <v>-4.937134314542218</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7910207693982618</v>
+        <v>0.791020769398262</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B16" t="n">
@@ -964,11 +976,11 @@
       <c r="I16" t="n">
         <v>7.860720000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K16" t="n">
-        <v>726.5630108224931</v>
+        <v>726.5630108224932</v>
       </c>
       <c r="L16" t="n">
         <v>-4.000066004887826</v>
@@ -977,14 +989,14 @@
         <v>0.1260730296417179</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.208038316892054</v>
+        <v>-5.208038316892053</v>
       </c>
       <c r="O16" t="n">
-        <v>1.081904787734984</v>
+        <v>1.081904787734983</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B17" t="n">
@@ -1011,27 +1023,27 @@
       <c r="I17" t="n">
         <v>9.52572</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K17" t="n">
-        <v>726.5630108224931</v>
+        <v>726.5630108224932</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.500453452923376</v>
+        <v>-3.500453452923375</v>
       </c>
       <c r="M17" t="n">
         <v>0.1328171109216788</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.944332351757518</v>
+        <v>-4.944332351757517</v>
       </c>
       <c r="O17" t="n">
         <v>1.311065916941818</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B18" t="n">
@@ -1058,27 +1070,27 @@
       <c r="I18" t="n">
         <v>10.32989</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="K18" t="n">
-        <v>726.5630108224931</v>
+        <v>726.5630108224932</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.060023655048379</v>
+        <v>-3.060023655048378</v>
       </c>
       <c r="M18" t="n">
         <v>0.2153976980232408</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.697165901876306</v>
+        <v>-4.697165901876305</v>
       </c>
       <c r="O18" t="n">
         <v>1.421747301490923</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B19" t="n">
@@ -1105,11 +1117,11 @@
       <c r="I19" t="n">
         <v>11.23285</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K19" t="n">
-        <v>680.888729676509</v>
+        <v>680.8887296765091</v>
       </c>
       <c r="L19" t="n">
         <v>-2.77358093575323</v>
@@ -1118,14 +1130,14 @@
         <v>0.3170855832825641</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.740398628030569</v>
+        <v>-4.740398628030568</v>
       </c>
       <c r="O19" t="n">
         <v>1.649733577663525</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B20" t="n">
@@ -1152,27 +1164,27 @@
       <c r="I20" t="n">
         <v>13.00463</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K20" t="n">
-        <v>680.888729676509</v>
+        <v>680.8887296765091</v>
       </c>
       <c r="L20" t="n">
         <v>-2.256756402371413</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2974054220227848</v>
+        <v>0.2974054220227847</v>
       </c>
       <c r="N20" t="n">
-        <v>-4.464109725305778</v>
+        <v>-4.464109725305776</v>
       </c>
       <c r="O20" t="n">
         <v>1.90994936958033</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B21" t="n">
@@ -1199,27 +1211,27 @@
       <c r="I21" t="n">
         <v>12.93374</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="K21" t="n">
-        <v>680.888729676509</v>
+        <v>680.8887296765091</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.891498484064912</v>
+        <v>-1.891498484064911</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4460346995966407</v>
+        <v>0.4460346995966406</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.237069691799208</v>
+        <v>-4.237069691799207</v>
       </c>
       <c r="O21" t="n">
         <v>1.899537976806406</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B22" t="n">
@@ -1246,7 +1258,7 @@
       <c r="I22" t="n">
         <v>10.54887</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K22" t="n">
@@ -1266,7 +1278,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B23" t="n">
@@ -1293,7 +1305,7 @@
       <c r="I23" t="n">
         <v>12.80883</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K23" t="n">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B24" t="n">
@@ -1340,7 +1352,7 @@
       <c r="I24" t="n">
         <v>11.9196</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="K24" t="n">
@@ -1360,7 +1372,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B25" t="n">
@@ -1387,14 +1399,14 @@
       <c r="I25" t="n">
         <v>11.61895</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K25" t="n">
-        <v>658.9902820733862</v>
+        <v>658.9902820733863</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.723545901809696</v>
+        <v>-1.723545901809695</v>
       </c>
       <c r="M25" t="n">
         <v>0.4563041492112831</v>
@@ -1407,7 +1419,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B26" t="n">
@@ -1434,27 +1446,27 @@
       <c r="I26" t="n">
         <v>10.08681</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K26" t="n">
-        <v>658.9902820733862</v>
+        <v>658.9902820733863</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.115357445961187</v>
+        <v>-2.115357445961186</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3314161163543208</v>
+        <v>0.3314161163543207</v>
       </c>
       <c r="N26" t="n">
         <v>-3.977416771235653</v>
       </c>
       <c r="O26" t="n">
-        <v>1.530646243866267</v>
+        <v>1.530646243866266</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B27" t="n">
@@ -1481,27 +1493,27 @@
       <c r="I27" t="n">
         <v>10.03788</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="K27" t="n">
-        <v>658.9902820733862</v>
+        <v>658.9902820733863</v>
       </c>
       <c r="L27" t="n">
         <v>-2.398973160918249</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09757351777281513</v>
+        <v>0.09757351777281512</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.019764891927504</v>
+        <v>-4.019764891927503</v>
       </c>
       <c r="O27" t="n">
         <v>1.523221248182559</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B28" t="n">
@@ -1528,27 +1540,27 @@
       <c r="I28" t="n">
         <v>8.120710000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K28" t="n">
-        <v>691.5463082981533</v>
+        <v>691.5463082981535</v>
       </c>
       <c r="L28" t="n">
         <v>-2.718834555891187</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.004048897328207282</v>
+        <v>-0.004048897328207281</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.889064214106777</v>
+        <v>-3.889064214106776</v>
       </c>
       <c r="O28" t="n">
         <v>1.174282893648076</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B29" t="n">
@@ -1575,11 +1587,11 @@
       <c r="I29" t="n">
         <v>6.80951</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K29" t="n">
-        <v>691.5463082981533</v>
+        <v>691.5463082981535</v>
       </c>
       <c r="L29" t="n">
         <v>-3.115481890579493</v>
@@ -1588,14 +1600,14 @@
         <v>-0.01879845188096237</v>
       </c>
       <c r="N29" t="n">
-        <v>-4.08135647046666</v>
+        <v>-4.081356470466659</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9846788159071695</v>
+        <v>0.9846788159071693</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B30" t="n">
@@ -1622,11 +1634,11 @@
       <c r="I30" t="n">
         <v>5.458740000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="K30" t="n">
-        <v>691.5463082981533</v>
+        <v>691.5463082981535</v>
       </c>
       <c r="L30" t="n">
         <v>-3.30274339200908</v>
@@ -1635,14 +1647,14 @@
         <v>0.08777430993649349</v>
       </c>
       <c r="N30" t="n">
-        <v>-4.179863250392424</v>
+        <v>-4.179863250392423</v>
       </c>
       <c r="O30" t="n">
         <v>0.78935277862065</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B31" t="n">
@@ -1669,14 +1681,14 @@
       <c r="I31" t="n">
         <v>4.53857</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K31" t="n">
-        <v>719.6885900927988</v>
+        <v>719.6885900927989</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.336443057531845</v>
+        <v>-3.336443057531844</v>
       </c>
       <c r="M31" t="n">
         <v>0.1161613524944454</v>
@@ -1685,11 +1697,11 @@
         <v>-4.083225773554478</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6306297004673623</v>
+        <v>0.6306297004673622</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B32" t="n">
@@ -1716,27 +1728,27 @@
       <c r="I32" t="n">
         <v>2.42634</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K32" t="n">
-        <v>719.6885900927988</v>
+        <v>719.6885900927989</v>
       </c>
       <c r="L32" t="n">
         <v>-3.7600985165696</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06711236035265208</v>
+        <v>0.06711236035265207</v>
       </c>
       <c r="N32" t="n">
-        <v>-4.16434002325027</v>
+        <v>-4.164340023250269</v>
       </c>
       <c r="O32" t="n">
         <v>0.3371374832671921</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B33" t="n">
@@ -1763,27 +1775,27 @@
       <c r="I33" t="n">
         <v>0.1354600000000002</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="K33" t="n">
-        <v>719.6885900927988</v>
+        <v>719.6885900927989</v>
       </c>
       <c r="L33" t="n">
         <v>-4.10469200243829</v>
       </c>
       <c r="M33" t="n">
-        <v>0.08420308565984917</v>
+        <v>0.08420308565984914</v>
       </c>
       <c r="N33" t="n">
-        <v>-4.20770878083468</v>
+        <v>-4.207708780834679</v>
       </c>
       <c r="O33" t="n">
         <v>0.01882202967571483</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B34" t="n">
@@ -1810,7 +1822,7 @@
       <c r="I34" t="n">
         <v>-1.641</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K34" t="n">
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B35" t="n">
@@ -1857,7 +1869,7 @@
       <c r="I35" t="n">
         <v>-4.08595</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K35" t="n">
@@ -1877,7 +1889,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B36" t="n">
@@ -1904,7 +1916,7 @@
       <c r="I36" t="n">
         <v>-7.33985</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="K36" t="n">
@@ -1924,7 +1936,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B37" t="n">
@@ -1951,27 +1963,27 @@
       <c r="I37" t="n">
         <v>-10.14424</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K37" t="n">
-        <v>784.9655005365126</v>
+        <v>784.9655005365125</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.68496322061281</v>
+        <v>-5.684963220612812</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.057709542609246</v>
+        <v>-0.05770954260924602</v>
       </c>
       <c r="N37" t="n">
-        <v>-4.334926818661785</v>
+        <v>-4.334926818661786</v>
       </c>
       <c r="O37" t="n">
         <v>-1.292316667811077</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B38" t="n">
@@ -1998,27 +2010,27 @@
       <c r="I38" t="n">
         <v>-11.7397</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K38" t="n">
-        <v>784.9655005365126</v>
+        <v>784.9655005365125</v>
       </c>
       <c r="L38" t="n">
-        <v>-6.061922462512941</v>
+        <v>-6.061922462512942</v>
       </c>
       <c r="M38" t="n">
         <v>-0.1451019183927841</v>
       </c>
       <c r="N38" t="n">
-        <v>-4.421241440073414</v>
+        <v>-4.421241440073415</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.495568912516038</v>
+        <v>-1.495568912516039</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B39" t="n">
@@ -2045,27 +2057,27 @@
       <c r="I39" t="n">
         <v>-14.14707</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="K39" t="n">
-        <v>784.9655005365126</v>
+        <v>784.9655005365125</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.556721278173673</v>
+        <v>-6.556721278173675</v>
       </c>
       <c r="M39" t="n">
         <v>-0.1833201585313576</v>
       </c>
       <c r="N39" t="n">
-        <v>-4.571135925779576</v>
+        <v>-4.571135925779577</v>
       </c>
       <c r="O39" t="n">
         <v>-1.802253728390698</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B40" t="n">
@@ -2092,17 +2104,17 @@
       <c r="I40" t="n">
         <v>-18.16812</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K40" t="n">
-        <v>810.3253924162481</v>
+        <v>810.3253924162482</v>
       </c>
       <c r="L40" t="n">
         <v>-7.009776631906647</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.2052261987053406</v>
+        <v>-0.2052261987053405</v>
       </c>
       <c r="N40" t="n">
         <v>-4.562462233814442</v>
@@ -2112,7 +2124,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B41" t="n">
@@ -2139,11 +2151,11 @@
       <c r="I41" t="n">
         <v>-20.5611</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K41" t="n">
-        <v>810.3253924162481</v>
+        <v>810.3253924162482</v>
       </c>
       <c r="L41" t="n">
         <v>-7.424178060200413</v>
@@ -2152,14 +2164,14 @@
         <v>-0.2268224613472134</v>
       </c>
       <c r="N41" t="n">
-        <v>-4.659956401884913</v>
+        <v>-4.659956401884912</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.537388090318929</v>
+        <v>-2.537388090318928</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B42" t="n">
@@ -2186,27 +2198,27 @@
       <c r="I42" t="n">
         <v>-23.39756</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="K42" t="n">
-        <v>810.3253924162481</v>
+        <v>810.3253924162482</v>
       </c>
       <c r="L42" t="n">
-        <v>-8.038869398595663</v>
+        <v>-8.038869398595661</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.3299908931678176</v>
+        <v>-0.3299908931678175</v>
       </c>
       <c r="N42" t="n">
-        <v>-4.821439679127178</v>
+        <v>-4.821439679127177</v>
       </c>
       <c r="O42" t="n">
-        <v>-2.88742771965131</v>
+        <v>-2.887427719651309</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B43" t="n">
@@ -2233,7 +2245,7 @@
       <c r="I43" t="n">
         <v>-26.26857</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K43" t="n">
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B44" t="n">
@@ -2280,7 +2292,7 @@
       <c r="I44" t="n">
         <v>-26.73468</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K44" t="n">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B45" t="n">
@@ -2327,7 +2339,7 @@
       <c r="I45" t="n">
         <v>-25.77266</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="K45" t="n">
@@ -2347,7 +2359,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B46" t="n">
@@ -2374,11 +2386,11 @@
       <c r="I46" t="n">
         <v>-25.75811</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K46" t="n">
-        <v>854.9653194859254</v>
+        <v>854.9653194859255</v>
       </c>
       <c r="L46" t="n">
         <v>-8.785151665001129</v>
@@ -2387,14 +2399,14 @@
         <v>-0.5844681516443967</v>
       </c>
       <c r="N46" t="n">
-        <v>-5.187905168676281</v>
+        <v>-5.18790516867628</v>
       </c>
       <c r="O46" t="n">
-        <v>-3.012766648299591</v>
+        <v>-3.01276664829959</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B47" t="n">
@@ -2421,27 +2433,27 @@
       <c r="I47" t="n">
         <v>-25.40919</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K47" t="n">
-        <v>854.9653194859254</v>
+        <v>854.9653194859255</v>
       </c>
       <c r="L47" t="n">
-        <v>-8.906092243108056</v>
+        <v>-8.906092243108054</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6077439495585922</v>
+        <v>-0.6077439495585921</v>
       </c>
       <c r="N47" t="n">
-        <v>-5.326380960970624</v>
+        <v>-5.326380960970623</v>
       </c>
       <c r="O47" t="n">
         <v>-2.971955636197977</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B48" t="n">
@@ -2468,27 +2480,27 @@
       <c r="I48" t="n">
         <v>-24.01676</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="K48" t="n">
-        <v>854.9653194859254</v>
+        <v>854.9653194859255</v>
       </c>
       <c r="L48" t="n">
-        <v>-8.824685432312677</v>
+        <v>-8.824685432312675</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.5637655575197104</v>
+        <v>-0.5637655575197102</v>
       </c>
       <c r="N48" t="n">
-        <v>-5.451816458242587</v>
+        <v>-5.451816458242586</v>
       </c>
       <c r="O48" t="n">
-        <v>-2.809091720169519</v>
+        <v>-2.809091720169518</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B49" t="n">
@@ -2515,7 +2527,7 @@
       <c r="I49" t="n">
         <v>-22.04643</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K49" t="n">
@@ -2535,7 +2547,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B50" t="n">
@@ -2562,7 +2574,7 @@
       <c r="I50" t="n">
         <v>-21.51568</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K50" t="n">
@@ -2582,7 +2594,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B51" t="n">
@@ -2609,7 +2621,7 @@
       <c r="I51" t="n">
         <v>-19.64396</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="K51" t="n">
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B52" t="n">
@@ -2656,7 +2668,7 @@
       <c r="I52" t="n">
         <v>-15.79015</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K52" t="n">
@@ -2676,7 +2688,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B53" t="n">
@@ -2703,7 +2715,7 @@
       <c r="I53" t="n">
         <v>-13.06127</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K53" t="n">
@@ -2723,7 +2735,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B54" t="n">
@@ -2750,7 +2762,7 @@
       <c r="I54" t="n">
         <v>-10.51409</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="K54" t="n">
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B55" t="n">
@@ -2797,11 +2809,11 @@
       <c r="I55" t="n">
         <v>-6.249130000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K55" t="n">
-        <v>841.9456698487621</v>
+        <v>841.945669848762</v>
       </c>
       <c r="L55" t="n">
         <v>-7.087036864352339</v>
@@ -2810,14 +2822,14 @@
         <v>-0.2076143464594327</v>
       </c>
       <c r="N55" t="n">
-        <v>-6.137186976599304</v>
+        <v>-6.137186976599305</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.7422248517677543</v>
+        <v>-0.7422248517677544</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B56" t="n">
@@ -2844,14 +2856,14 @@
       <c r="I56" t="n">
         <v>-4.688590000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K56" t="n">
-        <v>841.9456698487621</v>
+        <v>841.945669848762</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.792481041000281</v>
+        <v>-6.792481041000283</v>
       </c>
       <c r="M56" t="n">
         <v>-0.140389106129891</v>
@@ -2860,11 +2872,11 @@
         <v>-6.095206833146166</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.5568755999234735</v>
+        <v>-0.5568755999234736</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B57" t="n">
@@ -2891,14 +2903,14 @@
       <c r="I57" t="n">
         <v>-2.382240000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="K57" t="n">
-        <v>841.9456698487621</v>
+        <v>841.945669848762</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.312877647977863</v>
+        <v>-6.312877647977865</v>
       </c>
       <c r="M57" t="n">
         <v>0.1644999255413697</v>
@@ -2911,7 +2923,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B58" t="n">
@@ -2938,7 +2950,7 @@
       <c r="I58" t="n">
         <v>0.395989999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K58" t="n">
@@ -2958,7 +2970,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B59" t="n">
@@ -2985,7 +2997,7 @@
       <c r="I59" t="n">
         <v>1.845749999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K59" t="n">
@@ -3005,7 +3017,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B60" t="n">
@@ -3032,7 +3044,7 @@
       <c r="I60" t="n">
         <v>3.21682</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="K60" t="n">
@@ -3052,7 +3064,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B61" t="n">
@@ -3079,7 +3091,7 @@
       <c r="I61" t="n">
         <v>4.90424</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K61" t="n">
@@ -3099,7 +3111,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B62" t="n">
@@ -3126,7 +3138,7 @@
       <c r="I62" t="n">
         <v>5.24468</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K62" t="n">
@@ -3146,7 +3158,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B63" t="n">
@@ -3173,7 +3185,7 @@
       <c r="I63" t="n">
         <v>5.49649</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="K63" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B64" t="n">
@@ -3220,7 +3232,7 @@
       <c r="I64" t="n">
         <v>6.803089999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K64" t="n">
@@ -3240,7 +3252,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B65" t="n">
@@ -3267,7 +3279,7 @@
       <c r="I65" t="n">
         <v>7.07182</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K65" t="n">
@@ -3287,7 +3299,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B66" t="n">
@@ -3314,7 +3326,7 @@
       <c r="I66" t="n">
         <v>8.31753</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="K66" t="n">
@@ -3334,7 +3346,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B67" t="n">
@@ -3361,11 +3373,11 @@
       <c r="I67" t="n">
         <v>9.40043</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K67" t="n">
-        <v>946.0043097899547</v>
+        <v>946.0043097899548</v>
       </c>
       <c r="L67" t="n">
         <v>-4.563087033883022</v>
@@ -3374,14 +3386,14 @@
         <v>-0.3136349347772818</v>
       </c>
       <c r="N67" t="n">
-        <v>-5.243145246453791</v>
+        <v>-5.24314524645379</v>
       </c>
       <c r="O67" t="n">
         <v>0.9936984327362332</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B68" t="n">
@@ -3408,27 +3420,27 @@
       <c r="I68" t="n">
         <v>9.15676</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K68" t="n">
-        <v>946.0043097899547</v>
+        <v>946.0043097899548</v>
       </c>
       <c r="L68" t="n">
-        <v>-4.738984752612176</v>
+        <v>-4.738984752612175</v>
       </c>
       <c r="M68" t="n">
         <v>-0.4570803700630154</v>
       </c>
       <c r="N68" t="n">
-        <v>-5.249839719126336</v>
+        <v>-5.249839719126335</v>
       </c>
       <c r="O68" t="n">
         <v>0.96794062196536</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B69" t="n">
@@ -3455,17 +3467,17 @@
       <c r="I69" t="n">
         <v>9.691610000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="K69" t="n">
-        <v>946.0043097899547</v>
+        <v>946.0043097899548</v>
       </c>
       <c r="L69" t="n">
         <v>-4.782959182294463</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6621534315621482</v>
+        <v>-0.6621534315621481</v>
       </c>
       <c r="N69" t="n">
         <v>-5.145278884702694</v>
@@ -3475,7 +3487,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B70" t="n">
@@ -3502,7 +3514,7 @@
       <c r="I70" t="n">
         <v>10.6274</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K70" t="n">
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B71" t="n">
@@ -3549,7 +3561,7 @@
       <c r="I71" t="n">
         <v>10.15893</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K71" t="n">
@@ -3569,7 +3581,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B72" t="n">
@@ -3596,7 +3608,7 @@
       <c r="I72" t="n">
         <v>11.57857</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="K72" t="n">
@@ -3616,7 +3628,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B73" t="n">
@@ -3643,7 +3655,7 @@
       <c r="I73" t="n">
         <v>10.08393</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K73" t="n">
@@ -3663,7 +3675,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B74" t="n">
@@ -3690,7 +3702,7 @@
       <c r="I74" t="n">
         <v>11.61466</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K74" t="n">
@@ -3710,7 +3722,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B75" t="n">
@@ -3737,7 +3749,7 @@
       <c r="I75" t="n">
         <v>12.55543</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="K75" t="n">
@@ -3757,7 +3769,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B76" t="n">
@@ -3784,27 +3796,27 @@
       <c r="I76" t="n">
         <v>12.95175</v>
       </c>
-      <c r="J76" s="1" t="n">
+      <c r="J76" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K76" t="n">
-        <v>947.2834628100969</v>
+        <v>947.2834628100968</v>
       </c>
       <c r="L76" t="n">
         <v>-4.738180466790009</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9309779328184004</v>
+        <v>-0.9309779328184005</v>
       </c>
       <c r="N76" t="n">
-        <v>-5.174451146290774</v>
+        <v>-5.174451146290775</v>
       </c>
       <c r="O76" t="n">
         <v>1.36725177926984</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B77" t="n">
@@ -3831,17 +3843,17 @@
       <c r="I77" t="n">
         <v>13.82609</v>
       </c>
-      <c r="J77" s="1" t="n">
+      <c r="J77" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K77" t="n">
-        <v>947.2834628100969</v>
+        <v>947.2834628100968</v>
       </c>
       <c r="L77" t="n">
         <v>-4.474690170802399</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.7381106368370852</v>
+        <v>-0.7381106368370853</v>
       </c>
       <c r="N77" t="n">
         <v>-5.196128923646967</v>
@@ -3851,7 +3863,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B78" t="n">
@@ -3878,27 +3890,27 @@
       <c r="I78" t="n">
         <v>15.83389</v>
       </c>
-      <c r="J78" s="1" t="n">
+      <c r="J78" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="K78" t="n">
-        <v>947.2834628100969</v>
+        <v>947.2834628100968</v>
       </c>
       <c r="L78" t="n">
-        <v>-4.107323892742751</v>
+        <v>-4.107323892742752</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.6158663408620645</v>
+        <v>-0.6158663408620646</v>
       </c>
       <c r="N78" t="n">
         <v>-5.162960393599167</v>
       </c>
       <c r="O78" t="n">
-        <v>1.671504953018929</v>
+        <v>1.67150495301893</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B79" t="n">
@@ -3925,27 +3937,27 @@
       <c r="I79" t="n">
         <v>15.8046</v>
       </c>
-      <c r="J79" s="1" t="n">
+      <c r="J79" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K79" t="n">
-        <v>937.1937031513315</v>
+        <v>937.1937031513314</v>
       </c>
       <c r="L79" t="n">
-        <v>-4.125614573592226</v>
+        <v>-4.125614573592227</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.5494061668026994</v>
+        <v>-0.5494061668026995</v>
       </c>
       <c r="N79" t="n">
-        <v>-5.262581239519494</v>
+        <v>-5.262581239519495</v>
       </c>
       <c r="O79" t="n">
         <v>1.686374966760525</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B80" t="n">
@@ -3972,11 +3984,11 @@
       <c r="I80" t="n">
         <v>18.19608</v>
       </c>
-      <c r="J80" s="1" t="n">
+      <c r="J80" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K80" t="n">
-        <v>937.1937031513315</v>
+        <v>937.1937031513314</v>
       </c>
       <c r="L80" t="n">
         <v>-3.73498028020231</v>
@@ -3985,14 +3997,14 @@
         <v>-0.381244558940774</v>
       </c>
       <c r="N80" t="n">
-        <v>-5.295283123769192</v>
+        <v>-5.295283123769193</v>
       </c>
       <c r="O80" t="n">
         <v>1.941549536538214</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B81" t="n">
@@ -4019,11 +4031,11 @@
       <c r="I81" t="n">
         <v>18.488</v>
       </c>
-      <c r="J81" s="1" t="n">
+      <c r="J81" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="K81" t="n">
-        <v>937.1937031513315</v>
+        <v>937.1937031513314</v>
       </c>
       <c r="L81" t="n">
         <v>-3.693366684348153</v>
@@ -4032,14 +4044,14 @@
         <v>-0.3436856211442018</v>
       </c>
       <c r="N81" t="n">
-        <v>-5.322376775716083</v>
+        <v>-5.322376775716084</v>
       </c>
       <c r="O81" t="n">
         <v>1.972697846542689</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B82" t="n">
@@ -4066,27 +4078,27 @@
       <c r="I82" t="n">
         <v>19.80297</v>
       </c>
-      <c r="J82" s="1" t="n">
+      <c r="J82" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K82" t="n">
-        <v>940.6297640777782</v>
+        <v>940.6297640777781</v>
       </c>
       <c r="L82" t="n">
-        <v>-3.592380476406646</v>
+        <v>-3.592380476406647</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.4030278590766061</v>
+        <v>-0.4030278590766062</v>
       </c>
       <c r="N82" t="n">
-        <v>-5.294638964441903</v>
+        <v>-5.294638964441904</v>
       </c>
       <c r="O82" t="n">
         <v>2.105288473346942</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B83" t="n">
@@ -4113,11 +4125,11 @@
       <c r="I83" t="n">
         <v>20.59569</v>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="J83" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K83" t="n">
-        <v>940.6297640777782</v>
+        <v>940.6297640777781</v>
       </c>
       <c r="L83" t="n">
         <v>-3.459809719279627</v>
@@ -4126,14 +4138,14 @@
         <v>-0.3685828508094417</v>
       </c>
       <c r="N83" t="n">
-        <v>-5.280788669142378</v>
+        <v>-5.280788669142379</v>
       </c>
       <c r="O83" t="n">
         <v>2.189563926907271</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B84" t="n">
@@ -4160,11 +4172,11 @@
       <c r="I84" t="n">
         <v>19.85103</v>
       </c>
-      <c r="J84" s="1" t="n">
+      <c r="J84" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="K84" t="n">
-        <v>940.6297640777782</v>
+        <v>940.6297640777781</v>
       </c>
       <c r="L84" t="n">
         <v>-3.618852103130485</v>
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B85" t="n">
@@ -4207,27 +4219,27 @@
       <c r="I85" t="n">
         <v>20.46028</v>
       </c>
-      <c r="J85" s="1" t="n">
+      <c r="J85" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K85" t="n">
-        <v>942.8967695699521</v>
+        <v>942.8967695699519</v>
       </c>
       <c r="L85" t="n">
-        <v>-3.405675046977416</v>
+        <v>-3.405675046977417</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.4133008114745574</v>
+        <v>-0.4133008114745576</v>
       </c>
       <c r="N85" t="n">
-        <v>-5.16231061245447</v>
+        <v>-5.162310612454471</v>
       </c>
       <c r="O85" t="n">
         <v>2.169938498074585</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B86" t="n">
@@ -4254,27 +4266,27 @@
       <c r="I86" t="n">
         <v>20.80432</v>
       </c>
-      <c r="J86" s="1" t="n">
+      <c r="J86" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K86" t="n">
-        <v>942.8967695699521</v>
+        <v>942.8967695699519</v>
       </c>
       <c r="L86" t="n">
-        <v>-3.096203205077811</v>
+        <v>-3.096203205077812</v>
       </c>
       <c r="M86" t="n">
         <v>-0.2807306256025542</v>
       </c>
       <c r="N86" t="n">
-        <v>-5.021896513824792</v>
+        <v>-5.021896513824793</v>
       </c>
       <c r="O86" t="n">
-        <v>2.206426055472508</v>
+        <v>2.206426055472509</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B87" t="n">
@@ -4301,27 +4313,27 @@
       <c r="I87" t="n">
         <v>18.98794</v>
       </c>
-      <c r="J87" s="1" t="n">
+      <c r="J87" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="K87" t="n">
-        <v>942.8967695699521</v>
+        <v>942.8967695699519</v>
       </c>
       <c r="L87" t="n">
-        <v>-3.116565985627751</v>
+        <v>-3.116565985627752</v>
       </c>
       <c r="M87" t="n">
         <v>-0.1818862950163885</v>
       </c>
       <c r="N87" t="n">
-        <v>-4.948464297028058</v>
+        <v>-4.948464297028059</v>
       </c>
       <c r="O87" t="n">
         <v>2.013787788101157</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B88" t="n">
@@ -4348,7 +4360,7 @@
       <c r="I88" t="n">
         <v>17.46199</v>
       </c>
-      <c r="J88" s="1" t="n">
+      <c r="J88" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K88" t="n">
@@ -4368,7 +4380,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B89" t="n">
@@ -4395,7 +4407,7 @@
       <c r="I89" t="n">
         <v>15.2882</v>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="J89" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K89" t="n">
@@ -4415,7 +4427,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B90" t="n">
@@ -4442,7 +4454,7 @@
       <c r="I90" t="n">
         <v>12.95619</v>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="J90" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="K90" t="n">
@@ -4462,7 +4474,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B91" t="n">
@@ -4489,7 +4501,7 @@
       <c r="I91" t="n">
         <v>11.8918</v>
       </c>
-      <c r="J91" s="1" t="n">
+      <c r="J91" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K91" t="n">
@@ -4509,7 +4521,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B92" t="n">
@@ -4536,7 +4548,7 @@
       <c r="I92" t="n">
         <v>10.00618</v>
       </c>
-      <c r="J92" s="1" t="n">
+      <c r="J92" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K92" t="n">
@@ -4556,7 +4568,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B93" t="n">
@@ -4583,7 +4595,7 @@
       <c r="I93" t="n">
         <v>10.69088</v>
       </c>
-      <c r="J93" s="1" t="n">
+      <c r="J93" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="K93" t="n">
@@ -4603,7 +4615,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B94" t="n">
@@ -4630,7 +4642,7 @@
       <c r="I94" t="n">
         <v>9.682169999999999</v>
       </c>
-      <c r="J94" s="1" t="n">
+      <c r="J94" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K94" t="n">
@@ -4650,7 +4662,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B95" t="n">
@@ -4677,7 +4689,7 @@
       <c r="I95" t="n">
         <v>9.299630000000001</v>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="J95" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K95" t="n">
@@ -4697,7 +4709,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B96" t="n">
@@ -4724,7 +4736,7 @@
       <c r="I96" t="n">
         <v>9.04907</v>
       </c>
-      <c r="J96" s="1" t="n">
+      <c r="J96" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="K96" t="n">
@@ -4744,7 +4756,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B97" t="n">
@@ -4771,14 +4783,14 @@
       <c r="I97" t="n">
         <v>8.198219999999999</v>
       </c>
-      <c r="J97" s="1" t="n">
+      <c r="J97" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K97" t="n">
-        <v>863.9213665216579</v>
+        <v>863.921366521658</v>
       </c>
       <c r="L97" t="n">
-        <v>-2.471521231841732</v>
+        <v>-2.471521231841731</v>
       </c>
       <c r="M97" t="n">
         <v>0.4575647915638049</v>
@@ -4791,7 +4803,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B98" t="n">
@@ -4818,11 +4830,11 @@
       <c r="I98" t="n">
         <v>7.736389999999999</v>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="J98" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K98" t="n">
-        <v>863.9213665216579</v>
+        <v>863.921366521658</v>
       </c>
       <c r="L98" t="n">
         <v>-2.503584335121057</v>
@@ -4838,7 +4850,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B99" t="n">
@@ -4865,11 +4877,11 @@
       <c r="I99" t="n">
         <v>7.899969999999999</v>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="J99" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="K99" t="n">
-        <v>863.9213665216579</v>
+        <v>863.921366521658</v>
       </c>
       <c r="L99" t="n">
         <v>-2.355654205189728</v>
@@ -4878,14 +4890,14 @@
         <v>0.3043101029651514</v>
       </c>
       <c r="N99" t="n">
-        <v>-3.5743901235282</v>
+        <v>-3.574390123528199</v>
       </c>
       <c r="O99" t="n">
-        <v>0.9144316029370889</v>
+        <v>0.9144316029370887</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B100" t="n">
@@ -4912,11 +4924,11 @@
       <c r="I100" t="n">
         <v>7.502359999999999</v>
       </c>
-      <c r="J100" s="1" t="n">
+      <c r="J100" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K100" t="n">
-        <v>853.7046932188317</v>
+        <v>853.7046932188318</v>
       </c>
       <c r="L100" t="n">
         <v>-2.272682832144938</v>
@@ -4925,14 +4937,14 @@
         <v>0.3023293675789138</v>
       </c>
       <c r="N100" t="n">
-        <v>-3.453806712579707</v>
+        <v>-3.453806712579706</v>
       </c>
       <c r="O100" t="n">
-        <v>0.8788003696820378</v>
+        <v>0.8788003696820377</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B101" t="n">
@@ -4959,14 +4971,14 @@
       <c r="I101" t="n">
         <v>8.811169999999999</v>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="J101" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K101" t="n">
-        <v>853.7046932188317</v>
+        <v>853.7046932188318</v>
       </c>
       <c r="L101" t="n">
-        <v>-2.167494233893925</v>
+        <v>-2.167494233893924</v>
       </c>
       <c r="M101" t="n">
         <v>0.1567286686635361</v>
@@ -4975,11 +4987,11 @@
         <v>-3.356326868951075</v>
       </c>
       <c r="O101" t="n">
-        <v>1.032109823219798</v>
+        <v>1.032109823219797</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B102" t="n">
@@ -5006,14 +5018,14 @@
       <c r="I102" t="n">
         <v>7.943439999999999</v>
       </c>
-      <c r="J102" s="1" t="n">
+      <c r="J102" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="K102" t="n">
-        <v>853.7046932188317</v>
+        <v>853.7046932188318</v>
       </c>
       <c r="L102" t="n">
-        <v>-2.074019288009395</v>
+        <v>-2.074019288009394</v>
       </c>
       <c r="M102" t="n">
         <v>0.2287676307174036</v>
@@ -5022,11 +5034,11 @@
         <v>-3.233248009440734</v>
       </c>
       <c r="O102" t="n">
-        <v>0.9304669475401188</v>
+        <v>0.9304669475401187</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B103" t="n">
@@ -5053,11 +5065,11 @@
       <c r="I103" t="n">
         <v>4.534299999999999</v>
       </c>
-      <c r="J103" s="1" t="n">
+      <c r="J103" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K103" t="n">
-        <v>861.4305877129511</v>
+        <v>861.4305877129513</v>
       </c>
       <c r="L103" t="n">
         <v>-2.294671245942201</v>
@@ -5069,11 +5081,11 @@
         <v>-3.102657414448132</v>
       </c>
       <c r="O103" t="n">
-        <v>0.5263685855453898</v>
+        <v>0.5263685855453897</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B104" t="n">
@@ -5100,27 +5112,27 @@
       <c r="I104" t="n">
         <v>2.886419999999999</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="J104" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K104" t="n">
-        <v>861.4305877129511</v>
+        <v>861.4305877129513</v>
       </c>
       <c r="L104" t="n">
         <v>-2.250906837598992</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4071134749592402</v>
+        <v>0.4071134749592401</v>
       </c>
       <c r="N104" t="n">
-        <v>-2.993086194960101</v>
+        <v>-2.9930861949601</v>
       </c>
       <c r="O104" t="n">
         <v>0.3350728475596947</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B105" t="n">
@@ -5147,17 +5159,17 @@
       <c r="I105" t="n">
         <v>0.2952499999999989</v>
       </c>
-      <c r="J105" s="1" t="n">
+      <c r="J105" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K105" t="n">
-        <v>861.4305877129511</v>
+        <v>861.4305877129513</v>
       </c>
       <c r="L105" t="n">
         <v>-2.482846593221621</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4477435622805216</v>
+        <v>0.4477435622805215</v>
       </c>
       <c r="N105" t="n">
         <v>-2.964857571148912</v>
@@ -5167,7 +5179,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B106" t="n">
@@ -5194,7 +5206,7 @@
       <c r="I106" t="n">
         <v>-1.300060000000001</v>
       </c>
-      <c r="J106" s="1" t="n">
+      <c r="J106" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K106" t="n">
@@ -5214,7 +5226,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B107" t="n">
@@ -5241,7 +5253,7 @@
       <c r="I107" t="n">
         <v>-1.551580000000001</v>
       </c>
-      <c r="J107" s="1" t="n">
+      <c r="J107" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K107" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B108" t="n">
@@ -5288,7 +5300,7 @@
       <c r="I108" t="n">
         <v>-1.618070000000001</v>
       </c>
-      <c r="J108" s="1" t="n">
+      <c r="J108" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="K108" t="n">
@@ -5308,7 +5320,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B109" t="n">
@@ -5335,27 +5347,27 @@
       <c r="I109" t="n">
         <v>0.1297299999999989</v>
       </c>
-      <c r="J109" s="1" t="n">
+      <c r="J109" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K109" t="n">
-        <v>869.9030222927097</v>
+        <v>869.9030222927099</v>
       </c>
       <c r="L109" t="n">
         <v>-2.547985169839058</v>
       </c>
       <c r="M109" t="n">
-        <v>0.2057700633436461</v>
+        <v>0.205770063343646</v>
       </c>
       <c r="N109" t="n">
         <v>-2.76866149246414</v>
       </c>
       <c r="O109" t="n">
-        <v>0.01491315660199496</v>
+        <v>0.01491315660199495</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B110" t="n">
@@ -5382,27 +5394,27 @@
       <c r="I110" t="n">
         <v>0.3622699999999989</v>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="J110" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K110" t="n">
-        <v>869.9030222927097</v>
+        <v>869.9030222927099</v>
       </c>
       <c r="L110" t="n">
-        <v>-2.608566635415651</v>
+        <v>-2.60856663541565</v>
       </c>
       <c r="M110" t="n">
-        <v>0.2080691701966477</v>
+        <v>0.2080691701966476</v>
       </c>
       <c r="N110" t="n">
-        <v>-2.858273780273585</v>
+        <v>-2.858273780273584</v>
       </c>
       <c r="O110" t="n">
-        <v>0.04164487198184493</v>
+        <v>0.04164487198184492</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B111" t="n">
@@ -5429,27 +5441,27 @@
       <c r="I111" t="n">
         <v>2.062249999999999</v>
       </c>
-      <c r="J111" s="1" t="n">
+      <c r="J111" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="K111" t="n">
-        <v>869.9030222927097</v>
+        <v>869.9030222927099</v>
       </c>
       <c r="L111" t="n">
-        <v>-2.645697211091628</v>
+        <v>-2.645697211091627</v>
       </c>
       <c r="M111" t="n">
-        <v>0.04218861075257997</v>
+        <v>0.04218861075257995</v>
       </c>
       <c r="N111" t="n">
-        <v>-2.924946729457206</v>
+        <v>-2.924946729457205</v>
       </c>
       <c r="O111" t="n">
         <v>0.2370666553801306</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B112" t="n">
@@ -5476,11 +5488,11 @@
       <c r="I112" t="n">
         <v>4.506739999999999</v>
       </c>
-      <c r="J112" s="1" t="n">
+      <c r="J112" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K112" t="n">
-        <v>855.0244018960103</v>
+        <v>855.0244018960104</v>
       </c>
       <c r="L112" t="n">
         <v>-2.636883807059121</v>
@@ -5492,11 +5504,11 @@
         <v>-3.040345976366841</v>
       </c>
       <c r="O112" t="n">
-        <v>0.5270890503249189</v>
+        <v>0.5270890503249188</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B113" t="n">
@@ -5523,27 +5535,27 @@
       <c r="I113" t="n">
         <v>4.95311</v>
       </c>
-      <c r="J113" s="1" t="n">
+      <c r="J113" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K113" t="n">
-        <v>855.0244018960103</v>
+        <v>855.0244018960104</v>
       </c>
       <c r="L113" t="n">
-        <v>-2.719571505612781</v>
+        <v>-2.71957150561278</v>
       </c>
       <c r="M113" t="n">
         <v>-0.1638549726643231</v>
       </c>
       <c r="N113" t="n">
-        <v>-3.135006432630456</v>
+        <v>-3.135006432630455</v>
       </c>
       <c r="O113" t="n">
-        <v>0.5792945779110531</v>
+        <v>0.579294577911053</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B114" t="n">
@@ -5570,11 +5582,11 @@
       <c r="I114" t="n">
         <v>5.905279999999999</v>
       </c>
-      <c r="J114" s="1" t="n">
+      <c r="J114" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="K114" t="n">
-        <v>855.0244018960103</v>
+        <v>855.0244018960104</v>
       </c>
       <c r="L114" t="n">
         <v>-2.920969266446445</v>
@@ -5583,14 +5595,14 @@
         <v>-0.4046668132894775</v>
       </c>
       <c r="N114" t="n">
-        <v>-3.206954086830249</v>
+        <v>-3.206954086830248</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6906563119023368</v>
+        <v>0.6906563119023367</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B115" t="n">
@@ -5617,17 +5629,17 @@
       <c r="I115" t="n">
         <v>8.84371</v>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="J115" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K115" t="n">
-        <v>842.4624338405586</v>
+        <v>842.4624338405587</v>
       </c>
       <c r="L115" t="n">
-        <v>-2.833123358532705</v>
+        <v>-2.833123358532704</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.6031129455632928</v>
+        <v>-0.6031129455632926</v>
       </c>
       <c r="N115" t="n">
         <v>-3.279752175303437</v>
@@ -5637,7 +5649,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B116" t="n">
@@ -5664,17 +5676,17 @@
       <c r="I116" t="n">
         <v>9.860910000000001</v>
       </c>
-      <c r="J116" s="1" t="n">
+      <c r="J116" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K116" t="n">
-        <v>842.4624338405586</v>
+        <v>842.4624338405587</v>
       </c>
       <c r="L116" t="n">
         <v>-3.057228306618415</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.8652017831550565</v>
+        <v>-0.8652017831550562</v>
       </c>
       <c r="N116" t="n">
         <v>-3.362509574564749</v>
@@ -5684,7 +5696,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B117" t="n">
@@ -5711,17 +5723,17 @@
       <c r="I117" t="n">
         <v>12.08097</v>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="J117" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="K117" t="n">
-        <v>842.4624338405586</v>
+        <v>842.4624338405587</v>
       </c>
       <c r="L117" t="n">
         <v>-2.948974221526166</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.9328605863377127</v>
+        <v>-0.9328605863377125</v>
       </c>
       <c r="N117" t="n">
         <v>-3.450117041717365</v>
@@ -5731,7 +5743,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B118" t="n">
@@ -5758,7 +5770,7 @@
       <c r="I118" t="n">
         <v>10.99841</v>
       </c>
-      <c r="J118" s="1" t="n">
+      <c r="J118" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K118" t="n">
@@ -5778,7 +5790,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B119" t="n">
@@ -5805,7 +5817,7 @@
       <c r="I119" t="n">
         <v>9.6854</v>
       </c>
-      <c r="J119" s="1" t="n">
+      <c r="J119" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K119" t="n">
@@ -5825,7 +5837,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B120" t="n">
@@ -5852,7 +5864,7 @@
       <c r="I120" t="n">
         <v>9.236190000000001</v>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="J120" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="K120" t="n">
@@ -5872,7 +5884,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B121" t="n">
@@ -5899,11 +5911,11 @@
       <c r="I121" t="n">
         <v>7.685680000000001</v>
       </c>
-      <c r="J121" s="1" t="n">
+      <c r="J121" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K121" t="n">
-        <v>864.8788502660076</v>
+        <v>864.8788502660077</v>
       </c>
       <c r="L121" t="n">
         <v>-4.063112421952717</v>
@@ -5915,11 +5927,11 @@
         <v>-3.798873101116382</v>
       </c>
       <c r="O121" t="n">
-        <v>0.8886423801016922</v>
+        <v>0.8886423801016921</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B122" t="n">
@@ -5946,14 +5958,14 @@
       <c r="I122" t="n">
         <v>5.95812</v>
       </c>
-      <c r="J122" s="1" t="n">
+      <c r="J122" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K122" t="n">
-        <v>864.8788502660076</v>
+        <v>864.8788502660077</v>
       </c>
       <c r="L122" t="n">
-        <v>-4.577172859276692</v>
+        <v>-4.577172859276691</v>
       </c>
       <c r="M122" t="n">
         <v>-1.421355140806032</v>
@@ -5962,11 +5974,11 @@
         <v>-3.844709578662119</v>
       </c>
       <c r="O122" t="n">
-        <v>0.6888964851166708</v>
+        <v>0.6888964851166707</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B123" t="n">
@@ -5993,11 +6005,11 @@
       <c r="I123" t="n">
         <v>4.993270000000001</v>
       </c>
-      <c r="J123" s="1" t="n">
+      <c r="J123" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="K123" t="n">
-        <v>864.8788502660076</v>
+        <v>864.8788502660077</v>
       </c>
       <c r="L123" t="n">
         <v>-4.848540346096162</v>
@@ -6006,14 +6018,14 @@
         <v>-1.502406955147936</v>
       </c>
       <c r="N123" t="n">
-        <v>-3.92346511763622</v>
+        <v>-3.923465117636219</v>
       </c>
       <c r="O123" t="n">
-        <v>0.5773375078445079</v>
+        <v>0.5773375078445078</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B124" t="n">
@@ -6040,27 +6052,27 @@
       <c r="I124" t="n">
         <v>4.364470000000001</v>
       </c>
-      <c r="J124" s="1" t="n">
+      <c r="J124" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K124" t="n">
-        <v>898.2531105139537</v>
+        <v>898.2531105139536</v>
       </c>
       <c r="L124" t="n">
-        <v>-4.851416542834565</v>
+        <v>-4.851416542834566</v>
       </c>
       <c r="M124" t="n">
-        <v>-1.505032361342431</v>
+        <v>-1.505032361342432</v>
       </c>
       <c r="N124" t="n">
-        <v>-3.832261708540474</v>
+        <v>-3.832261708540475</v>
       </c>
       <c r="O124" t="n">
-        <v>0.485884206680095</v>
+        <v>0.4858842066800951</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B125" t="n">
@@ -6087,14 +6099,14 @@
       <c r="I125" t="n">
         <v>3.48327</v>
       </c>
-      <c r="J125" s="1" t="n">
+      <c r="J125" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K125" t="n">
-        <v>898.2531105139537</v>
+        <v>898.2531105139536</v>
       </c>
       <c r="L125" t="n">
-        <v>-5.067057321288614</v>
+        <v>-5.067057321288615</v>
       </c>
       <c r="M125" t="n">
         <v>-1.586857850327319</v>
@@ -6103,11 +6115,11 @@
         <v>-3.867975472984491</v>
       </c>
       <c r="O125" t="n">
-        <v>0.3877826816549487</v>
+        <v>0.3877826816549488</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B126" t="n">
@@ -6134,27 +6146,27 @@
       <c r="I126" t="n">
         <v>3.21001</v>
       </c>
-      <c r="J126" s="1" t="n">
+      <c r="J126" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="K126" t="n">
-        <v>898.2531105139537</v>
+        <v>898.2531105139536</v>
       </c>
       <c r="L126" t="n">
-        <v>-5.19252307106544</v>
+        <v>-5.192523071065441</v>
       </c>
       <c r="M126" t="n">
         <v>-1.588973067049377</v>
       </c>
       <c r="N126" t="n">
-        <v>-3.960904736488224</v>
+        <v>-3.960904736488225</v>
       </c>
       <c r="O126" t="n">
         <v>0.3573614121039145</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B127" t="n">
@@ -6181,14 +6193,14 @@
       <c r="I127" t="n">
         <v>3.74216</v>
       </c>
-      <c r="J127" s="1" t="n">
+      <c r="J127" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K127" t="n">
-        <v>898.9553869128589</v>
+        <v>898.9553869128588</v>
       </c>
       <c r="L127" t="n">
-        <v>-5.125282152012537</v>
+        <v>-5.125282152012538</v>
       </c>
       <c r="M127" t="n">
         <v>-1.494846150947269</v>
@@ -6197,11 +6209,11 @@
         <v>-4.046708049097697</v>
       </c>
       <c r="O127" t="n">
-        <v>0.4162787224459616</v>
+        <v>0.4162787224459617</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B128" t="n">
@@ -6228,27 +6240,27 @@
       <c r="I128" t="n">
         <v>6.06072</v>
       </c>
-      <c r="J128" s="1" t="n">
+      <c r="J128" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K128" t="n">
-        <v>898.9553869128589</v>
+        <v>898.9553869128588</v>
       </c>
       <c r="L128" t="n">
-        <v>-4.854523443022683</v>
+        <v>-4.854523443022684</v>
       </c>
       <c r="M128" t="n">
         <v>-1.366141209985371</v>
       </c>
       <c r="N128" t="n">
-        <v>-4.162571418422048</v>
+        <v>-4.162571418422049</v>
       </c>
       <c r="O128" t="n">
-        <v>0.6741958597982685</v>
+        <v>0.6741958597982686</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B129" t="n">
@@ -6275,14 +6287,14 @@
       <c r="I129" t="n">
         <v>7.804049999999999</v>
       </c>
-      <c r="J129" s="1" t="n">
+      <c r="J129" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="K129" t="n">
-        <v>898.9553869128589</v>
+        <v>898.9553869128588</v>
       </c>
       <c r="L129" t="n">
-        <v>-4.552172509976494</v>
+        <v>-4.552172509976495</v>
       </c>
       <c r="M129" t="n">
         <v>-1.254900984434897</v>
@@ -6295,7 +6307,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B130" t="n">
@@ -6322,27 +6334,27 @@
       <c r="I130" t="n">
         <v>14.08367</v>
       </c>
-      <c r="J130" s="1" t="n">
+      <c r="J130" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K130" t="n">
-        <v>846.4394557072658</v>
+        <v>846.4394557072657</v>
       </c>
       <c r="L130" t="n">
-        <v>-4.005838784023609</v>
+        <v>-4.00583878402361</v>
       </c>
       <c r="M130" t="n">
-        <v>-1.218988544358262</v>
+        <v>-1.218988544358263</v>
       </c>
       <c r="N130" t="n">
-        <v>-4.450715257421644</v>
+        <v>-4.450715257421645</v>
       </c>
       <c r="O130" t="n">
         <v>1.66387210627274</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B131" t="n">
@@ -6369,11 +6381,11 @@
       <c r="I131" t="n">
         <v>20.77072</v>
       </c>
-      <c r="J131" s="1" t="n">
+      <c r="J131" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K131" t="n">
-        <v>846.4394557072658</v>
+        <v>846.4394557072657</v>
       </c>
       <c r="L131" t="n">
         <v>-3.203182438765805</v>
@@ -6382,14 +6394,14 @@
         <v>-1.171731768069902</v>
       </c>
       <c r="N131" t="n">
-        <v>-4.485336753149904</v>
+        <v>-4.485336753149905</v>
       </c>
       <c r="O131" t="n">
         <v>2.453893170970445</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B132" t="n">
@@ -6416,14 +6428,14 @@
       <c r="I132" t="n">
         <v>26.56942</v>
       </c>
-      <c r="J132" s="1" t="n">
+      <c r="J132" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="K132" t="n">
-        <v>846.4394557072658</v>
+        <v>846.4394557072657</v>
       </c>
       <c r="L132" t="n">
-        <v>-2.5107525242006</v>
+        <v>-2.510752524200601</v>
       </c>
       <c r="M132" t="n">
         <v>-1.180710555564691</v>
@@ -6432,11 +6444,11 @@
         <v>-4.468997722748204</v>
       </c>
       <c r="O132" t="n">
-        <v>3.138962842628737</v>
+        <v>3.138962842628738</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B133" t="n">
@@ -6463,7 +6475,7 @@
       <c r="I133" t="n">
         <v>31.91968</v>
       </c>
-      <c r="J133" s="1" t="n">
+      <c r="J133" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K133" t="n">
@@ -6483,7 +6495,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B134" t="n">
@@ -6510,7 +6522,7 @@
       <c r="I134" t="n">
         <v>36.77216</v>
       </c>
-      <c r="J134" s="1" t="n">
+      <c r="J134" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K134" t="n">
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B135" t="n">
@@ -6557,7 +6569,7 @@
       <c r="I135" t="n">
         <v>40.31249</v>
       </c>
-      <c r="J135" s="1" t="n">
+      <c r="J135" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="K135" t="n">
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B136" t="n">
@@ -6604,7 +6616,7 @@
       <c r="I136" t="n">
         <v>44.4252</v>
       </c>
-      <c r="J136" s="1" t="n">
+      <c r="J136" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K136" t="n">
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B137" t="n">
@@ -6651,7 +6663,7 @@
       <c r="I137" t="n">
         <v>48.80586</v>
       </c>
-      <c r="J137" s="1" t="n">
+      <c r="J137" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K137" t="n">
@@ -6671,7 +6683,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B138" t="n">
@@ -6698,7 +6710,7 @@
       <c r="I138" t="n">
         <v>53.917</v>
       </c>
-      <c r="J138" s="1" t="n">
+      <c r="J138" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="K138" t="n">
@@ -6718,7 +6730,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B139" t="n">
@@ -6745,7 +6757,7 @@
       <c r="I139" t="n">
         <v>56.12547</v>
       </c>
-      <c r="J139" s="1" t="n">
+      <c r="J139" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K139" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B140" t="n">
@@ -6792,7 +6804,7 @@
       <c r="I140" t="n">
         <v>59.44548</v>
       </c>
-      <c r="J140" s="1" t="n">
+      <c r="J140" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K140" t="n">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B141" t="n">
@@ -6839,7 +6851,7 @@
       <c r="I141" t="n">
         <v>60.96964</v>
       </c>
-      <c r="J141" s="1" t="n">
+      <c r="J141" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="K141" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B142" t="n">
@@ -6886,27 +6898,27 @@
       <c r="I142" t="n">
         <v>61.12259999999999</v>
       </c>
-      <c r="J142" s="1" t="n">
+      <c r="J142" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K142" t="n">
-        <v>752.4178296031996</v>
+        <v>752.4178296031997</v>
       </c>
       <c r="L142" t="n">
         <v>2.688665686014994</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.8210863375284545</v>
+        <v>-0.8210863375284544</v>
       </c>
       <c r="N142" t="n">
-        <v>-4.613739684811474</v>
+        <v>-4.613739684811473</v>
       </c>
       <c r="O142" t="n">
-        <v>8.123491708354923</v>
+        <v>8.123491708354921</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B143" t="n">
@@ -6933,27 +6945,27 @@
       <c r="I143" t="n">
         <v>60.94875</v>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="J143" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K143" t="n">
-        <v>752.4178296031996</v>
+        <v>752.4178296031997</v>
       </c>
       <c r="L143" t="n">
         <v>2.580082400524423</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.9857554816200305</v>
+        <v>-0.9857554816200302</v>
       </c>
       <c r="N143" t="n">
-        <v>-4.534548313135151</v>
+        <v>-4.53454831313515</v>
       </c>
       <c r="O143" t="n">
-        <v>8.100386195279604</v>
+        <v>8.100386195279603</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B144" t="n">
@@ -6980,11 +6992,11 @@
       <c r="I144" t="n">
         <v>59.31162999999999</v>
       </c>
-      <c r="J144" s="1" t="n">
+      <c r="J144" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="K144" t="n">
-        <v>752.4178296031996</v>
+        <v>752.4178296031997</v>
       </c>
       <c r="L144" t="n">
         <v>2.27745799285976</v>
@@ -6993,14 +7005,14 @@
         <v>-1.121982981776499</v>
       </c>
       <c r="N144" t="n">
-        <v>-4.483363986442215</v>
+        <v>-4.483363986442214</v>
       </c>
       <c r="O144" t="n">
-        <v>7.882804961078474</v>
+        <v>7.882804961078473</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B145" t="n">
@@ -7027,7 +7039,7 @@
       <c r="I145" t="n">
         <v>57.56779</v>
       </c>
-      <c r="J145" s="1" t="n">
+      <c r="J145" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K145" t="n">
@@ -7047,7 +7059,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B146" t="n">
@@ -7074,7 +7086,7 @@
       <c r="I146" t="n">
         <v>57.90269</v>
       </c>
-      <c r="J146" s="1" t="n">
+      <c r="J146" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K146" t="n">
@@ -7094,7 +7106,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B147" t="n">
@@ -7121,7 +7133,7 @@
       <c r="I147" t="n">
         <v>57.78574999999999</v>
       </c>
-      <c r="J147" s="1" t="n">
+      <c r="J147" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="K147" t="n">
@@ -7141,7 +7153,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B148" t="n">
@@ -7168,27 +7180,27 @@
       <c r="I148" t="n">
         <v>52.78822</v>
       </c>
-      <c r="J148" s="1" t="n">
+      <c r="J148" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K148" t="n">
-        <v>778.2260275513437</v>
+        <v>778.2260275513438</v>
       </c>
       <c r="L148" t="n">
         <v>1.108675332685499</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.484658645554967</v>
+        <v>-1.484658645554966</v>
       </c>
       <c r="N148" t="n">
-        <v>-4.189812322596573</v>
+        <v>-4.189812322596572</v>
       </c>
       <c r="O148" t="n">
-        <v>6.783147585810767</v>
+        <v>6.783147585810766</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B149" t="n">
@@ -7215,11 +7227,11 @@
       <c r="I149" t="n">
         <v>46.00505</v>
       </c>
-      <c r="J149" s="1" t="n">
+      <c r="J149" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K149" t="n">
-        <v>778.2260275513437</v>
+        <v>778.2260275513438</v>
       </c>
       <c r="L149" t="n">
         <v>0.4912454562884402</v>
@@ -7228,14 +7240,14 @@
         <v>-1.45343378395986</v>
       </c>
       <c r="N149" t="n">
-        <v>-3.966846251227864</v>
+        <v>-3.966846251227863</v>
       </c>
       <c r="O149" t="n">
-        <v>5.911528061423621</v>
+        <v>5.91152806142362</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B150" t="n">
@@ -7262,27 +7274,27 @@
       <c r="I150" t="n">
         <v>39.39304</v>
       </c>
-      <c r="J150" s="1" t="n">
+      <c r="J150" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="K150" t="n">
-        <v>778.2260275513437</v>
+        <v>778.2260275513438</v>
       </c>
       <c r="L150" t="n">
-        <v>-0.1841367352501529</v>
+        <v>-0.1841367352501528</v>
       </c>
       <c r="M150" t="n">
         <v>-1.527962260195093</v>
       </c>
       <c r="N150" t="n">
-        <v>-3.718072767502113</v>
+        <v>-3.718072767502112</v>
       </c>
       <c r="O150" t="n">
         <v>5.061902147368238</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B151" t="n">
@@ -7309,27 +7321,27 @@
       <c r="I151" t="n">
         <v>37.28101</v>
       </c>
-      <c r="J151" s="1" t="n">
+      <c r="J151" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K151" t="n">
-        <v>754.008536326724</v>
+        <v>754.0085363267242</v>
       </c>
       <c r="L151" t="n">
-        <v>-0.5193575153774034</v>
+        <v>-0.5193575153774033</v>
       </c>
       <c r="M151" t="n">
-        <v>-1.758600779853006</v>
+        <v>-1.758600779853005</v>
       </c>
       <c r="N151" t="n">
         <v>-3.705127814082791</v>
       </c>
       <c r="O151" t="n">
-        <v>4.94437505729319</v>
+        <v>4.944375057293189</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B152" t="n">
@@ -7356,27 +7368,27 @@
       <c r="I152" t="n">
         <v>32.8163</v>
       </c>
-      <c r="J152" s="1" t="n">
+      <c r="J152" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K152" t="n">
-        <v>754.008536326724</v>
+        <v>754.0085363267242</v>
       </c>
       <c r="L152" t="n">
         <v>-1.184999846756154</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.924646645341389</v>
+        <v>-1.924646645341388</v>
       </c>
       <c r="N152" t="n">
-        <v>-3.612594378931114</v>
+        <v>-3.612594378931113</v>
       </c>
       <c r="O152" t="n">
-        <v>4.352245156251145</v>
+        <v>4.352245156251143</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B153" t="n">
@@ -7403,27 +7415,27 @@
       <c r="I153" t="n">
         <v>26.95827</v>
       </c>
-      <c r="J153" s="1" t="n">
+      <c r="J153" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="K153" t="n">
-        <v>754.008536326724</v>
+        <v>754.0085363267242</v>
       </c>
       <c r="L153" t="n">
-        <v>-2.316021524779264</v>
+        <v>-2.316021524779263</v>
       </c>
       <c r="M153" t="n">
-        <v>-2.373580554828751</v>
+        <v>-2.37358055482875</v>
       </c>
       <c r="N153" t="n">
         <v>-3.517763887557185</v>
       </c>
       <c r="O153" t="n">
-        <v>3.575326896341469</v>
+        <v>3.575326896341468</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B154" t="n">
@@ -7450,7 +7462,7 @@
       <c r="I154" t="n">
         <v>23.34406</v>
       </c>
-      <c r="J154" s="1" t="n">
+      <c r="J154" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K154" t="n">
@@ -7470,7 +7482,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B155" t="n">
@@ -7497,7 +7509,7 @@
       <c r="I155" t="n">
         <v>19.61043</v>
       </c>
-      <c r="J155" s="1" t="n">
+      <c r="J155" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K155" t="n">
@@ -7517,7 +7529,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B156" t="n">
@@ -7544,7 +7556,7 @@
       <c r="I156" t="n">
         <v>16.41961</v>
       </c>
-      <c r="J156" s="1" t="n">
+      <c r="J156" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="K156" t="n">
@@ -7564,7 +7576,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B157" t="n">
@@ -7591,7 +7603,7 @@
       <c r="I157" t="n">
         <v>15.58579</v>
       </c>
-      <c r="J157" s="1" t="n">
+      <c r="J157" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K157" t="n">
@@ -7611,7 +7623,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B158" t="n">
@@ -7638,7 +7650,7 @@
       <c r="I158" t="n">
         <v>13.06948</v>
       </c>
-      <c r="J158" s="1" t="n">
+      <c r="J158" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K158" t="n">
@@ -7658,7 +7670,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B159" t="n">
@@ -7685,7 +7697,7 @@
       <c r="I159" t="n">
         <v>10.72014</v>
       </c>
-      <c r="J159" s="1" t="n">
+      <c r="J159" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="K159" t="n">
@@ -7705,7 +7717,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B160" t="n">
@@ -7732,7 +7744,7 @@
       <c r="I160" t="n">
         <v>11.85764</v>
       </c>
-      <c r="J160" s="1" t="n">
+      <c r="J160" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K160" t="n">
@@ -7752,7 +7764,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B161" t="n">
@@ -7779,7 +7791,7 @@
       <c r="I161" t="n">
         <v>16.75192</v>
       </c>
-      <c r="J161" s="1" t="n">
+      <c r="J161" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K161" t="n">
@@ -7799,7 +7811,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B162" t="n">
@@ -7826,7 +7838,7 @@
       <c r="I162" t="n">
         <v>17.78087</v>
       </c>
-      <c r="J162" s="1" t="n">
+      <c r="J162" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="K162" t="n">
@@ -7846,7 +7858,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B163" t="n">
@@ -7873,7 +7885,7 @@
       <c r="I163" t="n">
         <v>19.18315</v>
       </c>
-      <c r="J163" s="1" t="n">
+      <c r="J163" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K163" t="n">
@@ -7893,7 +7905,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B164" t="n">
@@ -7920,7 +7932,7 @@
       <c r="I164" t="n">
         <v>21.03445</v>
       </c>
-      <c r="J164" s="1" t="n">
+      <c r="J164" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K164" t="n">
@@ -7940,7 +7952,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B165" t="n">
@@ -7967,7 +7979,7 @@
       <c r="I165" t="n">
         <v>25.49619</v>
       </c>
-      <c r="J165" s="1" t="n">
+      <c r="J165" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K165" t="n">
@@ -7987,7 +7999,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B166" t="n">
@@ -8014,7 +8026,7 @@
       <c r="I166" t="n">
         <v>28.66052</v>
       </c>
-      <c r="J166" s="1" t="n">
+      <c r="J166" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K166" t="n">
@@ -8034,7 +8046,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B167" t="n">
@@ -8061,7 +8073,7 @@
       <c r="I167" t="n">
         <v>33.67982</v>
       </c>
-      <c r="J167" s="1" t="n">
+      <c r="J167" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K167" t="n">
@@ -8081,7 +8093,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B168" t="n">
@@ -8108,7 +8120,7 @@
       <c r="I168" t="n">
         <v>35.21025</v>
       </c>
-      <c r="J168" s="1" t="n">
+      <c r="J168" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="K168" t="n">
@@ -8128,7 +8140,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B169" t="n">
@@ -8155,7 +8167,7 @@
       <c r="I169" t="n">
         <v>37.12937</v>
       </c>
-      <c r="J169" s="1" t="n">
+      <c r="J169" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K169" t="n">
@@ -8175,7 +8187,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B170" t="n">
@@ -8202,7 +8214,7 @@
       <c r="I170" t="n">
         <v>37.22411</v>
       </c>
-      <c r="J170" s="1" t="n">
+      <c r="J170" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K170" t="n">
@@ -8222,7 +8234,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B171" t="n">
@@ -8249,7 +8261,7 @@
       <c r="I171" t="n">
         <v>38.29664</v>
       </c>
-      <c r="J171" s="1" t="n">
+      <c r="J171" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="K171" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B172" t="n">
@@ -8296,7 +8308,7 @@
       <c r="I172" t="n">
         <v>40.84047</v>
       </c>
-      <c r="J172" s="1" t="n">
+      <c r="J172" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K172" t="n">
@@ -8316,7 +8328,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B173" t="n">
@@ -8343,7 +8355,7 @@
       <c r="I173" t="n">
         <v>43.37856</v>
       </c>
-      <c r="J173" s="1" t="n">
+      <c r="J173" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K173" t="n">
@@ -8363,7 +8375,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B174" t="n">
@@ -8390,7 +8402,7 @@
       <c r="I174" t="n">
         <v>45.0951</v>
       </c>
-      <c r="J174" s="1" t="n">
+      <c r="J174" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="K174" t="n">
@@ -8410,7 +8422,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B175" t="n">
@@ -8437,7 +8449,7 @@
       <c r="I175" t="n">
         <v>47.7854</v>
       </c>
-      <c r="J175" s="1" t="n">
+      <c r="J175" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K175" t="n">
@@ -8457,7 +8469,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B176" t="n">
@@ -8484,7 +8496,7 @@
       <c r="I176" t="n">
         <v>48.45027</v>
       </c>
-      <c r="J176" s="1" t="n">
+      <c r="J176" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K176" t="n">
@@ -8504,7 +8516,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B177" t="n">
@@ -8531,7 +8543,7 @@
       <c r="I177" t="n">
         <v>49.68133</v>
       </c>
-      <c r="J177" s="1" t="n">
+      <c r="J177" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K177" t="n">
@@ -8551,7 +8563,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B178" t="n">
@@ -8578,7 +8590,7 @@
       <c r="I178" t="n">
         <v>50.47562</v>
       </c>
-      <c r="J178" s="1" t="n">
+      <c r="J178" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K178" t="n">
@@ -8598,7 +8610,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B179" t="n">
@@ -8625,7 +8637,7 @@
       <c r="I179" t="n">
         <v>50.11399</v>
       </c>
-      <c r="J179" s="1" t="n">
+      <c r="J179" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K179" t="n">
@@ -8645,7 +8657,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B180" t="n">
@@ -8672,7 +8684,7 @@
       <c r="I180" t="n">
         <v>52.17445</v>
       </c>
-      <c r="J180" s="1" t="n">
+      <c r="J180" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="K180" t="n">
@@ -8692,7 +8704,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B181" t="n">
@@ -8719,27 +8731,27 @@
       <c r="I181" t="n">
         <v>52.84970999999999</v>
       </c>
-      <c r="J181" s="1" t="n">
+      <c r="J181" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K181" t="n">
-        <v>913.1863831015422</v>
+        <v>913.1863831015423</v>
       </c>
       <c r="L181" t="n">
-        <v>-5.110457280527664</v>
+        <v>-5.110457280527663</v>
       </c>
       <c r="M181" t="n">
-        <v>-2.122239266662941</v>
+        <v>-2.12223926666294</v>
       </c>
       <c r="N181" t="n">
-        <v>-8.77561377205611</v>
+        <v>-8.775613772056108</v>
       </c>
       <c r="O181" t="n">
-        <v>5.787395758191386</v>
+        <v>5.787395758191385</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B182" t="n">
@@ -8766,27 +8778,27 @@
       <c r="I182" t="n">
         <v>53.61758</v>
       </c>
-      <c r="J182" s="1" t="n">
+      <c r="J182" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K182" t="n">
-        <v>913.1863831015422</v>
+        <v>913.1863831015423</v>
       </c>
       <c r="L182" t="n">
-        <v>-5.448832891156584</v>
+        <v>-5.448832891156583</v>
       </c>
       <c r="M182" t="n">
         <v>-2.589613734677255</v>
       </c>
       <c r="N182" t="n">
-        <v>-8.730701801445353</v>
+        <v>-8.730701801445351</v>
       </c>
       <c r="O182" t="n">
-        <v>5.871482644966024</v>
+        <v>5.871482644966023</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B183" t="n">
@@ -8813,27 +8825,27 @@
       <c r="I183" t="n">
         <v>52.49454</v>
       </c>
-      <c r="J183" s="1" t="n">
+      <c r="J183" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="K183" t="n">
-        <v>913.1863831015422</v>
+        <v>913.1863831015423</v>
       </c>
       <c r="L183" t="n">
-        <v>-5.824221756281483</v>
+        <v>-5.824221756281482</v>
       </c>
       <c r="M183" t="n">
-        <v>-2.967411746544498</v>
+        <v>-2.967411746544497</v>
       </c>
       <c r="N183" t="n">
-        <v>-8.605312283906667</v>
+        <v>-8.605312283906665</v>
       </c>
       <c r="O183" t="n">
-        <v>5.74850227416968</v>
+        <v>5.748502274169679</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B184" t="n">
@@ -8860,7 +8872,7 @@
       <c r="I184" t="n">
         <v>50.79395</v>
       </c>
-      <c r="J184" s="1" t="n">
+      <c r="J184" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K184" t="n">
@@ -8880,7 +8892,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B185" t="n">
@@ -8907,7 +8919,7 @@
       <c r="I185" t="n">
         <v>46.78892</v>
       </c>
-      <c r="J185" s="1" t="n">
+      <c r="J185" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K185" t="n">
@@ -8927,7 +8939,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B186" t="n">
@@ -8954,7 +8966,7 @@
       <c r="I186" t="n">
         <v>45.03124</v>
       </c>
-      <c r="J186" s="1" t="n">
+      <c r="J186" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="K186" t="n">
@@ -8974,7 +8986,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B187" t="n">
@@ -9001,7 +9013,7 @@
       <c r="I187" t="n">
         <v>45.92217</v>
       </c>
-      <c r="J187" s="1" t="n">
+      <c r="J187" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K187" t="n">
@@ -9011,17 +9023,17 @@
         <v>-5.067266260666861</v>
       </c>
       <c r="M187" t="n">
-        <v>-2.879181220168937</v>
+        <v>-2.879181220168936</v>
       </c>
       <c r="N187" t="n">
-        <v>-6.621813643213901</v>
+        <v>-6.6218136432139</v>
       </c>
       <c r="O187" t="n">
-        <v>4.433729568203795</v>
+        <v>4.433729568203793</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B188" t="n">
@@ -9048,27 +9060,27 @@
       <c r="I188" t="n">
         <v>42.09453999999999</v>
       </c>
-      <c r="J188" s="1" t="n">
+      <c r="J188" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K188" t="n">
         <v>1035.745849934734</v>
       </c>
       <c r="L188" t="n">
-        <v>-5.281314909777037</v>
+        <v>-5.281314909777036</v>
       </c>
       <c r="M188" t="n">
-        <v>-2.953620330887902</v>
+        <v>-2.953620330887901</v>
       </c>
       <c r="N188" t="n">
-        <v>-6.39187016816642</v>
+        <v>-6.391870168166419</v>
       </c>
       <c r="O188" t="n">
-        <v>4.064176554765102</v>
+        <v>4.064176554765101</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B189" t="n">
@@ -9095,27 +9107,27 @@
       <c r="I189" t="n">
         <v>41.36029</v>
       </c>
-      <c r="J189" s="1" t="n">
+      <c r="J189" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="K189" t="n">
         <v>1035.745849934734</v>
       </c>
       <c r="L189" t="n">
-        <v>-5.092562041481867</v>
+        <v>-5.092562041481866</v>
       </c>
       <c r="M189" t="n">
-        <v>-3.028928380642497</v>
+        <v>-3.028928380642496</v>
       </c>
       <c r="N189" t="n">
-        <v>-6.056918307126512</v>
+        <v>-6.056918307126511</v>
       </c>
       <c r="O189" t="n">
-        <v>3.99328561177496</v>
+        <v>3.993285611774959</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B190" t="n">
@@ -9142,27 +9154,27 @@
       <c r="I190" t="n">
         <v>41.33475</v>
       </c>
-      <c r="J190" s="1" t="n">
+      <c r="J190" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K190" t="n">
         <v>1087.793792245752</v>
       </c>
       <c r="L190" t="n">
-        <v>-4.41784098627611</v>
+        <v>-4.417840986276109</v>
       </c>
       <c r="M190" t="n">
         <v>-2.743718544153749</v>
       </c>
       <c r="N190" t="n">
-        <v>-5.473991525275002</v>
+        <v>-5.473991525275</v>
       </c>
       <c r="O190" t="n">
-        <v>3.799870002444522</v>
+        <v>3.799870002444521</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B191" t="n">
@@ -9189,27 +9201,27 @@
       <c r="I191" t="n">
         <v>38.13951</v>
       </c>
-      <c r="J191" s="1" t="n">
+      <c r="J191" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K191" t="n">
         <v>1087.793792245752</v>
       </c>
       <c r="L191" t="n">
-        <v>-4.34677972397527</v>
+        <v>-4.346779723975269</v>
       </c>
       <c r="M191" t="n">
-        <v>-2.592035384003188</v>
+        <v>-2.592035384003187</v>
       </c>
       <c r="N191" t="n">
         <v>-5.260877604555341</v>
       </c>
       <c r="O191" t="n">
-        <v>3.506134183875139</v>
+        <v>3.506134183875138</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B192" t="n">
@@ -9236,27 +9248,27 @@
       <c r="I192" t="n">
         <v>35.59753</v>
       </c>
-      <c r="J192" s="1" t="n">
+      <c r="J192" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="K192" t="n">
         <v>1087.793792245752</v>
       </c>
       <c r="L192" t="n">
-        <v>-4.220836736456318</v>
+        <v>-4.220836736456317</v>
       </c>
       <c r="M192" t="n">
-        <v>-2.491280993988026</v>
+        <v>-2.491280993988025</v>
       </c>
       <c r="N192" t="n">
         <v>-5.002006849815474</v>
       </c>
       <c r="O192" t="n">
-        <v>3.272452026639062</v>
+        <v>3.272452026639061</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B193" t="n">
@@ -9283,7 +9295,7 @@
       <c r="I193" t="n">
         <v>36.55256</v>
       </c>
-      <c r="J193" s="1" t="n">
+      <c r="J193" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K193" t="n">
@@ -9303,7 +9315,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B194" t="n">
@@ -9330,7 +9342,7 @@
       <c r="I194" t="n">
         <v>37.88603</v>
       </c>
-      <c r="J194" s="1" t="n">
+      <c r="J194" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K194" t="n">
@@ -9350,7 +9362,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B195" t="n">
@@ -9377,7 +9389,7 @@
       <c r="I195" t="n">
         <v>39.20635</v>
       </c>
-      <c r="J195" s="1" t="n">
+      <c r="J195" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="K195" t="n">
@@ -9397,7 +9409,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B196" t="n">
@@ -9424,7 +9436,7 @@
       <c r="I196" t="n">
         <v>39.57944</v>
       </c>
-      <c r="J196" s="1" t="n">
+      <c r="J196" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K196" t="n">
@@ -9444,7 +9456,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B197" t="n">
@@ -9471,7 +9483,7 @@
       <c r="I197" t="n">
         <v>39.32009</v>
       </c>
-      <c r="J197" s="1" t="n">
+      <c r="J197" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K197" t="n">
@@ -9491,7 +9503,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B198" t="n">
@@ -9518,7 +9530,7 @@
       <c r="I198" t="n">
         <v>43.90715</v>
       </c>
-      <c r="J198" s="1" t="n">
+      <c r="J198" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="K198" t="n">
@@ -9538,7 +9550,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B199" t="n">
@@ -9565,7 +9577,7 @@
       <c r="I199" t="n">
         <v>42.71823</v>
       </c>
-      <c r="J199" s="1" t="n">
+      <c r="J199" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K199" t="n">
@@ -9585,7 +9597,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B200" t="n">
@@ -9612,7 +9624,7 @@
       <c r="I200" t="n">
         <v>47.2887</v>
       </c>
-      <c r="J200" s="1" t="n">
+      <c r="J200" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K200" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B201" t="n">
@@ -9659,7 +9671,7 @@
       <c r="I201" t="n">
         <v>49.28131</v>
       </c>
-      <c r="J201" s="1" t="n">
+      <c r="J201" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="K201" t="n">
@@ -9679,7 +9691,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B202" t="n">
@@ -9706,7 +9718,7 @@
       <c r="I202" t="n">
         <v>48.84308</v>
       </c>
-      <c r="J202" s="1" t="n">
+      <c r="J202" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K202" t="n">
@@ -9726,7 +9738,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B203" t="n">
@@ -9753,7 +9765,7 @@
       <c r="I203" t="n">
         <v>50.89373</v>
       </c>
-      <c r="J203" s="1" t="n">
+      <c r="J203" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K203" t="n">
@@ -9773,7 +9785,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B204" t="n">
@@ -9800,7 +9812,7 @@
       <c r="I204" t="n">
         <v>51.48607</v>
       </c>
-      <c r="J204" s="1" t="n">
+      <c r="J204" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="K204" t="n">
@@ -9820,7 +9832,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B205" t="n">
@@ -9847,7 +9859,7 @@
       <c r="I205" t="n">
         <v>49.10726</v>
       </c>
-      <c r="J205" s="1" t="n">
+      <c r="J205" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K205" t="n">
@@ -9867,7 +9879,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B206" t="n">
@@ -9894,7 +9906,7 @@
       <c r="I206" t="n">
         <v>47.72986</v>
       </c>
-      <c r="J206" s="1" t="n">
+      <c r="J206" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K206" t="n">
@@ -9914,7 +9926,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B207" t="n">
@@ -9941,7 +9953,7 @@
       <c r="I207" t="n">
         <v>46.85917999999999</v>
       </c>
-      <c r="J207" s="1" t="n">
+      <c r="J207" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="K207" t="n">
@@ -9961,7 +9973,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B208" t="n">
@@ -9988,7 +10000,7 @@
       <c r="I208" t="n">
         <v>46.18819</v>
       </c>
-      <c r="J208" s="1" t="n">
+      <c r="J208" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K208" t="n">
@@ -10008,7 +10020,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B209" t="n">
@@ -10035,7 +10047,7 @@
       <c r="I209" t="n">
         <v>43.77743</v>
       </c>
-      <c r="J209" s="1" t="n">
+      <c r="J209" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K209" t="n">
@@ -10055,7 +10067,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B210" t="n">
@@ -10082,7 +10094,7 @@
       <c r="I210" t="n">
         <v>43.79429</v>
       </c>
-      <c r="J210" s="1" t="n">
+      <c r="J210" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="K210" t="n">
@@ -10102,7 +10114,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B211" t="n">
@@ -10129,7 +10141,7 @@
       <c r="I211" t="n">
         <v>41.44814</v>
       </c>
-      <c r="J211" s="1" t="n">
+      <c r="J211" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K211" t="n">
@@ -10149,7 +10161,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B212" t="n">
@@ -10176,7 +10188,7 @@
       <c r="I212" t="n">
         <v>41.90796</v>
       </c>
-      <c r="J212" s="1" t="n">
+      <c r="J212" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K212" t="n">
@@ -10192,11 +10204,11 @@
         <v>-3.33730835715357</v>
       </c>
       <c r="O212" t="n">
-        <v>2.843490572800922</v>
+        <v>2.843490572800921</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B213" t="n">
@@ -10223,7 +10235,7 @@
       <c r="I213" t="n">
         <v>41.96055</v>
       </c>
-      <c r="J213" s="1" t="n">
+      <c r="J213" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="K213" t="n">
@@ -10243,7 +10255,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B214" t="n">
@@ -10270,7 +10282,7 @@
       <c r="I214" t="n">
         <v>40.90523</v>
       </c>
-      <c r="J214" s="1" t="n">
+      <c r="J214" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K214" t="n">
@@ -10290,7 +10302,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B215" t="n">
@@ -10317,7 +10329,7 @@
       <c r="I215" t="n">
         <v>40.92907</v>
       </c>
-      <c r="J215" s="1" t="n">
+      <c r="J215" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K215" t="n">
@@ -10337,7 +10349,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B216" t="n">
@@ -10364,7 +10376,7 @@
       <c r="I216" t="n">
         <v>39.97973999999999</v>
       </c>
-      <c r="J216" s="1" t="n">
+      <c r="J216" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="K216" t="n">
@@ -10384,7 +10396,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B217" t="n">
@@ -10411,7 +10423,7 @@
       <c r="I217" t="n">
         <v>37.07607</v>
       </c>
-      <c r="J217" s="1" t="n">
+      <c r="J217" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K217" t="n">
@@ -10431,7 +10443,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B218" t="n">
@@ -10458,7 +10470,7 @@
       <c r="I218" t="n">
         <v>33.66558</v>
       </c>
-      <c r="J218" s="1" t="n">
+      <c r="J218" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K218" t="n">
@@ -10478,7 +10490,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B219" t="n">
@@ -10505,7 +10517,7 @@
       <c r="I219" t="n">
         <v>30.87032999999999</v>
       </c>
-      <c r="J219" s="1" t="n">
+      <c r="J219" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="K219" t="n">
@@ -10525,7 +10537,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B220" t="n">
@@ -10552,27 +10564,27 @@
       <c r="I220" t="n">
         <v>26.2946</v>
       </c>
-      <c r="J220" s="1" t="n">
+      <c r="J220" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K220" t="n">
-        <v>1640.339363149402</v>
+        <v>1640.339363149401</v>
       </c>
       <c r="L220" t="n">
-        <v>-2.439190383335074</v>
+        <v>-2.439190383335075</v>
       </c>
       <c r="M220" t="n">
         <v>-1.274492368448753</v>
       </c>
       <c r="N220" t="n">
-        <v>-2.76769252874809</v>
+        <v>-2.767692528748091</v>
       </c>
       <c r="O220" t="n">
         <v>1.602997562011508</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B221" t="n">
@@ -10599,11 +10611,11 @@
       <c r="I221" t="n">
         <v>29.26144</v>
       </c>
-      <c r="J221" s="1" t="n">
+      <c r="J221" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K221" t="n">
-        <v>1640.339363149402</v>
+        <v>1640.339363149401</v>
       </c>
       <c r="L221" t="n">
         <v>-2.263495032437279</v>
@@ -10612,14 +10624,14 @@
         <v>-1.191521732580641</v>
       </c>
       <c r="N221" t="n">
-        <v>-2.855835874721573</v>
+        <v>-2.855835874721574</v>
       </c>
       <c r="O221" t="n">
         <v>1.783865013384726</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B222" t="n">
@@ -10646,11 +10658,11 @@
       <c r="I222" t="n">
         <v>29.34799999999999</v>
       </c>
-      <c r="J222" s="1" t="n">
+      <c r="J222" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="K222" t="n">
-        <v>1640.339363149402</v>
+        <v>1640.339363149401</v>
       </c>
       <c r="L222" t="n">
         <v>-2.282393560812822</v>
@@ -10659,14 +10671,14 @@
         <v>-1.117695545926501</v>
       </c>
       <c r="N222" t="n">
-        <v>-2.953837546577666</v>
+        <v>-2.953837546577667</v>
       </c>
       <c r="O222" t="n">
         <v>1.789141970211135</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B223" t="n">
@@ -10693,14 +10705,14 @@
       <c r="I223" t="n">
         <v>28.16202999999999</v>
       </c>
-      <c r="J223" s="1" t="n">
+      <c r="J223" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K223" t="n">
         <v>1700.354635555628</v>
       </c>
       <c r="L223" t="n">
-        <v>-2.335159923095995</v>
+        <v>-2.335159923095996</v>
       </c>
       <c r="M223" t="n">
         <v>-1.062778294722907</v>
@@ -10709,11 +10721,11 @@
         <v>-2.928623768166323</v>
       </c>
       <c r="O223" t="n">
-        <v>1.656244492243668</v>
+        <v>1.656244492243669</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B224" t="n">
@@ -10740,7 +10752,7 @@
       <c r="I224" t="n">
         <v>26.99909999999999</v>
       </c>
-      <c r="J224" s="1" t="n">
+      <c r="J224" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K224" t="n">
@@ -10760,7 +10772,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="B225" t="n">
@@ -10787,7 +10799,7 @@
       <c r="I225" t="n">
         <v>26.02626999999999</v>
       </c>
-      <c r="J225" s="1" t="n">
+      <c r="J225" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="K225" t="n">
@@ -10797,10 +10809,10 @@
         <v>-2.47613051534052</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.953859839638693</v>
+        <v>-0.9538598396386933</v>
       </c>
       <c r="N225" t="n">
-        <v>-3.052906077033582</v>
+        <v>-3.052906077033583</v>
       </c>
       <c r="O225" t="n">
         <v>1.530637753782189</v>
@@ -10821,27 +10833,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>gsyh_tl</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>usd_ort</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gsyh_usd</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
@@ -10858,7 +10870,7 @@
         <v>188.4470651431746</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>39538</v>
       </c>
     </row>
@@ -10873,7 +10885,7 @@
         <v>202.1165869692412</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>39629</v>
       </c>
     </row>
@@ -10888,7 +10900,7 @@
         <v>224.7668336608458</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>39721</v>
       </c>
     </row>
@@ -10900,12 +10912,12 @@
         <v>1.533215254237288</v>
       </c>
       <c r="C5" t="n">
-        <v>168.896710273562</v>
+        <v>168.8967102735621</v>
       </c>
       <c r="D5" t="n">
-        <v>784.2271960468237</v>
-      </c>
-      <c r="E5" s="1" t="n">
+        <v>784.2271960468236</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>39813</v>
       </c>
     </row>
@@ -10920,9 +10932,9 @@
         <v>130.7828799188441</v>
       </c>
       <c r="D6" t="n">
-        <v>726.5630108224931</v>
-      </c>
-      <c r="E6" s="1" t="n">
+        <v>726.5630108224932</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>39903</v>
       </c>
     </row>
@@ -10937,9 +10949,9 @@
         <v>156.4423058232571</v>
       </c>
       <c r="D7" t="n">
-        <v>680.888729676509</v>
-      </c>
-      <c r="E7" s="1" t="n">
+        <v>680.8887296765091</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>39994</v>
       </c>
     </row>
@@ -10956,7 +10968,7 @@
       <c r="D8" t="n">
         <v>640.0868793971713</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>40086</v>
       </c>
     </row>
@@ -10965,15 +10977,15 @@
         <v>278.165055869949</v>
       </c>
       <c r="B9" t="n">
-        <v>1.481176190476191</v>
+        <v>1.48117619047619</v>
       </c>
       <c r="C9" t="n">
-        <v>187.8001129497769</v>
+        <v>187.800112949777</v>
       </c>
       <c r="D9" t="n">
-        <v>658.9902820733862</v>
-      </c>
-      <c r="E9" s="1" t="n">
+        <v>658.9902820733863</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>40178</v>
       </c>
     </row>
@@ -10988,9 +11000,9 @@
         <v>163.3389061436113</v>
       </c>
       <c r="D10" t="n">
-        <v>691.5463082981533</v>
-      </c>
-      <c r="E10" s="1" t="n">
+        <v>691.5463082981535</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>40268</v>
       </c>
     </row>
@@ -11005,9 +11017,9 @@
         <v>184.5845876179025</v>
       </c>
       <c r="D11" t="n">
-        <v>719.6885900927988</v>
-      </c>
-      <c r="E11" s="1" t="n">
+        <v>719.6885900927989</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>40359</v>
       </c>
     </row>
@@ -11024,7 +11036,7 @@
       <c r="D12" t="n">
         <v>749.0397936010979</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>40451</v>
       </c>
     </row>
@@ -11036,12 +11048,12 @@
         <v>1.457427868852459</v>
       </c>
       <c r="C13" t="n">
-        <v>223.7258198851916</v>
+        <v>223.7258198851917</v>
       </c>
       <c r="D13" t="n">
-        <v>784.9655005365126</v>
-      </c>
-      <c r="E13" s="1" t="n">
+        <v>784.9655005365125</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>40543</v>
       </c>
     </row>
@@ -11056,9 +11068,9 @@
         <v>188.6987980233468</v>
       </c>
       <c r="D14" t="n">
-        <v>810.3253924162481</v>
-      </c>
-      <c r="E14" s="1" t="n">
+        <v>810.3253924162482</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>40633</v>
       </c>
     </row>
@@ -11075,7 +11087,7 @@
       <c r="D15" t="n">
         <v>844.646504931485</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>40724</v>
       </c>
     </row>
@@ -11090,9 +11102,9 @@
         <v>223.6350014442476</v>
       </c>
       <c r="D16" t="n">
-        <v>854.9653194859254</v>
-      </c>
-      <c r="E16" s="1" t="n">
+        <v>854.9653194859255</v>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>40816</v>
       </c>
     </row>
@@ -11109,7 +11121,7 @@
       <c r="D17" t="n">
         <v>844.5068243568147</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>40908</v>
       </c>
     </row>
@@ -11126,7 +11138,7 @@
       <c r="D18" t="n">
         <v>845.4079140024489</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>40999</v>
       </c>
     </row>
@@ -11135,15 +11147,15 @@
         <v>387.344421610499</v>
       </c>
       <c r="B19" t="n">
-        <v>1.79789365079365</v>
+        <v>1.797893650793651</v>
       </c>
       <c r="C19" t="n">
         <v>215.4434559794525</v>
       </c>
       <c r="D19" t="n">
-        <v>841.9456698487621</v>
-      </c>
-      <c r="E19" s="1" t="n">
+        <v>841.945669848762</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>41090</v>
       </c>
     </row>
@@ -11155,12 +11167,12 @@
         <v>1.795756451612903</v>
       </c>
       <c r="C20" t="n">
-        <v>238.8314118010919</v>
+        <v>238.831411801092</v>
       </c>
       <c r="D20" t="n">
         <v>857.1420802056064</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>41182</v>
       </c>
     </row>
@@ -11177,7 +11189,7 @@
       <c r="D21" t="n">
         <v>887.0698297363689</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>41274</v>
       </c>
     </row>
@@ -11194,7 +11206,7 @@
       <c r="D22" t="n">
         <v>918.0892150612981</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>41364</v>
       </c>
     </row>
@@ -11209,9 +11221,9 @@
         <v>243.3585507081091</v>
       </c>
       <c r="D23" t="n">
-        <v>946.0043097899547</v>
-      </c>
-      <c r="E23" s="1" t="n">
+        <v>946.0043097899548</v>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>41455</v>
       </c>
     </row>
@@ -11228,7 +11240,7 @@
       <c r="D24" t="n">
         <v>959.0932141449902</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>41547</v>
       </c>
     </row>
@@ -11240,12 +11252,12 @@
         <v>2.025490163934426</v>
       </c>
       <c r="C25" t="n">
-        <v>245.149968013603</v>
+        <v>245.1499680136029</v>
       </c>
       <c r="D25" t="n">
         <v>961.0481078717496</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>41639</v>
       </c>
     </row>
@@ -11260,9 +11272,9 @@
         <v>206.8546279322574</v>
       </c>
       <c r="D26" t="n">
-        <v>947.2834628100969</v>
-      </c>
-      <c r="E26" s="1" t="n">
+        <v>947.2834628100968</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>41729</v>
       </c>
     </row>
@@ -11277,9 +11289,9 @@
         <v>233.2687910493438</v>
       </c>
       <c r="D27" t="n">
-        <v>937.1937031513315</v>
-      </c>
-      <c r="E27" s="1" t="n">
+        <v>937.1937031513314</v>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -11288,15 +11300,15 @@
         <v>551.958483650141</v>
       </c>
       <c r="B28" t="n">
-        <v>2.161522222222222</v>
+        <v>2.161522222222223</v>
       </c>
       <c r="C28" t="n">
-        <v>255.356377082574</v>
+        <v>255.3563770825739</v>
       </c>
       <c r="D28" t="n">
-        <v>940.6297640777782</v>
-      </c>
-      <c r="E28" s="1" t="n">
+        <v>940.6297640777781</v>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>41912</v>
       </c>
     </row>
@@ -11311,9 +11323,9 @@
         <v>247.4169735057768</v>
       </c>
       <c r="D29" t="n">
-        <v>942.8967695699521</v>
-      </c>
-      <c r="E29" s="1" t="n">
+        <v>942.8967695699519</v>
+      </c>
+      <c r="E29" s="2" t="n">
         <v>42004</v>
       </c>
     </row>
@@ -11330,7 +11342,7 @@
       <c r="D30" t="n">
         <v>940.1806740814401</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>42094</v>
       </c>
     </row>
@@ -11339,15 +11351,15 @@
         <v>567.197911838763</v>
       </c>
       <c r="B31" t="n">
-        <v>2.666340322580646</v>
+        <v>2.666340322580645</v>
       </c>
       <c r="C31" t="n">
-        <v>212.725250049774</v>
+        <v>212.7252500497741</v>
       </c>
       <c r="D31" t="n">
         <v>919.6371330818704</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>42185</v>
       </c>
     </row>
@@ -11356,15 +11368,15 @@
         <v>634.163127850709</v>
       </c>
       <c r="B32" t="n">
-        <v>2.842734920634921</v>
+        <v>2.84273492063492</v>
       </c>
       <c r="C32" t="n">
-        <v>223.0820479417298</v>
+        <v>223.0820479417299</v>
       </c>
       <c r="D32" t="n">
         <v>887.3628039410262</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>42277</v>
       </c>
     </row>
@@ -11379,9 +11391,9 @@
         <v>223.9755360864084</v>
       </c>
       <c r="D33" t="n">
-        <v>863.9213665216579</v>
-      </c>
-      <c r="E33" s="1" t="n">
+        <v>863.921366521658</v>
+      </c>
+      <c r="E33" s="2" t="n">
         <v>42369</v>
       </c>
     </row>
@@ -11393,12 +11405,12 @@
         <v>2.9437953125</v>
       </c>
       <c r="C34" t="n">
-        <v>193.9218591409194</v>
+        <v>193.9218591409195</v>
       </c>
       <c r="D34" t="n">
-        <v>853.7046932188317</v>
-      </c>
-      <c r="E34" s="1" t="n">
+        <v>853.7046932188318</v>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>42460</v>
       </c>
     </row>
@@ -11413,9 +11425,9 @@
         <v>220.4511445438936</v>
       </c>
       <c r="D35" t="n">
-        <v>861.4305877129511</v>
-      </c>
-      <c r="E35" s="1" t="n">
+        <v>861.4305877129513</v>
+      </c>
+      <c r="E35" s="2" t="n">
         <v>42551</v>
       </c>
     </row>
@@ -11424,7 +11436,7 @@
         <v>670.039064862309</v>
       </c>
       <c r="B36" t="n">
-        <v>2.960358620689656</v>
+        <v>2.960358620689655</v>
       </c>
       <c r="C36" t="n">
         <v>226.3371269208642</v>
@@ -11432,7 +11444,7 @@
       <c r="D36" t="n">
         <v>864.6856666920855</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>42643</v>
       </c>
     </row>
@@ -11444,12 +11456,12 @@
         <v>3.277955384615385</v>
       </c>
       <c r="C37" t="n">
-        <v>229.1928916870325</v>
+        <v>229.1928916870326</v>
       </c>
       <c r="D37" t="n">
-        <v>869.9030222927097</v>
-      </c>
-      <c r="E37" s="1" t="n">
+        <v>869.9030222927099</v>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>42735</v>
       </c>
     </row>
@@ -11464,9 +11476,9 @@
         <v>179.04323874422</v>
       </c>
       <c r="D38" t="n">
-        <v>855.0244018960103</v>
-      </c>
-      <c r="E38" s="1" t="n">
+        <v>855.0244018960104</v>
+      </c>
+      <c r="E38" s="2" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -11481,9 +11493,9 @@
         <v>207.8891764884418</v>
       </c>
       <c r="D39" t="n">
-        <v>842.4624338405586</v>
-      </c>
-      <c r="E39" s="1" t="n">
+        <v>842.4624338405587</v>
+      </c>
+      <c r="E39" s="2" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -11495,12 +11507,12 @@
         <v>3.514912903225806</v>
       </c>
       <c r="C40" t="n">
-        <v>240.1538850482418</v>
+        <v>240.1538850482417</v>
       </c>
       <c r="D40" t="n">
         <v>856.2791919679362</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>43008</v>
       </c>
     </row>
@@ -11512,12 +11524,12 @@
         <v>3.795547692307693</v>
       </c>
       <c r="C41" t="n">
-        <v>237.7925499851039</v>
+        <v>237.792549985104</v>
       </c>
       <c r="D41" t="n">
-        <v>864.8788502660076</v>
-      </c>
-      <c r="E41" s="1" t="n">
+        <v>864.8788502660077</v>
+      </c>
+      <c r="E41" s="2" t="n">
         <v>43100</v>
       </c>
     </row>
@@ -11532,9 +11544,9 @@
         <v>212.4174989921661</v>
       </c>
       <c r="D42" t="n">
-        <v>898.2531105139537</v>
-      </c>
-      <c r="E42" s="1" t="n">
+        <v>898.2531105139536</v>
+      </c>
+      <c r="E42" s="2" t="n">
         <v>43190</v>
       </c>
     </row>
@@ -11543,15 +11555,15 @@
         <v>908.77201241503</v>
       </c>
       <c r="B43" t="n">
-        <v>4.356707812499999</v>
+        <v>4.3567078125</v>
       </c>
       <c r="C43" t="n">
         <v>208.5914528873469</v>
       </c>
       <c r="D43" t="n">
-        <v>898.9553869128589</v>
-      </c>
-      <c r="E43" s="1" t="n">
+        <v>898.9553869128588</v>
+      </c>
+      <c r="E43" s="2" t="n">
         <v>43281</v>
       </c>
     </row>
@@ -11566,9 +11578,9 @@
         <v>187.6379538426487</v>
       </c>
       <c r="D44" t="n">
-        <v>846.4394557072658</v>
-      </c>
-      <c r="E44" s="1" t="n">
+        <v>846.4394557072657</v>
+      </c>
+      <c r="E44" s="2" t="n">
         <v>43373</v>
       </c>
     </row>
@@ -11585,7 +11597,7 @@
       <c r="D45" t="n">
         <v>797.3238057726485</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>43465</v>
       </c>
     </row>
@@ -11602,7 +11614,7 @@
       <c r="D46" t="n">
         <v>761.796683470352</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -11611,7 +11623,7 @@
         <v>1051.61027178976</v>
       </c>
       <c r="B47" t="n">
-        <v>5.872364999999999</v>
+        <v>5.872365</v>
       </c>
       <c r="C47" t="n">
         <v>179.0778113740818</v>
@@ -11619,7 +11631,7 @@
       <c r="D47" t="n">
         <v>732.283041957087</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>43646</v>
       </c>
     </row>
@@ -11628,15 +11640,15 @@
         <v>1178.52377571783</v>
       </c>
       <c r="B48" t="n">
-        <v>5.67217704918033</v>
+        <v>5.672177049180328</v>
       </c>
       <c r="C48" t="n">
-        <v>207.7727414887614</v>
+        <v>207.7727414887615</v>
       </c>
       <c r="D48" t="n">
-        <v>752.4178296031996</v>
-      </c>
-      <c r="E48" s="1" t="n">
+        <v>752.4178296031997</v>
+      </c>
+      <c r="E48" s="2" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -11645,7 +11657,7 @@
         <v>1223.87257025994</v>
       </c>
       <c r="B49" t="n">
-        <v>5.785284615384616</v>
+        <v>5.785284615384615</v>
       </c>
       <c r="C49" t="n">
         <v>211.5492411566643</v>
@@ -11653,7 +11665,7 @@
       <c r="D49" t="n">
         <v>775.2901707093772</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>43830</v>
       </c>
     </row>
@@ -11662,15 +11674,15 @@
         <v>1095.83409320798</v>
       </c>
       <c r="B50" t="n">
-        <v>6.093850000000002</v>
+        <v>6.09385</v>
       </c>
       <c r="C50" t="n">
         <v>179.8262335318362</v>
       </c>
       <c r="D50" t="n">
-        <v>778.2260275513437</v>
-      </c>
-      <c r="E50" s="1" t="n">
+        <v>778.2260275513438</v>
+      </c>
+      <c r="E50" s="2" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -11679,15 +11691,15 @@
         <v>1061.24590135972</v>
       </c>
       <c r="B51" t="n">
-        <v>6.852923333333333</v>
+        <v>6.852923333333334</v>
       </c>
       <c r="C51" t="n">
         <v>154.8603201494622</v>
       </c>
       <c r="D51" t="n">
-        <v>754.008536326724</v>
-      </c>
-      <c r="E51" s="1" t="n">
+        <v>754.0085363267242</v>
+      </c>
+      <c r="E51" s="2" t="n">
         <v>44012</v>
       </c>
     </row>
@@ -11696,7 +11708,7 @@
         <v>1440.5085622707</v>
       </c>
       <c r="B52" t="n">
-        <v>7.207746031746031</v>
+        <v>7.207746031746032</v>
       </c>
       <c r="C52" t="n">
         <v>199.8556214281243</v>
@@ -11704,7 +11716,7 @@
       <c r="D52" t="n">
         <v>746.091416266087</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>44104</v>
       </c>
     </row>
@@ -11721,7 +11733,7 @@
       <c r="D53" t="n">
         <v>730.9546871917802</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>44196</v>
       </c>
     </row>
@@ -11738,7 +11750,7 @@
       <c r="D54" t="n">
         <v>746.2494624509136</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -11755,7 +11767,7 @@
       <c r="D55" t="n">
         <v>786.5387429577326</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>44377</v>
       </c>
     </row>
@@ -11772,7 +11784,7 @@
       <c r="D56" t="n">
         <v>818.3449224201991</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>44469</v>
       </c>
     </row>
@@ -11781,15 +11793,15 @@
         <v>2385.4197650929</v>
       </c>
       <c r="B57" t="n">
-        <v>11.16101692307693</v>
+        <v>11.16101692307692</v>
       </c>
       <c r="C57" t="n">
-        <v>213.7278154431178</v>
+        <v>213.7278154431179</v>
       </c>
       <c r="D57" t="n">
         <v>835.6602257809595</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>44561</v>
       </c>
     </row>
@@ -11806,7 +11818,7 @@
       <c r="D58" t="n">
         <v>826.4811453112486</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -11823,7 +11835,7 @@
       <c r="D59" t="n">
         <v>853.2410029660408</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>44742</v>
       </c>
     </row>
@@ -11832,15 +11844,15 @@
         <v>4351.145687052261</v>
       </c>
       <c r="B60" t="n">
-        <v>17.92024032258064</v>
+        <v>17.92024032258065</v>
       </c>
       <c r="C60" t="n">
-        <v>242.806212903827</v>
+        <v>242.8062129038269</v>
       </c>
       <c r="D60" t="n">
         <v>864.3854149792769</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>44834</v>
       </c>
     </row>
@@ -11855,9 +11867,9 @@
         <v>262.5287835653832</v>
       </c>
       <c r="D61" t="n">
-        <v>913.1863831015422</v>
-      </c>
-      <c r="E61" s="1" t="n">
+        <v>913.1863831015423</v>
+      </c>
+      <c r="E61" s="2" t="n">
         <v>44926</v>
       </c>
     </row>
@@ -11869,12 +11881,12 @@
         <v>18.85272153846154</v>
       </c>
       <c r="C62" t="n">
-        <v>254.5257482540331</v>
+        <v>254.5257482540332</v>
       </c>
       <c r="D62" t="n">
         <v>981.7702030343168</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11891,7 +11903,7 @@
       <c r="D63" t="n">
         <v>1035.745849934734</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>45107</v>
       </c>
     </row>
@@ -11908,7 +11920,7 @@
       <c r="D64" t="n">
         <v>1087.793792245752</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>45199</v>
       </c>
     </row>
@@ -11925,7 +11937,7 @@
       <c r="D65" t="n">
         <v>1131.01603472582</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -11942,7 +11954,7 @@
       <c r="D66" t="n">
         <v>1171.104959658617</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>45382</v>
       </c>
     </row>
@@ -11959,7 +11971,7 @@
       <c r="D67" t="n">
         <v>1209.872581317634</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -11976,7 +11988,7 @@
       <c r="D68" t="n">
         <v>1283.797451942341</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>45565</v>
       </c>
     </row>
@@ -11993,7 +12005,7 @@
       <c r="D69" t="n">
         <v>1357.572675785335</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="2" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -12002,7 +12014,7 @@
         <v>12570.1485248555</v>
       </c>
       <c r="B70" t="n">
-        <v>36.15040322580646</v>
+        <v>36.15040322580645</v>
       </c>
       <c r="C70" t="n">
         <v>347.7180723639102</v>
@@ -12010,7 +12022,7 @@
       <c r="D70" t="n">
         <v>1410.676074962415</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="2" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -12027,7 +12039,7 @@
       <c r="D71" t="n">
         <v>1473.820957975585</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -12039,12 +12051,12 @@
         <v>40.68386923076923</v>
       </c>
       <c r="C72" t="n">
-        <v>430.96742731237</v>
+        <v>430.9674273123699</v>
       </c>
       <c r="D72" t="n">
         <v>1536.009359448403</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="2" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -12053,15 +12065,15 @@
         <v>18527.1474036199</v>
       </c>
       <c r="B73" t="n">
-        <v>42.17121384615384</v>
+        <v>42.17121384615385</v>
       </c>
       <c r="C73" t="n">
-        <v>439.3316130574136</v>
+        <v>439.3316130574135</v>
       </c>
       <c r="D73" t="n">
         <v>1595.814722617371</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -12070,15 +12082,15 @@
         <v>17098.1382209303</v>
       </c>
       <c r="B74" t="n">
-        <v>43.59070967741936</v>
+        <v>43.59070967741935</v>
       </c>
       <c r="C74" t="n">
-        <v>392.2427128959406</v>
+        <v>392.2427128959407</v>
       </c>
       <c r="D74" t="n">
-        <v>1640.339363149402</v>
-      </c>
-      <c r="E74" s="1" t="n">
+        <v>1640.339363149401</v>
+      </c>
+      <c r="E74" s="2" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -12090,12 +12102,12 @@
         <v>45.38410847457627</v>
       </c>
       <c r="C75" t="n">
-        <v>437.8128822899042</v>
+        <v>437.8128822899041</v>
       </c>
       <c r="D75" t="n">
         <v>1700.354635555628</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="2" t="n">
         <v>46203</v>
       </c>
     </row>

--- a/cari acik/cari_bilesen.xlsx
+++ b/cari acik/cari_bilesen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ceyrek" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,84 +422,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cari</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>enerji</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cari_12</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>altin_12</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enerji_12</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>diger_12</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>gsyh_tarih</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cari_gsyh</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>altin_gsyh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>enerji_gsyh</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>diger_gsyh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B2" t="n">
@@ -538,7 +526,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B3" t="n">
@@ -565,7 +553,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B4" t="n">
@@ -592,7 +580,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B5" t="n">
@@ -619,7 +607,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B6" t="n">
@@ -646,7 +634,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B7" t="n">
@@ -673,7 +661,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B8" t="n">
@@ -700,7 +688,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B9" t="n">
@@ -727,7 +715,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B10" t="n">
@@ -754,7 +742,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B11" t="n">
@@ -781,7 +769,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B12" t="n">
@@ -808,7 +796,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B13" t="n">
@@ -835,11 +823,11 @@
       <c r="I13" t="n">
         <v>2.68842</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K13" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="L13" t="n">
         <v>-5.027369644758661</v>
@@ -848,14 +836,14 @@
         <v>-0.1740567028127523</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.196115386639434</v>
+        <v>-5.196115386639433</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3428113706782854</v>
+        <v>0.3428113706782853</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B14" t="n">
@@ -882,27 +870,27 @@
       <c r="I14" t="n">
         <v>5.004020000000001</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K14" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.554930022838334</v>
+        <v>-4.554930022838333</v>
       </c>
       <c r="M14" t="n">
         <v>-0.1109372391553806</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.082068079365663</v>
+        <v>-5.082068079365662</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6380829465267903</v>
+        <v>0.6380829465267902</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B15" t="n">
@@ -929,11 +917,11 @@
       <c r="I15" t="n">
         <v>6.2034</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="K15" t="n">
-        <v>784.2271960468236</v>
+        <v>784.2271960468237</v>
       </c>
       <c r="L15" t="n">
         <v>-4.096261920261432</v>
@@ -945,11 +933,11 @@
         <v>-4.937134314542218</v>
       </c>
       <c r="O15" t="n">
-        <v>0.791020769398262</v>
+        <v>0.7910207693982618</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B16" t="n">
@@ -976,11 +964,11 @@
       <c r="I16" t="n">
         <v>7.860720000000001</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K16" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="L16" t="n">
         <v>-4.000066004887826</v>
@@ -989,14 +977,14 @@
         <v>0.1260730296417179</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.208038316892053</v>
+        <v>-5.208038316892054</v>
       </c>
       <c r="O16" t="n">
-        <v>1.081904787734983</v>
+        <v>1.081904787734984</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B17" t="n">
@@ -1023,27 +1011,27 @@
       <c r="I17" t="n">
         <v>9.52572</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K17" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.500453452923375</v>
+        <v>-3.500453452923376</v>
       </c>
       <c r="M17" t="n">
         <v>0.1328171109216788</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.944332351757517</v>
+        <v>-4.944332351757518</v>
       </c>
       <c r="O17" t="n">
         <v>1.311065916941818</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B18" t="n">
@@ -1070,27 +1058,27 @@
       <c r="I18" t="n">
         <v>10.32989</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="K18" t="n">
-        <v>726.5630108224932</v>
+        <v>726.5630108224931</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.060023655048378</v>
+        <v>-3.060023655048379</v>
       </c>
       <c r="M18" t="n">
         <v>0.2153976980232408</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.697165901876305</v>
+        <v>-4.697165901876306</v>
       </c>
       <c r="O18" t="n">
         <v>1.421747301490923</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B19" t="n">
@@ -1117,11 +1105,11 @@
       <c r="I19" t="n">
         <v>11.23285</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K19" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="L19" t="n">
         <v>-2.77358093575323</v>
@@ -1130,14 +1118,14 @@
         <v>0.3170855832825641</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.740398628030568</v>
+        <v>-4.740398628030569</v>
       </c>
       <c r="O19" t="n">
         <v>1.649733577663525</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B20" t="n">
@@ -1164,27 +1152,27 @@
       <c r="I20" t="n">
         <v>13.00463</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K20" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="L20" t="n">
         <v>-2.256756402371413</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2974054220227847</v>
+        <v>0.2974054220227848</v>
       </c>
       <c r="N20" t="n">
-        <v>-4.464109725305776</v>
+        <v>-4.464109725305778</v>
       </c>
       <c r="O20" t="n">
         <v>1.90994936958033</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B21" t="n">
@@ -1211,27 +1199,27 @@
       <c r="I21" t="n">
         <v>12.93374</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="K21" t="n">
-        <v>680.8887296765091</v>
+        <v>680.888729676509</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.891498484064911</v>
+        <v>-1.891498484064912</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4460346995966406</v>
+        <v>0.4460346995966407</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.237069691799207</v>
+        <v>-4.237069691799208</v>
       </c>
       <c r="O21" t="n">
         <v>1.899537976806406</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B22" t="n">
@@ -1258,7 +1246,7 @@
       <c r="I22" t="n">
         <v>10.54887</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K22" t="n">
@@ -1278,7 +1266,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1293,7 @@
       <c r="I23" t="n">
         <v>12.80883</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K23" t="n">
@@ -1325,7 +1313,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B24" t="n">
@@ -1352,7 +1340,7 @@
       <c r="I24" t="n">
         <v>11.9196</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="K24" t="n">
@@ -1372,7 +1360,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B25" t="n">
@@ -1399,14 +1387,14 @@
       <c r="I25" t="n">
         <v>11.61895</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K25" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.723545901809695</v>
+        <v>-1.723545901809696</v>
       </c>
       <c r="M25" t="n">
         <v>0.4563041492112831</v>
@@ -1419,7 +1407,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B26" t="n">
@@ -1446,27 +1434,27 @@
       <c r="I26" t="n">
         <v>10.08681</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K26" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.115357445961186</v>
+        <v>-2.115357445961187</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3314161163543207</v>
+        <v>0.3314161163543208</v>
       </c>
       <c r="N26" t="n">
         <v>-3.977416771235653</v>
       </c>
       <c r="O26" t="n">
-        <v>1.530646243866266</v>
+        <v>1.530646243866267</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B27" t="n">
@@ -1493,27 +1481,27 @@
       <c r="I27" t="n">
         <v>10.03788</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="K27" t="n">
-        <v>658.9902820733863</v>
+        <v>658.9902820733862</v>
       </c>
       <c r="L27" t="n">
         <v>-2.398973160918249</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09757351777281512</v>
+        <v>0.09757351777281513</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.019764891927503</v>
+        <v>-4.019764891927504</v>
       </c>
       <c r="O27" t="n">
         <v>1.523221248182559</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B28" t="n">
@@ -1540,27 +1528,27 @@
       <c r="I28" t="n">
         <v>8.120710000000001</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K28" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="L28" t="n">
         <v>-2.718834555891187</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.004048897328207281</v>
+        <v>-0.004048897328207282</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.889064214106776</v>
+        <v>-3.889064214106777</v>
       </c>
       <c r="O28" t="n">
         <v>1.174282893648076</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B29" t="n">
@@ -1587,11 +1575,11 @@
       <c r="I29" t="n">
         <v>6.80951</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K29" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="L29" t="n">
         <v>-3.115481890579493</v>
@@ -1600,14 +1588,14 @@
         <v>-0.01879845188096237</v>
       </c>
       <c r="N29" t="n">
-        <v>-4.081356470466659</v>
+        <v>-4.08135647046666</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9846788159071693</v>
+        <v>0.9846788159071695</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B30" t="n">
@@ -1634,11 +1622,11 @@
       <c r="I30" t="n">
         <v>5.458740000000001</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="K30" t="n">
-        <v>691.5463082981535</v>
+        <v>691.5463082981533</v>
       </c>
       <c r="L30" t="n">
         <v>-3.30274339200908</v>
@@ -1647,14 +1635,14 @@
         <v>0.08777430993649349</v>
       </c>
       <c r="N30" t="n">
-        <v>-4.179863250392423</v>
+        <v>-4.179863250392424</v>
       </c>
       <c r="O30" t="n">
         <v>0.78935277862065</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B31" t="n">
@@ -1681,14 +1669,14 @@
       <c r="I31" t="n">
         <v>4.53857</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K31" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.336443057531844</v>
+        <v>-3.336443057531845</v>
       </c>
       <c r="M31" t="n">
         <v>0.1161613524944454</v>
@@ -1697,11 +1685,11 @@
         <v>-4.083225773554478</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6306297004673622</v>
+        <v>0.6306297004673623</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B32" t="n">
@@ -1728,27 +1716,27 @@
       <c r="I32" t="n">
         <v>2.42634</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K32" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="L32" t="n">
         <v>-3.7600985165696</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06711236035265207</v>
+        <v>0.06711236035265208</v>
       </c>
       <c r="N32" t="n">
-        <v>-4.164340023250269</v>
+        <v>-4.16434002325027</v>
       </c>
       <c r="O32" t="n">
         <v>0.3371374832671921</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B33" t="n">
@@ -1775,27 +1763,27 @@
       <c r="I33" t="n">
         <v>0.1354600000000002</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="K33" t="n">
-        <v>719.6885900927989</v>
+        <v>719.6885900927988</v>
       </c>
       <c r="L33" t="n">
         <v>-4.10469200243829</v>
       </c>
       <c r="M33" t="n">
-        <v>0.08420308565984914</v>
+        <v>0.08420308565984917</v>
       </c>
       <c r="N33" t="n">
-        <v>-4.207708780834679</v>
+        <v>-4.20770878083468</v>
       </c>
       <c r="O33" t="n">
         <v>0.01882202967571483</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B34" t="n">
@@ -1822,7 +1810,7 @@
       <c r="I34" t="n">
         <v>-1.641</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K34" t="n">
@@ -1842,7 +1830,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B35" t="n">
@@ -1869,7 +1857,7 @@
       <c r="I35" t="n">
         <v>-4.08595</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K35" t="n">
@@ -1889,7 +1877,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B36" t="n">
@@ -1916,7 +1904,7 @@
       <c r="I36" t="n">
         <v>-7.33985</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="K36" t="n">
@@ -1936,7 +1924,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B37" t="n">
@@ -1963,27 +1951,27 @@
       <c r="I37" t="n">
         <v>-10.14424</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K37" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.684963220612812</v>
+        <v>-5.68496322061281</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.05770954260924602</v>
+        <v>-0.057709542609246</v>
       </c>
       <c r="N37" t="n">
-        <v>-4.334926818661786</v>
+        <v>-4.334926818661785</v>
       </c>
       <c r="O37" t="n">
         <v>-1.292316667811077</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B38" t="n">
@@ -2010,27 +1998,27 @@
       <c r="I38" t="n">
         <v>-11.7397</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K38" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="L38" t="n">
-        <v>-6.061922462512942</v>
+        <v>-6.061922462512941</v>
       </c>
       <c r="M38" t="n">
         <v>-0.1451019183927841</v>
       </c>
       <c r="N38" t="n">
-        <v>-4.421241440073415</v>
+        <v>-4.421241440073414</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.495568912516039</v>
+        <v>-1.495568912516038</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B39" t="n">
@@ -2057,27 +2045,27 @@
       <c r="I39" t="n">
         <v>-14.14707</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="J39" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="K39" t="n">
-        <v>784.9655005365125</v>
+        <v>784.9655005365126</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.556721278173675</v>
+        <v>-6.556721278173673</v>
       </c>
       <c r="M39" t="n">
         <v>-0.1833201585313576</v>
       </c>
       <c r="N39" t="n">
-        <v>-4.571135925779577</v>
+        <v>-4.571135925779576</v>
       </c>
       <c r="O39" t="n">
         <v>-1.802253728390698</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B40" t="n">
@@ -2104,17 +2092,17 @@
       <c r="I40" t="n">
         <v>-18.16812</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K40" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="L40" t="n">
         <v>-7.009776631906647</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.2052261987053405</v>
+        <v>-0.2052261987053406</v>
       </c>
       <c r="N40" t="n">
         <v>-4.562462233814442</v>
@@ -2124,7 +2112,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B41" t="n">
@@ -2151,11 +2139,11 @@
       <c r="I41" t="n">
         <v>-20.5611</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="J41" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K41" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="L41" t="n">
         <v>-7.424178060200413</v>
@@ -2164,14 +2152,14 @@
         <v>-0.2268224613472134</v>
       </c>
       <c r="N41" t="n">
-        <v>-4.659956401884912</v>
+        <v>-4.659956401884913</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.537388090318928</v>
+        <v>-2.537388090318929</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B42" t="n">
@@ -2198,27 +2186,27 @@
       <c r="I42" t="n">
         <v>-23.39756</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="K42" t="n">
-        <v>810.3253924162482</v>
+        <v>810.3253924162481</v>
       </c>
       <c r="L42" t="n">
-        <v>-8.038869398595661</v>
+        <v>-8.038869398595663</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.3299908931678175</v>
+        <v>-0.3299908931678176</v>
       </c>
       <c r="N42" t="n">
-        <v>-4.821439679127177</v>
+        <v>-4.821439679127178</v>
       </c>
       <c r="O42" t="n">
-        <v>-2.887427719651309</v>
+        <v>-2.88742771965131</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B43" t="n">
@@ -2245,7 +2233,7 @@
       <c r="I43" t="n">
         <v>-26.26857</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J43" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K43" t="n">
@@ -2265,7 +2253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B44" t="n">
@@ -2292,7 +2280,7 @@
       <c r="I44" t="n">
         <v>-26.73468</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K44" t="n">
@@ -2312,7 +2300,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B45" t="n">
@@ -2339,7 +2327,7 @@
       <c r="I45" t="n">
         <v>-25.77266</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="K45" t="n">
@@ -2359,7 +2347,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B46" t="n">
@@ -2386,11 +2374,11 @@
       <c r="I46" t="n">
         <v>-25.75811</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K46" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="L46" t="n">
         <v>-8.785151665001129</v>
@@ -2399,14 +2387,14 @@
         <v>-0.5844681516443967</v>
       </c>
       <c r="N46" t="n">
-        <v>-5.18790516867628</v>
+        <v>-5.187905168676281</v>
       </c>
       <c r="O46" t="n">
-        <v>-3.01276664829959</v>
+        <v>-3.012766648299591</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B47" t="n">
@@ -2433,27 +2421,27 @@
       <c r="I47" t="n">
         <v>-25.40919</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K47" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="L47" t="n">
-        <v>-8.906092243108054</v>
+        <v>-8.906092243108056</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6077439495585921</v>
+        <v>-0.6077439495585922</v>
       </c>
       <c r="N47" t="n">
-        <v>-5.326380960970623</v>
+        <v>-5.326380960970624</v>
       </c>
       <c r="O47" t="n">
         <v>-2.971955636197977</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B48" t="n">
@@ -2480,27 +2468,27 @@
       <c r="I48" t="n">
         <v>-24.01676</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="K48" t="n">
-        <v>854.9653194859255</v>
+        <v>854.9653194859254</v>
       </c>
       <c r="L48" t="n">
-        <v>-8.824685432312675</v>
+        <v>-8.824685432312677</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.5637655575197102</v>
+        <v>-0.5637655575197104</v>
       </c>
       <c r="N48" t="n">
-        <v>-5.451816458242586</v>
+        <v>-5.451816458242587</v>
       </c>
       <c r="O48" t="n">
-        <v>-2.809091720169518</v>
+        <v>-2.809091720169519</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B49" t="n">
@@ -2527,7 +2515,7 @@
       <c r="I49" t="n">
         <v>-22.04643</v>
       </c>
-      <c r="J49" s="2" t="n">
+      <c r="J49" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K49" t="n">
@@ -2547,7 +2535,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B50" t="n">
@@ -2574,7 +2562,7 @@
       <c r="I50" t="n">
         <v>-21.51568</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K50" t="n">
@@ -2594,7 +2582,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B51" t="n">
@@ -2621,7 +2609,7 @@
       <c r="I51" t="n">
         <v>-19.64396</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="K51" t="n">
@@ -2641,7 +2629,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B52" t="n">
@@ -2668,7 +2656,7 @@
       <c r="I52" t="n">
         <v>-15.79015</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K52" t="n">
@@ -2688,7 +2676,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B53" t="n">
@@ -2715,7 +2703,7 @@
       <c r="I53" t="n">
         <v>-13.06127</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K53" t="n">
@@ -2735,7 +2723,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B54" t="n">
@@ -2762,7 +2750,7 @@
       <c r="I54" t="n">
         <v>-10.51409</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="K54" t="n">
@@ -2782,7 +2770,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B55" t="n">
@@ -2809,11 +2797,11 @@
       <c r="I55" t="n">
         <v>-6.249130000000001</v>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K55" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="L55" t="n">
         <v>-7.087036864352339</v>
@@ -2822,14 +2810,14 @@
         <v>-0.2076143464594327</v>
       </c>
       <c r="N55" t="n">
-        <v>-6.137186976599305</v>
+        <v>-6.137186976599304</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.7422248517677544</v>
+        <v>-0.7422248517677543</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B56" t="n">
@@ -2856,14 +2844,14 @@
       <c r="I56" t="n">
         <v>-4.688590000000001</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K56" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.792481041000283</v>
+        <v>-6.792481041000281</v>
       </c>
       <c r="M56" t="n">
         <v>-0.140389106129891</v>
@@ -2872,11 +2860,11 @@
         <v>-6.095206833146166</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.5568755999234736</v>
+        <v>-0.5568755999234735</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B57" t="n">
@@ -2903,14 +2891,14 @@
       <c r="I57" t="n">
         <v>-2.382240000000001</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="K57" t="n">
-        <v>841.945669848762</v>
+        <v>841.9456698487621</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.312877647977865</v>
+        <v>-6.312877647977863</v>
       </c>
       <c r="M57" t="n">
         <v>0.1644999255413697</v>
@@ -2923,7 +2911,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B58" t="n">
@@ -2950,7 +2938,7 @@
       <c r="I58" t="n">
         <v>0.395989999999999</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K58" t="n">
@@ -2970,7 +2958,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B59" t="n">
@@ -2997,7 +2985,7 @@
       <c r="I59" t="n">
         <v>1.845749999999999</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K59" t="n">
@@ -3017,7 +3005,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B60" t="n">
@@ -3044,7 +3032,7 @@
       <c r="I60" t="n">
         <v>3.21682</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="K60" t="n">
@@ -3064,7 +3052,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B61" t="n">
@@ -3091,7 +3079,7 @@
       <c r="I61" t="n">
         <v>4.90424</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K61" t="n">
@@ -3111,7 +3099,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B62" t="n">
@@ -3138,7 +3126,7 @@
       <c r="I62" t="n">
         <v>5.24468</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K62" t="n">
@@ -3158,7 +3146,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B63" t="n">
@@ -3185,7 +3173,7 @@
       <c r="I63" t="n">
         <v>5.49649</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="K63" t="n">
@@ -3205,7 +3193,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B64" t="n">
@@ -3232,7 +3220,7 @@
       <c r="I64" t="n">
         <v>6.803089999999999</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K64" t="n">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B65" t="n">
@@ -3279,7 +3267,7 @@
       <c r="I65" t="n">
         <v>7.07182</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K65" t="n">
@@ -3299,7 +3287,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B66" t="n">
@@ -3326,7 +3314,7 @@
       <c r="I66" t="n">
         <v>8.31753</v>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="K66" t="n">
@@ -3346,7 +3334,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B67" t="n">
@@ -3373,11 +3361,11 @@
       <c r="I67" t="n">
         <v>9.40043</v>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K67" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="L67" t="n">
         <v>-4.563087033883022</v>
@@ -3386,14 +3374,14 @@
         <v>-0.3136349347772818</v>
       </c>
       <c r="N67" t="n">
-        <v>-5.24314524645379</v>
+        <v>-5.243145246453791</v>
       </c>
       <c r="O67" t="n">
         <v>0.9936984327362332</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B68" t="n">
@@ -3420,27 +3408,27 @@
       <c r="I68" t="n">
         <v>9.15676</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K68" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="L68" t="n">
-        <v>-4.738984752612175</v>
+        <v>-4.738984752612176</v>
       </c>
       <c r="M68" t="n">
         <v>-0.4570803700630154</v>
       </c>
       <c r="N68" t="n">
-        <v>-5.249839719126335</v>
+        <v>-5.249839719126336</v>
       </c>
       <c r="O68" t="n">
         <v>0.96794062196536</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B69" t="n">
@@ -3467,17 +3455,17 @@
       <c r="I69" t="n">
         <v>9.691610000000001</v>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="K69" t="n">
-        <v>946.0043097899548</v>
+        <v>946.0043097899547</v>
       </c>
       <c r="L69" t="n">
         <v>-4.782959182294463</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6621534315621481</v>
+        <v>-0.6621534315621482</v>
       </c>
       <c r="N69" t="n">
         <v>-5.145278884702694</v>
@@ -3487,7 +3475,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B70" t="n">
@@ -3514,7 +3502,7 @@
       <c r="I70" t="n">
         <v>10.6274</v>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K70" t="n">
@@ -3534,7 +3522,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B71" t="n">
@@ -3561,7 +3549,7 @@
       <c r="I71" t="n">
         <v>10.15893</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K71" t="n">
@@ -3581,7 +3569,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B72" t="n">
@@ -3608,7 +3596,7 @@
       <c r="I72" t="n">
         <v>11.57857</v>
       </c>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="K72" t="n">
@@ -3628,7 +3616,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B73" t="n">
@@ -3655,7 +3643,7 @@
       <c r="I73" t="n">
         <v>10.08393</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K73" t="n">
@@ -3675,7 +3663,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B74" t="n">
@@ -3702,7 +3690,7 @@
       <c r="I74" t="n">
         <v>11.61466</v>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K74" t="n">
@@ -3722,7 +3710,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B75" t="n">
@@ -3749,7 +3737,7 @@
       <c r="I75" t="n">
         <v>12.55543</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="K75" t="n">
@@ -3769,7 +3757,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B76" t="n">
@@ -3796,27 +3784,27 @@
       <c r="I76" t="n">
         <v>12.95175</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K76" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="L76" t="n">
         <v>-4.738180466790009</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9309779328184005</v>
+        <v>-0.9309779328184004</v>
       </c>
       <c r="N76" t="n">
-        <v>-5.174451146290775</v>
+        <v>-5.174451146290774</v>
       </c>
       <c r="O76" t="n">
         <v>1.36725177926984</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B77" t="n">
@@ -3843,17 +3831,17 @@
       <c r="I77" t="n">
         <v>13.82609</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K77" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="L77" t="n">
         <v>-4.474690170802399</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.7381106368370853</v>
+        <v>-0.7381106368370852</v>
       </c>
       <c r="N77" t="n">
         <v>-5.196128923646967</v>
@@ -3863,7 +3851,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B78" t="n">
@@ -3890,27 +3878,27 @@
       <c r="I78" t="n">
         <v>15.83389</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="K78" t="n">
-        <v>947.2834628100968</v>
+        <v>947.2834628100969</v>
       </c>
       <c r="L78" t="n">
-        <v>-4.107323892742752</v>
+        <v>-4.107323892742751</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.6158663408620646</v>
+        <v>-0.6158663408620645</v>
       </c>
       <c r="N78" t="n">
         <v>-5.162960393599167</v>
       </c>
       <c r="O78" t="n">
-        <v>1.67150495301893</v>
+        <v>1.671504953018929</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B79" t="n">
@@ -3937,27 +3925,27 @@
       <c r="I79" t="n">
         <v>15.8046</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K79" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="L79" t="n">
-        <v>-4.125614573592227</v>
+        <v>-4.125614573592226</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.5494061668026995</v>
+        <v>-0.5494061668026994</v>
       </c>
       <c r="N79" t="n">
-        <v>-5.262581239519495</v>
+        <v>-5.262581239519494</v>
       </c>
       <c r="O79" t="n">
         <v>1.686374966760525</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B80" t="n">
@@ -3984,11 +3972,11 @@
       <c r="I80" t="n">
         <v>18.19608</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K80" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="L80" t="n">
         <v>-3.73498028020231</v>
@@ -3997,14 +3985,14 @@
         <v>-0.381244558940774</v>
       </c>
       <c r="N80" t="n">
-        <v>-5.295283123769193</v>
+        <v>-5.295283123769192</v>
       </c>
       <c r="O80" t="n">
         <v>1.941549536538214</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B81" t="n">
@@ -4031,11 +4019,11 @@
       <c r="I81" t="n">
         <v>18.488</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="K81" t="n">
-        <v>937.1937031513314</v>
+        <v>937.1937031513315</v>
       </c>
       <c r="L81" t="n">
         <v>-3.693366684348153</v>
@@ -4044,14 +4032,14 @@
         <v>-0.3436856211442018</v>
       </c>
       <c r="N81" t="n">
-        <v>-5.322376775716084</v>
+        <v>-5.322376775716083</v>
       </c>
       <c r="O81" t="n">
         <v>1.972697846542689</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B82" t="n">
@@ -4078,27 +4066,27 @@
       <c r="I82" t="n">
         <v>19.80297</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K82" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="L82" t="n">
-        <v>-3.592380476406647</v>
+        <v>-3.592380476406646</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.4030278590766062</v>
+        <v>-0.4030278590766061</v>
       </c>
       <c r="N82" t="n">
-        <v>-5.294638964441904</v>
+        <v>-5.294638964441903</v>
       </c>
       <c r="O82" t="n">
         <v>2.105288473346942</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B83" t="n">
@@ -4125,11 +4113,11 @@
       <c r="I83" t="n">
         <v>20.59569</v>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J83" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K83" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="L83" t="n">
         <v>-3.459809719279627</v>
@@ -4138,14 +4126,14 @@
         <v>-0.3685828508094417</v>
       </c>
       <c r="N83" t="n">
-        <v>-5.280788669142379</v>
+        <v>-5.280788669142378</v>
       </c>
       <c r="O83" t="n">
         <v>2.189563926907271</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B84" t="n">
@@ -4172,11 +4160,11 @@
       <c r="I84" t="n">
         <v>19.85103</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="K84" t="n">
-        <v>940.6297640777781</v>
+        <v>940.6297640777782</v>
       </c>
       <c r="L84" t="n">
         <v>-3.618852103130485</v>
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B85" t="n">
@@ -4219,27 +4207,27 @@
       <c r="I85" t="n">
         <v>20.46028</v>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="J85" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K85" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="L85" t="n">
-        <v>-3.405675046977417</v>
+        <v>-3.405675046977416</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.4133008114745576</v>
+        <v>-0.4133008114745574</v>
       </c>
       <c r="N85" t="n">
-        <v>-5.162310612454471</v>
+        <v>-5.16231061245447</v>
       </c>
       <c r="O85" t="n">
         <v>2.169938498074585</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B86" t="n">
@@ -4266,27 +4254,27 @@
       <c r="I86" t="n">
         <v>20.80432</v>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K86" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="L86" t="n">
-        <v>-3.096203205077812</v>
+        <v>-3.096203205077811</v>
       </c>
       <c r="M86" t="n">
         <v>-0.2807306256025542</v>
       </c>
       <c r="N86" t="n">
-        <v>-5.021896513824793</v>
+        <v>-5.021896513824792</v>
       </c>
       <c r="O86" t="n">
-        <v>2.206426055472509</v>
+        <v>2.206426055472508</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B87" t="n">
@@ -4313,27 +4301,27 @@
       <c r="I87" t="n">
         <v>18.98794</v>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="K87" t="n">
-        <v>942.8967695699519</v>
+        <v>942.8967695699521</v>
       </c>
       <c r="L87" t="n">
-        <v>-3.116565985627752</v>
+        <v>-3.116565985627751</v>
       </c>
       <c r="M87" t="n">
         <v>-0.1818862950163885</v>
       </c>
       <c r="N87" t="n">
-        <v>-4.948464297028059</v>
+        <v>-4.948464297028058</v>
       </c>
       <c r="O87" t="n">
         <v>2.013787788101157</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B88" t="n">
@@ -4360,7 +4348,7 @@
       <c r="I88" t="n">
         <v>17.46199</v>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K88" t="n">
@@ -4380,7 +4368,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B89" t="n">
@@ -4407,7 +4395,7 @@
       <c r="I89" t="n">
         <v>15.2882</v>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J89" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K89" t="n">
@@ -4427,7 +4415,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B90" t="n">
@@ -4454,7 +4442,7 @@
       <c r="I90" t="n">
         <v>12.95619</v>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="K90" t="n">
@@ -4474,7 +4462,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B91" t="n">
@@ -4501,7 +4489,7 @@
       <c r="I91" t="n">
         <v>11.8918</v>
       </c>
-      <c r="J91" s="2" t="n">
+      <c r="J91" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K91" t="n">
@@ -4521,7 +4509,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B92" t="n">
@@ -4548,7 +4536,7 @@
       <c r="I92" t="n">
         <v>10.00618</v>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K92" t="n">
@@ -4568,7 +4556,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B93" t="n">
@@ -4595,7 +4583,7 @@
       <c r="I93" t="n">
         <v>10.69088</v>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="K93" t="n">
@@ -4615,7 +4603,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B94" t="n">
@@ -4642,7 +4630,7 @@
       <c r="I94" t="n">
         <v>9.682169999999999</v>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K94" t="n">
@@ -4662,7 +4650,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B95" t="n">
@@ -4689,7 +4677,7 @@
       <c r="I95" t="n">
         <v>9.299630000000001</v>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J95" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K95" t="n">
@@ -4709,7 +4697,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B96" t="n">
@@ -4736,7 +4724,7 @@
       <c r="I96" t="n">
         <v>9.04907</v>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="K96" t="n">
@@ -4756,7 +4744,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B97" t="n">
@@ -4783,14 +4771,14 @@
       <c r="I97" t="n">
         <v>8.198219999999999</v>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K97" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="L97" t="n">
-        <v>-2.471521231841731</v>
+        <v>-2.471521231841732</v>
       </c>
       <c r="M97" t="n">
         <v>0.4575647915638049</v>
@@ -4803,7 +4791,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B98" t="n">
@@ -4830,11 +4818,11 @@
       <c r="I98" t="n">
         <v>7.736389999999999</v>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K98" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="L98" t="n">
         <v>-2.503584335121057</v>
@@ -4850,7 +4838,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B99" t="n">
@@ -4877,11 +4865,11 @@
       <c r="I99" t="n">
         <v>7.899969999999999</v>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J99" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="K99" t="n">
-        <v>863.921366521658</v>
+        <v>863.9213665216579</v>
       </c>
       <c r="L99" t="n">
         <v>-2.355654205189728</v>
@@ -4890,14 +4878,14 @@
         <v>0.3043101029651514</v>
       </c>
       <c r="N99" t="n">
-        <v>-3.574390123528199</v>
+        <v>-3.5743901235282</v>
       </c>
       <c r="O99" t="n">
-        <v>0.9144316029370887</v>
+        <v>0.9144316029370889</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B100" t="n">
@@ -4924,11 +4912,11 @@
       <c r="I100" t="n">
         <v>7.502359999999999</v>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K100" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="L100" t="n">
         <v>-2.272682832144938</v>
@@ -4937,14 +4925,14 @@
         <v>0.3023293675789138</v>
       </c>
       <c r="N100" t="n">
-        <v>-3.453806712579706</v>
+        <v>-3.453806712579707</v>
       </c>
       <c r="O100" t="n">
-        <v>0.8788003696820377</v>
+        <v>0.8788003696820378</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B101" t="n">
@@ -4971,14 +4959,14 @@
       <c r="I101" t="n">
         <v>8.811169999999999</v>
       </c>
-      <c r="J101" s="2" t="n">
+      <c r="J101" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K101" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="L101" t="n">
-        <v>-2.167494233893924</v>
+        <v>-2.167494233893925</v>
       </c>
       <c r="M101" t="n">
         <v>0.1567286686635361</v>
@@ -4987,11 +4975,11 @@
         <v>-3.356326868951075</v>
       </c>
       <c r="O101" t="n">
-        <v>1.032109823219797</v>
+        <v>1.032109823219798</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B102" t="n">
@@ -5018,14 +5006,14 @@
       <c r="I102" t="n">
         <v>7.943439999999999</v>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="K102" t="n">
-        <v>853.7046932188318</v>
+        <v>853.7046932188317</v>
       </c>
       <c r="L102" t="n">
-        <v>-2.074019288009394</v>
+        <v>-2.074019288009395</v>
       </c>
       <c r="M102" t="n">
         <v>0.2287676307174036</v>
@@ -5034,11 +5022,11 @@
         <v>-3.233248009440734</v>
       </c>
       <c r="O102" t="n">
-        <v>0.9304669475401187</v>
+        <v>0.9304669475401188</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B103" t="n">
@@ -5065,11 +5053,11 @@
       <c r="I103" t="n">
         <v>4.534299999999999</v>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J103" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K103" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="L103" t="n">
         <v>-2.294671245942201</v>
@@ -5081,11 +5069,11 @@
         <v>-3.102657414448132</v>
       </c>
       <c r="O103" t="n">
-        <v>0.5263685855453897</v>
+        <v>0.5263685855453898</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B104" t="n">
@@ -5112,27 +5100,27 @@
       <c r="I104" t="n">
         <v>2.886419999999999</v>
       </c>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K104" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="L104" t="n">
         <v>-2.250906837598992</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4071134749592401</v>
+        <v>0.4071134749592402</v>
       </c>
       <c r="N104" t="n">
-        <v>-2.9930861949601</v>
+        <v>-2.993086194960101</v>
       </c>
       <c r="O104" t="n">
         <v>0.3350728475596947</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B105" t="n">
@@ -5159,17 +5147,17 @@
       <c r="I105" t="n">
         <v>0.2952499999999989</v>
       </c>
-      <c r="J105" s="2" t="n">
+      <c r="J105" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="K105" t="n">
-        <v>861.4305877129513</v>
+        <v>861.4305877129511</v>
       </c>
       <c r="L105" t="n">
         <v>-2.482846593221621</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4477435622805215</v>
+        <v>0.4477435622805216</v>
       </c>
       <c r="N105" t="n">
         <v>-2.964857571148912</v>
@@ -5179,7 +5167,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B106" t="n">
@@ -5206,7 +5194,7 @@
       <c r="I106" t="n">
         <v>-1.300060000000001</v>
       </c>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K106" t="n">
@@ -5226,7 +5214,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B107" t="n">
@@ -5253,7 +5241,7 @@
       <c r="I107" t="n">
         <v>-1.551580000000001</v>
       </c>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K107" t="n">
@@ -5273,7 +5261,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B108" t="n">
@@ -5300,7 +5288,7 @@
       <c r="I108" t="n">
         <v>-1.618070000000001</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="K108" t="n">
@@ -5320,7 +5308,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B109" t="n">
@@ -5347,27 +5335,27 @@
       <c r="I109" t="n">
         <v>0.1297299999999989</v>
       </c>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K109" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="L109" t="n">
         <v>-2.547985169839058</v>
       </c>
       <c r="M109" t="n">
-        <v>0.205770063343646</v>
+        <v>0.2057700633436461</v>
       </c>
       <c r="N109" t="n">
         <v>-2.76866149246414</v>
       </c>
       <c r="O109" t="n">
-        <v>0.01491315660199495</v>
+        <v>0.01491315660199496</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B110" t="n">
@@ -5394,27 +5382,27 @@
       <c r="I110" t="n">
         <v>0.3622699999999989</v>
       </c>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K110" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="L110" t="n">
-        <v>-2.60856663541565</v>
+        <v>-2.608566635415651</v>
       </c>
       <c r="M110" t="n">
-        <v>0.2080691701966476</v>
+        <v>0.2080691701966477</v>
       </c>
       <c r="N110" t="n">
-        <v>-2.858273780273584</v>
+        <v>-2.858273780273585</v>
       </c>
       <c r="O110" t="n">
-        <v>0.04164487198184492</v>
+        <v>0.04164487198184493</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B111" t="n">
@@ -5441,27 +5429,27 @@
       <c r="I111" t="n">
         <v>2.062249999999999</v>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="K111" t="n">
-        <v>869.9030222927099</v>
+        <v>869.9030222927097</v>
       </c>
       <c r="L111" t="n">
-        <v>-2.645697211091627</v>
+        <v>-2.645697211091628</v>
       </c>
       <c r="M111" t="n">
-        <v>0.04218861075257995</v>
+        <v>0.04218861075257997</v>
       </c>
       <c r="N111" t="n">
-        <v>-2.924946729457205</v>
+        <v>-2.924946729457206</v>
       </c>
       <c r="O111" t="n">
         <v>0.2370666553801306</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B112" t="n">
@@ -5488,11 +5476,11 @@
       <c r="I112" t="n">
         <v>4.506739999999999</v>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K112" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="L112" t="n">
         <v>-2.636883807059121</v>
@@ -5504,11 +5492,11 @@
         <v>-3.040345976366841</v>
       </c>
       <c r="O112" t="n">
-        <v>0.5270890503249188</v>
+        <v>0.5270890503249189</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B113" t="n">
@@ -5535,27 +5523,27 @@
       <c r="I113" t="n">
         <v>4.95311</v>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K113" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="L113" t="n">
-        <v>-2.71957150561278</v>
+        <v>-2.719571505612781</v>
       </c>
       <c r="M113" t="n">
         <v>-0.1638549726643231</v>
       </c>
       <c r="N113" t="n">
-        <v>-3.135006432630455</v>
+        <v>-3.135006432630456</v>
       </c>
       <c r="O113" t="n">
-        <v>0.579294577911053</v>
+        <v>0.5792945779110531</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B114" t="n">
@@ -5582,11 +5570,11 @@
       <c r="I114" t="n">
         <v>5.905279999999999</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="K114" t="n">
-        <v>855.0244018960104</v>
+        <v>855.0244018960103</v>
       </c>
       <c r="L114" t="n">
         <v>-2.920969266446445</v>
@@ -5595,14 +5583,14 @@
         <v>-0.4046668132894775</v>
       </c>
       <c r="N114" t="n">
-        <v>-3.206954086830248</v>
+        <v>-3.206954086830249</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6906563119023367</v>
+        <v>0.6906563119023368</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B115" t="n">
@@ -5629,17 +5617,17 @@
       <c r="I115" t="n">
         <v>8.84371</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K115" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="L115" t="n">
-        <v>-2.833123358532704</v>
+        <v>-2.833123358532705</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.6031129455632926</v>
+        <v>-0.6031129455632928</v>
       </c>
       <c r="N115" t="n">
         <v>-3.279752175303437</v>
@@ -5649,7 +5637,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B116" t="n">
@@ -5676,17 +5664,17 @@
       <c r="I116" t="n">
         <v>9.860910000000001</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K116" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="L116" t="n">
         <v>-3.057228306618415</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.8652017831550562</v>
+        <v>-0.8652017831550565</v>
       </c>
       <c r="N116" t="n">
         <v>-3.362509574564749</v>
@@ -5696,7 +5684,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B117" t="n">
@@ -5723,17 +5711,17 @@
       <c r="I117" t="n">
         <v>12.08097</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="K117" t="n">
-        <v>842.4624338405587</v>
+        <v>842.4624338405586</v>
       </c>
       <c r="L117" t="n">
         <v>-2.948974221526166</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.9328605863377125</v>
+        <v>-0.9328605863377127</v>
       </c>
       <c r="N117" t="n">
         <v>-3.450117041717365</v>
@@ -5743,7 +5731,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B118" t="n">
@@ -5770,7 +5758,7 @@
       <c r="I118" t="n">
         <v>10.99841</v>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K118" t="n">
@@ -5790,7 +5778,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B119" t="n">
@@ -5817,7 +5805,7 @@
       <c r="I119" t="n">
         <v>9.6854</v>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J119" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K119" t="n">
@@ -5837,7 +5825,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B120" t="n">
@@ -5864,7 +5852,7 @@
       <c r="I120" t="n">
         <v>9.236190000000001</v>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J120" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="K120" t="n">
@@ -5884,7 +5872,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B121" t="n">
@@ -5911,11 +5899,11 @@
       <c r="I121" t="n">
         <v>7.685680000000001</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J121" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K121" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="L121" t="n">
         <v>-4.063112421952717</v>
@@ -5927,11 +5915,11 @@
         <v>-3.798873101116382</v>
       </c>
       <c r="O121" t="n">
-        <v>0.8886423801016921</v>
+        <v>0.8886423801016922</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B122" t="n">
@@ -5958,14 +5946,14 @@
       <c r="I122" t="n">
         <v>5.95812</v>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J122" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K122" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="L122" t="n">
-        <v>-4.577172859276691</v>
+        <v>-4.577172859276692</v>
       </c>
       <c r="M122" t="n">
         <v>-1.421355140806032</v>
@@ -5974,11 +5962,11 @@
         <v>-3.844709578662119</v>
       </c>
       <c r="O122" t="n">
-        <v>0.6888964851166707</v>
+        <v>0.6888964851166708</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B123" t="n">
@@ -6005,11 +5993,11 @@
       <c r="I123" t="n">
         <v>4.993270000000001</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J123" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="K123" t="n">
-        <v>864.8788502660077</v>
+        <v>864.8788502660076</v>
       </c>
       <c r="L123" t="n">
         <v>-4.848540346096162</v>
@@ -6018,14 +6006,14 @@
         <v>-1.502406955147936</v>
       </c>
       <c r="N123" t="n">
-        <v>-3.923465117636219</v>
+        <v>-3.92346511763622</v>
       </c>
       <c r="O123" t="n">
-        <v>0.5773375078445078</v>
+        <v>0.5773375078445079</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B124" t="n">
@@ -6052,27 +6040,27 @@
       <c r="I124" t="n">
         <v>4.364470000000001</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J124" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K124" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="L124" t="n">
-        <v>-4.851416542834566</v>
+        <v>-4.851416542834565</v>
       </c>
       <c r="M124" t="n">
-        <v>-1.505032361342432</v>
+        <v>-1.505032361342431</v>
       </c>
       <c r="N124" t="n">
-        <v>-3.832261708540475</v>
+        <v>-3.832261708540474</v>
       </c>
       <c r="O124" t="n">
-        <v>0.4858842066800951</v>
+        <v>0.485884206680095</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B125" t="n">
@@ -6099,14 +6087,14 @@
       <c r="I125" t="n">
         <v>3.48327</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J125" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K125" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="L125" t="n">
-        <v>-5.067057321288615</v>
+        <v>-5.067057321288614</v>
       </c>
       <c r="M125" t="n">
         <v>-1.586857850327319</v>
@@ -6115,11 +6103,11 @@
         <v>-3.867975472984491</v>
       </c>
       <c r="O125" t="n">
-        <v>0.3877826816549488</v>
+        <v>0.3877826816549487</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B126" t="n">
@@ -6146,27 +6134,27 @@
       <c r="I126" t="n">
         <v>3.21001</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J126" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="K126" t="n">
-        <v>898.2531105139536</v>
+        <v>898.2531105139537</v>
       </c>
       <c r="L126" t="n">
-        <v>-5.192523071065441</v>
+        <v>-5.19252307106544</v>
       </c>
       <c r="M126" t="n">
         <v>-1.588973067049377</v>
       </c>
       <c r="N126" t="n">
-        <v>-3.960904736488225</v>
+        <v>-3.960904736488224</v>
       </c>
       <c r="O126" t="n">
         <v>0.3573614121039145</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B127" t="n">
@@ -6193,14 +6181,14 @@
       <c r="I127" t="n">
         <v>3.74216</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J127" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K127" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="L127" t="n">
-        <v>-5.125282152012538</v>
+        <v>-5.125282152012537</v>
       </c>
       <c r="M127" t="n">
         <v>-1.494846150947269</v>
@@ -6209,11 +6197,11 @@
         <v>-4.046708049097697</v>
       </c>
       <c r="O127" t="n">
-        <v>0.4162787224459617</v>
+        <v>0.4162787224459616</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B128" t="n">
@@ -6240,27 +6228,27 @@
       <c r="I128" t="n">
         <v>6.06072</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J128" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K128" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="L128" t="n">
-        <v>-4.854523443022684</v>
+        <v>-4.854523443022683</v>
       </c>
       <c r="M128" t="n">
         <v>-1.366141209985371</v>
       </c>
       <c r="N128" t="n">
-        <v>-4.162571418422049</v>
+        <v>-4.162571418422048</v>
       </c>
       <c r="O128" t="n">
-        <v>0.6741958597982686</v>
+        <v>0.6741958597982685</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B129" t="n">
@@ -6287,14 +6275,14 @@
       <c r="I129" t="n">
         <v>7.804049999999999</v>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J129" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="K129" t="n">
-        <v>898.9553869128588</v>
+        <v>898.9553869128589</v>
       </c>
       <c r="L129" t="n">
-        <v>-4.552172509976495</v>
+        <v>-4.552172509976494</v>
       </c>
       <c r="M129" t="n">
         <v>-1.254900984434897</v>
@@ -6307,7 +6295,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B130" t="n">
@@ -6334,27 +6322,27 @@
       <c r="I130" t="n">
         <v>14.08367</v>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J130" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K130" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="L130" t="n">
-        <v>-4.00583878402361</v>
+        <v>-4.005838784023609</v>
       </c>
       <c r="M130" t="n">
-        <v>-1.218988544358263</v>
+        <v>-1.218988544358262</v>
       </c>
       <c r="N130" t="n">
-        <v>-4.450715257421645</v>
+        <v>-4.450715257421644</v>
       </c>
       <c r="O130" t="n">
         <v>1.66387210627274</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B131" t="n">
@@ -6381,11 +6369,11 @@
       <c r="I131" t="n">
         <v>20.77072</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J131" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K131" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="L131" t="n">
         <v>-3.203182438765805</v>
@@ -6394,14 +6382,14 @@
         <v>-1.171731768069902</v>
       </c>
       <c r="N131" t="n">
-        <v>-4.485336753149905</v>
+        <v>-4.485336753149904</v>
       </c>
       <c r="O131" t="n">
         <v>2.453893170970445</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B132" t="n">
@@ -6428,14 +6416,14 @@
       <c r="I132" t="n">
         <v>26.56942</v>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J132" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="K132" t="n">
-        <v>846.4394557072657</v>
+        <v>846.4394557072658</v>
       </c>
       <c r="L132" t="n">
-        <v>-2.510752524200601</v>
+        <v>-2.5107525242006</v>
       </c>
       <c r="M132" t="n">
         <v>-1.180710555564691</v>
@@ -6444,11 +6432,11 @@
         <v>-4.468997722748204</v>
       </c>
       <c r="O132" t="n">
-        <v>3.138962842628738</v>
+        <v>3.138962842628737</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B133" t="n">
@@ -6475,7 +6463,7 @@
       <c r="I133" t="n">
         <v>31.91968</v>
       </c>
-      <c r="J133" s="2" t="n">
+      <c r="J133" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K133" t="n">
@@ -6495,7 +6483,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B134" t="n">
@@ -6522,7 +6510,7 @@
       <c r="I134" t="n">
         <v>36.77216</v>
       </c>
-      <c r="J134" s="2" t="n">
+      <c r="J134" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K134" t="n">
@@ -6542,7 +6530,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B135" t="n">
@@ -6569,7 +6557,7 @@
       <c r="I135" t="n">
         <v>40.31249</v>
       </c>
-      <c r="J135" s="2" t="n">
+      <c r="J135" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="K135" t="n">
@@ -6589,7 +6577,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B136" t="n">
@@ -6616,7 +6604,7 @@
       <c r="I136" t="n">
         <v>44.4252</v>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J136" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K136" t="n">
@@ -6636,7 +6624,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B137" t="n">
@@ -6663,7 +6651,7 @@
       <c r="I137" t="n">
         <v>48.80586</v>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J137" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K137" t="n">
@@ -6683,7 +6671,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B138" t="n">
@@ -6710,7 +6698,7 @@
       <c r="I138" t="n">
         <v>53.917</v>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="J138" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="K138" t="n">
@@ -6730,7 +6718,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B139" t="n">
@@ -6757,7 +6745,7 @@
       <c r="I139" t="n">
         <v>56.12547</v>
       </c>
-      <c r="J139" s="2" t="n">
+      <c r="J139" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K139" t="n">
@@ -6777,7 +6765,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B140" t="n">
@@ -6804,7 +6792,7 @@
       <c r="I140" t="n">
         <v>59.44548</v>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="J140" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K140" t="n">
@@ -6824,7 +6812,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B141" t="n">
@@ -6851,7 +6839,7 @@
       <c r="I141" t="n">
         <v>60.96964</v>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="J141" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="K141" t="n">
@@ -6871,7 +6859,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B142" t="n">
@@ -6898,27 +6886,27 @@
       <c r="I142" t="n">
         <v>61.12259999999999</v>
       </c>
-      <c r="J142" s="2" t="n">
+      <c r="J142" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K142" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="L142" t="n">
         <v>2.688665686014994</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.8210863375284544</v>
+        <v>-0.8210863375284545</v>
       </c>
       <c r="N142" t="n">
-        <v>-4.613739684811473</v>
+        <v>-4.613739684811474</v>
       </c>
       <c r="O142" t="n">
-        <v>8.123491708354921</v>
+        <v>8.123491708354923</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B143" t="n">
@@ -6945,27 +6933,27 @@
       <c r="I143" t="n">
         <v>60.94875</v>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J143" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K143" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="L143" t="n">
         <v>2.580082400524423</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.9857554816200302</v>
+        <v>-0.9857554816200305</v>
       </c>
       <c r="N143" t="n">
-        <v>-4.53454831313515</v>
+        <v>-4.534548313135151</v>
       </c>
       <c r="O143" t="n">
-        <v>8.100386195279603</v>
+        <v>8.100386195279604</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B144" t="n">
@@ -6992,11 +6980,11 @@
       <c r="I144" t="n">
         <v>59.31162999999999</v>
       </c>
-      <c r="J144" s="2" t="n">
+      <c r="J144" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="K144" t="n">
-        <v>752.4178296031997</v>
+        <v>752.4178296031996</v>
       </c>
       <c r="L144" t="n">
         <v>2.27745799285976</v>
@@ -7005,14 +6993,14 @@
         <v>-1.121982981776499</v>
       </c>
       <c r="N144" t="n">
-        <v>-4.483363986442214</v>
+        <v>-4.483363986442215</v>
       </c>
       <c r="O144" t="n">
-        <v>7.882804961078473</v>
+        <v>7.882804961078474</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B145" t="n">
@@ -7039,7 +7027,7 @@
       <c r="I145" t="n">
         <v>57.56779</v>
       </c>
-      <c r="J145" s="2" t="n">
+      <c r="J145" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K145" t="n">
@@ -7059,7 +7047,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B146" t="n">
@@ -7086,7 +7074,7 @@
       <c r="I146" t="n">
         <v>57.90269</v>
       </c>
-      <c r="J146" s="2" t="n">
+      <c r="J146" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K146" t="n">
@@ -7106,7 +7094,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B147" t="n">
@@ -7133,7 +7121,7 @@
       <c r="I147" t="n">
         <v>57.78574999999999</v>
       </c>
-      <c r="J147" s="2" t="n">
+      <c r="J147" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="K147" t="n">
@@ -7153,7 +7141,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B148" t="n">
@@ -7180,27 +7168,27 @@
       <c r="I148" t="n">
         <v>52.78822</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J148" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K148" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="L148" t="n">
         <v>1.108675332685499</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.484658645554966</v>
+        <v>-1.484658645554967</v>
       </c>
       <c r="N148" t="n">
-        <v>-4.189812322596572</v>
+        <v>-4.189812322596573</v>
       </c>
       <c r="O148" t="n">
-        <v>6.783147585810766</v>
+        <v>6.783147585810767</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B149" t="n">
@@ -7227,11 +7215,11 @@
       <c r="I149" t="n">
         <v>46.00505</v>
       </c>
-      <c r="J149" s="2" t="n">
+      <c r="J149" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K149" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="L149" t="n">
         <v>0.4912454562884402</v>
@@ -7240,14 +7228,14 @@
         <v>-1.45343378395986</v>
       </c>
       <c r="N149" t="n">
-        <v>-3.966846251227863</v>
+        <v>-3.966846251227864</v>
       </c>
       <c r="O149" t="n">
-        <v>5.91152806142362</v>
+        <v>5.911528061423621</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B150" t="n">
@@ -7274,27 +7262,27 @@
       <c r="I150" t="n">
         <v>39.39304</v>
       </c>
-      <c r="J150" s="2" t="n">
+      <c r="J150" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="K150" t="n">
-        <v>778.2260275513438</v>
+        <v>778.2260275513437</v>
       </c>
       <c r="L150" t="n">
-        <v>-0.1841367352501528</v>
+        <v>-0.1841367352501529</v>
       </c>
       <c r="M150" t="n">
         <v>-1.527962260195093</v>
       </c>
       <c r="N150" t="n">
-        <v>-3.718072767502112</v>
+        <v>-3.718072767502113</v>
       </c>
       <c r="O150" t="n">
         <v>5.061902147368238</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B151" t="n">
@@ -7321,27 +7309,27 @@
       <c r="I151" t="n">
         <v>37.28101</v>
       </c>
-      <c r="J151" s="2" t="n">
+      <c r="J151" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K151" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="L151" t="n">
-        <v>-0.5193575153774033</v>
+        <v>-0.5193575153774034</v>
       </c>
       <c r="M151" t="n">
-        <v>-1.758600779853005</v>
+        <v>-1.758600779853006</v>
       </c>
       <c r="N151" t="n">
         <v>-3.705127814082791</v>
       </c>
       <c r="O151" t="n">
-        <v>4.944375057293189</v>
+        <v>4.94437505729319</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B152" t="n">
@@ -7368,27 +7356,27 @@
       <c r="I152" t="n">
         <v>32.8163</v>
       </c>
-      <c r="J152" s="2" t="n">
+      <c r="J152" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K152" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="L152" t="n">
         <v>-1.184999846756154</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.924646645341388</v>
+        <v>-1.924646645341389</v>
       </c>
       <c r="N152" t="n">
-        <v>-3.612594378931113</v>
+        <v>-3.612594378931114</v>
       </c>
       <c r="O152" t="n">
-        <v>4.352245156251143</v>
+        <v>4.352245156251145</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B153" t="n">
@@ -7415,27 +7403,27 @@
       <c r="I153" t="n">
         <v>26.95827</v>
       </c>
-      <c r="J153" s="2" t="n">
+      <c r="J153" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="K153" t="n">
-        <v>754.0085363267242</v>
+        <v>754.008536326724</v>
       </c>
       <c r="L153" t="n">
-        <v>-2.316021524779263</v>
+        <v>-2.316021524779264</v>
       </c>
       <c r="M153" t="n">
-        <v>-2.37358055482875</v>
+        <v>-2.373580554828751</v>
       </c>
       <c r="N153" t="n">
         <v>-3.517763887557185</v>
       </c>
       <c r="O153" t="n">
-        <v>3.575326896341468</v>
+        <v>3.575326896341469</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B154" t="n">
@@ -7462,7 +7450,7 @@
       <c r="I154" t="n">
         <v>23.34406</v>
       </c>
-      <c r="J154" s="2" t="n">
+      <c r="J154" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K154" t="n">
@@ -7482,7 +7470,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B155" t="n">
@@ -7509,7 +7497,7 @@
       <c r="I155" t="n">
         <v>19.61043</v>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J155" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K155" t="n">
@@ -7529,7 +7517,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B156" t="n">
@@ -7556,7 +7544,7 @@
       <c r="I156" t="n">
         <v>16.41961</v>
       </c>
-      <c r="J156" s="2" t="n">
+      <c r="J156" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="K156" t="n">
@@ -7576,7 +7564,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B157" t="n">
@@ -7603,7 +7591,7 @@
       <c r="I157" t="n">
         <v>15.58579</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J157" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K157" t="n">
@@ -7623,7 +7611,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B158" t="n">
@@ -7650,7 +7638,7 @@
       <c r="I158" t="n">
         <v>13.06948</v>
       </c>
-      <c r="J158" s="2" t="n">
+      <c r="J158" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K158" t="n">
@@ -7670,7 +7658,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B159" t="n">
@@ -7697,7 +7685,7 @@
       <c r="I159" t="n">
         <v>10.72014</v>
       </c>
-      <c r="J159" s="2" t="n">
+      <c r="J159" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="K159" t="n">
@@ -7717,7 +7705,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B160" t="n">
@@ -7744,7 +7732,7 @@
       <c r="I160" t="n">
         <v>11.85764</v>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="J160" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K160" t="n">
@@ -7764,7 +7752,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B161" t="n">
@@ -7791,7 +7779,7 @@
       <c r="I161" t="n">
         <v>16.75192</v>
       </c>
-      <c r="J161" s="2" t="n">
+      <c r="J161" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K161" t="n">
@@ -7811,7 +7799,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B162" t="n">
@@ -7838,7 +7826,7 @@
       <c r="I162" t="n">
         <v>17.78087</v>
       </c>
-      <c r="J162" s="2" t="n">
+      <c r="J162" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="K162" t="n">
@@ -7858,7 +7846,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B163" t="n">
@@ -7885,7 +7873,7 @@
       <c r="I163" t="n">
         <v>19.18315</v>
       </c>
-      <c r="J163" s="2" t="n">
+      <c r="J163" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K163" t="n">
@@ -7905,7 +7893,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B164" t="n">
@@ -7932,7 +7920,7 @@
       <c r="I164" t="n">
         <v>21.03445</v>
       </c>
-      <c r="J164" s="2" t="n">
+      <c r="J164" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K164" t="n">
@@ -7952,7 +7940,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B165" t="n">
@@ -7979,7 +7967,7 @@
       <c r="I165" t="n">
         <v>25.49619</v>
       </c>
-      <c r="J165" s="2" t="n">
+      <c r="J165" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="K165" t="n">
@@ -7999,7 +7987,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B166" t="n">
@@ -8026,7 +8014,7 @@
       <c r="I166" t="n">
         <v>28.66052</v>
       </c>
-      <c r="J166" s="2" t="n">
+      <c r="J166" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K166" t="n">
@@ -8046,7 +8034,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B167" t="n">
@@ -8073,7 +8061,7 @@
       <c r="I167" t="n">
         <v>33.67982</v>
       </c>
-      <c r="J167" s="2" t="n">
+      <c r="J167" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K167" t="n">
@@ -8093,7 +8081,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B168" t="n">
@@ -8120,7 +8108,7 @@
       <c r="I168" t="n">
         <v>35.21025</v>
       </c>
-      <c r="J168" s="2" t="n">
+      <c r="J168" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="K168" t="n">
@@ -8140,7 +8128,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B169" t="n">
@@ -8167,7 +8155,7 @@
       <c r="I169" t="n">
         <v>37.12937</v>
       </c>
-      <c r="J169" s="2" t="n">
+      <c r="J169" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K169" t="n">
@@ -8187,7 +8175,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B170" t="n">
@@ -8214,7 +8202,7 @@
       <c r="I170" t="n">
         <v>37.22411</v>
       </c>
-      <c r="J170" s="2" t="n">
+      <c r="J170" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K170" t="n">
@@ -8234,7 +8222,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B171" t="n">
@@ -8261,7 +8249,7 @@
       <c r="I171" t="n">
         <v>38.29664</v>
       </c>
-      <c r="J171" s="2" t="n">
+      <c r="J171" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="K171" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B172" t="n">
@@ -8308,7 +8296,7 @@
       <c r="I172" t="n">
         <v>40.84047</v>
       </c>
-      <c r="J172" s="2" t="n">
+      <c r="J172" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K172" t="n">
@@ -8328,7 +8316,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B173" t="n">
@@ -8355,7 +8343,7 @@
       <c r="I173" t="n">
         <v>43.37856</v>
       </c>
-      <c r="J173" s="2" t="n">
+      <c r="J173" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K173" t="n">
@@ -8375,7 +8363,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B174" t="n">
@@ -8402,7 +8390,7 @@
       <c r="I174" t="n">
         <v>45.0951</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J174" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="K174" t="n">
@@ -8422,7 +8410,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B175" t="n">
@@ -8449,7 +8437,7 @@
       <c r="I175" t="n">
         <v>47.7854</v>
       </c>
-      <c r="J175" s="2" t="n">
+      <c r="J175" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K175" t="n">
@@ -8469,7 +8457,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B176" t="n">
@@ -8496,7 +8484,7 @@
       <c r="I176" t="n">
         <v>48.45027</v>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="J176" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K176" t="n">
@@ -8516,7 +8504,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B177" t="n">
@@ -8543,7 +8531,7 @@
       <c r="I177" t="n">
         <v>49.68133</v>
       </c>
-      <c r="J177" s="2" t="n">
+      <c r="J177" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="K177" t="n">
@@ -8563,7 +8551,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B178" t="n">
@@ -8590,7 +8578,7 @@
       <c r="I178" t="n">
         <v>50.47562</v>
       </c>
-      <c r="J178" s="2" t="n">
+      <c r="J178" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K178" t="n">
@@ -8610,7 +8598,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B179" t="n">
@@ -8637,7 +8625,7 @@
       <c r="I179" t="n">
         <v>50.11399</v>
       </c>
-      <c r="J179" s="2" t="n">
+      <c r="J179" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K179" t="n">
@@ -8657,7 +8645,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B180" t="n">
@@ -8684,7 +8672,7 @@
       <c r="I180" t="n">
         <v>52.17445</v>
       </c>
-      <c r="J180" s="2" t="n">
+      <c r="J180" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="K180" t="n">
@@ -8704,7 +8692,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B181" t="n">
@@ -8731,27 +8719,27 @@
       <c r="I181" t="n">
         <v>52.84970999999999</v>
       </c>
-      <c r="J181" s="2" t="n">
+      <c r="J181" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K181" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="L181" t="n">
-        <v>-5.110457280527663</v>
+        <v>-5.110457280527664</v>
       </c>
       <c r="M181" t="n">
-        <v>-2.12223926666294</v>
+        <v>-2.122239266662941</v>
       </c>
       <c r="N181" t="n">
-        <v>-8.775613772056108</v>
+        <v>-8.77561377205611</v>
       </c>
       <c r="O181" t="n">
-        <v>5.787395758191385</v>
+        <v>5.787395758191386</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B182" t="n">
@@ -8778,27 +8766,27 @@
       <c r="I182" t="n">
         <v>53.61758</v>
       </c>
-      <c r="J182" s="2" t="n">
+      <c r="J182" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K182" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="L182" t="n">
-        <v>-5.448832891156583</v>
+        <v>-5.448832891156584</v>
       </c>
       <c r="M182" t="n">
         <v>-2.589613734677255</v>
       </c>
       <c r="N182" t="n">
-        <v>-8.730701801445351</v>
+        <v>-8.730701801445353</v>
       </c>
       <c r="O182" t="n">
-        <v>5.871482644966023</v>
+        <v>5.871482644966024</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B183" t="n">
@@ -8825,27 +8813,27 @@
       <c r="I183" t="n">
         <v>52.49454</v>
       </c>
-      <c r="J183" s="2" t="n">
+      <c r="J183" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="K183" t="n">
-        <v>913.1863831015423</v>
+        <v>913.1863831015422</v>
       </c>
       <c r="L183" t="n">
-        <v>-5.824221756281482</v>
+        <v>-5.824221756281483</v>
       </c>
       <c r="M183" t="n">
-        <v>-2.967411746544497</v>
+        <v>-2.967411746544498</v>
       </c>
       <c r="N183" t="n">
-        <v>-8.605312283906665</v>
+        <v>-8.605312283906667</v>
       </c>
       <c r="O183" t="n">
-        <v>5.748502274169679</v>
+        <v>5.74850227416968</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B184" t="n">
@@ -8872,7 +8860,7 @@
       <c r="I184" t="n">
         <v>50.79395</v>
       </c>
-      <c r="J184" s="2" t="n">
+      <c r="J184" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K184" t="n">
@@ -8892,7 +8880,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B185" t="n">
@@ -8919,7 +8907,7 @@
       <c r="I185" t="n">
         <v>46.78892</v>
       </c>
-      <c r="J185" s="2" t="n">
+      <c r="J185" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K185" t="n">
@@ -8939,7 +8927,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B186" t="n">
@@ -8966,7 +8954,7 @@
       <c r="I186" t="n">
         <v>45.03124</v>
       </c>
-      <c r="J186" s="2" t="n">
+      <c r="J186" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="K186" t="n">
@@ -8986,7 +8974,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B187" t="n">
@@ -9013,7 +9001,7 @@
       <c r="I187" t="n">
         <v>45.92217</v>
       </c>
-      <c r="J187" s="2" t="n">
+      <c r="J187" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K187" t="n">
@@ -9023,17 +9011,17 @@
         <v>-5.067266260666861</v>
       </c>
       <c r="M187" t="n">
-        <v>-2.879181220168936</v>
+        <v>-2.879181220168937</v>
       </c>
       <c r="N187" t="n">
-        <v>-6.6218136432139</v>
+        <v>-6.621813643213901</v>
       </c>
       <c r="O187" t="n">
-        <v>4.433729568203793</v>
+        <v>4.433729568203795</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B188" t="n">
@@ -9060,27 +9048,27 @@
       <c r="I188" t="n">
         <v>42.09453999999999</v>
       </c>
-      <c r="J188" s="2" t="n">
+      <c r="J188" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K188" t="n">
         <v>1035.745849934734</v>
       </c>
       <c r="L188" t="n">
-        <v>-5.281314909777036</v>
+        <v>-5.281314909777037</v>
       </c>
       <c r="M188" t="n">
-        <v>-2.953620330887901</v>
+        <v>-2.953620330887902</v>
       </c>
       <c r="N188" t="n">
-        <v>-6.391870168166419</v>
+        <v>-6.39187016816642</v>
       </c>
       <c r="O188" t="n">
-        <v>4.064176554765101</v>
+        <v>4.064176554765102</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B189" t="n">
@@ -9107,27 +9095,27 @@
       <c r="I189" t="n">
         <v>41.36029</v>
       </c>
-      <c r="J189" s="2" t="n">
+      <c r="J189" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="K189" t="n">
         <v>1035.745849934734</v>
       </c>
       <c r="L189" t="n">
-        <v>-5.092562041481866</v>
+        <v>-5.092562041481867</v>
       </c>
       <c r="M189" t="n">
-        <v>-3.028928380642496</v>
+        <v>-3.028928380642497</v>
       </c>
       <c r="N189" t="n">
-        <v>-6.056918307126511</v>
+        <v>-6.056918307126512</v>
       </c>
       <c r="O189" t="n">
-        <v>3.993285611774959</v>
+        <v>3.99328561177496</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B190" t="n">
@@ -9154,27 +9142,27 @@
       <c r="I190" t="n">
         <v>41.33475</v>
       </c>
-      <c r="J190" s="2" t="n">
+      <c r="J190" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K190" t="n">
         <v>1087.793792245752</v>
       </c>
       <c r="L190" t="n">
-        <v>-4.417840986276109</v>
+        <v>-4.41784098627611</v>
       </c>
       <c r="M190" t="n">
         <v>-2.743718544153749</v>
       </c>
       <c r="N190" t="n">
-        <v>-5.473991525275</v>
+        <v>-5.473991525275002</v>
       </c>
       <c r="O190" t="n">
-        <v>3.799870002444521</v>
+        <v>3.799870002444522</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B191" t="n">
@@ -9201,27 +9189,27 @@
       <c r="I191" t="n">
         <v>38.13951</v>
       </c>
-      <c r="J191" s="2" t="n">
+      <c r="J191" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K191" t="n">
         <v>1087.793792245752</v>
       </c>
       <c r="L191" t="n">
-        <v>-4.346779723975269</v>
+        <v>-4.34677972397527</v>
       </c>
       <c r="M191" t="n">
-        <v>-2.592035384003187</v>
+        <v>-2.592035384003188</v>
       </c>
       <c r="N191" t="n">
         <v>-5.260877604555341</v>
       </c>
       <c r="O191" t="n">
-        <v>3.506134183875138</v>
+        <v>3.506134183875139</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B192" t="n">
@@ -9248,27 +9236,27 @@
       <c r="I192" t="n">
         <v>35.59753</v>
       </c>
-      <c r="J192" s="2" t="n">
+      <c r="J192" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="K192" t="n">
         <v>1087.793792245752</v>
       </c>
       <c r="L192" t="n">
-        <v>-4.220836736456317</v>
+        <v>-4.220836736456318</v>
       </c>
       <c r="M192" t="n">
-        <v>-2.491280993988025</v>
+        <v>-2.491280993988026</v>
       </c>
       <c r="N192" t="n">
         <v>-5.002006849815474</v>
       </c>
       <c r="O192" t="n">
-        <v>3.272452026639061</v>
+        <v>3.272452026639062</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B193" t="n">
@@ -9295,7 +9283,7 @@
       <c r="I193" t="n">
         <v>36.55256</v>
       </c>
-      <c r="J193" s="2" t="n">
+      <c r="J193" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K193" t="n">
@@ -9315,7 +9303,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B194" t="n">
@@ -9342,7 +9330,7 @@
       <c r="I194" t="n">
         <v>37.88603</v>
       </c>
-      <c r="J194" s="2" t="n">
+      <c r="J194" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K194" t="n">
@@ -9362,7 +9350,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B195" t="n">
@@ -9389,7 +9377,7 @@
       <c r="I195" t="n">
         <v>39.20635</v>
       </c>
-      <c r="J195" s="2" t="n">
+      <c r="J195" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="K195" t="n">
@@ -9409,7 +9397,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B196" t="n">
@@ -9436,7 +9424,7 @@
       <c r="I196" t="n">
         <v>39.57944</v>
       </c>
-      <c r="J196" s="2" t="n">
+      <c r="J196" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K196" t="n">
@@ -9456,7 +9444,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B197" t="n">
@@ -9483,7 +9471,7 @@
       <c r="I197" t="n">
         <v>39.32009</v>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="J197" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K197" t="n">
@@ -9503,7 +9491,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B198" t="n">
@@ -9530,7 +9518,7 @@
       <c r="I198" t="n">
         <v>43.90715</v>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="J198" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="K198" t="n">
@@ -9550,7 +9538,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B199" t="n">
@@ -9577,7 +9565,7 @@
       <c r="I199" t="n">
         <v>42.71823</v>
       </c>
-      <c r="J199" s="2" t="n">
+      <c r="J199" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K199" t="n">
@@ -9597,7 +9585,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B200" t="n">
@@ -9624,7 +9612,7 @@
       <c r="I200" t="n">
         <v>47.2887</v>
       </c>
-      <c r="J200" s="2" t="n">
+      <c r="J200" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K200" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B201" t="n">
@@ -9671,7 +9659,7 @@
       <c r="I201" t="n">
         <v>49.28131</v>
       </c>
-      <c r="J201" s="2" t="n">
+      <c r="J201" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="K201" t="n">
@@ -9691,7 +9679,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B202" t="n">
@@ -9718,7 +9706,7 @@
       <c r="I202" t="n">
         <v>48.84308</v>
       </c>
-      <c r="J202" s="2" t="n">
+      <c r="J202" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K202" t="n">
@@ -9738,7 +9726,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B203" t="n">
@@ -9765,7 +9753,7 @@
       <c r="I203" t="n">
         <v>50.89373</v>
       </c>
-      <c r="J203" s="2" t="n">
+      <c r="J203" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K203" t="n">
@@ -9785,7 +9773,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B204" t="n">
@@ -9812,7 +9800,7 @@
       <c r="I204" t="n">
         <v>51.48607</v>
       </c>
-      <c r="J204" s="2" t="n">
+      <c r="J204" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="K204" t="n">
@@ -9832,7 +9820,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B205" t="n">
@@ -9859,7 +9847,7 @@
       <c r="I205" t="n">
         <v>49.10726</v>
       </c>
-      <c r="J205" s="2" t="n">
+      <c r="J205" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K205" t="n">
@@ -9879,7 +9867,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B206" t="n">
@@ -9906,7 +9894,7 @@
       <c r="I206" t="n">
         <v>47.72986</v>
       </c>
-      <c r="J206" s="2" t="n">
+      <c r="J206" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K206" t="n">
@@ -9926,7 +9914,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B207" t="n">
@@ -9953,7 +9941,7 @@
       <c r="I207" t="n">
         <v>46.85917999999999</v>
       </c>
-      <c r="J207" s="2" t="n">
+      <c r="J207" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="K207" t="n">
@@ -9973,7 +9961,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B208" t="n">
@@ -10000,7 +9988,7 @@
       <c r="I208" t="n">
         <v>46.18819</v>
       </c>
-      <c r="J208" s="2" t="n">
+      <c r="J208" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K208" t="n">
@@ -10020,7 +10008,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B209" t="n">
@@ -10047,7 +10035,7 @@
       <c r="I209" t="n">
         <v>43.77743</v>
       </c>
-      <c r="J209" s="2" t="n">
+      <c r="J209" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K209" t="n">
@@ -10067,7 +10055,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B210" t="n">
@@ -10094,7 +10082,7 @@
       <c r="I210" t="n">
         <v>43.79429</v>
       </c>
-      <c r="J210" s="2" t="n">
+      <c r="J210" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="K210" t="n">
@@ -10114,7 +10102,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B211" t="n">
@@ -10141,7 +10129,7 @@
       <c r="I211" t="n">
         <v>41.44814</v>
       </c>
-      <c r="J211" s="2" t="n">
+      <c r="J211" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K211" t="n">
@@ -10161,7 +10149,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B212" t="n">
@@ -10188,7 +10176,7 @@
       <c r="I212" t="n">
         <v>41.90796</v>
       </c>
-      <c r="J212" s="2" t="n">
+      <c r="J212" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K212" t="n">
@@ -10204,11 +10192,11 @@
         <v>-3.33730835715357</v>
       </c>
       <c r="O212" t="n">
-        <v>2.843490572800921</v>
+        <v>2.843490572800922</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B213" t="n">
@@ -10235,7 +10223,7 @@
       <c r="I213" t="n">
         <v>41.96055</v>
       </c>
-      <c r="J213" s="2" t="n">
+      <c r="J213" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="K213" t="n">
@@ -10255,7 +10243,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B214" t="n">
@@ -10282,7 +10270,7 @@
       <c r="I214" t="n">
         <v>40.90523</v>
       </c>
-      <c r="J214" s="2" t="n">
+      <c r="J214" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K214" t="n">
@@ -10302,7 +10290,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B215" t="n">
@@ -10329,7 +10317,7 @@
       <c r="I215" t="n">
         <v>40.92907</v>
       </c>
-      <c r="J215" s="2" t="n">
+      <c r="J215" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K215" t="n">
@@ -10349,7 +10337,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B216" t="n">
@@ -10376,7 +10364,7 @@
       <c r="I216" t="n">
         <v>39.97973999999999</v>
       </c>
-      <c r="J216" s="2" t="n">
+      <c r="J216" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="K216" t="n">
@@ -10396,7 +10384,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B217" t="n">
@@ -10423,7 +10411,7 @@
       <c r="I217" t="n">
         <v>37.07607</v>
       </c>
-      <c r="J217" s="2" t="n">
+      <c r="J217" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K217" t="n">
@@ -10443,7 +10431,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B218" t="n">
@@ -10470,7 +10458,7 @@
       <c r="I218" t="n">
         <v>33.66558</v>
       </c>
-      <c r="J218" s="2" t="n">
+      <c r="J218" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K218" t="n">
@@ -10490,7 +10478,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B219" t="n">
@@ -10517,7 +10505,7 @@
       <c r="I219" t="n">
         <v>30.87032999999999</v>
       </c>
-      <c r="J219" s="2" t="n">
+      <c r="J219" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="K219" t="n">
@@ -10537,7 +10525,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B220" t="n">
@@ -10564,27 +10552,27 @@
       <c r="I220" t="n">
         <v>26.2946</v>
       </c>
-      <c r="J220" s="2" t="n">
+      <c r="J220" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K220" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="L220" t="n">
-        <v>-2.439190383335075</v>
+        <v>-2.439190383335074</v>
       </c>
       <c r="M220" t="n">
         <v>-1.274492368448753</v>
       </c>
       <c r="N220" t="n">
-        <v>-2.767692528748091</v>
+        <v>-2.76769252874809</v>
       </c>
       <c r="O220" t="n">
         <v>1.602997562011508</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B221" t="n">
@@ -10611,11 +10599,11 @@
       <c r="I221" t="n">
         <v>29.26144</v>
       </c>
-      <c r="J221" s="2" t="n">
+      <c r="J221" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K221" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="L221" t="n">
         <v>-2.263495032437279</v>
@@ -10624,14 +10612,14 @@
         <v>-1.191521732580641</v>
       </c>
       <c r="N221" t="n">
-        <v>-2.855835874721574</v>
+        <v>-2.855835874721573</v>
       </c>
       <c r="O221" t="n">
         <v>1.783865013384726</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B222" t="n">
@@ -10658,11 +10646,11 @@
       <c r="I222" t="n">
         <v>29.34799999999999</v>
       </c>
-      <c r="J222" s="2" t="n">
+      <c r="J222" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="K222" t="n">
-        <v>1640.339363149401</v>
+        <v>1640.339363149402</v>
       </c>
       <c r="L222" t="n">
         <v>-2.282393560812822</v>
@@ -10671,14 +10659,14 @@
         <v>-1.117695545926501</v>
       </c>
       <c r="N222" t="n">
-        <v>-2.953837546577667</v>
+        <v>-2.953837546577666</v>
       </c>
       <c r="O222" t="n">
         <v>1.789141970211135</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B223" t="n">
@@ -10705,14 +10693,14 @@
       <c r="I223" t="n">
         <v>28.16202999999999</v>
       </c>
-      <c r="J223" s="2" t="n">
+      <c r="J223" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K223" t="n">
         <v>1700.354635555628</v>
       </c>
       <c r="L223" t="n">
-        <v>-2.335159923095996</v>
+        <v>-2.335159923095995</v>
       </c>
       <c r="M223" t="n">
         <v>-1.062778294722907</v>
@@ -10721,11 +10709,11 @@
         <v>-2.928623768166323</v>
       </c>
       <c r="O223" t="n">
-        <v>1.656244492243669</v>
+        <v>1.656244492243668</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B224" t="n">
@@ -10752,7 +10740,7 @@
       <c r="I224" t="n">
         <v>26.99909999999999</v>
       </c>
-      <c r="J224" s="2" t="n">
+      <c r="J224" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K224" t="n">
@@ -10772,7 +10760,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="B225" t="n">
@@ -10799,7 +10787,7 @@
       <c r="I225" t="n">
         <v>26.02626999999999</v>
       </c>
-      <c r="J225" s="2" t="n">
+      <c r="J225" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="K225" t="n">
@@ -10809,10 +10797,10 @@
         <v>-2.47613051534052</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.9538598396386933</v>
+        <v>-0.953859839638693</v>
       </c>
       <c r="N225" t="n">
-        <v>-3.052906077033583</v>
+        <v>-3.052906077033582</v>
       </c>
       <c r="O225" t="n">
         <v>1.530637753782189</v>
@@ -10833,27 +10821,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>gsyh_tl</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>usd_ort</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gsyh_usd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gsyh_4c_usd</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
@@ -10870,7 +10858,7 @@
         <v>188.4470651431746</v>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>39538</v>
       </c>
     </row>
@@ -10885,7 +10873,7 @@
         <v>202.1165869692412</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>39629</v>
       </c>
     </row>
@@ -10900,7 +10888,7 @@
         <v>224.7668336608458</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>39721</v>
       </c>
     </row>
@@ -10912,12 +10900,12 @@
         <v>1.533215254237288</v>
       </c>
       <c r="C5" t="n">
-        <v>168.8967102735621</v>
+        <v>168.896710273562</v>
       </c>
       <c r="D5" t="n">
-        <v>784.2271960468236</v>
-      </c>
-      <c r="E5" s="2" t="n">
+        <v>784.2271960468237</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>39813</v>
       </c>
     </row>
@@ -10932,9 +10920,9 @@
         <v>130.7828799188441</v>
       </c>
       <c r="D6" t="n">
-        <v>726.5630108224932</v>
-      </c>
-      <c r="E6" s="2" t="n">
+        <v>726.5630108224931</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>39903</v>
       </c>
     </row>
@@ -10949,9 +10937,9 @@
         <v>156.4423058232571</v>
       </c>
       <c r="D7" t="n">
-        <v>680.8887296765091</v>
-      </c>
-      <c r="E7" s="2" t="n">
+        <v>680.888729676509</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>39994</v>
       </c>
     </row>
@@ -10968,7 +10956,7 @@
       <c r="D8" t="n">
         <v>640.0868793971713</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>40086</v>
       </c>
     </row>
@@ -10977,15 +10965,15 @@
         <v>278.165055869949</v>
       </c>
       <c r="B9" t="n">
-        <v>1.48117619047619</v>
+        <v>1.481176190476191</v>
       </c>
       <c r="C9" t="n">
-        <v>187.800112949777</v>
+        <v>187.8001129497769</v>
       </c>
       <c r="D9" t="n">
-        <v>658.9902820733863</v>
-      </c>
-      <c r="E9" s="2" t="n">
+        <v>658.9902820733862</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>40178</v>
       </c>
     </row>
@@ -11000,9 +10988,9 @@
         <v>163.3389061436113</v>
       </c>
       <c r="D10" t="n">
-        <v>691.5463082981535</v>
-      </c>
-      <c r="E10" s="2" t="n">
+        <v>691.5463082981533</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>40268</v>
       </c>
     </row>
@@ -11017,9 +11005,9 @@
         <v>184.5845876179025</v>
       </c>
       <c r="D11" t="n">
-        <v>719.6885900927989</v>
-      </c>
-      <c r="E11" s="2" t="n">
+        <v>719.6885900927988</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>40359</v>
       </c>
     </row>
@@ -11036,7 +11024,7 @@
       <c r="D12" t="n">
         <v>749.0397936010979</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="1" t="n">
         <v>40451</v>
       </c>
     </row>
@@ -11048,12 +11036,12 @@
         <v>1.457427868852459</v>
       </c>
       <c r="C13" t="n">
-        <v>223.7258198851917</v>
+        <v>223.7258198851916</v>
       </c>
       <c r="D13" t="n">
-        <v>784.9655005365125</v>
-      </c>
-      <c r="E13" s="2" t="n">
+        <v>784.9655005365126</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>40543</v>
       </c>
     </row>
@@ -11068,9 +11056,9 @@
         <v>188.6987980233468</v>
       </c>
       <c r="D14" t="n">
-        <v>810.3253924162482</v>
-      </c>
-      <c r="E14" s="2" t="n">
+        <v>810.3253924162481</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>40633</v>
       </c>
     </row>
@@ -11087,7 +11075,7 @@
       <c r="D15" t="n">
         <v>844.646504931485</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>40724</v>
       </c>
     </row>
@@ -11102,9 +11090,9 @@
         <v>223.6350014442476</v>
       </c>
       <c r="D16" t="n">
-        <v>854.9653194859255</v>
-      </c>
-      <c r="E16" s="2" t="n">
+        <v>854.9653194859254</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>40816</v>
       </c>
     </row>
@@ -11121,7 +11109,7 @@
       <c r="D17" t="n">
         <v>844.5068243568147</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="1" t="n">
         <v>40908</v>
       </c>
     </row>
@@ -11138,7 +11126,7 @@
       <c r="D18" t="n">
         <v>845.4079140024489</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>40999</v>
       </c>
     </row>
@@ -11147,15 +11135,15 @@
         <v>387.344421610499</v>
       </c>
       <c r="B19" t="n">
-        <v>1.797893650793651</v>
+        <v>1.79789365079365</v>
       </c>
       <c r="C19" t="n">
         <v>215.4434559794525</v>
       </c>
       <c r="D19" t="n">
-        <v>841.945669848762</v>
-      </c>
-      <c r="E19" s="2" t="n">
+        <v>841.9456698487621</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>41090</v>
       </c>
     </row>
@@ -11167,12 +11155,12 @@
         <v>1.795756451612903</v>
       </c>
       <c r="C20" t="n">
-        <v>238.831411801092</v>
+        <v>238.8314118010919</v>
       </c>
       <c r="D20" t="n">
         <v>857.1420802056064</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="1" t="n">
         <v>41182</v>
       </c>
     </row>
@@ -11189,7 +11177,7 @@
       <c r="D21" t="n">
         <v>887.0698297363689</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="1" t="n">
         <v>41274</v>
       </c>
     </row>
@@ -11206,7 +11194,7 @@
       <c r="D22" t="n">
         <v>918.0892150612981</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="1" t="n">
         <v>41364</v>
       </c>
     </row>
@@ -11221,9 +11209,9 @@
         <v>243.3585507081091</v>
       </c>
       <c r="D23" t="n">
-        <v>946.0043097899548</v>
-      </c>
-      <c r="E23" s="2" t="n">
+        <v>946.0043097899547</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>41455</v>
       </c>
     </row>
@@ -11240,7 +11228,7 @@
       <c r="D24" t="n">
         <v>959.0932141449902</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="1" t="n">
         <v>41547</v>
       </c>
     </row>
@@ -11252,12 +11240,12 @@
         <v>2.025490163934426</v>
       </c>
       <c r="C25" t="n">
-        <v>245.1499680136029</v>
+        <v>245.149968013603</v>
       </c>
       <c r="D25" t="n">
         <v>961.0481078717496</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="1" t="n">
         <v>41639</v>
       </c>
     </row>
@@ -11272,9 +11260,9 @@
         <v>206.8546279322574</v>
       </c>
       <c r="D26" t="n">
-        <v>947.2834628100968</v>
-      </c>
-      <c r="E26" s="2" t="n">
+        <v>947.2834628100969</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>41729</v>
       </c>
     </row>
@@ -11289,9 +11277,9 @@
         <v>233.2687910493438</v>
       </c>
       <c r="D27" t="n">
-        <v>937.1937031513314</v>
-      </c>
-      <c r="E27" s="2" t="n">
+        <v>937.1937031513315</v>
+      </c>
+      <c r="E27" s="1" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -11300,15 +11288,15 @@
         <v>551.958483650141</v>
       </c>
       <c r="B28" t="n">
-        <v>2.161522222222223</v>
+        <v>2.161522222222222</v>
       </c>
       <c r="C28" t="n">
-        <v>255.3563770825739</v>
+        <v>255.356377082574</v>
       </c>
       <c r="D28" t="n">
-        <v>940.6297640777781</v>
-      </c>
-      <c r="E28" s="2" t="n">
+        <v>940.6297640777782</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>41912</v>
       </c>
     </row>
@@ -11323,9 +11311,9 @@
         <v>247.4169735057768</v>
       </c>
       <c r="D29" t="n">
-        <v>942.8967695699519</v>
-      </c>
-      <c r="E29" s="2" t="n">
+        <v>942.8967695699521</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>42004</v>
       </c>
     </row>
@@ -11342,7 +11330,7 @@
       <c r="D30" t="n">
         <v>940.1806740814401</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="1" t="n">
         <v>42094</v>
       </c>
     </row>
@@ -11351,15 +11339,15 @@
         <v>567.197911838763</v>
       </c>
       <c r="B31" t="n">
-        <v>2.666340322580645</v>
+        <v>2.666340322580646</v>
       </c>
       <c r="C31" t="n">
-        <v>212.7252500497741</v>
+        <v>212.725250049774</v>
       </c>
       <c r="D31" t="n">
         <v>919.6371330818704</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="1" t="n">
         <v>42185</v>
       </c>
     </row>
@@ -11368,15 +11356,15 @@
         <v>634.163127850709</v>
       </c>
       <c r="B32" t="n">
-        <v>2.84273492063492</v>
+        <v>2.842734920634921</v>
       </c>
       <c r="C32" t="n">
-        <v>223.0820479417299</v>
+        <v>223.0820479417298</v>
       </c>
       <c r="D32" t="n">
         <v>887.3628039410262</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="1" t="n">
         <v>42277</v>
       </c>
     </row>
@@ -11391,9 +11379,9 @@
         <v>223.9755360864084</v>
       </c>
       <c r="D33" t="n">
-        <v>863.921366521658</v>
-      </c>
-      <c r="E33" s="2" t="n">
+        <v>863.9213665216579</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>42369</v>
       </c>
     </row>
@@ -11405,12 +11393,12 @@
         <v>2.9437953125</v>
       </c>
       <c r="C34" t="n">
-        <v>193.9218591409195</v>
+        <v>193.9218591409194</v>
       </c>
       <c r="D34" t="n">
-        <v>853.7046932188318</v>
-      </c>
-      <c r="E34" s="2" t="n">
+        <v>853.7046932188317</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>42460</v>
       </c>
     </row>
@@ -11425,9 +11413,9 @@
         <v>220.4511445438936</v>
       </c>
       <c r="D35" t="n">
-        <v>861.4305877129513</v>
-      </c>
-      <c r="E35" s="2" t="n">
+        <v>861.4305877129511</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>42551</v>
       </c>
     </row>
@@ -11436,7 +11424,7 @@
         <v>670.039064862309</v>
       </c>
       <c r="B36" t="n">
-        <v>2.960358620689655</v>
+        <v>2.960358620689656</v>
       </c>
       <c r="C36" t="n">
         <v>226.3371269208642</v>
@@ -11444,7 +11432,7 @@
       <c r="D36" t="n">
         <v>864.6856666920855</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="1" t="n">
         <v>42643</v>
       </c>
     </row>
@@ -11456,12 +11444,12 @@
         <v>3.277955384615385</v>
       </c>
       <c r="C37" t="n">
-        <v>229.1928916870326</v>
+        <v>229.1928916870325</v>
       </c>
       <c r="D37" t="n">
-        <v>869.9030222927099</v>
-      </c>
-      <c r="E37" s="2" t="n">
+        <v>869.9030222927097</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>42735</v>
       </c>
     </row>
@@ -11476,9 +11464,9 @@
         <v>179.04323874422</v>
       </c>
       <c r="D38" t="n">
-        <v>855.0244018960104</v>
-      </c>
-      <c r="E38" s="2" t="n">
+        <v>855.0244018960103</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -11493,9 +11481,9 @@
         <v>207.8891764884418</v>
       </c>
       <c r="D39" t="n">
-        <v>842.4624338405587</v>
-      </c>
-      <c r="E39" s="2" t="n">
+        <v>842.4624338405586</v>
+      </c>
+      <c r="E39" s="1" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -11507,12 +11495,12 @@
         <v>3.514912903225806</v>
       </c>
       <c r="C40" t="n">
-        <v>240.1538850482417</v>
+        <v>240.1538850482418</v>
       </c>
       <c r="D40" t="n">
         <v>856.2791919679362</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="1" t="n">
         <v>43008</v>
       </c>
     </row>
@@ -11524,12 +11512,12 @@
         <v>3.795547692307693</v>
       </c>
       <c r="C41" t="n">
-        <v>237.792549985104</v>
+        <v>237.7925499851039</v>
       </c>
       <c r="D41" t="n">
-        <v>864.8788502660077</v>
-      </c>
-      <c r="E41" s="2" t="n">
+        <v>864.8788502660076</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>43100</v>
       </c>
     </row>
@@ -11544,9 +11532,9 @@
         <v>212.4174989921661</v>
       </c>
       <c r="D42" t="n">
-        <v>898.2531105139536</v>
-      </c>
-      <c r="E42" s="2" t="n">
+        <v>898.2531105139537</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>43190</v>
       </c>
     </row>
@@ -11555,15 +11543,15 @@
         <v>908.77201241503</v>
       </c>
       <c r="B43" t="n">
-        <v>4.3567078125</v>
+        <v>4.356707812499999</v>
       </c>
       <c r="C43" t="n">
         <v>208.5914528873469</v>
       </c>
       <c r="D43" t="n">
-        <v>898.9553869128588</v>
-      </c>
-      <c r="E43" s="2" t="n">
+        <v>898.9553869128589</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>43281</v>
       </c>
     </row>
@@ -11578,9 +11566,9 @@
         <v>187.6379538426487</v>
       </c>
       <c r="D44" t="n">
-        <v>846.4394557072657</v>
-      </c>
-      <c r="E44" s="2" t="n">
+        <v>846.4394557072658</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>43373</v>
       </c>
     </row>
@@ -11597,7 +11585,7 @@
       <c r="D45" t="n">
         <v>797.3238057726485</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="1" t="n">
         <v>43465</v>
       </c>
     </row>
@@ -11614,7 +11602,7 @@
       <c r="D46" t="n">
         <v>761.796683470352</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="1" t="n">
         <v>43555</v>
       </c>
     </row>
@@ -11623,7 +11611,7 @@
         <v>1051.61027178976</v>
       </c>
       <c r="B47" t="n">
-        <v>5.872365</v>
+        <v>5.872364999999999</v>
       </c>
       <c r="C47" t="n">
         <v>179.0778113740818</v>
@@ -11631,7 +11619,7 @@
       <c r="D47" t="n">
         <v>732.283041957087</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="1" t="n">
         <v>43646</v>
       </c>
     </row>
@@ -11640,15 +11628,15 @@
         <v>1178.52377571783</v>
       </c>
       <c r="B48" t="n">
-        <v>5.672177049180328</v>
+        <v>5.67217704918033</v>
       </c>
       <c r="C48" t="n">
-        <v>207.7727414887615</v>
+        <v>207.7727414887614</v>
       </c>
       <c r="D48" t="n">
-        <v>752.4178296031997</v>
-      </c>
-      <c r="E48" s="2" t="n">
+        <v>752.4178296031996</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>43738</v>
       </c>
     </row>
@@ -11657,7 +11645,7 @@
         <v>1223.87257025994</v>
       </c>
       <c r="B49" t="n">
-        <v>5.785284615384615</v>
+        <v>5.785284615384616</v>
       </c>
       <c r="C49" t="n">
         <v>211.5492411566643</v>
@@ -11665,7 +11653,7 @@
       <c r="D49" t="n">
         <v>775.2901707093772</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="1" t="n">
         <v>43830</v>
       </c>
     </row>
@@ -11674,15 +11662,15 @@
         <v>1095.83409320798</v>
       </c>
       <c r="B50" t="n">
-        <v>6.09385</v>
+        <v>6.093850000000002</v>
       </c>
       <c r="C50" t="n">
         <v>179.8262335318362</v>
       </c>
       <c r="D50" t="n">
-        <v>778.2260275513438</v>
-      </c>
-      <c r="E50" s="2" t="n">
+        <v>778.2260275513437</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -11691,15 +11679,15 @@
         <v>1061.24590135972</v>
       </c>
       <c r="B51" t="n">
-        <v>6.852923333333334</v>
+        <v>6.852923333333333</v>
       </c>
       <c r="C51" t="n">
         <v>154.8603201494622</v>
       </c>
       <c r="D51" t="n">
-        <v>754.0085363267242</v>
-      </c>
-      <c r="E51" s="2" t="n">
+        <v>754.008536326724</v>
+      </c>
+      <c r="E51" s="1" t="n">
         <v>44012</v>
       </c>
     </row>
@@ -11708,7 +11696,7 @@
         <v>1440.5085622707</v>
       </c>
       <c r="B52" t="n">
-        <v>7.207746031746032</v>
+        <v>7.207746031746031</v>
       </c>
       <c r="C52" t="n">
         <v>199.8556214281243</v>
@@ -11716,7 +11704,7 @@
       <c r="D52" t="n">
         <v>746.091416266087</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="1" t="n">
         <v>44104</v>
       </c>
     </row>
@@ -11733,7 +11721,7 @@
       <c r="D53" t="n">
         <v>730.9546871917802</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="1" t="n">
         <v>44196</v>
       </c>
     </row>
@@ -11750,7 +11738,7 @@
       <c r="D54" t="n">
         <v>746.2494624509136</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="1" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -11767,7 +11755,7 @@
       <c r="D55" t="n">
         <v>786.5387429577326</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="1" t="n">
         <v>44377</v>
       </c>
     </row>
@@ -11784,7 +11772,7 @@
       <c r="D56" t="n">
         <v>818.3449224201991</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="1" t="n">
         <v>44469</v>
       </c>
     </row>
@@ -11793,15 +11781,15 @@
         <v>2385.4197650929</v>
       </c>
       <c r="B57" t="n">
-        <v>11.16101692307692</v>
+        <v>11.16101692307693</v>
       </c>
       <c r="C57" t="n">
-        <v>213.7278154431179</v>
+        <v>213.7278154431178</v>
       </c>
       <c r="D57" t="n">
         <v>835.6602257809595</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="1" t="n">
         <v>44561</v>
       </c>
     </row>
@@ -11818,7 +11806,7 @@
       <c r="D58" t="n">
         <v>826.4811453112486</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="1" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -11835,7 +11823,7 @@
       <c r="D59" t="n">
         <v>853.2410029660408</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="1" t="n">
         <v>44742</v>
       </c>
     </row>
@@ -11844,15 +11832,15 @@
         <v>4351.145687052261</v>
       </c>
       <c r="B60" t="n">
-        <v>17.92024032258065</v>
+        <v>17.92024032258064</v>
       </c>
       <c r="C60" t="n">
-        <v>242.8062129038269</v>
+        <v>242.806212903827</v>
       </c>
       <c r="D60" t="n">
         <v>864.3854149792769</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="1" t="n">
         <v>44834</v>
       </c>
     </row>
@@ -11867,9 +11855,9 @@
         <v>262.5287835653832</v>
       </c>
       <c r="D61" t="n">
-        <v>913.1863831015423</v>
-      </c>
-      <c r="E61" s="2" t="n">
+        <v>913.1863831015422</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>44926</v>
       </c>
     </row>
@@ -11881,12 +11869,12 @@
         <v>18.85272153846154</v>
       </c>
       <c r="C62" t="n">
-        <v>254.5257482540332</v>
+        <v>254.5257482540331</v>
       </c>
       <c r="D62" t="n">
         <v>981.7702030343168</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="1" t="n">
         <v>45016</v>
       </c>
     </row>
@@ -11903,7 +11891,7 @@
       <c r="D63" t="n">
         <v>1035.745849934734</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="1" t="n">
         <v>45107</v>
       </c>
     </row>
@@ -11920,7 +11908,7 @@
       <c r="D64" t="n">
         <v>1087.793792245752</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="1" t="n">
         <v>45199</v>
       </c>
     </row>
@@ -11937,7 +11925,7 @@
       <c r="D65" t="n">
         <v>1131.01603472582</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="1" t="n">
         <v>45291</v>
       </c>
     </row>
@@ -11954,7 +11942,7 @@
       <c r="D66" t="n">
         <v>1171.104959658617</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="1" t="n">
         <v>45382</v>
       </c>
     </row>
@@ -11971,7 +11959,7 @@
       <c r="D67" t="n">
         <v>1209.872581317634</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="1" t="n">
         <v>45473</v>
       </c>
     </row>
@@ -11988,7 +11976,7 @@
       <c r="D68" t="n">
         <v>1283.797451942341</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="1" t="n">
         <v>45565</v>
       </c>
     </row>
@@ -12005,7 +11993,7 @@
       <c r="D69" t="n">
         <v>1357.572675785335</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="1" t="n">
         <v>45657</v>
       </c>
     </row>
@@ -12014,7 +12002,7 @@
         <v>12570.1485248555</v>
       </c>
       <c r="B70" t="n">
-        <v>36.15040322580645</v>
+        <v>36.15040322580646</v>
       </c>
       <c r="C70" t="n">
         <v>347.7180723639102</v>
@@ -12022,7 +12010,7 @@
       <c r="D70" t="n">
         <v>1410.676074962415</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="1" t="n">
         <v>45747</v>
       </c>
     </row>
@@ -12039,7 +12027,7 @@
       <c r="D71" t="n">
         <v>1473.820957975585</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="1" t="n">
         <v>45838</v>
       </c>
     </row>
@@ -12051,12 +12039,12 @@
         <v>40.68386923076923</v>
       </c>
       <c r="C72" t="n">
-        <v>430.9674273123699</v>
+        <v>430.96742731237</v>
       </c>
       <c r="D72" t="n">
         <v>1536.009359448403</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="1" t="n">
         <v>45930</v>
       </c>
     </row>
@@ -12065,15 +12053,15 @@
         <v>18527.1474036199</v>
       </c>
       <c r="B73" t="n">
-        <v>42.17121384615385</v>
+        <v>42.17121384615384</v>
       </c>
       <c r="C73" t="n">
-        <v>439.3316130574135</v>
+        <v>439.3316130574136</v>
       </c>
       <c r="D73" t="n">
         <v>1595.814722617371</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -12082,15 +12070,15 @@
         <v>17098.1382209303</v>
       </c>
       <c r="B74" t="n">
-        <v>43.59070967741935</v>
+        <v>43.59070967741936</v>
       </c>
       <c r="C74" t="n">
-        <v>392.2427128959407</v>
+        <v>392.2427128959406</v>
       </c>
       <c r="D74" t="n">
-        <v>1640.339363149401</v>
-      </c>
-      <c r="E74" s="2" t="n">
+        <v>1640.339363149402</v>
+      </c>
+      <c r="E74" s="1" t="n">
         <v>46112</v>
       </c>
     </row>
@@ -12102,12 +12090,12 @@
         <v>45.38410847457627</v>
       </c>
       <c r="C75" t="n">
-        <v>437.8128822899041</v>
+        <v>437.8128822899042</v>
       </c>
       <c r="D75" t="n">
         <v>1700.354635555628</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
